--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440004</v>
+        <v>440005</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19-11-2025 04:08</t>
+          <t>19-11-2025 04:09</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>415833</v>
+        <v>415835</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19-11-2025 04:04</t>
+          <t>19-11-2025 04:13</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379356</v>
+        <v>379357</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 04:13</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>269954</v>
+        <v>269955</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 04:11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115596</v>
+        <v>115597</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19-11-2025 03:43</t>
+          <t>19-11-2025 04:14</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83097</v>
+        <v>83098</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19-11-2025 04:03</t>
+          <t>19-11-2025 04:13</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>78890</v>
+        <v>78891</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19-11-2025 04:02</t>
+          <t>19-11-2025 04:13</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51189</v>
+        <v>51190</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19-11-2025 02:24</t>
+          <t>19-11-2025 04:12</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44046</v>
+        <v>44047</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 04:03</t>
+          <t>19-11-2025 04:12</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>42613</v>
+        <v>42615</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19-11-2025 04:00</t>
+          <t>19-11-2025 04:11</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>41647</v>
+        <v>41648</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>19-11-2025 04:04</t>
+          <t>19-11-2025 04:13</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 04:13</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>23775</v>
+        <v>23774</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>19-11-2025 03:48</t>
+          <t>19-11-2025 04:12</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>17389</v>
+        <v>17390</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>19-11-2025 03:21</t>
+          <t>19-11-2025 04:11</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>11464</v>
+        <v>11465</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>19-11-2025 03:51</t>
+          <t>19-11-2025 04:14</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>7270</v>
+        <v>7271</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>19-11-2025 04:01</t>
+          <t>19-11-2025 04:09</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6723</v>
+        <v>6724</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>18-11-2025 10:17</t>
+          <t>19-11-2025 04:11</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4671</v>
+        <v>4672</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>19-11-2025 04:07</t>
+          <t>19-11-2025 04:12</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>269955</v>
+        <v>269956</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-11-2025 04:11</t>
+          <t>19-11-2025 04:15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>194686</v>
+        <v>194685</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19-11-2025 04:09</t>
+          <t>19-11-2025 04:15</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115597</v>
+        <v>115598</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19-11-2025 04:14</t>
+          <t>19-11-2025 04:15</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83197</v>
+        <v>83199</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 04:15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>59556</v>
+        <v>59557</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19-11-2025 02:24</t>
+          <t>19-11-2025 04:14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19-11-2025 04:13</t>
+          <t>19-11-2025 04:14</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>7271</v>
+        <v>7272</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>19-11-2025 04:09</t>
+          <t>19-11-2025 04:15</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>19-11-2025 00:49</t>
+          <t>19-11-2025 04:15</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440004</v>
+        <v>440007</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19-11-2025 04:08</t>
+          <t>19-11-2025 04:20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>415833</v>
+        <v>415839</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19-11-2025 04:04</t>
+          <t>19-11-2025 04:24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379356</v>
+        <v>379359</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 04:23</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>269954</v>
+        <v>269960</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 04:22</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258847</v>
+        <v>258853</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 04:26</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250248</v>
+        <v>250249</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 04:21</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>197877</v>
+        <v>197878</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19-11-2025 04:00</t>
+          <t>19-11-2025 04:21</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>194686</v>
+        <v>194688</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19-11-2025 04:09</t>
+          <t>19-11-2025 04:26</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157209</v>
+        <v>157211</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19-11-2025 04:07</t>
+          <t>19-11-2025 04:25</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156641</v>
+        <v>156642</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 04:22</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135556</v>
+        <v>135557</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19-11-2025 04:08</t>
+          <t>19-11-2025 04:20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131263</v>
+        <v>131264</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19-11-2025 03:24</t>
+          <t>19-11-2025 04:23</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115596</v>
+        <v>115598</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19-11-2025 03:43</t>
+          <t>19-11-2025 04:15</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102690</v>
+        <v>102691</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 04:16</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,11 +1342,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100869</v>
+        <v>100870</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19-11-2025 03:31</t>
+          <t>19-11-2025 04:21</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>84476</v>
+        <v>84478</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>19-11-2025 03:32</t>
+          <t>19-11-2025 04:22</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83197</v>
+        <v>83203</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 04:26</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83097</v>
+        <v>83099</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19-11-2025 04:03</t>
+          <t>19-11-2025 04:23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,11 +1737,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>79836</v>
+        <v>79837</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19-11-2025 02:27</t>
+          <t>19-11-2025 04:19</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>78890</v>
+        <v>78891</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19-11-2025 04:02</t>
+          <t>19-11-2025 04:13</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2047,11 +2047,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>66747</v>
+        <v>66748</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19-11-2025 00:56</t>
+          <t>19-11-2025 04:19</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2132,11 +2132,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63732</v>
+        <v>63733</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19-11-2025 03:53</t>
+          <t>19-11-2025 04:19</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>59556</v>
+        <v>59557</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19-11-2025 02:24</t>
+          <t>19-11-2025 04:14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>58625</v>
+        <v>58626</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 04:22</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2433,11 +2433,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53565</v>
+        <v>53567</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>19-11-2025 02:52</t>
+          <t>19-11-2025 04:23</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51189</v>
+        <v>51191</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19-11-2025 02:24</t>
+          <t>19-11-2025 04:23</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2784,11 +2784,11 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47453</v>
+        <v>47454</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19-11-2025 01:29</t>
+          <t>19-11-2025 04:20</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>47444</v>
+        <v>47445</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>19-11-2025 02:21</t>
+          <t>19-11-2025 04:18</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47210</v>
+        <v>47212</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 04:20</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44046</v>
+        <v>44050</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 04:03</t>
+          <t>19-11-2025 04:20</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>42613</v>
+        <v>42619</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19-11-2025 04:00</t>
+          <t>19-11-2025 04:20</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>42455</v>
+        <v>42456</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>19-11-2025 02:26</t>
+          <t>19-11-2025 04:20</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>41647</v>
+        <v>41651</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>19-11-2025 04:04</t>
+          <t>19-11-2025 04:19</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19-11-2025 02:23</t>
+          <t>19-11-2025 04:26</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>39156</v>
+        <v>39157</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19-11-2025 03:52</t>
+          <t>19-11-2025 04:27</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>38773</v>
+        <v>38774</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19-11-2025 04:00</t>
+          <t>19-11-2025 04:19</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>38607</v>
+        <v>38608</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18-11-2025 08:37</t>
+          <t>19-11-2025 04:25</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>35864</v>
+        <v>35865</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18-11-2025 18:39</t>
+          <t>19-11-2025 04:21</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31766</v>
+        <v>31765</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>19-11-2025 04:03</t>
+          <t>19-11-2025 04:22</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>31284</v>
+        <v>31286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 04:22</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28030</v>
+        <v>28031</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>19-11-2025 04:04</t>
+          <t>19-11-2025 04:21</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>25719</v>
+        <v>25720</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>18-11-2025 22:57</t>
+          <t>19-11-2025 04:27</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4878,11 +4878,11 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>25579</v>
+        <v>25580</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>19-11-2025 03:13</t>
+          <t>19-11-2025 04:23</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>23775</v>
+        <v>23774</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>19-11-2025 03:48</t>
+          <t>19-11-2025 04:12</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>22099</v>
+        <v>22100</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>19-11-2025 02:46</t>
+          <t>19-11-2025 04:21</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21942</v>
+        <v>21943</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>19-11-2025 03:51</t>
+          <t>19-11-2025 04:18</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>19-11-2025 03:35</t>
+          <t>19-11-2025 04:19</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>17389</v>
+        <v>17390</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>19-11-2025 03:21</t>
+          <t>19-11-2025 04:11</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6461,11 +6461,11 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17057</v>
+        <v>17058</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>18-11-2025 12:22</t>
+          <t>19-11-2025 04:17</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>16251</v>
+        <v>16252</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>19-11-2025 04:03</t>
+          <t>19-11-2025 04:19</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>19-11-2025 03:44</t>
+          <t>19-11-2025 04:23</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>15510</v>
+        <v>15512</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>19-11-2025 04:07</t>
+          <t>19-11-2025 04:26</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>15202</v>
+        <v>15203</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>18-11-2025 17:16</t>
+          <t>19-11-2025 04:18</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>13518</v>
+        <v>13519</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>19-11-2025 02:39</t>
+          <t>19-11-2025 04:25</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7920,11 +7920,11 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>13301</v>
+        <v>13302</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>18-11-2025 23:17</t>
+          <t>19-11-2025 04:24</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>12566</v>
+        <v>12567</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>19-11-2025 03:26</t>
+          <t>19-11-2025 04:24</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>12421</v>
+        <v>12424</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>19-11-2025 04:07</t>
+          <t>19-11-2025 04:19</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>11464</v>
+        <v>11465</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>19-11-2025 03:51</t>
+          <t>19-11-2025 04:14</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -9062,11 +9062,11 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>9991</v>
+        <v>9992</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>19-11-2025 03:24</t>
+          <t>19-11-2025 04:17</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>9566</v>
+        <v>9568</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>19-11-2025 03:59</t>
+          <t>19-11-2025 04:26</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>7270</v>
+        <v>7274</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>19-11-2025 04:01</t>
+          <t>19-11-2025 04:25</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6723</v>
+        <v>6724</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>18-11-2025 10:17</t>
+          <t>19-11-2025 04:11</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -11335,7 +11335,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5130</v>
+        <v>5131</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>18-11-2025 19:19</t>
+          <t>19-11-2025 04:25</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4671</v>
+        <v>4673</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>19-11-2025 04:07</t>
+          <t>19-11-2025 04:19</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3555</v>
+        <v>3556</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>19-11-2025 04:01</t>
+          <t>19-11-2025 04:25</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -14559,7 +14559,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>19-11-2025 04:01</t>
+          <t>19-11-2025 04:25</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>19-11-2025 00:49</t>
+          <t>19-11-2025 04:15</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440007</v>
+        <v>440008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19-11-2025 04:20</t>
+          <t>19-11-2025 04:28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135557</v>
+        <v>135559</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19-11-2025 04:20</t>
+          <t>19-11-2025 04:28</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 04:26</t>
+          <t>19-11-2025 04:28</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44050</v>
+        <v>44051</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 04:20</t>
+          <t>19-11-2025 04:28</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>42619</v>
+        <v>42620</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19-11-2025 04:20</t>
+          <t>19-11-2025 04:29</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>8945</v>
+        <v>8946</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>19-11-2025 04:00</t>
+          <t>19-11-2025 04:29</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>19-11-2025 03:51</t>
+          <t>19-11-2025 04:29</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -14604,7 +14604,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>19-11-2025 00:55</t>
+          <t>19-11-2025 04:28</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20909,7 +20909,7 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>18-11-2025 06:04</t>
+          <t>19-11-2025 04:29</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440008</v>
+        <v>440007</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19-11-2025 04:28</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>415839</v>
+        <v>415841</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19-11-2025 04:24</t>
+          <t>19-11-2025 04:35</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19-11-2025 04:23</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>269960</v>
+        <v>269959</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-11-2025 04:22</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258853</v>
+        <v>258854</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19-11-2025 04:26</t>
+          <t>19-11-2025 04:29</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19-11-2025 04:26</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19-11-2025 02:56</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157211</v>
+        <v>157210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156642</v>
+        <v>156643</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19-11-2025 04:22</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135559</v>
+        <v>135558</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19-11-2025 04:28</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125796</v>
+        <v>125797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19-11-2025 03:19</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115598</v>
+        <v>115597</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19-11-2025 04:15</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19-11-2025 03:39</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 04:28</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1737,11 +1737,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>79837</v>
+        <v>79838</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>75826</v>
+        <v>75827</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19-11-2025 02:14</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>68050</v>
+        <v>68053</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19-11-2025 03:41</t>
+          <t>19-11-2025 04:35</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>51663</v>
+        <v>51662</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19-11-2025 02:27</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44051</v>
+        <v>44053</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 04:28</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>34440</v>
+        <v>34441</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>19-11-2025 03:31</t>
+          <t>19-11-2025 04:30</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19-11-2025 04:22</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>26956</v>
+        <v>26958</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>19-11-2025 03:14</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>23837</v>
+        <v>23835</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>19-11-2025 03:09</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>19-11-2025 04:11</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>16252</v>
+        <v>16253</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:31</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>14640</v>
+        <v>14641</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>19-11-2025 03:24</t>
+          <t>19-11-2025 04:31</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>13519</v>
+        <v>13520</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>12424</v>
+        <v>12425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:31</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>12181</v>
+        <v>12182</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 04:30</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>10711</v>
+        <v>10709</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>19-11-2025 02:03</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>19-11-2025 04:26</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9671,11 +9671,11 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>8798</v>
+        <v>8799</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>18-11-2025 20:10</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>8297</v>
+        <v>8298</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>19-11-2025 04:08</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10111,11 +10111,11 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>8026</v>
+        <v>8025</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>18-11-2025 14:35</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>7274</v>
+        <v>7273</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4673</v>
+        <v>4674</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:30</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -14073,7 +14073,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>18-11-2025 23:59</t>
+          <t>19-11-2025 04:30</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -16050,7 +16050,7 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>18-11-2025 23:37</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>415841</v>
+        <v>415842</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>194688</v>
+        <v>194690</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157210</v>
+        <v>157211</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156643</v>
+        <v>156644</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19-11-2025 04:33</t>
+          <t>19-11-2025 04:35</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83203</v>
+        <v>83205</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 04:33</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83099</v>
+        <v>83100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19-11-2025 04:23</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47212</v>
+        <v>47213</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19-11-2025 04:20</t>
+          <t>19-11-2025 04:35</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44053</v>
+        <v>44054</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 04:34</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19-11-2025 04:29</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>23774</v>
+        <v>23775</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>19-11-2025 04:12</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>18364</v>
+        <v>18365</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>19-11-2025 03:53</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>13520</v>
+        <v>13521</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>19-11-2025 04:34</t>
+          <t>19-11-2025 04:35</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>12182</v>
+        <v>12183</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>19-11-2025 04:30</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6097</v>
+        <v>6098</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>19-11-2025 04:01</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>18-11-2025 10:42</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>19-11-2025 03:11</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19-11-2025 04:28</t>
+          <t>19-11-2025 04:43</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>415839</v>
+        <v>415842</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19-11-2025 04:24</t>
+          <t>19-11-2025 04:35</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379359</v>
+        <v>379360</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19-11-2025 04:23</t>
+          <t>19-11-2025 04:42</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>269960</v>
+        <v>269959</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-11-2025 04:22</t>
+          <t>19-11-2025 04:42</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258853</v>
+        <v>258855</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19-11-2025 04:26</t>
+          <t>19-11-2025 04:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250249</v>
+        <v>250250</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19-11-2025 04:21</t>
+          <t>19-11-2025 04:42</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>194688</v>
+        <v>194690</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19-11-2025 04:26</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19-11-2025 02:56</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156642</v>
+        <v>156644</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19-11-2025 04:22</t>
+          <t>19-11-2025 04:35</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19-11-2025 04:28</t>
+          <t>19-11-2025 04:39</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131264</v>
+        <v>131265</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19-11-2025 04:23</t>
+          <t>19-11-2025 04:40</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125796</v>
+        <v>125797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19-11-2025 03:19</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19-11-2025 04:15</t>
+          <t>19-11-2025 04:38</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19-11-2025 03:39</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>88041</v>
+        <v>88042</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19-11-2025 04:01</t>
+          <t>19-11-2025 04:40</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83203</v>
+        <v>83208</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 04:28</t>
+          <t>19-11-2025 04:40</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83099</v>
+        <v>83100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19-11-2025 04:23</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,11 +1737,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>79837</v>
+        <v>79838</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>75826</v>
+        <v>75827</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19-11-2025 02:14</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>68050</v>
+        <v>68053</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19-11-2025 03:41</t>
+          <t>19-11-2025 04:35</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>58626</v>
+        <v>58627</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19-11-2025 04:22</t>
+          <t>19-11-2025 04:38</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>56065</v>
+        <v>56066</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19-11-2025 03:30</t>
+          <t>19-11-2025 04:39</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>51663</v>
+        <v>51662</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19-11-2025 02:27</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>48620</v>
+        <v>48621</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>19-11-2025 02:21</t>
+          <t>19-11-2025 04:41</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47212</v>
+        <v>47214</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19-11-2025 04:20</t>
+          <t>19-11-2025 04:41</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44051</v>
+        <v>44056</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 04:28</t>
+          <t>19-11-2025 04:43</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>42620</v>
+        <v>42622</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19-11-2025 04:29</t>
+          <t>19-11-2025 04:43</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19-11-2025 04:26</t>
+          <t>19-11-2025 04:42</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>38774</v>
+        <v>38775</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:39</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>34440</v>
+        <v>34441</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>19-11-2025 03:31</t>
+          <t>19-11-2025 04:30</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19-11-2025 04:22</t>
+          <t>19-11-2025 04:37</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>26956</v>
+        <v>26958</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>19-11-2025 03:14</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>23837</v>
+        <v>23835</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>19-11-2025 03:09</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>23774</v>
+        <v>23775</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>19-11-2025 04:12</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21943</v>
+        <v>21945</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>19-11-2025 04:18</t>
+          <t>19-11-2025 04:40</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5836,11 +5836,11 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>19154</v>
+        <v>19155</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>19-11-2025 02:30</t>
+          <t>19-11-2025 04:38</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>18364</v>
+        <v>18366</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>19-11-2025 03:53</t>
+          <t>19-11-2025 04:42</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>19-11-2025 04:11</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>16252</v>
+        <v>16253</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:31</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>15541</v>
+        <v>15542</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>19-11-2025 04:23</t>
+          <t>19-11-2025 04:38</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>15512</v>
+        <v>15513</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>19-11-2025 04:26</t>
+          <t>19-11-2025 04:38</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>14640</v>
+        <v>14641</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>19-11-2025 03:24</t>
+          <t>19-11-2025 04:31</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7676,26 +7676,26 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>budtmo/docker-android</t>
+          <t>MustardChef/WSABuilds</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://github.com/budtmo/docker-android</t>
+          <t>https://github.com/MustardChef/WSABuilds</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Android in docker solution with noVNC supported and video recording</t>
+          <t>Run Windows Subsystem For Android on your Windows 10 and Windows 11 PC using prebuilt binaries with Google Play Store (MindTheGapps) and/or Magisk or KernelSU (root solutions) built in.</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>13521</v>
+        <v>13522</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -7704,43 +7704,43 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>19-11-2025 03:51</t>
+          <t>19-11-2025 04:40</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>22-12-2016 13:02</t>
+          <t>30-12-2022 21:43</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>alibabacloud, android, android-emulator, aws, azure</t>
+          <t>android, android-emulator, google-apps, kernelsu, magisk</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MustardChef/WSABuilds</t>
+          <t>budtmo/docker-android</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://github.com/MustardChef/WSABuilds</t>
+          <t>https://github.com/budtmo/docker-android</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Run Windows Subsystem For Android on your Windows 10 and Windows 11 PC using prebuilt binaries with Google Play Store (MindTheGapps) and/or Magisk or KernelSU (root solutions) built in.</t>
+          <t>Android in docker solution with noVNC supported and video recording</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>13519</v>
+        <v>13521</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -7749,17 +7749,17 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 03:51</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>30-12-2022 21:43</t>
+          <t>22-12-2016 13:02</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>android, android-emulator, google-apps, kernelsu, magisk</t>
+          <t>alibabacloud, android, android-emulator, aws, azure</t>
         </is>
       </c>
     </row>
@@ -8157,26 +8157,26 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ytisf/theZoo</t>
+          <t>usestrix/strix</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://github.com/ytisf/theZoo</t>
+          <t>https://github.com/usestrix/strix</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>A repository of LIVE malwares for your own joy and pleasure. theZoo is a project created to make the possibility of malware analysis open and available to the public.</t>
+          <t>Open-source AI agents for penetration testing</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>12427</v>
+        <v>12428</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -8185,43 +8185,43 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>19-11-2025 03:43</t>
+          <t>19-11-2025 04:41</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>09-01-2014 18:55</t>
+          <t>05-08-2025 21:28</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>malware, malware-analysis, malware-research, malware-samples, malwareanalysis</t>
+          <t>agents, artificial-intelligence, cybersecurity, generative-ai, llm</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>usestrix/strix</t>
+          <t>ytisf/theZoo</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://github.com/usestrix/strix</t>
+          <t>https://github.com/ytisf/theZoo</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Open-source AI agents for penetration testing</t>
+          <t>A repository of LIVE malwares for your own joy and pleasure. theZoo is a project created to make the possibility of malware analysis open and available to the public.</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>12424</v>
+        <v>12427</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -8230,17 +8230,17 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 03:43</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>05-08-2025 21:28</t>
+          <t>09-01-2014 18:55</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>agents, artificial-intelligence, cybersecurity, generative-ai, llm</t>
+          <t>malware, malware-analysis, malware-research, malware-samples, malwareanalysis</t>
         </is>
       </c>
     </row>
@@ -8306,11 +8306,11 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>12227</v>
+        <v>12228</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>19-11-2025 03:26</t>
+          <t>19-11-2025 04:41</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>12181</v>
+        <v>12183</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>11635</v>
+        <v>11634</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>19-11-2025 01:57</t>
+          <t>19-11-2025 04:43</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>11465</v>
+        <v>11466</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>19-11-2025 04:14</t>
+          <t>19-11-2025 04:43</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>10711</v>
+        <v>10709</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>19-11-2025 02:03</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>19-11-2025 04:26</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9671,11 +9671,11 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>8798</v>
+        <v>8799</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>18-11-2025 20:10</t>
+          <t>19-11-2025 04:34</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>8297</v>
+        <v>8298</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>19-11-2025 04:08</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10111,11 +10111,11 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>8026</v>
+        <v>8025</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>18-11-2025 14:35</t>
+          <t>19-11-2025 04:32</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>7274</v>
+        <v>7273</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6097</v>
+        <v>6098</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>19-11-2025 04:01</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4673</v>
+        <v>4675</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:43</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>19-11-2025 03:22</t>
+          <t>19-11-2025 04:38</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>18-11-2025 10:42</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>19-11-2025 03:11</t>
+          <t>19-11-2025 04:36</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -14073,7 +14073,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>18-11-2025 23:59</t>
+          <t>19-11-2025 04:30</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -16050,7 +16050,7 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>18-11-2025 23:37</t>
+          <t>19-11-2025 04:33</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440008</v>
+        <v>440009</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19-11-2025 04:43</t>
+          <t>19-11-2025 04:46</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2047,11 +2047,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>66748</v>
+        <v>66749</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:46</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2132,11 +2132,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63733</v>
+        <v>63734</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 04:46</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51191</v>
+        <v>51192</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19-11-2025 04:23</t>
+          <t>19-11-2025 04:46</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2914,11 +2914,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19-11-2025 03:48</t>
+          <t>19-11-2025 04:46</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44056</v>
+        <v>44057</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 04:43</t>
+          <t>19-11-2025 04:44</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>39349</v>
+        <v>39350</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19-11-2025 04:42</t>
+          <t>19-11-2025 04:44</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>19-11-2025 04:44</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>19-11-2025 04:21</t>
+          <t>19-11-2025 04:44</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>14883</v>
+        <v>14884</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 04:45</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>13522</v>
+        <v>13523</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>19-11-2025 04:40</t>
+          <t>19-11-2025 04:45</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>9284</v>
+        <v>9283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>19-11-2025 03:35</t>
+          <t>19-11-2025 04:45</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>9116</v>
+        <v>9117</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>19-11-2025 03:29</t>
+          <t>19-11-2025 04:45</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>7737</v>
+        <v>7738</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>18-11-2025 12:50</t>
+          <t>19-11-2025 04:45</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -13772,11 +13772,11 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>19-11-2025 04:29</t>
+          <t>19-11-2025 04:46</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440009</v>
+        <v>440017</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19-11-2025 04:46</t>
+          <t>19-11-2025 05:08</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>415842</v>
+        <v>415844</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19-11-2025 04:35</t>
+          <t>19-11-2025 05:05</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379360</v>
+        <v>379365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19-11-2025 04:42</t>
+          <t>19-11-2025 04:58</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>269959</v>
+        <v>269958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-11-2025 04:42</t>
+          <t>19-11-2025 05:08</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258855</v>
+        <v>258856</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19-11-2025 04:40</t>
+          <t>19-11-2025 05:04</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250250</v>
+        <v>250252</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19-11-2025 04:42</t>
+          <t>19-11-2025 04:47</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>197878</v>
+        <v>197879</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19-11-2025 04:21</t>
+          <t>19-11-2025 05:03</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>194690</v>
+        <v>194693</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19-11-2025 04:36</t>
+          <t>19-11-2025 05:09</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157211</v>
+        <v>157217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19-11-2025 04:37</t>
+          <t>19-11-2025 05:06</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156644</v>
+        <v>156645</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19-11-2025 04:35</t>
+          <t>19-11-2025 04:50</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>136642</v>
+        <v>136643</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 05:07</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135559</v>
+        <v>135562</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19-11-2025 04:39</t>
+          <t>19-11-2025 04:52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131265</v>
+        <v>131267</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19-11-2025 04:40</t>
+          <t>19-11-2025 05:09</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115598</v>
+        <v>115600</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19-11-2025 04:38</t>
+          <t>19-11-2025 04:53</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115116</v>
+        <v>115117</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19-11-2025 03:45</t>
+          <t>19-11-2025 05:04</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102691</v>
+        <v>102692</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19-11-2025 04:16</t>
+          <t>19-11-2025 05:07</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>86463</v>
+        <v>86464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19-11-2025 04:01</t>
+          <t>19-11-2025 04:49</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83208</v>
+        <v>83213</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 04:40</t>
+          <t>19-11-2025 05:08</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1737,11 +1737,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>79838</v>
+        <v>79837</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19-11-2025 04:34</t>
+          <t>19-11-2025 05:05</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>78618</v>
+        <v>78621</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19-11-2025 03:53</t>
+          <t>19-11-2025 05:06</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>67825</v>
+        <v>67826</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 05:01</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>58627</v>
+        <v>58628</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19-11-2025 04:38</t>
+          <t>19-11-2025 05:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>51738</v>
+        <v>51739</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18-11-2025 22:24</t>
+          <t>19-11-2025 05:04</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51192</v>
+        <v>51193</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19-11-2025 04:46</t>
+          <t>19-11-2025 04:52</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>47818</v>
+        <v>47820</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>19-11-2025 03:37</t>
+          <t>19-11-2025 04:49</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>47762</v>
+        <v>47763</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>19-11-2025 04:03</t>
+          <t>19-11-2025 05:01</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47214</v>
+        <v>47217</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19-11-2025 04:41</t>
+          <t>19-11-2025 04:53</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2914,11 +2914,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19-11-2025 04:46</t>
+          <t>19-11-2025 04:55</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44057</v>
+        <v>44062</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 04:44</t>
+          <t>19-11-2025 05:09</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>42622</v>
+        <v>42629</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19-11-2025 04:43</t>
+          <t>19-11-2025 05:09</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>41651</v>
+        <v>41654</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>19-11-2025 05:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3211,11 +3211,11 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>40952</v>
+        <v>40953</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>19-11-2025 03:33</t>
+          <t>19-11-2025 04:52</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>39350</v>
+        <v>39351</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19-11-2025 04:44</t>
+          <t>19-11-2025 04:59</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>38775</v>
+        <v>38776</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19-11-2025 04:39</t>
+          <t>19-11-2025 04:48</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>37941</v>
+        <v>37940</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19-11-2025 03:10</t>
+          <t>19-11-2025 05:07</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>34441</v>
+        <v>34442</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>19-11-2025 04:30</t>
+          <t>19-11-2025 04:57</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31765</v>
+        <v>31766</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>19-11-2025 04:22</t>
+          <t>19-11-2025 04:52</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>27101</v>
+        <v>27102</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>19-11-2025 00:23</t>
+          <t>19-11-2025 05:08</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>19-11-2025 04:44</t>
+          <t>19-11-2025 05:03</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>23860</v>
+        <v>23861</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>18-11-2025 22:05</t>
+          <t>19-11-2025 05:07</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>22100</v>
+        <v>22099</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>19-11-2025 04:44</t>
+          <t>19-11-2025 05:07</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21945</v>
+        <v>21946</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>19-11-2025 04:40</t>
+          <t>19-11-2025 05:08</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>20573</v>
+        <v>20574</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>19-11-2025 03:04</t>
+          <t>19-11-2025 04:59</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>20571</v>
+        <v>20572</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>19-11-2025 03:02</t>
+          <t>19-11-2025 05:01</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>19-11-2025 03:30</t>
+          <t>19-11-2025 05:07</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>18945</v>
+        <v>18946</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>19-11-2025 03:54</t>
+          <t>19-11-2025 05:05</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>18366</v>
+        <v>18369</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>19-11-2025 04:42</t>
+          <t>19-11-2025 05:06</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>17390</v>
+        <v>17391</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>19-11-2025 04:34</t>
+          <t>19-11-2025 05:06</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>19-11-2025 02:37</t>
+          <t>19-11-2025 04:50</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>16253</v>
+        <v>16255</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>19-11-2025 04:31</t>
+          <t>19-11-2025 04:56</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>15675</v>
+        <v>15677</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>19-11-2025 03:19</t>
+          <t>19-11-2025 05:05</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>15542</v>
+        <v>15543</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>19-11-2025 04:38</t>
+          <t>19-11-2025 04:57</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>15513</v>
+        <v>15515</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>19-11-2025 04:38</t>
+          <t>19-11-2025 05:00</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>14884</v>
+        <v>14886</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>19-11-2025 04:45</t>
+          <t>19-11-2025 05:04</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>13523</v>
+        <v>13524</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>19-11-2025 04:45</t>
+          <t>19-11-2025 05:00</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>13438</v>
+        <v>13440</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>19-11-2025 03:25</t>
+          <t>19-11-2025 05:03</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>13336</v>
+        <v>13338</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>18-11-2025 10:34</t>
+          <t>19-11-2025 04:59</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>12428</v>
+        <v>12435</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>19-11-2025 04:41</t>
+          <t>19-11-2025 05:08</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>10821</v>
+        <v>10822</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>18-11-2025 19:27</t>
+          <t>19-11-2025 04:52</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>9659</v>
+        <v>9660</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>19-11-2025 03:01</t>
+          <t>19-11-2025 05:02</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>8946</v>
+        <v>8948</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>19-11-2025 04:29</t>
+          <t>19-11-2025 05:03</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>8541</v>
+        <v>8542</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>19-11-2025 04:08</t>
+          <t>19-11-2025 05:01</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>7273</v>
+        <v>7274</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>19-11-2025 04:33</t>
+          <t>19-11-2025 04:51</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -11290,7 +11290,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5425</v>
+        <v>5426</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>19-11-2025 00:59</t>
+          <t>19-11-2025 04:58</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4675</v>
+        <v>4676</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>19-11-2025 04:43</t>
+          <t>19-11-2025 05:01</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3555</v>
+        <v>3556</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>19-11-2025 04:33</t>
+          <t>19-11-2025 04:51</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -13708,85 +13708,85 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>kevinzg/facebook-scraper</t>
+          <t>proxifly/free-proxy-list</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://github.com/kevinzg/facebook-scraper</t>
+          <t>https://github.com/proxifly/free-proxy-list</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Scrape Facebook public pages without an API key</t>
+          <t>🚀 Free HTTP, SOCKS4, &amp; SOCKS5 Proxy List * Updated every 5 minutes *</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>2958</v>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
+        <v>2960</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>18-11-2025 22:24</t>
+          <t>19-11-2025 04:58</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>15-03-2019 04:36</t>
+          <t>13-07-2023 06:26</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>facebook, facebook-scraper, facebook-scraping, hacktoberfest, scraping</t>
+          <t>free-proxy, free-proxy-list, fresh-proxies, http, http-proxy</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>proxifly/free-proxy-list</t>
+          <t>kevinzg/facebook-scraper</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://github.com/proxifly/free-proxy-list</t>
+          <t>https://github.com/kevinzg/facebook-scraper</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>🚀 Free HTTP, SOCKS4, &amp; SOCKS5 Proxy List * Updated every 5 minutes *</t>
+          <t>Scrape Facebook public pages without an API key</t>
         </is>
       </c>
       <c r="E304" t="n">
         <v>2958</v>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>19-11-2025 04:46</t>
+          <t>18-11-2025 22:24</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>13-07-2023 06:26</t>
+          <t>15-03-2019 04:36</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>free-proxy, free-proxy-list, fresh-proxies, http, http-proxy</t>
+          <t>facebook, facebook-scraper, facebook-scraping, hacktoberfest, scraping</t>
         </is>
       </c>
     </row>
@@ -14559,7 +14559,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 04:51</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -14604,7 +14604,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>19-11-2025 04:28</t>
+          <t>19-11-2025 04:57</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>19-11-2025 04:01</t>
+          <t>19-11-2025 05:05</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -17449,7 +17449,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>18-11-2025 10:25</t>
+          <t>19-11-2025 05:07</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17805,7 +17805,7 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>19-11-2025 03:09</t>
+          <t>19-11-2025 04:52</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -18102,7 +18102,7 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>19-11-2025 01:33</t>
+          <t>19-11-2025 05:09</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -18229,7 +18229,7 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>19-11-2025 03:21</t>
+          <t>19-11-2025 04:58</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>19-11-2025 01:50</t>
+          <t>19-11-2025 04:56</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440017</v>
+        <v>440018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19-11-2025 05:08</t>
+          <t>19-11-2025 05:10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>415844</v>
+        <v>415845</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19-11-2025 05:05</t>
+          <t>19-11-2025 05:10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379365</v>
+        <v>379366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19-11-2025 04:58</t>
+          <t>19-11-2025 05:11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250252</v>
+        <v>250253</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19-11-2025 04:47</t>
+          <t>19-11-2025 05:10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156645</v>
+        <v>156644</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19-11-2025 04:50</t>
+          <t>19-11-2025 05:11</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83213</v>
+        <v>83214</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 05:08</t>
+          <t>19-11-2025 05:10</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44062</v>
+        <v>44063</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 05:09</t>
+          <t>19-11-2025 05:11</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>25011</v>
+        <v>25012</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>19-11-2025 03:33</t>
+          <t>19-11-2025 05:10</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>19-11-2025 02:29</t>
+          <t>19-11-2025 05:11</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>15515</v>
+        <v>15516</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>19-11-2025 05:00</t>
+          <t>19-11-2025 05:10</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>12435</v>
+        <v>12436</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>19-11-2025 05:08</t>
+          <t>19-11-2025 05:11</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5886</v>
+        <v>5887</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>18-11-2025 20:31</t>
+          <t>19-11-2025 05:10</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440018</v>
+        <v>440326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19-11-2025 05:10</t>
+          <t>20-11-2025 00:51</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>415845</v>
+        <v>416060</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19-11-2025 05:10</t>
+          <t>20-11-2025 00:50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379366</v>
+        <v>379569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19-11-2025 05:11</t>
+          <t>20-11-2025 00:51</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>269958</v>
+        <v>270093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-11-2025 05:08</t>
+          <t>20-11-2025 00:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258856</v>
+        <v>258988</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19-11-2025 05:04</t>
+          <t>20-11-2025 00:30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250253</v>
+        <v>250321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19-11-2025 05:10</t>
+          <t>20-11-2025 00:40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>197879</v>
+        <v>197935</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19-11-2025 05:03</t>
+          <t>20-11-2025 00:43</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>194693</v>
+        <v>194829</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19-11-2025 05:09</t>
+          <t>20-11-2025 00:47</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>182827</v>
+        <v>182848</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>19-11-2025 23:17</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157217</v>
+        <v>157407</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19-11-2025 05:06</t>
+          <t>20-11-2025 00:50</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156644</v>
+        <v>156785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19-11-2025 05:11</t>
+          <t>20-11-2025 00:46</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>136643</v>
+        <v>136679</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19-11-2025 05:07</t>
+          <t>20-11-2025 00:46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135562</v>
+        <v>135669</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19-11-2025 04:52</t>
+          <t>20-11-2025 00:39</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131267</v>
+        <v>131305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19-11-2025 05:09</t>
+          <t>20-11-2025 00:29</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125797</v>
+        <v>125822</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>20-11-2025 00:36</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1167,11 +1167,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115708</v>
+        <v>115719</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19-11-2025 02:27</t>
+          <t>19-11-2025 23:28</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115600</v>
+        <v>115688</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19-11-2025 04:53</t>
+          <t>20-11-2025 00:52</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115117</v>
+        <v>115135</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19-11-2025 05:04</t>
+          <t>19-11-2025 23:52</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102692</v>
+        <v>102755</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19-11-2025 05:07</t>
+          <t>20-11-2025 00:39</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,11 +1342,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100870</v>
+        <v>100901</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19-11-2025 04:21</t>
+          <t>20-11-2025 00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>93628</v>
+        <v>93671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>19-11-2025 04:07</t>
+          <t>20-11-2025 00:05</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>92890</v>
+        <v>92893</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19-11-2025 03:59</t>
+          <t>19-11-2025 23:35</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>92061</v>
+        <v>92083</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>20-11-2025 00:03</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>88042</v>
+        <v>88078</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19-11-2025 04:40</t>
+          <t>20-11-2025 00:45</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>86464</v>
+        <v>86467</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19-11-2025 04:49</t>
+          <t>20-11-2025 00:01</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>84478</v>
+        <v>84527</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>19-11-2025 04:22</t>
+          <t>20-11-2025 00:49</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83214</v>
+        <v>83513</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 05:10</t>
+          <t>20-11-2025 00:42</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83100</v>
+        <v>83122</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19-11-2025 04:37</t>
+          <t>20-11-2025 00:05</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,11 +1737,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>79837</v>
+        <v>79852</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19-11-2025 05:05</t>
+          <t>19-11-2025 22:25</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>78891</v>
+        <v>79065</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19-11-2025 04:13</t>
+          <t>20-11-2025 00:32</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>78621</v>
+        <v>78675</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19-11-2025 05:06</t>
+          <t>20-11-2025 00:43</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>75827</v>
+        <v>75852</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19-11-2025 04:33</t>
+          <t>19-11-2025 23:15</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>70384</v>
+        <v>70409</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19-11-2025 03:41</t>
+          <t>20-11-2025 00:12</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>68053</v>
+        <v>68112</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19-11-2025 04:35</t>
+          <t>20-11-2025 00:05</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>67826</v>
+        <v>67863</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19-11-2025 05:01</t>
+          <t>20-11-2025 00:03</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2047,11 +2047,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>66749</v>
+        <v>66772</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19-11-2025 04:46</t>
+          <t>20-11-2025 00:49</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65545</v>
+        <v>65553</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19-11-2025 01:54</t>
+          <t>20-11-2025 00:47</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2132,11 +2132,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63734</v>
+        <v>63746</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19-11-2025 04:46</t>
+          <t>20-11-2025 00:06</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>59557</v>
+        <v>59577</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19-11-2025 04:14</t>
+          <t>20-11-2025 00:21</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>58628</v>
+        <v>58727</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19-11-2025 05:00</t>
+          <t>20-11-2025 00:41</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2262,11 +2262,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>56772</v>
+        <v>56777</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19-11-2025 02:55</t>
+          <t>19-11-2025 19:57</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>56066</v>
+        <v>56105</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19-11-2025 04:39</t>
+          <t>20-11-2025 00:47</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53607</v>
+        <v>53621</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19-11-2025 01:53</t>
+          <t>20-11-2025 00:08</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53586</v>
+        <v>53611</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>19-11-2025 04:05</t>
+          <t>19-11-2025 23:29</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2433,11 +2433,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53567</v>
+        <v>53577</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>19-11-2025 04:23</t>
+          <t>19-11-2025 23:42</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18-11-2025 17:09</t>
+          <t>19-11-2025 19:11</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>51739</v>
+        <v>51742</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>19-11-2025 05:04</t>
+          <t>20-11-2025 00:27</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>51662</v>
+        <v>51669</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>19-11-2025 19:52</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51193</v>
+        <v>51215</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19-11-2025 04:52</t>
+          <t>20-11-2025 00:44</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>48621</v>
+        <v>48652</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>19-11-2025 04:41</t>
+          <t>20-11-2025 00:07</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>47820</v>
+        <v>47839</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>19-11-2025 04:49</t>
+          <t>19-11-2025 19:40</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>47763</v>
+        <v>47821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>19-11-2025 05:01</t>
+          <t>20-11-2025 00:35</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2765,85 +2765,85 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dkhamsing/open-source-ios-apps</t>
+          <t>coollabsio/coolify</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://github.com/dkhamsing/open-source-ios-apps</t>
+          <t>https://github.com/coollabsio/coolify</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>:iphone: Collaborative List of Open-Source iOS Apps</t>
+          <t>An open-source, self-hostable PaaS alternative to Vercel, Heroku &amp; Netlify that lets you easily deploy static sites, databases, full-stack applications and 280+ one-click services on your own servers.</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47454</v>
+        <v>47484</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19-11-2025 04:20</t>
+          <t>20-11-2025 00:25</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>26-01-2015 23:32</t>
+          <t>25-01-2021 20:54</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>app, apple, apple-tv, apple-vision-pro, apple-watch</t>
+          <t>coolify, databases, deployment, docker, docker-compose</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>coollabsio/coolify</t>
+          <t>dkhamsing/open-source-ios-apps</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://github.com/coollabsio/coolify</t>
+          <t>https://github.com/dkhamsing/open-source-ios-apps</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>An open-source, self-hostable PaaS alternative to Vercel, Heroku &amp; Netlify that lets you easily deploy static sites, databases, full-stack applications and 280+ one-click services on your own servers.</t>
+          <t>:iphone: Collaborative List of Open-Source iOS Apps</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>47445</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>PHP</t>
-        </is>
+        <v>47461</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>19-11-2025 04:18</t>
+          <t>20-11-2025 00:05</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>25-01-2021 20:54</t>
+          <t>26-01-2015 23:32</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>coolify, databases, deployment, docker, docker-compose</t>
+          <t>app, apple, apple-tv, apple-vision-pro, apple-watch</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47217</v>
+        <v>47257</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19-11-2025 04:53</t>
+          <t>19-11-2025 20:41</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2914,11 +2914,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19-11-2025 04:55</t>
+          <t>20-11-2025 00:05</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>46175</v>
+        <v>46214</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19-11-2025 03:02</t>
+          <t>20-11-2025 00:12</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2999,11 +2999,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44063</v>
+        <v>44209</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19-11-2025 05:11</t>
+          <t>20-11-2025 00:44</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>42852</v>
+        <v>42885</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>19-11-2025 01:58</t>
+          <t>20-11-2025 00:35</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>42629</v>
+        <v>42782</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19-11-2025 05:09</t>
+          <t>20-11-2025 00:51</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>42456</v>
+        <v>42476</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>19-11-2025 04:20</t>
+          <t>19-11-2025 23:11</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>41654</v>
+        <v>42238</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>19-11-2025 05:00</t>
+          <t>20-11-2025 00:49</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3211,11 +3211,11 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>40953</v>
+        <v>40962</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>19-11-2025 04:52</t>
+          <t>20-11-2025 00:15</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>39351</v>
+        <v>39366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19-11-2025 04:59</t>
+          <t>20-11-2025 00:46</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>39157</v>
+        <v>39173</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19-11-2025 04:27</t>
+          <t>19-11-2025 22:04</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>39056</v>
+        <v>39074</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>19-11-2025 03:19</t>
+          <t>20-11-2025 00:43</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>38776</v>
+        <v>38833</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19-11-2025 04:48</t>
+          <t>20-11-2025 00:05</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>38608</v>
+        <v>38610</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 22:42</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>37940</v>
+        <v>37944</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19-11-2025 05:07</t>
+          <t>19-11-2025 22:45</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>37326</v>
+        <v>37348</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>19-11-2025 02:40</t>
+          <t>20-11-2025 00:15</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>36921</v>
+        <v>36928</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>19-11-2025 02:55</t>
+          <t>19-11-2025 23:34</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>35865</v>
+        <v>35873</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19-11-2025 04:21</t>
+          <t>19-11-2025 21:16</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>35560</v>
+        <v>35593</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>19-11-2025 03:38</t>
+          <t>20-11-2025 00:42</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>35474</v>
+        <v>35487</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>19-11-2025 02:45</t>
+          <t>19-11-2025 20:31</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3746,11 +3746,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>34559</v>
+        <v>34566</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>19-11-2025 02:30</t>
+          <t>19-11-2025 22:45</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>34442</v>
+        <v>34463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>19-11-2025 04:57</t>
+          <t>19-11-2025 21:42</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34222</v>
+        <v>34226</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>19-11-2025 02:51</t>
+          <t>19-11-2025 14:07</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>33392</v>
+        <v>33401</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>19-11-2025 04:08</t>
+          <t>20-11-2025 00:14</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3921,11 +3921,11 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>32669</v>
+        <v>32682</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18-11-2025 22:33</t>
+          <t>20-11-2025 00:42</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>31897</v>
+        <v>31900</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18-11-2025 15:01</t>
+          <t>19-11-2025 13:45</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4042,11 +4042,11 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>31779</v>
+        <v>31794</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>19-11-2025 04:00</t>
+          <t>19-11-2025 21:01</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31766</v>
+        <v>31793</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>19-11-2025 04:52</t>
+          <t>19-11-2025 23:31</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>31604</v>
+        <v>31614</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>19-11-2025 03:05</t>
+          <t>20-11-2025 00:45</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>31286</v>
+        <v>31329</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19-11-2025 04:37</t>
+          <t>20-11-2025 00:26</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>29783</v>
+        <v>29798</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>19-11-2025 02:37</t>
+          <t>20-11-2025 00:19</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>29281</v>
+        <v>29288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>19-11-2025 03:46</t>
+          <t>19-11-2025 20:28</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>28859</v>
+        <v>28866</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>20-11-2025 00:46</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4352,11 +4352,11 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>28436</v>
+        <v>28442</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>19-11-2025 03:27</t>
+          <t>19-11-2025 20:36</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>28423</v>
+        <v>28425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18-11-2025 15:09</t>
+          <t>19-11-2025 20:58</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28031</v>
+        <v>28048</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>19-11-2025 04:21</t>
+          <t>19-11-2025 23:22</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4527,11 +4527,11 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>27094</v>
+        <v>27097</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18-11-2025 23:06</t>
+          <t>19-11-2025 13:30</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>26958</v>
+        <v>26989</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>19-11-2025 05:03</t>
+          <t>20-11-2025 00:34</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>26821</v>
+        <v>26836</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>19-11-2025 03:26</t>
+          <t>19-11-2025 23:32</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>26307</v>
+        <v>26315</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>19-11-2025 03:53</t>
+          <t>19-11-2025 16:40</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>26048</v>
+        <v>26063</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>19-11-2025 02:43</t>
+          <t>19-11-2025 19:29</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26043</v>
+        <v>26051</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 20:44</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>25980</v>
+        <v>25983</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>18-11-2025 15:32</t>
+          <t>19-11-2025 17:23</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>25720</v>
+        <v>25728</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>19-11-2025 04:27</t>
+          <t>20-11-2025 00:49</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4878,11 +4878,11 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>25580</v>
+        <v>25587</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>19-11-2025 04:23</t>
+          <t>19-11-2025 14:45</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>25547</v>
+        <v>25563</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>19-11-2025 03:58</t>
+          <t>19-11-2025 23:29</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>25431</v>
+        <v>25443</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>19-11-2025 01:44</t>
+          <t>19-11-2025 23:24</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>25012</v>
+        <v>25028</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>19-11-2025 05:10</t>
+          <t>20-11-2025 00:17</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5049,11 +5049,11 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>24515</v>
+        <v>24517</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>18-11-2025 23:08</t>
+          <t>19-11-2025 21:21</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>24428</v>
+        <v>24431</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>18-11-2025 20:03</t>
+          <t>19-11-2025 12:22</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>23861</v>
+        <v>23864</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>19-11-2025 05:07</t>
+          <t>19-11-2025 21:46</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>23835</v>
+        <v>23843</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>20-11-2025 00:15</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>23775</v>
+        <v>23787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>19-11-2025 04:36</t>
+          <t>20-11-2025 00:07</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>23116</v>
+        <v>23122</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>19-11-2025 03:26</t>
+          <t>19-11-2025 21:27</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5314,11 +5314,11 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>22441</v>
+        <v>22442</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>18-11-2025 17:46</t>
+          <t>19-11-2025 11:13</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>22099</v>
+        <v>22131</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>19-11-2025 05:07</t>
+          <t>19-11-2025 23:55</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21946</v>
+        <v>21993</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>19-11-2025 05:08</t>
+          <t>19-11-2025 22:18</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>21903</v>
+        <v>21907</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>18-11-2025 23:21</t>
+          <t>19-11-2025 14:08</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>21817</v>
+        <v>21829</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>19-11-2025 03:41</t>
+          <t>19-11-2025 21:39</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>21331</v>
+        <v>21353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>19-11-2025 05:11</t>
+          <t>19-11-2025 22:59</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>21028</v>
+        <v>21037</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>19-11-2025 03:11</t>
+          <t>19-11-2025 16:16</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>20657</v>
+        <v>20666</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>19-11-2025 00:12</t>
+          <t>19-11-2025 22:00</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5642,90 +5642,90 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LiLittleCat/awesome-free-chatgpt</t>
+          <t>apify/crawlee</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://github.com/LiLittleCat/awesome-free-chatgpt</t>
+          <t>https://github.com/apify/crawlee</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>🆓免费的 ChatGPT 镜像网站列表，持续更新。List of free ChatGPT mirror sites, continuously updated.</t>
+          <t>Crawlee—A web scraping and browser automation library for Node.js to build reliable crawlers. In JavaScript and TypeScript. Extract data for AI, LLMs, RAG, or GPTs.</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>20574</v>
+        <v>20584</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>19-11-2025 04:59</t>
+          <t>19-11-2025 22:13</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>09-03-2023 07:37</t>
+          <t>26-08-2016 18:35</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, chat, chatgpt, free</t>
+          <t>apify, automation, crawler, crawling, headless</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>apify/crawlee</t>
+          <t>LiLittleCat/awesome-free-chatgpt</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://github.com/apify/crawlee</t>
+          <t>https://github.com/LiLittleCat/awesome-free-chatgpt</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Crawlee—A web scraping and browser automation library for Node.js to build reliable crawlers. In JavaScript and TypeScript. Extract data for AI, LLMs, RAG, or GPTs.</t>
+          <t>🆓免费的 ChatGPT 镜像网站列表，持续更新。List of free ChatGPT mirror sites, continuously updated.</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>20572</v>
+        <v>20578</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>19-11-2025 05:01</t>
+          <t>19-11-2025 12:24</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>26-08-2016 18:35</t>
+          <t>09-03-2023 07:37</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>apify, automation, crawler, crawling, headless</t>
+          <t>awesome, awesome-list, chat, chatgpt, free</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>20114</v>
+        <v>20117</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>19-11-2025 03:35</t>
+          <t>19-11-2025 23:14</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5796,11 +5796,11 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>19474</v>
+        <v>19480</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>19-11-2025 05:07</t>
+          <t>20-11-2025 00:44</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5836,11 +5836,11 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>19155</v>
+        <v>19165</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>19-11-2025 04:38</t>
+          <t>19-11-2025 18:01</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>18946</v>
+        <v>18989</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>19-11-2025 05:05</t>
+          <t>19-11-2025 23:08</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>18369</v>
+        <v>18446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>19-11-2025 05:06</t>
+          <t>20-11-2025 00:38</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>18228</v>
+        <v>18233</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>19-11-2025 01:33</t>
+          <t>19-11-2025 18:05</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>18-11-2025 23:24</t>
+          <t>19-11-2025 20:39</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>18031</v>
+        <v>18040</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>19-11-2025 02:32</t>
+          <t>19-11-2025 17:35</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>17910</v>
+        <v>17914</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>18-11-2025 20:46</t>
+          <t>19-11-2025 23:14</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>17850</v>
+        <v>17853</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>19-11-2025 03:28</t>
+          <t>19-11-2025 23:58</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>17675</v>
+        <v>17688</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>19-11-2025 02:27</t>
+          <t>19-11-2025 23:08</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>17602</v>
+        <v>17608</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>19-11-2025 04:19</t>
+          <t>20-11-2025 00:47</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>17416</v>
+        <v>17423</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>19-11-2025 03:38</t>
+          <t>19-11-2025 18:38</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>17391</v>
+        <v>17404</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>19-11-2025 05:06</t>
+          <t>19-11-2025 22:21</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>17242</v>
+        <v>17250</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>19-11-2025 02:53</t>
+          <t>19-11-2025 21:18</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>17184</v>
+        <v>17193</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>19-11-2025 03:53</t>
+          <t>20-11-2025 00:10</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6461,11 +6461,11 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17058</v>
+        <v>17059</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>19-11-2025 04:17</t>
+          <t>19-11-2025 13:27</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>16669</v>
+        <v>16689</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>19-11-2025 04:50</t>
+          <t>19-11-2025 23:52</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>16255</v>
+        <v>16277</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>19-11-2025 04:56</t>
+          <t>20-11-2025 00:05</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>15892</v>
+        <v>15894</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>18-11-2025 13:58</t>
+          <t>19-11-2025 12:13</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>15882</v>
+        <v>15888</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>18-11-2025 22:24</t>
+          <t>19-11-2025 16:56</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6681,11 +6681,11 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>15815</v>
+        <v>15839</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 23:01</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6702,90 +6702,90 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>jeessy2/ddns-go</t>
+          <t>TibixDev/winboat</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://github.com/jeessy2/ddns-go</t>
+          <t>https://github.com/TibixDev/winboat</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Simple and easy to use DDNS. Support Aliyun, Tencent Cloud, Dnspod, Cloudflare, Callback, Huawei Cloud, Baidu Cloud, Porkbun, GoDaddy, Namecheap, NameSilo...</t>
+          <t>Run Windows apps on 🐧 Linux with ✨ seamless integration</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>15677</v>
+        <v>15693</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>19-11-2025 05:05</t>
+          <t>20-11-2025 00:04</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>26-08-2020 08:17</t>
+          <t>04-04-2025 12:03</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>alidns, baiduyun, cloudflare, ddns, ddns-go</t>
+          <t>docker, docker-compose, linux, rdp, virtualization</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TibixDev/winboat</t>
+          <t>jeessy2/ddns-go</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://github.com/TibixDev/winboat</t>
+          <t>https://github.com/jeessy2/ddns-go</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Run Windows apps on 🐧 Linux with ✨ seamless integration</t>
+          <t>Simple and easy to use DDNS. Support Aliyun, Tencent Cloud, Dnspod, Cloudflare, Callback, Huawei Cloud, Baidu Cloud, Porkbun, GoDaddy, Namecheap, NameSilo...</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>15664</v>
+        <v>15682</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>19-11-2025 03:53</t>
+          <t>19-11-2025 23:57</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>04-04-2025 12:03</t>
+          <t>26-08-2020 08:17</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>docker, docker-compose, linux, rdp, virtualization</t>
+          <t>alidns, baiduyun, cloudflare, ddns, ddns-go</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>15645</v>
+        <v>15668</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>19-11-2025 03:59</t>
+          <t>19-11-2025 22:54</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>15543</v>
+        <v>15560</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>19-11-2025 04:57</t>
+          <t>20-11-2025 00:48</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>15516</v>
+        <v>15551</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>19-11-2025 05:10</t>
+          <t>20-11-2025 00:39</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>15203</v>
+        <v>15208</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>19-11-2025 04:18</t>
+          <t>19-11-2025 22:43</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15046</v>
+        <v>15048</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>19-11-2025 02:50</t>
+          <t>19-11-2025 22:48</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>14998</v>
+        <v>15008</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>18-11-2025 23:46</t>
+          <t>20-11-2025 00:31</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>14886</v>
+        <v>14944</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>19-11-2025 05:04</t>
+          <t>20-11-2025 00:46</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>14870</v>
+        <v>14877</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>19-11-2025 00:50</t>
+          <t>19-11-2025 22:01</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>14836</v>
+        <v>14846</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>19-11-2025 03:21</t>
+          <t>19-11-2025 20:28</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>14740</v>
+        <v>14747</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>18-11-2025 13:16</t>
+          <t>20-11-2025 00:44</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7234,26 +7234,26 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ag-grid/ag-grid</t>
+          <t>ahmedkhaleel2004/gitdiagram</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://github.com/ag-grid/ag-grid</t>
+          <t>https://github.com/ahmedkhaleel2004/gitdiagram</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>The best JavaScript Data Table for building Enterprise Applications. Supports React / Angular / Vue / Plain JavaScript.</t>
+          <t>Free, simple, fast interactive diagrams for any GitHub repository</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>14729</v>
+        <v>14731</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -7262,43 +7262,43 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>19-11-2025 02:58</t>
+          <t>19-11-2025 14:12</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>23-12-2014 16:20</t>
+          <t>15-12-2024 10:32</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>angular, angular-grid, angular-table, charting, datagrid</t>
+          <t>ai, code, github, system-design</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ahmedkhaleel2004/gitdiagram</t>
+          <t>ag-grid/ag-grid</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://github.com/ahmedkhaleel2004/gitdiagram</t>
+          <t>https://github.com/ag-grid/ag-grid</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Free, simple, fast interactive diagrams for any GitHub repository</t>
+          <t>The best JavaScript Data Table for building Enterprise Applications. Supports React / Angular / Vue / Plain JavaScript.</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>14728</v>
+        <v>14731</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7307,17 +7307,17 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>19-11-2025 01:28</t>
+          <t>19-11-2025 16:05</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>15-12-2024 10:32</t>
+          <t>23-12-2014 16:20</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>ai, code, github, system-design</t>
+          <t>angular, angular-grid, angular-table, charting, datagrid</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>14641</v>
+        <v>14653</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>19-11-2025 04:31</t>
+          <t>19-11-2025 18:48</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>14624</v>
+        <v>14628</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>18-11-2025 13:54</t>
+          <t>19-11-2025 16:27</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>14093</v>
+        <v>14098</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>18-11-2025 20:57</t>
+          <t>19-11-2025 20:45</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>18-11-2025 20:55</t>
+          <t>19-11-2025 19:05</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>13841</v>
+        <v>13847</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>19-11-2025 02:15</t>
+          <t>19-11-2025 20:50</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7605,7 +7605,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>13807</v>
+        <v>13811</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>19-11-2025 00:29</t>
+          <t>19-11-2025 19:15</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>13761</v>
+        <v>13762</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>18-11-2025 22:56</t>
+          <t>19-11-2025 13:58</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>13524</v>
+        <v>13577</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>19-11-2025 05:00</t>
+          <t>20-11-2025 00:22</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>13521</v>
+        <v>13529</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>19-11-2025 03:51</t>
+          <t>19-11-2025 14:54</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7766,90 +7766,90 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Powerlevel9k/powerlevel9k</t>
+          <t>AstrBotDevs/AstrBot</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://github.com/Powerlevel9k/powerlevel9k</t>
+          <t>https://github.com/AstrBotDevs/AstrBot</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CLI Tools</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Powerlevel9k was a tool for building a beautiful and highly functional CLI, customized for you. P9k had a substantial impact on CLI UX, and its legacy is now continued by P10k.</t>
+          <t>✨ Agentic IM ChatBot Infrastructure ✨ Integration with multiple IMs, easy-to-use plugin system, supports OpenAI, Gemini, Anthropic, Dify, Coze, built-in Knowledge Base, Agent. ✨ 一站式大模型聊天机器人平台及开发框架 ...</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>13444</v>
+        <v>13461</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>13-11-2025 09:03</t>
+          <t>19-11-2025 18:05</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>29-01-2015 04:36</t>
+          <t>08-12-2022 13:27</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>eye-candy, powerline-fonts, terminal, terminal-themes, tools</t>
+          <t>agent, ai, chatbot, chatgpt, docker</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AstrBotDevs/AstrBot</t>
+          <t>Powerlevel9k/powerlevel9k</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://github.com/AstrBotDevs/AstrBot</t>
+          <t>https://github.com/Powerlevel9k/powerlevel9k</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>CLI Tools</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>✨ Agentic IM ChatBot Infrastructure ✨ Integration with multiple IMs, easy-to-use plugin system, supports OpenAI, Gemini, Anthropic, Dify, Coze, built-in Knowledge Base, Agent. ✨ 一站式大模型聊天机器人平台及开发框架 ...</t>
+          <t>Powerlevel9k was a tool for building a beautiful and highly functional CLI, customized for you. P9k had a substantial impact on CLI UX, and its legacy is now continued by P10k.</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>13440</v>
+        <v>13445</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>19-11-2025 05:03</t>
+          <t>19-11-2025 11:13</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>08-12-2022 13:27</t>
+          <t>29-01-2015 04:36</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>agent, ai, chatbot, chatgpt, docker</t>
+          <t>eye-candy, powerline-fonts, terminal, terminal-themes, tools</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>13338</v>
+        <v>13340</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>19-11-2025 04:59</t>
+          <t>19-11-2025 21:45</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7920,11 +7920,11 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>13302</v>
+        <v>13308</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>19-11-2025 04:24</t>
+          <t>19-11-2025 19:13</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>13163</v>
+        <v>13167</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>19-11-2025 02:06</t>
+          <t>19-11-2025 23:29</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13109</v>
+        <v>13115</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>19-11-2025 02:14</t>
+          <t>19-11-2025 18:07</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8050,11 +8050,11 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>12861</v>
+        <v>12865</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>18-11-2025 17:59</t>
+          <t>19-11-2025 23:26</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8071,26 +8071,26 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>trustedsec/social-engineer-toolkit</t>
+          <t>usestrix/strix</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://github.com/trustedsec/social-engineer-toolkit</t>
+          <t>https://github.com/usestrix/strix</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>The Social-Engineer Toolkit (SET) repository from TrustedSec - All new versions of SET will be deployed here.</t>
+          <t>Open-source AI agents for penetration testing</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>12609</v>
+        <v>12614</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -8099,70 +8099,70 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>19-11-2025 01:23</t>
+          <t>20-11-2025 00:49</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>31-12-2012 22:01</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>05-08-2025 21:28</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>agents, artificial-intelligence, cybersecurity, generative-ai, llm</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>projectdiscovery/subfinder</t>
+          <t>trustedsec/social-engineer-toolkit</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://github.com/projectdiscovery/subfinder</t>
+          <t>https://github.com/trustedsec/social-engineer-toolkit</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Fast passive subdomain enumeration tool.</t>
+          <t>The Social-Engineer Toolkit (SET) repository from TrustedSec - All new versions of SET will be deployed here.</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>12567</v>
+        <v>12612</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>19-11-2025 04:24</t>
+          <t>19-11-2025 14:38</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>31-03-2018 09:44</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>bugbounty, hacking, hacktoberfest, osint, reconnaissance</t>
-        </is>
-      </c>
+          <t>31-12-2012 22:01</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>usestrix/strix</t>
+          <t>projectdiscovery/subfinder</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://github.com/usestrix/strix</t>
+          <t>https://github.com/projectdiscovery/subfinder</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8172,30 +8172,30 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Open-source AI agents for penetration testing</t>
+          <t>Fast passive subdomain enumeration tool.</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>12436</v>
+        <v>12570</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>19-11-2025 05:11</t>
+          <t>19-11-2025 17:27</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>05-08-2025 21:28</t>
+          <t>31-03-2018 09:44</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>agents, artificial-intelligence, cybersecurity, generative-ai, llm</t>
+          <t>bugbounty, hacking, hacktoberfest, osint, reconnaissance</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>12427</v>
+        <v>12431</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>19-11-2025 03:43</t>
+          <t>20-11-2025 00:35</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8266,11 +8266,11 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>12303</v>
+        <v>12305</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>18-11-2025 21:09</t>
+          <t>19-11-2025 23:34</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8306,11 +8306,11 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>12228</v>
+        <v>12239</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>19-11-2025 04:41</t>
+          <t>19-11-2025 19:34</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8342,7 +8342,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>12214</v>
+        <v>12213</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>18-11-2025 16:54</t>
+          <t>19-11-2025 14:40</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>12183</v>
+        <v>12203</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>19-11-2025 04:36</t>
+          <t>19-11-2025 23:39</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>11974</v>
+        <v>11992</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>19-11-2025 01:54</t>
+          <t>20-11-2025 00:30</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>11921</v>
+        <v>11926</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>19-11-2025 02:26</t>
+          <t>19-11-2025 22:29</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8522,7 +8522,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>11846</v>
+        <v>11851</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>19-11-2025 03:49</t>
+          <t>19-11-2025 20:23</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>11634</v>
+        <v>11636</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>19-11-2025 04:43</t>
+          <t>19-11-2025 15:10</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>11539</v>
+        <v>11542</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>19-11-2025 00:09</t>
+          <t>19-11-2025 14:57</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>11466</v>
+        <v>11480</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>19-11-2025 04:43</t>
+          <t>19-11-2025 21:10</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>11364</v>
+        <v>11374</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>19-11-2025 02:35</t>
+          <t>19-11-2025 21:54</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>11291</v>
+        <v>11298</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>18-11-2025 23:39</t>
+          <t>19-11-2025 23:01</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>10822</v>
+        <v>10832</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>19-11-2025 04:52</t>
+          <t>19-11-2025 22:17</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>10709</v>
+        <v>10710</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>19-11-2025 15:56</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>10569</v>
+        <v>10574</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>19-11-2025 02:47</t>
+          <t>19-11-2025 23:45</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -8998,83 +8998,83 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>screego/server</t>
+          <t>microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://github.com/screego/server</t>
+          <t>https://github.com/microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>screen sharing for developers https://screego.net/</t>
+          <t>Frontier Open-Source Text-to-Speech</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>10002</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
+        <v>10007</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>19-11-2025 02:59</t>
+          <t>20-11-2025 00:49</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>16-07-2020 18:46</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>docker, go, privacy, screensharing-tool, selfhosted</t>
-        </is>
-      </c>
+          <t>25-08-2025 13:24</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>microsoft/VibeVoice</t>
+          <t>screego/server</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/VibeVoice</t>
+          <t>https://github.com/screego/server</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Frontier Open-Source Text-to-Speech</t>
+          <t>screen sharing for developers https://screego.net/</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>9992</v>
+        <v>10004</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>19-11-2025 04:17</t>
+          <t>19-11-2025 23:29</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>25-08-2025 13:24</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>16-07-2020 18:46</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>docker, go, privacy, screensharing-tool, selfhosted</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>9861</v>
+        <v>9863</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>18-11-2025 10:43</t>
+          <t>20-11-2025 00:50</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>9678</v>
+        <v>9691</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>19-11-2025 01:47</t>
+          <t>20-11-2025 00:14</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>9660</v>
+        <v>9673</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>19-11-2025 05:02</t>
+          <t>19-11-2025 22:26</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9251,26 +9251,26 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>C4illin/ConvertX</t>
+          <t>Fission-AI/OpenSpec</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://github.com/C4illin/ConvertX</t>
+          <t>https://github.com/Fission-AI/OpenSpec</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>💾 Self-hosted online file converter. Supports 1000+ formats ⚙️</t>
+          <t>Spec-driven development for AI coding assistants.</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>9594</v>
+        <v>9661</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -9279,43 +9279,43 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>19-11-2025 03:26</t>
+          <t>20-11-2025 00:28</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>07-04-2024 16:21</t>
+          <t>05-08-2025 10:37</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>bun, conversion, convert, converter, document-conversion</t>
+          <t>spec</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Fission-AI/OpenSpec</t>
+          <t>C4illin/ConvertX</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://github.com/Fission-AI/OpenSpec</t>
+          <t>https://github.com/C4illin/ConvertX</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Spec-driven development for AI coding assistants.</t>
+          <t>💾 Self-hosted online file converter. Supports 1000+ formats ⚙️</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>9568</v>
+        <v>9602</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9324,17 +9324,17 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>19-11-2025 04:34</t>
+          <t>20-11-2025 00:43</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>05-08-2025 10:37</t>
+          <t>07-04-2024 16:21</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>bun, conversion, convert, converter, document-conversion</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>9403</v>
+        <v>9406</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>19-11-2025 00:19</t>
+          <t>19-11-2025 21:53</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>9283</v>
+        <v>9294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>19-11-2025 04:45</t>
+          <t>20-11-2025 00:50</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>9117</v>
+        <v>9138</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>19-11-2025 04:45</t>
+          <t>19-11-2025 23:03</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>9108</v>
+        <v>9114</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>19-11-2025 04:07</t>
+          <t>19-11-2025 20:42</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>8954</v>
+        <v>8963</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>19-11-2025 00:39</t>
+          <t>19-11-2025 20:40</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>8948</v>
+        <v>8953</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>19-11-2025 05:03</t>
+          <t>20-11-2025 00:43</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>8931</v>
+        <v>8935</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>19-11-2025 03:41</t>
+          <t>19-11-2025 19:48</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9671,11 +9671,11 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>8799</v>
+        <v>8802</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>19-11-2025 04:34</t>
+          <t>19-11-2025 18:02</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>8654</v>
+        <v>8658</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>19-11-2025 01:31</t>
+          <t>20-11-2025 00:01</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>18-11-2025 23:07</t>
+          <t>19-11-2025 23:28</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9796,7 +9796,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>8604</v>
+        <v>8606</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>18-11-2025 01:54</t>
+          <t>19-11-2025 11:14</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9822,90 +9822,90 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Abdenasser/neohtop</t>
+          <t>YaoFANGUK/video-subtitle-remover</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://github.com/Abdenasser/neohtop</t>
+          <t>https://github.com/YaoFANGUK/video-subtitle-remover</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Svelte</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>💪🏻 Blazing-fast system monitoring for your desktop (built with Rust, Tauri &amp; Svelte)</t>
+          <t>基于AI的图片/视频硬字幕去除、文本水印去除，无损分辨率生成去字幕、去水印后的图片/视频文件。无需申请第三方API，本地实现。AI-based tool for removing hard-coded subtitles and text-like watermarks from videos or Pictures.</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>8545</v>
+        <v>8550</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Svelte</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>18-11-2025 16:03</t>
+          <t>19-11-2025 23:29</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>30-10-2024 20:44</t>
+          <t>25-10-2023 02:50</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>activity, btop, cross-platform, htop, monitoring</t>
+          <t>ai, deepleanring, sub-remove, subtile, vsr</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>YaoFANGUK/video-subtitle-remover</t>
+          <t>Abdenasser/neohtop</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://github.com/YaoFANGUK/video-subtitle-remover</t>
+          <t>https://github.com/Abdenasser/neohtop</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Svelte</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>基于AI的图片/视频硬字幕去除、文本水印去除，无损分辨率生成去字幕、去水印后的图片/视频文件。无需申请第三方API，本地实现。AI-based tool for removing hard-coded subtitles and text-like watermarks from videos or Pictures.</t>
+          <t>💪🏻 Blazing-fast system monitoring for your desktop (built with Rust, Tauri &amp; Svelte)</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>8542</v>
+        <v>8546</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Svelte</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>19-11-2025 05:01</t>
+          <t>19-11-2025 18:09</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>25-10-2023 02:50</t>
+          <t>30-10-2024 20:44</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>ai, deepleanring, sub-remove, subtile, vsr</t>
+          <t>activity, btop, cross-platform, htop, monitoring</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>8483</v>
+        <v>8484</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>18-11-2025 22:57</t>
+          <t>19-11-2025 21:12</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>8388</v>
+        <v>8401</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>18-11-2025 20:31</t>
+          <t>19-11-2025 22:49</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>8298</v>
+        <v>8308</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>19-11-2025 23:29</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10066,7 +10066,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>8169</v>
+        <v>8179</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>19-11-2025 00:19</t>
+          <t>19-11-2025 22:57</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10111,11 +10111,11 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>8025</v>
+        <v>8027</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>19-11-2025 04:32</t>
+          <t>19-11-2025 14:44</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>8012</v>
+        <v>8018</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>18-11-2025 20:34</t>
+          <t>19-11-2025 17:14</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>7738</v>
+        <v>7740</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>19-11-2025 04:45</t>
+          <t>19-11-2025 20:08</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10237,11 +10237,11 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>7589</v>
+        <v>7591</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>18-11-2025 17:43</t>
+          <t>19-11-2025 18:54</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>7542</v>
+        <v>7561</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>19-11-2025 02:33</t>
+          <t>19-11-2025 23:41</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>7539</v>
+        <v>7549</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>19-11-2025 02:30</t>
+          <t>19-11-2025 20:55</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10348,135 +10348,135 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>WindowsAddict/IDM-Activation-Script</t>
+          <t>Sjj1024/PakePlus</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://github.com/WindowsAddict/IDM-Activation-Script</t>
+          <t>https://github.com/Sjj1024/PakePlus</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Batchfile</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>An open source tool to activate and reset trial of Internet Download Manager</t>
+          <t>Turn any webpage/Vue/React and so on into desktop and mobile app under 5M with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>7318</v>
+        <v>7320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Batchfile</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>19-11-2025 02:46</t>
+          <t>19-11-2025 22:19</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>07-08-2023 09:34</t>
+          <t>10-09-2024 13:12</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>ias, idm, idm-activation-script, idm-crack, idm-trial-reset</t>
+          <t>pacbao, pake, pakeplus, rust, tauri</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>v1s1t0r1sh3r3/airgeddon</t>
+          <t>WindowsAddict/IDM-Activation-Script</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://github.com/v1s1t0r1sh3r3/airgeddon</t>
+          <t>https://github.com/WindowsAddict/IDM-Activation-Script</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Batchfile</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>This is a multi-use bash script for Linux systems to audit wireless networks.</t>
+          <t>An open source tool to activate and reset trial of Internet Download Manager</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7301</v>
+        <v>7319</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Batchfile</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>19-11-2025 00:51</t>
+          <t>19-11-2025 15:58</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>18-03-2016 10:34</t>
+          <t>07-08-2023 09:34</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>aircrack, bash, beef, denial-of-service, enterprise</t>
+          <t>ias, idm, idm-activation-script, idm-crack, idm-trial-reset</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Sjj1024/PakePlus</t>
+          <t>v1s1t0r1sh3r3/airgeddon</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://github.com/Sjj1024/PakePlus</t>
+          <t>https://github.com/v1s1t0r1sh3r3/airgeddon</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Turn any webpage/Vue/React and so on into desktop and mobile app under 5M with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app</t>
+          <t>This is a multi-use bash script for Linux systems to audit wireless networks.</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>7274</v>
+        <v>7303</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>19-11-2025 04:51</t>
+          <t>19-11-2025 18:31</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>10-09-2024 13:12</t>
+          <t>18-03-2016 10:34</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>pacbao, pake, pakeplus, rust, tauri</t>
+          <t>aircrack, bash, beef, denial-of-service, enterprise</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>7212</v>
+        <v>7214</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>18-11-2025 18:35</t>
+          <t>19-11-2025 21:16</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6724</v>
+        <v>6728</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>19-11-2025 04:11</t>
+          <t>19-11-2025 22:36</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10588,7 +10588,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6621</v>
+        <v>6631</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>19-11-2025 01:29</t>
+          <t>20-11-2025 00:38</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6563</v>
+        <v>6565</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>19-11-2025 03:41</t>
+          <t>19-11-2025 14:19</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10719,7 +10719,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6459</v>
+        <v>6461</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>18-11-2025 17:02</t>
+          <t>19-11-2025 22:46</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>17-11-2025 22:30</t>
+          <t>19-11-2025 15:32</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10809,7 +10809,7 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6374</v>
+        <v>6386</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>19-11-2025 03:21</t>
+          <t>19-11-2025 20:45</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6249</v>
+        <v>6250</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>18-11-2025 22:57</t>
+          <t>19-11-2025 11:20</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -10899,7 +10899,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6123</v>
+        <v>6124</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>17-11-2025 19:02</t>
+          <t>19-11-2025 13:02</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -10921,45 +10921,40 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>pawelmalak/flame</t>
+          <t>cloudcommunity/Cloud-Free-Tier-Comparison</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://github.com/pawelmalak/flame</t>
+          <t>https://github.com/cloudcommunity/Cloud-Free-Tier-Comparison</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Flame is self-hosted startpage for your server. Easily manage your apps and bookmarks with built-in editors.</t>
+          <t>Comparing the free tier offers of the major cloud providers like AWS, Azure, GCP, Oracle etc.</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6100</v>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
+        <v>6106</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>18-11-2025 22:57</t>
+          <t>19-11-2025 23:48</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>08-05-2021 16:49</t>
+          <t>13-08-2020 08:46</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>homepage, self-hosted, startpage</t>
+          <t>aws, azure, cloud, cloud-computing, cloud-providers</t>
         </is>
       </c>
     </row>
@@ -10985,7 +10980,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -10994,7 +10989,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>19-11-2025 04:36</t>
+          <t>19-11-2025 11:14</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -11011,40 +11006,45 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>cloudcommunity/Cloud-Free-Tier-Comparison</t>
+          <t>pawelmalak/flame</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://github.com/cloudcommunity/Cloud-Free-Tier-Comparison</t>
+          <t>https://github.com/pawelmalak/flame</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Comparing the free tier offers of the major cloud providers like AWS, Azure, GCP, Oracle etc.</t>
+          <t>Flame is self-hosted startpage for your server. Easily manage your apps and bookmarks with built-in editors.</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6094</v>
+        <v>6101</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00</t>
+          <t>19-11-2025 19:36</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>13-08-2020 08:46</t>
+          <t>08-05-2021 16:49</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>aws, azure, cloud, cloud-computing, cloud-providers</t>
+          <t>homepage, self-hosted, startpage</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5887</v>
+        <v>5892</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>19-11-2025 05:10</t>
+          <t>19-11-2025 18:40</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5829</v>
+        <v>5831</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>18-11-2025 15:47</t>
+          <t>20-11-2025 00:03</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5674</v>
+        <v>5673</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>18-11-2025 17:05</t>
+          <t>19-11-2025 17:04</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5587</v>
+        <v>5588</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>19-11-2025 03:45</t>
+          <t>19-11-2025 18:23</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -11290,7 +11290,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5426</v>
+        <v>5433</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>19-11-2025 04:58</t>
+          <t>19-11-2025 19:26</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -11335,7 +11335,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5131</v>
+        <v>5148</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>19-11-2025 04:25</t>
+          <t>19-11-2025 22:48</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5113</v>
+        <v>5112</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>16-11-2025 12:24</t>
+          <t>19-11-2025 16:05</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>5084</v>
+        <v>5088</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>18-11-2025 16:21</t>
+          <t>19-11-2025 23:10</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5076</v>
+        <v>5079</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>18-11-2025 22:51</t>
+          <t>19-11-2025 18:50</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>5009</v>
+        <v>5013</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>18-11-2025 19:18</t>
+          <t>19-11-2025 22:09</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4966</v>
+        <v>4967</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>18-11-2025 13:02</t>
+          <t>19-11-2025 11:14</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>4934</v>
+        <v>4940</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>19-11-2025 02:20</t>
+          <t>19-11-2025 22:12</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -11650,11 +11650,11 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>4927</v>
+        <v>4932</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>18-11-2025 20:53</t>
+          <t>19-11-2025 18:15</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -11690,7 +11690,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4863</v>
+        <v>4864</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>18-11-2025 22:29</t>
+          <t>19-11-2025 15:56</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -11780,7 +11780,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4776</v>
+        <v>4782</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>19-11-2025 03:46</t>
+          <t>19-11-2025 20:20</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -11806,116 +11806,116 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>UnigramDev/Unigram</t>
+          <t>taubyte/tau</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://github.com/UnigramDev/Unigram</t>
+          <t>https://github.com/taubyte/tau</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Telegram for Windows</t>
+          <t>Fullstack Workspace for Humans &amp; Machines</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>4741</v>
+        <v>4761</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>18-11-2025 12:38</t>
+          <t>20-11-2025 00:14</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>23-05-2016 09:03</t>
+          <t>13-07-2023 17:12</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>mtproto, secret-chats, telegram, tgcalls, unigram</t>
+          <t>5g, ai, cdn, cloud-computing, cloud-native</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>jaypyles/Scraperr</t>
+          <t>UnigramDev/Unigram</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://github.com/jaypyles/Scraperr</t>
+          <t>https://github.com/UnigramDev/Unigram</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Self-hosted webscraper.</t>
+          <t>Telegram for Windows</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>4709</v>
+        <v>4743</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>18-11-2025 19:47</t>
+          <t>19-11-2025 23:29</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>06-07-2024 16:55</t>
+          <t>23-05-2016 09:03</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>docker, helm, kubernetes, opensource, playwright</t>
+          <t>mtproto, secret-chats, telegram, tgcalls, unigram</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>LLM-Red-Team/kimi-free-api</t>
+          <t>jaypyles/Scraperr</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://github.com/LLM-Red-Team/kimi-free-api</t>
+          <t>https://github.com/jaypyles/Scraperr</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>🚀 KIMI AI 长文本大模型逆向API【特长：长文本解读整理】，支持高速流式输出、智能体对话、联网搜索、探索版、K1思考模型、长文档解读、图像解析、多轮对话，零配置部署，多路token支持，自动清理会话痕迹，仅供测试，如需商用请前往官方开放平台。</t>
+          <t>Self-hosted webscraper.</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>4703</v>
+        <v>4708</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -11924,29 +11924,29 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>19-11-2025 03:09</t>
+          <t>19-11-2025 15:34</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>08-03-2024 11:21</t>
+          <t>06-07-2024 16:55</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>chat-api, chatbot, chatgpt-api, kimi-ai, kimi-api</t>
+          <t>docker, helm, kubernetes, opensource, playwright</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>reacherhq/check-if-email-exists</t>
+          <t>LLM-Red-Team/kimi-free-api</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://github.com/reacherhq/check-if-email-exists</t>
+          <t>https://github.com/LLM-Red-Team/kimi-free-api</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -11956,42 +11956,42 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Check if an email address exists without sending any email, written in Rust. Comes with a ⚙️ HTTP backend.</t>
+          <t>🚀 KIMI AI 长文本大模型逆向API【特长：长文本解读整理】，支持高速流式输出、智能体对话、联网搜索、探索版、K1思考模型、长文档解读、图像解析、多轮对话，零配置部署，多路token支持，自动清理会话痕迹，仅供测试，如需商用请前往官方开放平台。</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4686</v>
+        <v>4703</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>18-11-2025 19:20</t>
+          <t>19-11-2025 13:12</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>25-04-2017 12:47</t>
+          <t>08-03-2024 11:21</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>email, email-validation, email-validation-api, email-verification, email-verification-api</t>
+          <t>chat-api, chatbot, chatgpt-api, kimi-ai, kimi-api</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>taubyte/tau</t>
+          <t>reacherhq/check-if-email-exists</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://github.com/taubyte/tau</t>
+          <t>https://github.com/reacherhq/check-if-email-exists</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -12001,30 +12001,30 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Fullstack Workspace for Humans &amp; Machines</t>
+          <t>Check if an email address exists without sending any email, written in Rust. Comes with a ⚙️ HTTP backend.</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4676</v>
+        <v>4686</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>19-11-2025 05:01</t>
+          <t>18-11-2025 19:20</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>13-07-2023 17:12</t>
+          <t>25-04-2017 12:47</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>5g, ai, cdn, cloud-computing, cloud-native</t>
+          <t>email, email-validation, email-validation-api, email-verification, email-verification-api</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12050,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4598</v>
+        <v>4599</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>18-11-2025 07:36</t>
+          <t>19-11-2025 12:07</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>4574</v>
+        <v>4575</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>18-11-2025 13:24</t>
+          <t>19-11-2025 19:27</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>4287</v>
+        <v>4284</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>17-11-2025 02:55</t>
+          <t>19-11-2025 15:31</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -12275,7 +12275,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>4268</v>
+        <v>4269</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>17-11-2025 12:22</t>
+          <t>19-11-2025 23:29</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -12320,7 +12320,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>4254</v>
+        <v>4256</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>18-11-2025 06:05</t>
+          <t>20-11-2025 00:29</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>18-11-2025 15:02</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4133</v>
+        <v>4136</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>19-11-2025 00:18</t>
+          <t>19-11-2025 20:54</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>4028</v>
+        <v>4031</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>18-11-2025 14:58</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3949</v>
+        <v>3953</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>19-11-2025 03:56</t>
+          <t>19-11-2025 17:33</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3901</v>
+        <v>3929</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>19-11-2025 04:06</t>
+          <t>19-11-2025 21:28</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>18-11-2025 17:59</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -12825,53 +12825,57 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>lijiejie/subDomainsBrute</t>
+          <t>Sjj1024/PakePlus-Android</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://github.com/lijiejie/subDomainsBrute</t>
+          <t>https://github.com/Sjj1024/PakePlus-Android</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Lua</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>A fast sub domain brute tool for pentesters</t>
+          <t>Turn any webpage/Vue/React and so on into desktop and mobile app with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app/</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>3589</v>
+        <v>3590</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Lua</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>17-11-2025 10:32</t>
+          <t>19-11-2025 16:06</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>01-04-2015 07:22</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr"/>
+          <t>28-03-2025 14:47</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>build, pacbao, pack, pake, pakeplus</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>cloudflare/workers-sdk</t>
+          <t>lijiejie/subDomainsBrute</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://github.com/cloudflare/workers-sdk</t>
+          <t>https://github.com/lijiejie/subDomainsBrute</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -12881,75 +12885,71 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>⛅️ Home to Wrangler, the CLI for Cloudflare Workers®</t>
+          <t>A fast sub domain brute tool for pentesters</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>3574</v>
+        <v>3589</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>18-11-2025 22:38</t>
+          <t>17-11-2025 10:32</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>10-11-2021 14:45</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>cli, cloudflare, cloudflare-workers, javascript, serverless</t>
-        </is>
-      </c>
+          <t>01-04-2015 07:22</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Sjj1024/PakePlus-Android</t>
+          <t>cloudflare/workers-sdk</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://github.com/Sjj1024/PakePlus-Android</t>
+          <t>https://github.com/cloudflare/workers-sdk</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Lua</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Turn any webpage/Vue/React and so on into desktop and mobile app with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app/</t>
+          <t>⛅️ Home to Wrangler, the CLI for Cloudflare Workers®</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3556</v>
+        <v>3577</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Lua</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>19-11-2025 04:51</t>
+          <t>19-11-2025 22:46</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>28-03-2025 14:47</t>
+          <t>10-11-2021 14:45</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>build, pacbao, pack, pake, pakeplus</t>
+          <t>cli, cloudflare, cloudflare-workers, javascript, serverless</t>
         </is>
       </c>
     </row>
@@ -12975,11 +12975,11 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>3525</v>
+        <v>3526</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>18-11-2025 18:56</t>
+          <t>19-11-2025 15:52</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -13015,7 +13015,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>3332</v>
+        <v>3338</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>19-11-2025 03:03</t>
+          <t>19-11-2025 17:53</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -13060,7 +13060,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>3262</v>
+        <v>3268</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>18-11-2025 12:53</t>
+          <t>19-11-2025 17:37</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3220</v>
+        <v>3229</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>19-11-2025 04:38</t>
+          <t>20-11-2025 00:21</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -13131,90 +13131,90 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>LinkStackOrg/LinkStack</t>
+          <t>maillab/cloud-mail</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://github.com/LinkStackOrg/LinkStack</t>
+          <t>https://github.com/maillab/cloud-mail</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LinkStack - the ultimate solution for creating a personalized &amp; professional profile page. Showcase all your important links in one place, forget the limitation of one link on social media. Set up ...</t>
+          <t>cloudflare email 邮箱  临时邮箱 邮件发送 mail</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>3218</v>
+        <v>3229</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>19-11-2025 01:27</t>
+          <t>19-11-2025 23:44</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>14-02-2022 09:29</t>
+          <t>24-04-2025 11:36</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>blade, hacktoberfest, laravel, linkstack, linktree</t>
+          <t>cloudflare, cloudflare-email, email, mail</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>maillab/cloud-mail</t>
+          <t>LinkStackOrg/LinkStack</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://github.com/maillab/cloud-mail</t>
+          <t>https://github.com/LinkStackOrg/LinkStack</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>cloudflare email 邮箱  临时邮箱 邮件发送 mail</t>
+          <t>LinkStack - the ultimate solution for creating a personalized &amp; professional profile page. Showcase all your important links in one place, forget the limitation of one link on social media. Set up ...</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3213</v>
+        <v>3217</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>19-11-2025 02:10</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>24-04-2025 11:36</t>
+          <t>14-02-2022 09:29</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>cloudflare, cloudflare-email, email, mail</t>
+          <t>blade, hacktoberfest, laravel, linkstack, linktree</t>
         </is>
       </c>
     </row>
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>3197</v>
+        <v>3199</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>19-11-2025 03:14</t>
+          <t>19-11-2025 13:01</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -13285,7 +13285,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>3151</v>
+        <v>3155</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>19-11-2025 03:39</t>
+          <t>19-11-2025 23:32</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>19-11-2025 04:36</t>
+          <t>19-11-2025 13:53</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>19-11-2025 02:33</t>
+          <t>19-11-2025 22:56</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3124</v>
+        <v>3128</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>19-11-2025 04:03</t>
+          <t>19-11-2025 21:12</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -13465,7 +13465,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3111</v>
+        <v>3115</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>18-11-2025 12:48</t>
+          <t>19-11-2025 13:50</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -13510,7 +13510,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>18-11-2025 15:09</t>
+          <t>19-11-2025 16:04</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>3032</v>
+        <v>3037</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>18-11-2025 19:57</t>
+          <t>19-11-2025 16:43</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>19-11-2025 00:52</t>
+          <t>19-11-2025 20:55</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -13618,12 +13618,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>aviaryan/awesome-no-login-web-apps</t>
+          <t>aldinokemal/go-whatsapp-web-multidevice</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://github.com/aviaryan/awesome-no-login-web-apps</t>
+          <t>https://github.com/aldinokemal/go-whatsapp-web-multidevice</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -13633,205 +13633,205 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>🚀 Awesome (free) web apps that work without login</t>
+          <t>GOWA - WhatsApp REST API with support for UI, Webhooks, and MCP. Built with Golang for efficient memory use.</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>2967</v>
+        <v>2985</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>16-11-2025 14:19</t>
+          <t>20-11-2025 00:33</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>06-12-2016 10:54</t>
+          <t>09-02-2022 16:19</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>application, applications, awesome, awesome-list, awesomeness</t>
+          <t>bot, go, golang, golang-whatsapp, golang-whatsapp-api</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Nain57/Smart-AutoClicker</t>
+          <t>aviaryan/awesome-no-login-web-apps</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://github.com/Nain57/Smart-AutoClicker</t>
+          <t>https://github.com/aviaryan/awesome-no-login-web-apps</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>An open-source auto clicker on images for Android</t>
+          <t>🚀 Awesome (free) web apps that work without login</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>2962</v>
+        <v>2968</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Kotlin</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>19-11-2025 01:21</t>
+          <t>19-11-2025 09:20</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>30-08-2020 13:07</t>
+          <t>06-12-2016 10:54</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>android, autoclicker, fdroid, kotlin, material-design</t>
+          <t>application, applications, awesome, awesome-list, awesomeness</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>proxifly/free-proxy-list</t>
+          <t>Nain57/Smart-AutoClicker</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://github.com/proxifly/free-proxy-list</t>
+          <t>https://github.com/Nain57/Smart-AutoClicker</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>🚀 Free HTTP, SOCKS4, &amp; SOCKS5 Proxy List * Updated every 5 minutes *</t>
+          <t>An open-source auto clicker on images for Android</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>2960</v>
+        <v>2968</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Kotlin</t>
+        </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>19-11-2025 04:58</t>
+          <t>19-11-2025 23:29</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>13-07-2023 06:26</t>
+          <t>30-08-2020 13:07</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>free-proxy, free-proxy-list, fresh-proxies, http, http-proxy</t>
+          <t>android, autoclicker, fdroid, kotlin, material-design</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kevinzg/facebook-scraper</t>
+          <t>proxifly/free-proxy-list</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://github.com/kevinzg/facebook-scraper</t>
+          <t>https://github.com/proxifly/free-proxy-list</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Scrape Facebook public pages without an API key</t>
+          <t>🚀 Free HTTP, SOCKS4, &amp; SOCKS5 Proxy List * Updated every 5 minutes *</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>2958</v>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
+        <v>2964</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>18-11-2025 22:24</t>
+          <t>19-11-2025 23:52</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>15-03-2019 04:36</t>
+          <t>13-07-2023 06:26</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>facebook, facebook-scraper, facebook-scraping, hacktoberfest, scraping</t>
+          <t>free-proxy, free-proxy-list, fresh-proxies, http, http-proxy</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>aldinokemal/go-whatsapp-web-multidevice</t>
+          <t>kevinzg/facebook-scraper</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://github.com/aldinokemal/go-whatsapp-web-multidevice</t>
+          <t>https://github.com/kevinzg/facebook-scraper</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>GOWA - WhatsApp REST API with support for UI, Webhooks, and MCP. Built with Golang for efficient memory use.</t>
+          <t>Scrape Facebook public pages without an API key</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>2955</v>
+        <v>2959</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>19-11-2025 04:36</t>
+          <t>19-11-2025 18:20</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>09-02-2022 16:19</t>
+          <t>15-03-2019 04:36</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>bot, go, golang, golang-whatsapp, golang-whatsapp-api</t>
+          <t>facebook, facebook-scraper, facebook-scraping, hacktoberfest, scraping</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13857,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>2924</v>
+        <v>2934</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>19-11-2025 03:46</t>
+          <t>19-11-2025 16:58</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -13943,7 +13943,7 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>2833</v>
+        <v>2843</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>19-11-2025 03:46</t>
+          <t>20-11-2025 00:39</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -13988,7 +13988,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>18-11-2025 22:59</t>
+          <t>20-11-2025 00:27</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -14033,11 +14033,11 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>2816</v>
+        <v>2820</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>19-11-2025 03:21</t>
+          <t>20-11-2025 00:51</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -14118,7 +14118,7 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>2799</v>
+        <v>2797</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>19-11-2025 02:07</t>
+          <t>19-11-2025 15:32</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -14163,7 +14163,7 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>19-11-2025 03:34</t>
+          <t>20-11-2025 00:24</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -14204,7 +14204,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>2768</v>
+        <v>2770</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>18-11-2025 17:43</t>
+          <t>19-11-2025 14:47</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>2744</v>
+        <v>2747</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>19-11-2025 01:04</t>
+          <t>19-11-2025 21:59</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -14275,85 +14275,85 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>LLM-Red-Team/deepseek-free-api</t>
+          <t>EnergizedProtection/block</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://github.com/LLM-Red-Team/deepseek-free-api</t>
+          <t>https://github.com/EnergizedProtection/block</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>🚀 DeepSeek-V3 &amp; R1大模型逆向API【特长：良心厂商】（官方贼便宜，建议直接走官方），支持高速流式输出、多轮对话，联网搜索，R1深度思考，零配置部署，多路token支持，仅供测试，如需商用请前往官方开放平台。</t>
+          <t>Let's make an annoyance free, better open internet, altogether!</t>
         </is>
       </c>
       <c r="E316" t="n">
         <v>2742</v>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>19-11-2025 03:09</t>
+          <t>19-11-2025 18:11</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>07-05-2024 06:23</t>
+          <t>16-07-2018 14:38</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>chat-api, chatbot, chatgpt-api, deepseek, deepseek-api</t>
+          <t>ad, ad-blocker, adblock, adblocker, admiral</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>EnergizedProtection/block</t>
+          <t>LLM-Red-Team/deepseek-free-api</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://github.com/EnergizedProtection/block</t>
+          <t>https://github.com/LLM-Red-Team/deepseek-free-api</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Let's make an annoyance free, better open internet, altogether!</t>
+          <t>🚀 DeepSeek-V3 &amp; R1大模型逆向API【特长：良心厂商】（官方贼便宜，建议直接走官方），支持高速流式输出、多轮对话，联网搜索，R1深度思考，零配置部署，多路token支持，仅供测试，如需商用请前往官方开放平台。</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>2742</v>
+        <v>2741</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>18-11-2025 18:11</t>
+          <t>19-11-2025 14:39</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>16-07-2018 14:38</t>
+          <t>07-05-2024 06:23</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>ad, ad-blocker, adblock, adblocker, admiral</t>
+          <t>chat-api, chatbot, chatgpt-api, deepseek, deepseek-api</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>2722</v>
+        <v>2724</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>19-11-2025 03:12</t>
+          <t>19-11-2025 12:03</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>18-11-2025 17:19</t>
+          <t>19-11-2025 12:26</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>2613</v>
+        <v>2598</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>19-11-2025 03:43</t>
+          <t>19-11-2025 17:50</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -14514,7 +14514,7 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>18-11-2025 23:17</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -14559,7 +14559,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>2485</v>
+        <v>2517</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>19-11-2025 04:51</t>
+          <t>19-11-2025 16:06</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -14604,7 +14604,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>2432</v>
+        <v>2439</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>19-11-2025 04:57</t>
+          <t>19-11-2025 14:24</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14649,11 +14649,11 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>2408</v>
+        <v>2413</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>18-11-2025 22:25</t>
+          <t>19-11-2025 17:17</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>19-11-2025 02:44</t>
+          <t>19-11-2025 21:35</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -14730,7 +14730,7 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>2313</v>
+        <v>2331</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>19-11-2025 00:41</t>
+          <t>19-11-2025 09:05</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14775,7 +14775,7 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>16-11-2025 23:51</t>
+          <t>19-11-2025 10:28</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>19-11-2025 02:08</t>
+          <t>19-11-2025 20:18</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>19-11-2025 02:39</t>
+          <t>19-11-2025 20:42</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2189</v>
+        <v>2241</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>19-11-2025 05:05</t>
+          <t>20-11-2025 00:05</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>19-11-2025 01:34</t>
+          <t>19-11-2025 10:21</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15067,90 +15067,90 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>adafruit/DHT-sensor-library</t>
+          <t>favonia/cloudflare-ddns</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://github.com/adafruit/DHT-sensor-library</t>
+          <t>https://github.com/favonia/cloudflare-ddns</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Arduino library for DHT11, DHT22, etc Temperature &amp; Humidity Sensors</t>
+          <t>🌟 A small, feature-rich, and robust Cloudflare DDNS updater</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>12-11-2025 20:50</t>
+          <t>19-11-2025 18:42</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>20-06-2011 23:45</t>
+          <t>04-06-2021 14:20</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>arduino-library</t>
+          <t>cloudflare, ddns, ddns-client, ddns-updater, dns</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>favonia/cloudflare-ddns</t>
+          <t>adafruit/DHT-sensor-library</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://github.com/favonia/cloudflare-ddns</t>
+          <t>https://github.com/adafruit/DHT-sensor-library</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>🌟 A small, feature-rich, and robust Cloudflare DDNS updater</t>
+          <t>Arduino library for DHT11, DHT22, etc Temperature &amp; Humidity Sensors</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>18-11-2025 12:16</t>
+          <t>12-11-2025 20:50</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>04-06-2021 14:20</t>
+          <t>20-06-2011 23:45</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>cloudflare, ddns, ddns-client, ddns-updater, dns</t>
+          <t>arduino-library</t>
         </is>
       </c>
     </row>
@@ -15176,7 +15176,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>18-11-2025 22:48</t>
+          <t>20-11-2025 00:01</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -15221,11 +15221,11 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>2040</v>
+        <v>2054</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>19-11-2025 00:41</t>
+          <t>19-11-2025 22:28</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>19-11-2025 04:15</t>
+          <t>19-11-2025 16:17</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -15302,7 +15302,7 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>18-11-2025 13:51</t>
+          <t>20-11-2025 00:26</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>18-11-2025 19:15</t>
+          <t>19-11-2025 10:30</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>18-11-2025 01:43</t>
+          <t>19-11-2025 17:58</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>17-11-2025 17:17</t>
+          <t>19-11-2025 07:12</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>19-11-2025 00:40</t>
+          <t>19-11-2025 11:43</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -15519,7 +15519,7 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>19-11-2025 03:35</t>
+          <t>19-11-2025 20:29</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -15605,7 +15605,7 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>19-11-2025 01:14</t>
+          <t>19-11-2025 12:06</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -15650,7 +15650,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>18-11-2025 15:17</t>
+          <t>19-11-2025 15:32</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>18-11-2025 16:07</t>
+          <t>19-11-2025 10:06</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>19-11-2025 02:37</t>
+          <t>20-11-2025 00:39</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -16050,7 +16050,7 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>1675</v>
+        <v>1681</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>19-11-2025 04:33</t>
+          <t>19-11-2025 22:36</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -16136,7 +16136,7 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>17-11-2025 13:06</t>
+          <t>19-11-2025 06:01</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>18-11-2025 15:30</t>
+          <t>19-11-2025 07:25</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>1601</v>
+        <v>1608</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>19-11-2025 02:58</t>
+          <t>20-11-2025 00:05</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -16316,7 +16316,7 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>18-11-2025 13:00</t>
+          <t>19-11-2025 07:23</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -16361,7 +16361,7 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>17-11-2025 17:43</t>
+          <t>19-11-2025 11:40</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -16406,7 +16406,7 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>1540</v>
+        <v>1548</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>19-11-2025 00:31</t>
+          <t>20-11-2025 00:48</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16451,11 +16451,11 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>19-11-2025 03:19</t>
+          <t>19-11-2025 19:33</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>11-11-2025 18:16</t>
+          <t>19-11-2025 10:34</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>18-11-2025 18:58</t>
+          <t>19-11-2025 19:19</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>1492</v>
+        <v>1497</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>18-11-2025 20:11</t>
+          <t>19-11-2025 23:04</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -16666,11 +16666,11 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>19-11-2025 02:37</t>
+          <t>20-11-2025 00:37</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16783,7 +16783,7 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>19-11-2025 02:58</t>
+          <t>19-11-2025 19:42</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>19-11-2025 03:36</t>
+          <t>19-11-2025 23:56</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16869,7 +16869,7 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>18-11-2025 18:20</t>
+          <t>19-11-2025 14:34</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16914,7 +16914,7 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>1317</v>
+        <v>1324</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>19-11-2025 03:43</t>
+          <t>19-11-2025 12:54</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -16940,22 +16940,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>emalderson/ThePhish</t>
+          <t>lane711/sonicjs</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://github.com/emalderson/ThePhish</t>
+          <t>https://github.com/lane711/sonicjs</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>ThePhish: an automated phishing email analysis tool</t>
+          <t>SonicJs Headless CMS - Blazing Fast Headless CMS built on Cloudflare Workers. 100% Javascript Based</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -16963,44 +16963,44 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>19-11-2025 02:40</t>
+          <t>19-11-2025 20:13</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>27-09-2021 16:00</t>
+          <t>15-08-2018 22:49</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>attack, cyberdefense, cybersecurity, detection, digital-forensics</t>
+          <t>api-framework, cloudfl, cloudflare-kv, cloudflare-workers, cms</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>BiZken/PhishMailer</t>
+          <t>emalderson/ThePhish</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://github.com/BiZken/PhishMailer</t>
+          <t>https://github.com/emalderson/ThePhish</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Generate Professional Phishing Emails Fast And Easy</t>
+          <t>ThePhish: an automated phishing email analysis tool</t>
         </is>
       </c>
       <c r="E378" t="n">
@@ -17013,29 +17013,29 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>16-11-2025 13:06</t>
+          <t>19-11-2025 02:40</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>04-04-2020 21:23</t>
+          <t>27-09-2021 16:00</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>hacking, phishing, phishing-attacks, social-engineering</t>
+          <t>attack, cyberdefense, cybersecurity, detection, digital-forensics</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>lane711/sonicjs</t>
+          <t>BiZken/PhishMailer</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://github.com/lane711/sonicjs</t>
+          <t>https://github.com/BiZken/PhishMailer</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -17045,30 +17045,30 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>SonicJs Headless CMS - Blazing Fast Headless CMS built on Cloudflare Workers. 100% Javascript Based</t>
+          <t>Generate Professional Phishing Emails Fast And Easy</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>18-11-2025 23:18</t>
+          <t>16-11-2025 13:06</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>15-08-2018 22:49</t>
+          <t>04-04-2020 21:23</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>api-framework, cloudfl, cloudflare-kv, cloudflare-workers, cms</t>
+          <t>hacking, phishing, phishing-attacks, social-engineering</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>16-11-2025 18:52</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17139,7 +17139,7 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>17-11-2025 10:53</t>
+          <t>19-11-2025 18:36</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -17184,7 +17184,7 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>17-11-2025 18:31</t>
+          <t>19-11-2025 21:41</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>18-11-2025 21:38</t>
+          <t>19-11-2025 19:23</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -17274,7 +17274,7 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>18-11-2025 06:17</t>
+          <t>19-11-2025 18:19</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -17404,7 +17404,7 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>19-11-2025 03:44</t>
+          <t>19-11-2025 05:25</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -17449,7 +17449,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>19-11-2025 05:07</t>
+          <t>20-11-2025 00:08</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>16-11-2025 02:39</t>
+          <t>19-11-2025 12:13</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>17-11-2025 05:12</t>
+          <t>19-11-2025 17:54</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -17760,7 +17760,7 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>19-11-2025 02:46</t>
+          <t>19-11-2025 21:03</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>19-11-2025 04:52</t>
+          <t>19-11-2025 12:55</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>16-11-2025 12:56</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -17935,7 +17935,7 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>19-11-2025 02:22</t>
+          <t>19-11-2025 22:20</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>19-11-2025 03:37</t>
+          <t>19-11-2025 15:34</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18143,7 +18143,7 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>18-11-2025 09:51</t>
+          <t>19-11-2025 17:28</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18184,7 +18184,7 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>16-11-2025 13:54</t>
+          <t>19-11-2025 11:55</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -18229,7 +18229,7 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>19-11-2025 04:58</t>
+          <t>19-11-2025 11:38</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>18-11-2025 02:56</t>
+          <t>19-11-2025 11:46</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18360,7 +18360,7 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>17-11-2025 03:58</t>
+          <t>19-11-2025 06:07</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>18-11-2025 05:23</t>
+          <t>19-11-2025 16:15</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -18490,7 +18490,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>19-11-2025 00:37</t>
+          <t>19-11-2025 19:49</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>18-11-2025 16:47</t>
+          <t>19-11-2025 20:59</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -18580,7 +18580,7 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>19-11-2025 02:35</t>
+          <t>19-11-2025 13:54</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -18801,7 +18801,7 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>16-11-2025 13:24</t>
+          <t>19-11-2025 11:46</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>19-11-2025 03:09</t>
+          <t>19-11-2025 11:46</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>16-11-2025 18:52</t>
+          <t>19-11-2025 15:32</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -19022,7 +19022,7 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>18-11-2025 17:41</t>
+          <t>19-11-2025 15:32</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -19133,12 +19133,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>mifi/ezshare</t>
+          <t>GewoonJaap/gemini-cli-openai</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://github.com/mifi/ezshare</t>
+          <t>https://github.com/GewoonJaap/gemini-cli-openai</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Easily share files, folders and clipboard over LAN - Like Google Drive but without internet</t>
+          <t>Expose Gemini CLI endpoints as OpenAI API with Cloudflare Workers</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -19161,29 +19161,29 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>17-11-2025 02:13</t>
+          <t>20-11-2025 00:46</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>16-08-2019 11:25</t>
+          <t>26-06-2025 11:07</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>airdrop, cli, easy, filesharing, receive</t>
+          <t>gemini, gemini-cli, llm, openai, openai-api</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>GewoonJaap/gemini-cli-openai</t>
+          <t>mifi/ezshare</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://github.com/GewoonJaap/gemini-cli-openai</t>
+          <t>https://github.com/mifi/ezshare</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -19193,11 +19193,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Expose Gemini CLI endpoints as OpenAI API with Cloudflare Workers</t>
+          <t>Easily share files, folders and clipboard over LAN - Like Google Drive but without internet</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -19206,17 +19206,17 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>18-11-2025 20:26</t>
+          <t>17-11-2025 02:13</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>26-06-2025 11:07</t>
+          <t>16-08-2019 11:25</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>gemini, gemini-cli, llm, openai, openai-api</t>
+          <t>airdrop, cli, easy, filesharing, receive</t>
         </is>
       </c>
     </row>
@@ -19268,62 +19268,62 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>The-Osint-Toolbox/Social-Media-OSINT</t>
+          <t>UCYBERS/Awesome-Blackhat-Tools</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://github.com/The-Osint-Toolbox/Social-Media-OSINT</t>
+          <t>https://github.com/UCYBERS/Awesome-Blackhat-Tools</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Social Media OSINT collection containing - tools, techniques &amp; tradecraft.</t>
+          <t>A curated list of tools officially presented at Black Hat events</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>18-11-2025 06:57</t>
+          <t>19-11-2025 20:42</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>19-03-2023 16:19</t>
+          <t>08-06-2025 13:20</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>bluesky, dating-app, discord, facebook, instagram</t>
+          <t>appsec, awesome-list, blackhat, blue-teaming, cybersecurity</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>UCYBERS/Awesome-Blackhat-Tools</t>
+          <t>The-Osint-Toolbox/Social-Media-OSINT</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://github.com/UCYBERS/Awesome-Blackhat-Tools</t>
+          <t>https://github.com/The-Osint-Toolbox/Social-Media-OSINT</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>A curated list of tools officially presented at Black Hat events</t>
+          <t>Social Media OSINT collection containing - tools, techniques &amp; tradecraft.</t>
         </is>
       </c>
       <c r="E431" t="n">
@@ -19331,17 +19331,17 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>18-11-2025 22:23</t>
+          <t>18-11-2025 06:57</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>08-06-2025 13:20</t>
+          <t>19-03-2023 16:19</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>appsec, awesome-list, blackhat, blue-teaming, cybersecurity</t>
+          <t>bluesky, dating-app, discord, facebook, instagram</t>
         </is>
       </c>
     </row>
@@ -19408,7 +19408,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>18-11-2025 12:53</t>
+          <t>19-11-2025 22:47</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -19494,7 +19494,7 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>03-11-2025 11:04</t>
+          <t>19-11-2025 11:49</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -19584,7 +19584,7 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>19-11-2025 01:51</t>
+          <t>19-11-2025 15:08</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -19629,7 +19629,7 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>19-11-2025 02:43</t>
+          <t>19-11-2025 10:31</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>18-11-2025 00:13</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -19854,7 +19854,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>18-11-2025 15:04</t>
+          <t>19-11-2025 11:46</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>18-11-2025 14:10</t>
+          <t>19-11-2025 18:16</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -19989,7 +19989,7 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>27-10-2025 11:57</t>
+          <t>19-11-2025 11:12</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -20030,7 +20030,7 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>18-11-2025 18:12</t>
+          <t>19-11-2025 13:06</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>19-11-2025 04:56</t>
+          <t>20-11-2025 00:47</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -20205,7 +20205,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>18-11-2025 22:35</t>
+          <t>19-11-2025 10:11</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -20246,7 +20246,7 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>19-11-2025 02:37</t>
+          <t>19-11-2025 15:34</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>09-11-2025 00:57</t>
+          <t>19-11-2025 15:28</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>13-11-2025 01:45</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>17-11-2025 21:35</t>
+          <t>19-11-2025 12:56</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>16-11-2025 15:21</t>
+          <t>19-11-2025 18:38</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -20594,7 +20594,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>18-11-2025 09:21</t>
+          <t>19-11-2025 22:42</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -20774,7 +20774,7 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>13-11-2025 09:56</t>
+          <t>19-11-2025 11:38</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -20819,7 +20819,7 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>18-11-2025 14:34</t>
+          <t>19-11-2025 14:08</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -20864,7 +20864,7 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>12-11-2025 07:17</t>
+          <t>19-11-2025 15:33</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -20909,7 +20909,7 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>19-11-2025 04:29</t>
+          <t>19-11-2025 17:36</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -20954,7 +20954,7 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>18-11-2025 11:51</t>
+          <t>19-11-2025 10:17</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -21076,7 +21076,7 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>18-11-2025 04:32</t>
+          <t>19-11-2025 21:18</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -21284,7 +21284,7 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>18-11-2025 11:56</t>
+          <t>19-11-2025 06:49</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>13-11-2025 22:51</t>
+          <t>19-11-2025 16:00</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -21689,7 +21689,7 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>18-11-2025 08:22</t>
+          <t>19-11-2025 17:41</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -21878,63 +21878,67 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>tom-doerr/repo_posts</t>
+          <t>Kikobeats/free-email-domains</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://github.com/tom-doerr/repo_posts</t>
+          <t>https://github.com/Kikobeats/free-email-domains</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>No description available</t>
+          <t>A comprehensive list of all free email domain providers.</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>19-11-2025 03:36</t>
+          <t>19-11-2025 08:58</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>17-02-2025 04:32</t>
-        </is>
-      </c>
-      <c r="I490" t="inlineStr"/>
+          <t>29-11-2017 09:17</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>domain, email, free</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Kikobeats/free-email-domains</t>
+          <t>tom-doerr/repo_posts</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://github.com/Kikobeats/free-email-domains</t>
+          <t>https://github.com/tom-doerr/repo_posts</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>A comprehensive list of all free email domain providers.</t>
+          <t>No description available</t>
         </is>
       </c>
       <c r="E491" t="n">
@@ -21942,24 +21946,20 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>01-11-2025 21:21</t>
+          <t>20-11-2025 00:26</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>29-11-2017 09:17</t>
-        </is>
-      </c>
-      <c r="I491" t="inlineStr">
-        <is>
-          <t>domain, email, free</t>
-        </is>
-      </c>
+          <t>17-02-2025 04:32</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -21983,7 +21983,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>17-11-2025 21:08</t>
+          <t>19-11-2025 15:36</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -22028,11 +22028,11 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>18-11-2025 22:14</t>
+          <t>19-11-2025 19:52</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>18-11-2025 22:29</t>
+          <t>19-11-2025 19:30</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -22229,83 +22229,83 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>sensepost/mail-in-the-middle</t>
+          <t>cloudcommunity/Free-for-Startups</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://github.com/sensepost/mail-in-the-middle</t>
+          <t>https://github.com/cloudcommunity/Free-for-Startups</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>No description available</t>
+          <t>A curated collection of free resources for startups and entrepreneurs. Also available at https://freeforstartups.com/</t>
         </is>
       </c>
       <c r="E498" t="n">
         <v>109</v>
       </c>
-      <c r="F498" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>10-10-2025 19:04</t>
+          <t>19-11-2025 16:39</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>21-02-2024 07:25</t>
-        </is>
-      </c>
-      <c r="I498" t="inlineStr"/>
+          <t>13-02-2025 05:25</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, startup</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>cloudcommunity/Free-for-Startups</t>
+          <t>sensepost/mail-in-the-middle</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://github.com/cloudcommunity/Free-for-Startups</t>
+          <t>https://github.com/sensepost/mail-in-the-middle</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>A curated collection of free resources for startups and entrepreneurs. Also available at https://freeforstartups.com/</t>
+          <t>No description available</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>18-11-2025 20:04</t>
+          <t>10-10-2025 19:04</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>13-02-2025 05:25</t>
-        </is>
-      </c>
-      <c r="I499" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, startup</t>
-        </is>
-      </c>
+          <t>21-02-2024 07:25</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440912</v>
+        <v>440914</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21-11-2025 10:25</t>
+          <t>21-11-2025 10:35</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379855</v>
+        <v>379857</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21-11-2025 10:24</t>
+          <t>21-11-2025 10:35</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>21-11-2025 10:21</t>
+          <t>21-11-2025 10:32</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250475</v>
+        <v>250476</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21-11-2025 10:21</t>
+          <t>21-11-2025 10:31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21-11-2025 10:29</t>
+          <t>21-11-2025 10:35</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156928</v>
+        <v>156929</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>21-11-2025 10:31</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>21-11-2025 10:34</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115260</v>
+        <v>115262</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21-11-2025 10:30</t>
+          <t>21-11-2025 10:35</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102834</v>
+        <v>102835</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21-11-2025 10:02</t>
+          <t>21-11-2025 10:33</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93747</v>
+        <v>93748</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21-11-2025 10:04</t>
+          <t>21-11-2025 10:34</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88163</v>
+        <v>88164</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>21-11-2025 09:35</t>
+          <t>21-11-2025 10:32</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83843</v>
+        <v>83844</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21-11-2025 10:24</t>
+          <t>21-11-2025 10:32</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>76993</v>
+        <v>76994</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21-11-2025 10:15</t>
+          <t>21-11-2025 10:32</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68238</v>
+        <v>68239</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>21-11-2025 10:33</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65558</v>
+        <v>65559</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21-11-2025 07:57</t>
+          <t>21-11-2025 10:35</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47370</v>
+        <v>47371</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21-11-2025 10:08</t>
+          <t>21-11-2025 10:35</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43002</v>
+        <v>43003</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21-11-2025 10:29</t>
+          <t>21-11-2025 10:34</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31839</v>
+        <v>31838</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>21-11-2025 10:32</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>20120</v>
+        <v>20119</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>21-11-2025 09:53</t>
+          <t>21-11-2025 10:32</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18564</v>
+        <v>18565</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>21-11-2025 09:58</t>
+          <t>21-11-2025 10:31</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15726</v>
+        <v>15727</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>21-11-2025 10:19</t>
+          <t>21-11-2025 10:31</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>14669</v>
+        <v>14670</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>21-11-2025 09:33</t>
+          <t>21-11-2025 10:33</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7781,7 +7781,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>13856</v>
+        <v>13855</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>21-11-2025 09:25</t>
+          <t>21-11-2025 10:34</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>12909</v>
+        <v>12911</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>21-11-2025 10:24</t>
+          <t>21-11-2025 10:35</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7954</v>
+        <v>7955</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>21-11-2025 10:19</t>
+          <t>21-11-2025 10:31</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>7390</v>
+        <v>7391</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>21-11-2025 10:21</t>
+          <t>21-11-2025 10:33</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>21-11-2025 10:14</t>
+          <t>21-11-2025 10:31</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3625</v>
+        <v>3626</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>21-11-2025 10:21</t>
+          <t>21-11-2025 10:33</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>21-11-2025 10:21</t>
+          <t>21-11-2025 10:33</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -15081,7 +15081,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2365</v>
+        <v>2368</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>21-11-2025 10:18</t>
+          <t>21-11-2025 10:35</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -16757,7 +16757,7 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>21-11-2025 08:22</t>
+          <t>21-11-2025 10:34</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>21-11-2025 10:20</t>
+          <t>21-11-2025 10:35</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440914</v>
+        <v>440915</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21-11-2025 10:35</t>
+          <t>21-11-2025 10:41</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416447</v>
+        <v>416448</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21-11-2025 10:24</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270355</v>
+        <v>270357</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>21-11-2025 10:32</t>
+          <t>21-11-2025 10:41</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250476</v>
+        <v>250477</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21-11-2025 10:31</t>
+          <t>21-11-2025 10:41</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21-11-2025 10:35</t>
+          <t>21-11-2025 10:40</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125871</v>
+        <v>125872</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21-11-2025 10:34</t>
+          <t>21-11-2025 10:41</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115262</v>
+        <v>115263</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21-11-2025 10:35</t>
+          <t>21-11-2025 10:41</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102835</v>
+        <v>102836</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21-11-2025 10:33</t>
+          <t>21-11-2025 10:40</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>86466</v>
+        <v>86467</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21-11-2025 09:46</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84646</v>
+        <v>84647</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83844</v>
+        <v>83845</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21-11-2025 10:32</t>
+          <t>21-11-2025 10:40</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83184</v>
+        <v>83185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21-11-2025 10:24</t>
+          <t>21-11-2025 10:40</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21-11-2025 10:14</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>67907</v>
+        <v>67908</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21-11-2025 10:22</t>
+          <t>21-11-2025 10:37</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53629</v>
+        <v>53628</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21-11-2025 03:28</t>
+          <t>21-11-2025 10:38</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2523,11 +2523,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53602</v>
+        <v>53601</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21-11-2025 10:25</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51274</v>
+        <v>51275</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21-11-2025 10:12</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47371</v>
+        <v>47372</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21-11-2025 10:35</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21-11-2025 09:41</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44362</v>
+        <v>44363</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21-11-2025 10:10</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43059</v>
+        <v>43060</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21-11-2025 10:30</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43003</v>
+        <v>43004</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21-11-2025 10:34</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>39110</v>
+        <v>39111</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21-11-2025 10:01</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>35647</v>
+        <v>35648</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>21-11-2025 09:28</t>
+          <t>21-11-2025 10:40</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>31629</v>
+        <v>31631</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>21-11-2025 10:21</t>
+          <t>21-11-2025 10:42</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>29814</v>
+        <v>29815</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>21-11-2025 08:43</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26850</v>
+        <v>26851</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>21-11-2025 10:08</t>
+          <t>21-11-2025 10:40</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>25049</v>
+        <v>25050</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>21-11-2025 10:19</t>
+          <t>21-11-2025 10:40</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>23138</v>
+        <v>23137</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>21-11-2025 09:48</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>19038</v>
+        <v>19039</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>21-11-2025 09:58</t>
+          <t>21-11-2025 10:38</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>17438</v>
+        <v>17439</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>21-11-2025 10:11</t>
+          <t>21-11-2025 10:38</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15727</v>
+        <v>15728</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>21-11-2025 10:31</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15051</v>
+        <v>15052</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>21-11-2025 10:27</t>
+          <t>21-11-2025 10:42</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>13676</v>
+        <v>13677</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>21-11-2025 09:44</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13527</v>
+        <v>13528</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>21-11-2025 10:19</t>
+          <t>21-11-2025 10:38</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>12911</v>
+        <v>12913</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>21-11-2025 10:35</t>
+          <t>21-11-2025 10:40</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>12577</v>
+        <v>12575</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>21-11-2025 08:51</t>
+          <t>21-11-2025 10:38</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>12213</v>
+        <v>12212</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>19-11-2025 14:40</t>
+          <t>21-11-2025 10:37</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>11868</v>
+        <v>11869</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>21-11-2025 10:01</t>
+          <t>21-11-2025 10:41</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>9869</v>
+        <v>9870</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>21-11-2025 10:36</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>8964</v>
+        <v>8965</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>21-11-2025 10:30</t>
+          <t>21-11-2025 10:38</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>8409</v>
+        <v>8408</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>21-11-2025 09:03</t>
+          <t>21-11-2025 10:41</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>7391</v>
+        <v>7392</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>21-11-2025 10:33</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -12131,7 +12131,7 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>4793</v>
+        <v>4794</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>21-11-2025 06:54</t>
+          <t>21-11-2025 10:42</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3626</v>
+        <v>3627</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>21-11-2025 10:33</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -13861,7 +13861,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>21-11-2025 09:37</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>21-11-2025 10:33</t>
+          <t>21-11-2025 10:39</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>21-11-2025 09:09</t>
+          <t>21-11-2025 10:37</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -19638,7 +19638,7 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>21-11-2025 10:04</t>
+          <t>21-11-2025 10:40</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>20-11-2025 10:35</t>
+          <t>21-11-2025 10:41</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>440915</v>
+        <v>441358</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21-11-2025 10:41</t>
+          <t>22-11-2025 00:48</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416448</v>
+        <v>416577</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>22-11-2025 00:38</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379857</v>
+        <v>379971</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21-11-2025 10:35</t>
+          <t>22-11-2025 00:14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270357</v>
+        <v>270446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>21-11-2025 10:41</t>
+          <t>22-11-2025 00:48</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259206</v>
+        <v>259286</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21-11-2025 10:05</t>
+          <t>22-11-2025 00:21</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250477</v>
+        <v>250544</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21-11-2025 10:41</t>
+          <t>22-11-2025 00:21</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198002</v>
+        <v>198025</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21-11-2025 10:06</t>
+          <t>22-11-2025 00:45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195038</v>
+        <v>195097</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21-11-2025 10:31</t>
+          <t>21-11-2025 23:39</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>182881</v>
+        <v>182889</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21-11-2025 10:07</t>
+          <t>21-11-2025 22:12</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157720</v>
+        <v>157849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21-11-2025 10:40</t>
+          <t>22-11-2025 00:47</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156929</v>
+        <v>156992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21-11-2025 10:31</t>
+          <t>21-11-2025 23:29</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>136738</v>
+        <v>136761</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>22-11-2025 00:41</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135814</v>
+        <v>135863</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21-11-2025 10:26</t>
+          <t>22-11-2025 00:42</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131372</v>
+        <v>131395</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>22-11-2025 00:32</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125872</v>
+        <v>125892</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21-11-2025 10:41</t>
+          <t>22-11-2025 00:42</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115844</v>
+        <v>115887</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21-11-2025 10:23</t>
+          <t>22-11-2025 00:45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21-11-2025 09:26</t>
+          <t>21-11-2025 22:12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115263</v>
+        <v>115412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21-11-2025 10:41</t>
+          <t>22-11-2025 00:47</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102836</v>
+        <v>102864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21-11-2025 10:40</t>
+          <t>22-11-2025 00:14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102339</v>
+        <v>102420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>22-11-2025 00:48</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100974</v>
+        <v>101000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21-11-2025 09:58</t>
+          <t>22-11-2025 00:38</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93748</v>
+        <v>93777</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21-11-2025 10:34</t>
+          <t>21-11-2025 23:40</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>92901</v>
+        <v>92904</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21-11-2025 07:55</t>
+          <t>21-11-2025 19:50</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>92122</v>
+        <v>92139</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21-11-2025 10:23</t>
+          <t>21-11-2025 22:14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88164</v>
+        <v>88182</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>21-11-2025 10:32</t>
+          <t>21-11-2025 22:01</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>86467</v>
+        <v>86466</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>21-11-2025 22:13</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84647</v>
+        <v>84707</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>22-11-2025 00:26</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83845</v>
+        <v>83933</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21-11-2025 10:40</t>
+          <t>22-11-2025 00:47</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83185</v>
+        <v>83194</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21-11-2025 10:40</t>
+          <t>21-11-2025 23:05</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>79914</v>
+        <v>79929</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>21-11-2025 09:46</t>
+          <t>22-11-2025 00:44</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>79328</v>
+        <v>79377</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>22-11-2025 00:20</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>78733</v>
+        <v>78747</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21-11-2025 10:30</t>
+          <t>21-11-2025 23:39</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>76994</v>
+        <v>76998</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21-11-2025 10:32</t>
+          <t>21-11-2025 22:42</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75884</v>
+        <v>75892</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21-11-2025 09:01</t>
+          <t>22-11-2025 00:05</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>70447</v>
+        <v>70461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21-11-2025 10:05</t>
+          <t>21-11-2025 23:23</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68239</v>
+        <v>68282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21-11-2025 10:33</t>
+          <t>22-11-2025 00:42</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>67908</v>
+        <v>67929</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21-11-2025 10:37</t>
+          <t>21-11-2025 23:19</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2137,11 +2137,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>66803</v>
+        <v>66811</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21-11-2025 10:04</t>
+          <t>22-11-2025 00:07</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65559</v>
+        <v>65563</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21-11-2025 10:35</t>
+          <t>22-11-2025 00:45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2222,11 +2222,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>63767</v>
+        <v>63777</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21-11-2025 09:53</t>
+          <t>21-11-2025 23:41</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>59601</v>
+        <v>59602</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21-11-2025 09:59</t>
+          <t>21-11-2025 20:14</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>58884</v>
+        <v>58951</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>21-11-2025 10:24</t>
+          <t>22-11-2025 00:49</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2352,11 +2352,11 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>21-11-2025 10:05</t>
+          <t>21-11-2025 22:18</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56182</v>
+        <v>56208</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21-11-2025 09:20</t>
+          <t>21-11-2025 23:56</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53634</v>
+        <v>53638</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21-11-2025 09:58</t>
+          <t>22-11-2025 00:10</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53628</v>
+        <v>53632</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21-11-2025 10:38</t>
+          <t>21-11-2025 23:03</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2523,11 +2523,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53601</v>
+        <v>53609</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>21-11-2025 23:42</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>21-11-2025 07:36</t>
+          <t>22-11-2025 00:23</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51753</v>
+        <v>51754</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21-11-2025 09:35</t>
+          <t>21-11-2025 21:10</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51699</v>
+        <v>51705</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21-11-2025 09:06</t>
+          <t>21-11-2025 21:09</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51275</v>
+        <v>51311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>22-11-2025 00:41</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>48677</v>
+        <v>48683</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>21-11-2025 09:31</t>
+          <t>22-11-2025 00:33</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47866</v>
+        <v>47892</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>21-11-2025 08:36</t>
+          <t>22-11-2025 00:46</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>47858</v>
+        <v>47864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21-11-2025 09:13</t>
+          <t>21-11-2025 20:52</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47540</v>
+        <v>47561</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>21-11-2025 10:09</t>
+          <t>22-11-2025 00:05</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2919,11 +2919,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>47485</v>
+        <v>47495</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21-11-2025 09:47</t>
+          <t>21-11-2025 22:16</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47372</v>
+        <v>47430</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>21-11-2025 21:06</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3004,11 +3004,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>46339</v>
+        <v>46343</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21-11-2025 09:56</t>
+          <t>21-11-2025 17:50</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>46275</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>22-11-2025 00:24</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44363</v>
+        <v>44398</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>21-11-2025 23:41</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3110,26 +3110,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>yeongpin/cursor-free-vip</t>
+          <t>Zie619/n8n-workflows</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://github.com/yeongpin/cursor-free-vip</t>
+          <t>https://github.com/Zie619/n8n-workflows</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[Support 0.49.x]（Reset Cursor AI MachineID &amp; Bypass Higher Token Limit） Cursor Ai ，自动重置机器ID ， 免费升级使用Pro功能: You've reached your trial request limit. / Too many free trial accounts used on this machi...</t>
+          <t>all of the workflows of n8n i could find (also from the site itself)</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43060</v>
+        <v>43168</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,43 +3138,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>22-11-2025 00:47</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>11-01-2025 08:14</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>automation, cursor, cursor-ai, cursor-ide, cursorai</t>
-        </is>
-      </c>
+          <t>14-05-2025 08:43</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zie619/n8n-workflows</t>
+          <t>yeongpin/cursor-free-vip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://github.com/Zie619/n8n-workflows</t>
+          <t>https://github.com/yeongpin/cursor-free-vip</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>all of the workflows of n8n i could find (also from the site itself)</t>
+          <t>[Support 0.49.x]（Reset Cursor AI MachineID &amp; Bypass Higher Token Limit） Cursor Ai ，自动重置机器ID ， 免费升级使用Pro功能: You've reached your trial request limit. / Too many free trial accounts used on this machi...</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43004</v>
+        <v>43120</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3183,15 +3179,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>21-11-2025 23:59</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>14-05-2025 08:43</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>11-01-2025 08:14</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>automation, cursor, cursor-ai, cursor-ide, cursorai</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42935</v>
+        <v>42966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>21-11-2025 10:05</t>
+          <t>22-11-2025 00:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>42503</v>
+        <v>42510</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>21-11-2025 09:33</t>
+          <t>21-11-2025 23:14</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3301,11 +3301,11 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>40985</v>
+        <v>40991</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21-11-2025 09:48</t>
+          <t>21-11-2025 23:28</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>39394</v>
+        <v>39414</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21-11-2025 09:11</t>
+          <t>22-11-2025 00:18</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>39201</v>
+        <v>39209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>21-11-2025 10:29</t>
+          <t>22-11-2025 00:16</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>39111</v>
+        <v>39114</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>22-11-2025 00:14</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>38934</v>
+        <v>38970</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>21-11-2025 10:16</t>
+          <t>22-11-2025 00:35</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>38616</v>
+        <v>38619</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>21-11-2025 03:31</t>
+          <t>21-11-2025 18:38</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>37951</v>
+        <v>37953</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>21-11-2025 09:53</t>
+          <t>21-11-2025 20:07</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37373</v>
+        <v>37381</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21-11-2025 08:17</t>
+          <t>21-11-2025 21:22</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>21-11-2025 10:13</t>
+          <t>22-11-2025 00:46</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>35896</v>
+        <v>35902</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>21-11-2025 10:27</t>
+          <t>21-11-2025 23:11</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>35648</v>
+        <v>35654</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>21-11-2025 10:40</t>
+          <t>22-11-2025 00:32</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>35496</v>
+        <v>35498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>21-11-2025 10:05</t>
+          <t>22-11-2025 00:48</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3836,11 +3836,11 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34578</v>
+        <v>34590</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>21-11-2025 09:58</t>
+          <t>21-11-2025 23:03</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>34493</v>
+        <v>34503</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>21-11-2025 10:22</t>
+          <t>21-11-2025 21:55</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>34227</v>
+        <v>34230</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>21-11-2025 07:05</t>
+          <t>21-11-2025 18:57</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>33417</v>
+        <v>33421</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>21-11-2025 10:27</t>
+          <t>22-11-2025 00:14</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4011,11 +4011,11 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>32693</v>
+        <v>32695</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>21-11-2025 10:30</t>
+          <t>21-11-2025 22:14</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>31901</v>
+        <v>31902</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>21-11-2025 08:16</t>
+          <t>21-11-2025 12:18</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31838</v>
+        <v>31851</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21-11-2025 10:32</t>
+          <t>22-11-2025 00:24</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4177,11 +4177,11 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>31813</v>
+        <v>31817</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>21-11-2025 09:32</t>
+          <t>21-11-2025 23:23</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>31631</v>
+        <v>31639</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>21-11-2025 10:42</t>
+          <t>21-11-2025 23:38</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31416</v>
+        <v>31434</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>21-11-2025 10:26</t>
+          <t>22-11-2025 00:48</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>31125</v>
+        <v>31131</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>21-11-2025 10:01</t>
+          <t>22-11-2025 00:04</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>29815</v>
+        <v>29825</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>21-11-2025 23:19</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>29297</v>
+        <v>29302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>21-11-2025 09:39</t>
+          <t>22-11-2025 00:00</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28886</v>
+        <v>28896</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>21-11-2025 10:12</t>
+          <t>21-11-2025 23:24</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4487,11 +4487,11 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>28454</v>
+        <v>28463</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>21-11-2025 09:14</t>
+          <t>21-11-2025 23:02</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>28428</v>
+        <v>28427</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>21-11-2025 03:58</t>
+          <t>21-11-2025 22:24</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>28084</v>
+        <v>28090</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>21-11-2025 10:06</t>
+          <t>21-11-2025 17:33</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>27108</v>
+        <v>27109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>21-11-2025 06:01</t>
+          <t>21-11-2025 17:53</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4662,11 +4662,11 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>27102</v>
+        <v>27104</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>21-11-2025 04:58</t>
+          <t>21-11-2025 23:02</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>27043</v>
+        <v>27060</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>21-11-2025 10:27</t>
+          <t>22-11-2025 00:36</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26851</v>
+        <v>26857</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>21-11-2025 10:40</t>
+          <t>21-11-2025 22:13</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>26330</v>
+        <v>26329</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>21-11-2025 10:05</t>
+          <t>21-11-2025 14:10</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>26082</v>
+        <v>26089</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>21-11-2025 10:05</t>
+          <t>22-11-2025 00:31</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>26064</v>
+        <v>26071</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>21-11-2025 09:50</t>
+          <t>22-11-2025 00:11</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>21-11-2025 10:15</t>
+          <t>21-11-2025 12:42</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>25745</v>
+        <v>25748</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>21-11-2025 09:14</t>
+          <t>21-11-2025 21:24</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5013,11 +5013,11 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>25599</v>
+        <v>25601</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>21-11-2025 08:55</t>
+          <t>21-11-2025 20:20</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25581</v>
+        <v>25585</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>21-11-2025 08:54</t>
+          <t>22-11-2025 00:25</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>25453</v>
+        <v>25454</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>21-11-2025 07:24</t>
+          <t>21-11-2025 20:10</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>25050</v>
+        <v>25056</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>21-11-2025 10:40</t>
+          <t>21-11-2025 23:10</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5184,11 +5184,11 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>24526</v>
+        <v>24536</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>21-11-2025 09:32</t>
+          <t>22-11-2025 00:07</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>24434</v>
+        <v>24436</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>21-11-2025 07:09</t>
+          <t>22-11-2025 00:36</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>23866</v>
+        <v>23869</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>21-11-2025 08:08</t>
+          <t>21-11-2025 22:42</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>23854</v>
+        <v>23857</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>21-11-2025 06:24</t>
+          <t>22-11-2025 00:31</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>23803</v>
+        <v>23807</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>21-11-2025 09:41</t>
+          <t>21-11-2025 22:24</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>23137</v>
+        <v>23141</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>21-11-2025 21:55</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22248</v>
+        <v>22301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>21-11-2025 09:59</t>
+          <t>22-11-2025 00:13</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>22100</v>
+        <v>22119</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>21-11-2025 10:17</t>
+          <t>22-11-2025 00:02</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>21911</v>
+        <v>21914</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20-11-2025 15:37</t>
+          <t>21-11-2025 21:41</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>21889</v>
+        <v>21904</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>21-11-2025 09:57</t>
+          <t>22-11-2025 00:09</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>21837</v>
+        <v>21840</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>21-11-2025 08:30</t>
+          <t>21-11-2025 22:17</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>21389</v>
+        <v>21399</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>21-11-2025 08:30</t>
+          <t>21-11-2025 18:49</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>21056</v>
+        <v>21059</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>21-11-2025 10:06</t>
+          <t>21-11-2025 16:43</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>20679</v>
+        <v>20684</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>21-11-2025 09:23</t>
+          <t>21-11-2025 23:24</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>21-11-2025 09:42</t>
+          <t>21-11-2025 16:37</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>20582</v>
+        <v>20583</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>21-11-2025 09:33</t>
+          <t>21-11-2025 22:21</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>20119</v>
+        <v>20126</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>21-11-2025 10:32</t>
+          <t>21-11-2025 20:31</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>19588</v>
+        <v>19592</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>21-11-2025 08:40</t>
+          <t>22-11-2025 00:46</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6017,11 +6017,11 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>19493</v>
+        <v>19496</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>21-11-2025 10:25</t>
+          <t>21-11-2025 23:06</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6057,11 +6057,11 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>19180</v>
+        <v>19181</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>21-11-2025 09:15</t>
+          <t>21-11-2025 21:24</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>19039</v>
+        <v>19058</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>21-11-2025 10:38</t>
+          <t>22-11-2025 00:28</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18565</v>
+        <v>18598</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>21-11-2025 10:31</t>
+          <t>22-11-2025 00:21</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>18243</v>
+        <v>18246</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>21-11-2025 10:22</t>
+          <t>21-11-2025 19:42</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>18120</v>
+        <v>18124</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>21-11-2025 07:51</t>
+          <t>21-11-2025 21:25</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>18044</v>
+        <v>18045</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>21-11-2025 04:50</t>
+          <t>21-11-2025 20:43</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>17922</v>
+        <v>17923</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>21-11-2025 09:12</t>
+          <t>21-11-2025 22:44</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>17852</v>
+        <v>17857</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>21-11-2025 05:00</t>
+          <t>21-11-2025 21:35</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>17697</v>
+        <v>17703</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>21-11-2025 09:33</t>
+          <t>21-11-2025 23:55</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17619</v>
+        <v>17630</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>21-11-2025 08:30</t>
+          <t>21-11-2025 21:37</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>17439</v>
+        <v>17445</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>21-11-2025 10:38</t>
+          <t>21-11-2025 19:00</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>17428</v>
+        <v>17433</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>21-11-2025 02:57</t>
+          <t>22-11-2025 00:16</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>17270</v>
+        <v>17274</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>21-11-2025 08:23</t>
+          <t>22-11-2025 00:35</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>17209</v>
+        <v>17211</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>21-11-2025 10:06</t>
+          <t>21-11-2025 19:47</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6682,11 +6682,11 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>17062</v>
+        <v>17061</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>21-11-2025 10:13</t>
+          <t>21-11-2025 14:20</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>16737</v>
+        <v>16765</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>21-11-2025 10:16</t>
+          <t>22-11-2025 00:11</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>16318</v>
+        <v>16326</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>21-11-2025 09:28</t>
+          <t>21-11-2025 21:13</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6793,85 +6793,85 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>m1k1o/neko</t>
+          <t>enescingoz/awesome-n8n-templates</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://github.com/m1k1o/neko</t>
+          <t>https://github.com/enescingoz/awesome-n8n-templates</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>A self hosted virtual browser that runs in docker and uses WebRTC.</t>
+          <t>Supercharge your workflow automation with this curated collection of n8n templates! Instantly connect your favorite apps-like Gmail, Telegram, Google Drive, Slack, and more-with ready-to-use, AI-po...</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>15902</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
+        <v>15917</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>21-11-2025 09:53</t>
+          <t>21-11-2025 23:43</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>14-03-2020 20:46</t>
+          <t>08-05-2025 18:34</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>docker, golang, media-streaming, remote-control, remote-desktop</t>
+          <t>automation, automation-templates, integration, n8n, n8n-automation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>enescingoz/awesome-n8n-templates</t>
+          <t>m1k1o/neko</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://github.com/enescingoz/awesome-n8n-templates</t>
+          <t>https://github.com/m1k1o/neko</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Supercharge your workflow automation with this curated collection of n8n templates! Instantly connect your favorite apps-like Gmail, Telegram, Google Drive, Slack, and more-with ready-to-use, AI-po...</t>
+          <t>A self hosted virtual browser that runs in docker and uses WebRTC.</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>15900</v>
+        <v>15907</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>21-11-2025 09:42</t>
+          <t>22-11-2025 00:28</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>08-05-2025 18:34</t>
+          <t>14-03-2020 20:46</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>automation, automation-templates, integration, n8n, n8n-automation</t>
+          <t>docker, golang, media-streaming, remote-control, remote-desktop</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>15894</v>
+        <v>15896</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20-11-2025 19:26</t>
+          <t>21-11-2025 17:28</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6923,26 +6923,26 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TibixDev/winboat</t>
+          <t>QwenLM/qwen-code</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://github.com/TibixDev/winboat</t>
+          <t>https://github.com/QwenLM/qwen-code</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Run Windows apps on 🐧 Linux with ✨ seamless integration</t>
+          <t>Qwen Code is a coding agent that lives in the digital world.</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>15731</v>
+        <v>15744</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -6951,43 +6951,39 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>21-11-2025 09:46</t>
+          <t>21-11-2025 23:17</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>04-04-2025 12:03</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>docker, docker-compose, linux, rdp, virtualization</t>
-        </is>
-      </c>
+          <t>26-06-2025 01:37</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>QwenLM/qwen-code</t>
+          <t>TibixDev/winboat</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://github.com/QwenLM/qwen-code</t>
+          <t>https://github.com/TibixDev/winboat</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Qwen Code is a coding agent that lives in the digital world.</t>
+          <t>Run Windows apps on 🐧 Linux with ✨ seamless integration</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15728</v>
+        <v>15741</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6996,15 +6992,19 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>22-11-2025 00:30</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>26-06-2025 01:37</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>04-04-2025 12:03</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>docker, docker-compose, linux, rdp, virtualization</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>15689</v>
+        <v>15693</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>21-11-2025 07:58</t>
+          <t>22-11-2025 00:39</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15628</v>
+        <v>15657</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>21-11-2025 09:11</t>
+          <t>22-11-2025 00:00</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>15579</v>
+        <v>15588</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>21-11-2025 07:34</t>
+          <t>21-11-2025 23:55</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>15214</v>
+        <v>15218</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>21-11-2025 10:00</t>
+          <t>21-11-2025 17:44</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7185,12 +7185,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MatrixTM/MHDDoS</t>
+          <t>ChromeDevTools/chrome-devtools-mcp</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://github.com/MatrixTM/MHDDoS</t>
+          <t>https://github.com/ChromeDevTools/chrome-devtools-mcp</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7200,42 +7200,42 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Best DDoS Attack Script  Python3, (Cyber / DDos) Attack With 56 Methods</t>
+          <t>Chrome DevTools for coding agents</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15052</v>
+        <v>15087</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>21-11-2025 10:42</t>
+          <t>22-11-2025 00:36</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>13-10-2020 19:02</t>
+          <t>11-09-2025 10:39</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>amazon-bypass, attack, auto-proxy, bypass, cloudflare</t>
+          <t>browser, chrome, chrome-devtools, debugging, devtools</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ChromeDevTools/chrome-devtools-mcp</t>
+          <t>MatrixTM/MHDDoS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://github.com/ChromeDevTools/chrome-devtools-mcp</t>
+          <t>https://github.com/MatrixTM/MHDDoS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7245,30 +7245,30 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Chrome DevTools for coding agents</t>
+          <t>Best DDoS Attack Script  Python3, (Cyber / DDos) Attack With 56 Methods</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>15047</v>
+        <v>15060</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>21-11-2025 10:28</t>
+          <t>21-11-2025 23:45</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>11-09-2025 10:39</t>
+          <t>13-10-2020 19:02</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>browser, chrome, chrome-devtools, debugging, devtools</t>
+          <t>amazon-bypass, attack, auto-proxy, bypass, cloudflare</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>15033</v>
+        <v>15038</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>21-11-2025 09:53</t>
+          <t>21-11-2025 22:47</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>14882</v>
+        <v>14889</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20-11-2025 14:50</t>
+          <t>22-11-2025 00:11</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>14862</v>
+        <v>14863</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>21-11-2025 09:36</t>
+          <t>22-11-2025 00:44</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>14759</v>
+        <v>14761</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>21-11-2025 08:37</t>
+          <t>21-11-2025 13:12</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>14740</v>
+        <v>14743</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>21-11-2025 09:54</t>
+          <t>21-11-2025 14:54</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>14670</v>
+        <v>14675</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>21-11-2025 10:33</t>
+          <t>22-11-2025 00:10</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7605,7 +7605,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>14630</v>
+        <v>14632</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>21-11-2025 05:36</t>
+          <t>21-11-2025 20:28</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>14446</v>
+        <v>14445</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20-11-2025 20:56</t>
+          <t>21-11-2025 14:35</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>14102</v>
+        <v>14105</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>21-11-2025 10:07</t>
+          <t>21-11-2025 18:19</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7781,7 +7781,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>13855</v>
+        <v>13858</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>21-11-2025 10:34</t>
+          <t>21-11-2025 21:45</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>13762</v>
+        <v>13767</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>21-11-2025 09:32</t>
+          <t>21-11-2025 19:58</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>13677</v>
+        <v>13731</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>22-11-2025 00:38</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>13540</v>
+        <v>13545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>21-11-2025 10:00</t>
+          <t>21-11-2025 23:17</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13528</v>
+        <v>13539</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>21-11-2025 10:38</t>
+          <t>21-11-2025 17:11</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>13445</v>
+        <v>13444</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>19-11-2025 11:13</t>
+          <t>21-11-2025 17:01</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>13342</v>
+        <v>13345</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>21-11-2025 06:15</t>
+          <t>21-11-2025 18:54</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8141,11 +8141,11 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>13323</v>
+        <v>13332</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>21-11-2025 09:29</t>
+          <t>21-11-2025 23:22</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>13177</v>
+        <v>13180</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>21-11-2025 08:31</t>
+          <t>22-11-2025 00:39</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>13128</v>
+        <v>13135</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>21-11-2025 09:38</t>
+          <t>21-11-2025 21:14</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>12913</v>
+        <v>13005</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>21-11-2025 10:40</t>
+          <t>22-11-2025 00:34</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8316,11 +8316,11 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>12871</v>
+        <v>12872</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>21-11-2025 09:36</t>
+          <t>21-11-2025 21:42</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>12623</v>
+        <v>12627</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>21-11-2025 03:03</t>
+          <t>21-11-2025 17:12</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>12575</v>
+        <v>12576</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>21-11-2025 10:38</t>
+          <t>21-11-2025 16:37</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>12434</v>
+        <v>12438</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>20-11-2025 20:28</t>
+          <t>21-11-2025 20:57</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8527,11 +8527,11 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>12244</v>
+        <v>12246</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>21-11-2025 09:18</t>
+          <t>21-11-2025 14:14</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>12218</v>
+        <v>12225</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>21-11-2025 10:21</t>
+          <t>22-11-2025 00:45</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>12212</v>
+        <v>12214</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>21-11-2025 10:37</t>
+          <t>21-11-2025 22:59</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>12007</v>
+        <v>12010</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>21-11-2025 10:25</t>
+          <t>21-11-2025 22:50</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>11928</v>
+        <v>11941</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>21-11-2025 10:22</t>
+          <t>21-11-2025 23:39</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>11647</v>
+        <v>11651</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>20-11-2025 22:27</t>
+          <t>21-11-2025 21:25</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>11546</v>
+        <v>11548</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>17-11-2025 21:35</t>
+          <t>21-11-2025 16:43</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>11497</v>
+        <v>11507</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>21-11-2025 09:47</t>
+          <t>22-11-2025 00:38</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>11380</v>
+        <v>11385</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>21-11-2025 08:47</t>
+          <t>21-11-2025 20:06</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>11313</v>
+        <v>11318</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>21-11-2025 10:03</t>
+          <t>21-11-2025 21:42</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>10843</v>
+        <v>10848</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>21-11-2025 06:13</t>
+          <t>21-11-2025 23:09</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>10579</v>
+        <v>10581</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>21-11-2025 09:42</t>
+          <t>21-11-2025 23:55</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9238,11 +9238,11 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>10020</v>
+        <v>10027</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>21-11-2025 09:35</t>
+          <t>22-11-2025 00:36</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>10008</v>
+        <v>10010</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>21-11-2025 09:43</t>
+          <t>21-11-2025 16:45</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>9870</v>
+        <v>9936</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>21-11-2025 10:36</t>
+          <t>22-11-2025 00:49</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>9869</v>
+        <v>9870</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>21-11-2025 09:50</t>
+          <t>21-11-2025 20:25</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>9703</v>
+        <v>9709</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>21-11-2025 09:53</t>
+          <t>21-11-2025 22:14</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>9696</v>
+        <v>9706</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>21-11-2025 08:30</t>
+          <t>21-11-2025 22:58</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>9613</v>
+        <v>9615</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>21-11-2025 10:13</t>
+          <t>21-11-2025 14:54</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>9306</v>
+        <v>9311</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>21-11-2025 09:24</t>
+          <t>21-11-2025 20:18</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>9192</v>
+        <v>9218</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>21-11-2025 10:21</t>
+          <t>22-11-2025 00:35</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>9123</v>
+        <v>9126</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>21-11-2025 08:38</t>
+          <t>21-11-2025 22:09</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>8968</v>
+        <v>8980</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>21-11-2025 09:01</t>
+          <t>21-11-2025 22:23</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>8965</v>
+        <v>8974</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>21-11-2025 10:38</t>
+          <t>21-11-2025 23:51</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>8940</v>
+        <v>8941</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>21-11-2025 05:01</t>
+          <t>21-11-2025 14:52</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9887,11 +9887,11 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>8812</v>
+        <v>8815</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>21-11-2025 09:33</t>
+          <t>21-11-2025 22:06</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>8661</v>
+        <v>8672</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>20-11-2025 23:02</t>
+          <t>22-11-2025 00:21</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -9972,11 +9972,11 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>8613</v>
+        <v>8614</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>21-11-2025 09:33</t>
+          <t>21-11-2025 15:05</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10012,7 +10012,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>8608</v>
+        <v>8606</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>20-11-2025 21:26</t>
+          <t>21-11-2025 18:42</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>8560</v>
+        <v>8561</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>21-11-2025 10:16</t>
+          <t>21-11-2025 13:05</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>8487</v>
+        <v>8489</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>21-11-2025 09:33</t>
+          <t>21-11-2025 23:31</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>8408</v>
+        <v>8415</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>21-11-2025 10:41</t>
+          <t>22-11-2025 00:02</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10237,7 +10237,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>8327</v>
+        <v>8335</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>21-11-2025 08:28</t>
+          <t>21-11-2025 22:19</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>8191</v>
+        <v>8194</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>21-11-2025 01:22</t>
+          <t>21-11-2025 19:00</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10308,83 +10308,83 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>photopea/photopea</t>
+          <t>mandiant/flare-vm</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://github.com/photopea/photopea</t>
+          <t>https://github.com/mandiant/flare-vm</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>PowerShell</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Photopea is online image editor</t>
+          <t>A collection of software installations scripts for Windows systems that allows you to easily setup and maintain a reverse engineering environment on a VM.</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>8027</v>
+        <v>8034</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>PowerShell</t>
+        </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>21-11-2025 08:06</t>
+          <t>22-11-2025 00:17</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>21-11-2015 12:05</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>05-07-2017 21:17</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>flare, malware-analysis, reverse-engineering</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>mandiant/flare-vm</t>
+          <t>photopea/photopea</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://github.com/mandiant/flare-vm</t>
+          <t>https://github.com/photopea/photopea</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>PowerShell</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>A collection of software installations scripts for Windows systems that allows you to easily setup and maintain a reverse engineering environment on a VM.</t>
+          <t>Photopea is online image editor</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>8026</v>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>PowerShell</t>
-        </is>
+        <v>8028</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>21-11-2025 08:48</t>
+          <t>21-11-2025 11:44</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>05-07-2017 21:17</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>flare, malware-analysis, reverse-engineering</t>
-        </is>
-      </c>
+          <t>21-11-2015 12:05</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7955</v>
+        <v>7986</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>21-11-2025 10:31</t>
+          <t>22-11-2025 00:01</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>7742</v>
+        <v>7743</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>21-11-2025 09:23</t>
+          <t>21-11-2025 22:36</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10479,66 +10479,71 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>yeyintminthuhtut/Awesome-Red-Teaming</t>
+          <t>iib0011/omni-tools</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://github.com/yeyintminthuhtut/Awesome-Red-Teaming</t>
+          <t>https://github.com/iib0011/omni-tools</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>List of Awesome Red Teaming Resources</t>
+          <t>Self-hosted collection of powerful web-based tools for everyday tasks. No ads, no tracking, just fast, accessible utilities right from your browser!</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>7594</v>
+        <v>7610</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>21-11-2025 06:54</t>
+          <t>22-11-2025 00:46</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>27-09-2017 07:39</t>
+          <t>13-06-2024 23:06</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>cobalt-strike, empire, phishing, redteam, redteaming</t>
+          <t>alternative, converter, data-manipulation, developer-tools, devtools</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>iib0011/omni-tools</t>
+          <t>Termix-SSH/Termix</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://github.com/iib0011/omni-tools</t>
+          <t>https://github.com/Termix-SSH/Termix</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Self-hosted collection of powerful web-based tools for everyday tasks. No ads, no tracking, just fast, accessible utilities right from your browser!</t>
+          <t>Termix is a web-based server management platform with SSH terminal, tunneling, and file editing capabilities.</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>7590</v>
+        <v>7596</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -10547,62 +10552,57 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>21-11-2025 10:29</t>
+          <t>21-11-2025 22:43</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>13-06-2024 23:06</t>
+          <t>25-11-2024 02:46</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>alternative, converter, data-manipulation, developer-tools, devtools</t>
+          <t>docker, file-management, self-hosted, ssh, ssh-tunnel</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Termix-SSH/Termix</t>
+          <t>yeyintminthuhtut/Awesome-Red-Teaming</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://github.com/Termix-SSH/Termix</t>
+          <t>https://github.com/yeyintminthuhtut/Awesome-Red-Teaming</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Termix is a web-based server management platform with SSH terminal, tunneling, and file editing capabilities.</t>
+          <t>List of Awesome Red Teaming Resources</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>7581</v>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
+        <v>7595</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>21-11-2025 10:24</t>
+          <t>21-11-2025 22:34</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>25-11-2024 02:46</t>
+          <t>27-09-2017 07:39</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>docker, file-management, self-hosted, ssh, ssh-tunnel</t>
+          <t>cobalt-strike, empire, phishing, redteam, redteaming</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>7392</v>
+        <v>7403</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>21-11-2025 19:40</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>7308</v>
+        <v>7310</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>20-11-2025 19:44</t>
+          <t>21-11-2025 16:56</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>7218</v>
+        <v>7223</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>21-11-2025 06:34</t>
+          <t>21-11-2025 23:48</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10808,7 +10808,7 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6729</v>
+        <v>6730</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>21-11-2025 08:52</t>
+          <t>21-11-2025 15:04</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -10849,7 +10849,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6647</v>
+        <v>6655</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>21-11-2025 10:15</t>
+          <t>21-11-2025 23:41</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6601</v>
+        <v>6600</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>20-11-2025 01:08</t>
+          <t>21-11-2025 15:15</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6474</v>
+        <v>6476</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>21-11-2025 09:13</t>
+          <t>22-11-2025 00:17</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6415</v>
+        <v>6421</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>21-11-2025 10:09</t>
+          <t>21-11-2025 20:36</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6251</v>
+        <v>6252</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>21-11-2025 07:54</t>
+          <t>21-11-2025 13:36</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -11201,11 +11201,11 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6116</v>
+        <v>6122</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>21-11-2025 09:14</t>
+          <t>21-11-2025 22:47</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6106</v>
+        <v>6107</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>21-11-2025 07:34</t>
+          <t>21-11-2025 23:04</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6100</v>
+        <v>6101</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>20-11-2025 23:15</t>
+          <t>21-11-2025 14:00</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>21-11-2025 09:22</t>
+          <t>21-11-2025 11:22</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -11421,11 +11421,11 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>5675</v>
+        <v>5676</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>21-11-2025 09:15</t>
+          <t>21-11-2025 18:32</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -11461,7 +11461,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5595</v>
+        <v>5596</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>21-11-2025 06:54</t>
+          <t>21-11-2025 17:07</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -11551,7 +11551,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5481</v>
+        <v>5482</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>21-11-2025 05:58</t>
+          <t>21-11-2025 23:52</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5468</v>
+        <v>5479</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>21-11-2025 08:15</t>
+          <t>22-11-2025 00:41</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -11641,7 +11641,7 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5442</v>
+        <v>5444</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>20-11-2025 19:00</t>
+          <t>21-11-2025 18:28</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5179</v>
+        <v>5194</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>21-11-2025 10:31</t>
+          <t>22-11-2025 00:36</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5112</v>
+        <v>5114</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>19-11-2025 16:05</t>
+          <t>21-11-2025 20:45</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5088</v>
+        <v>5090</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>20-11-2025 21:36</t>
+          <t>21-11-2025 23:42</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>20-11-2025 20:33</t>
+          <t>21-11-2025 22:10</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5018</v>
+        <v>5020</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>21-11-2025 03:27</t>
+          <t>21-11-2025 18:56</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -11911,7 +11911,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>4971</v>
+        <v>4972</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>21-11-2025 04:19</t>
+          <t>21-11-2025 18:15</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -11956,7 +11956,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4949</v>
+        <v>4950</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>21-11-2025 08:57</t>
+          <t>21-11-2025 15:27</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -12001,11 +12001,11 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4944</v>
+        <v>4947</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>21-11-2025 09:42</t>
+          <t>22-11-2025 00:49</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4870</v>
+        <v>4871</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>21-11-2025 07:03</t>
+          <t>21-11-2025 22:47</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -12131,7 +12131,7 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>4794</v>
+        <v>4798</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>21-11-2025 10:42</t>
+          <t>21-11-2025 23:44</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -12176,7 +12176,7 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4784</v>
+        <v>4790</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>21-11-2025 08:58</t>
+          <t>22-11-2025 00:35</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>4745</v>
+        <v>4746</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>21-11-2025 07:25</t>
+          <t>21-11-2025 21:24</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -12266,7 +12266,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>4711</v>
+        <v>4712</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>20-11-2025 22:12</t>
+          <t>21-11-2025 16:24</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -12356,7 +12356,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>4687</v>
+        <v>4688</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>20-11-2025 12:11</t>
+          <t>21-11-2025 18:40</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -12536,7 +12536,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>4331</v>
+        <v>4333</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>21-11-2025 08:29</t>
+          <t>21-11-2025 23:53</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -12626,7 +12626,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4271</v>
+        <v>4272</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>21-11-2025 07:33</t>
+          <t>21-11-2025 22:33</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>21-11-2025 08:53</t>
+          <t>21-11-2025 22:42</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4213</v>
+        <v>4214</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>20-11-2025 10:19</t>
+          <t>21-11-2025 20:55</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>4145</v>
+        <v>4146</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>21-11-2025 09:31</t>
+          <t>21-11-2025 22:45</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -12802,7 +12802,7 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4137</v>
+        <v>4142</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>20-11-2025 14:39</t>
+          <t>22-11-2025 00:14</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -12843,7 +12843,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>4130</v>
+        <v>4132</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>17-11-2025 09:48</t>
+          <t>21-11-2025 18:45</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -12884,7 +12884,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>4034</v>
+        <v>4035</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>21-11-2025 07:16</t>
+          <t>21-11-2025 17:09</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4018</v>
+        <v>4019</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>18-11-2025 19:14</t>
+          <t>21-11-2025 18:45</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -13015,7 +13015,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>21-11-2025 05:03</t>
+          <t>21-11-2025 15:59</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>21-11-2025 01:07</t>
+          <t>21-11-2025 17:51</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>3718</v>
+        <v>3720</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>19-11-2025 15:33</t>
+          <t>21-11-2025 19:35</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3627</v>
+        <v>3632</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>21-11-2025 17:53</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>21-11-2025 01:32</t>
+          <t>21-11-2025 16:51</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -13326,11 +13326,11 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>3529</v>
+        <v>3531</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>21-11-2025 05:03</t>
+          <t>21-11-2025 22:45</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>20-11-2025 15:38</t>
+          <t>21-11-2025 22:57</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -13411,7 +13411,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3359</v>
+        <v>3365</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>21-11-2025 08:50</t>
+          <t>22-11-2025 00:50</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3273</v>
+        <v>3275</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>21-11-2025 09:14</t>
+          <t>21-11-2025 23:03</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -13482,12 +13482,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>dayanch96/YTLite</t>
+          <t>maillab/cloud-mail</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://github.com/dayanch96/YTLite</t>
+          <t>https://github.com/maillab/cloud-mail</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -13497,42 +13497,42 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>A flexible enhancer for YouTube on iOS</t>
+          <t>cloudflare email 邮箱  临时邮箱 邮件发送 mail</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3241</v>
+        <v>3243</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Logos</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>21-11-2025 09:58</t>
+          <t>21-11-2025 22:57</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>18-06-2023 15:53</t>
+          <t>24-04-2025 11:36</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>downloader, ios, jailbreak, sponsorblock, tweak</t>
+          <t>cloudflare, cloudflare-email, email, mail</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>maillab/cloud-mail</t>
+          <t>dayanch96/YTLite</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://github.com/maillab/cloud-mail</t>
+          <t>https://github.com/dayanch96/YTLite</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -13542,30 +13542,30 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>cloudflare email 邮箱  临时邮箱 邮件发送 mail</t>
+          <t>A flexible enhancer for YouTube on iOS</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>3238</v>
+        <v>3240</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Logos</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>21-11-2025 09:32</t>
+          <t>21-11-2025 22:42</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>24-04-2025 11:36</t>
+          <t>18-06-2023 15:53</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>cloudflare, cloudflare-email, email, mail</t>
+          <t>downloader, ios, jailbreak, sponsorblock, tweak</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>3218</v>
+        <v>3219</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>21-11-2025 06:10</t>
+          <t>21-11-2025 16:47</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>21-11-2025 02:08</t>
+          <t>21-11-2025 19:18</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>3161</v>
+        <v>3163</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>21-11-2025 07:13</t>
+          <t>21-11-2025 18:21</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -13771,7 +13771,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>21-11-2025 06:52</t>
+          <t>21-11-2025 23:17</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3131</v>
+        <v>3133</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>20-11-2025 21:36</t>
+          <t>21-11-2025 17:36</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -13861,7 +13861,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>21-11-2025 22:42</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -13951,7 +13951,7 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>3041</v>
+        <v>3043</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>20-11-2025 21:41</t>
+          <t>21-11-2025 20:50</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -13992,7 +13992,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>21-11-2025 08:30</t>
+          <t>21-11-2025 14:22</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>2997</v>
+        <v>3000</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>21-11-2025 09:53</t>
+          <t>21-11-2025 22:25</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -14078,11 +14078,11 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>2977</v>
+        <v>2981</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>21-11-2025 10:26</t>
+          <t>21-11-2025 23:52</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14208,7 +14208,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>2963</v>
+        <v>2966</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>21-11-2025 08:23</t>
+          <t>21-11-2025 19:44</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>2950</v>
+        <v>2953</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>21-11-2025 10:27</t>
+          <t>21-11-2025 22:55</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>19-11-2025 02:21</t>
+          <t>21-11-2025 14:12</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -14339,7 +14339,7 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>2860</v>
+        <v>2868</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>21-11-2025 10:01</t>
+          <t>21-11-2025 19:40</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -14384,7 +14384,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>21-11-2025 08:29</t>
+          <t>21-11-2025 18:06</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -14429,11 +14429,11 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2820</v>
+        <v>2822</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>21-11-2025 09:33</t>
+          <t>21-11-2025 19:02</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>20-11-2025 10:42</t>
+          <t>21-11-2025 23:29</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>21-11-2025 08:02</t>
+          <t>21-11-2025 22:37</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -14600,7 +14600,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>21-11-2025 04:22</t>
+          <t>21-11-2025 22:45</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>21-11-2025 06:28</t>
+          <t>21-11-2025 13:17</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>ai, audio-generation, generative-ai, generator, gradio</t>
+          <t>ace-step, ai, audio-generation, cosyvoice, generative-ai</t>
         </is>
       </c>
     </row>
@@ -14690,11 +14690,11 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>2742</v>
+        <v>2743</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>21-11-2025 06:11</t>
+          <t>22-11-2025 00:46</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -14730,7 +14730,7 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>20-11-2025 21:36</t>
+          <t>21-11-2025 13:16</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14775,7 +14775,7 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>2728</v>
+        <v>2730</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>21-11-2025 02:57</t>
+          <t>21-11-2025 16:10</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>21-11-2025 07:25</t>
+          <t>21-11-2025 22:31</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2552</v>
+        <v>2557</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>21-11-2025 10:39</t>
+          <t>21-11-2025 17:53</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>21-11-2025 00:04</t>
+          <t>21-11-2025 19:16</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>2468</v>
+        <v>2474</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>21-11-2025 08:37</t>
+          <t>21-11-2025 21:14</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15045,11 +15045,11 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2417</v>
+        <v>2421</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>21-11-2025 10:15</t>
+          <t>21-11-2025 19:26</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -15081,7 +15081,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2368</v>
+        <v>2420</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>21-11-2025 10:35</t>
+          <t>21-11-2025 23:25</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -15126,7 +15126,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>21-11-2025 08:25</t>
+          <t>21-11-2025 13:09</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -15171,7 +15171,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>21-11-2025 01:22</t>
+          <t>21-11-2025 18:10</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>20-11-2025 21:35</t>
+          <t>21-11-2025 20:54</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -15306,7 +15306,7 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>21-11-2025 03:27</t>
+          <t>21-11-2025 16:08</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>21-11-2025 09:57</t>
+          <t>21-11-2025 13:29</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -15482,11 +15482,11 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>2098</v>
+        <v>2104</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>21-11-2025 09:17</t>
+          <t>21-11-2025 23:34</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>20-11-2025 14:57</t>
+          <t>21-11-2025 19:29</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -15567,7 +15567,7 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>12-11-2025 20:50</t>
+          <t>21-11-2025 13:20</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>21-11-2025 08:30</t>
+          <t>21-11-2025 17:21</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -15698,7 +15698,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>20-11-2025 22:13</t>
+          <t>21-11-2025 13:27</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -15743,7 +15743,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>21-11-2025 03:32</t>
+          <t>21-11-2025 15:11</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>20-11-2025 10:57</t>
+          <t>21-11-2025 19:38</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15915,7 +15915,7 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>21-11-2025 10:19</t>
+          <t>21-11-2025 19:37</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15960,7 +15960,7 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>14-11-2025 02:17</t>
+          <t>21-11-2025 21:24</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16001,7 +16001,7 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>21-11-2025 07:49</t>
+          <t>22-11-2025 00:02</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -16091,7 +16091,7 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>21-11-2025 08:42</t>
+          <t>21-11-2025 13:20</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>21-11-2025 03:58</t>
+          <t>21-11-2025 18:16</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>21-11-2025 05:42</t>
+          <t>21-11-2025 23:21</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -16271,7 +16271,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>20-11-2025 21:13</t>
+          <t>21-11-2025 21:14</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -16401,7 +16401,7 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>20-11-2025 03:44</t>
+          <t>21-11-2025 13:08</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16427,90 +16427,90 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>xoureldeen/Vectras-VM-Android</t>
+          <t>Marktechpost/AI-Tutorial-Codes-Included</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://github.com/xoureldeen/Vectras-VM-Android</t>
+          <t>https://github.com/Marktechpost/AI-Tutorial-Codes-Included</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>It's a Virtual Machine App for Android Which is Based on QEMU</t>
+          <t>Codes/Notebooks for AI Projects</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>21-11-2025 04:54</t>
+          <t>21-11-2025 23:42</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>08-11-2023 00:09</t>
+          <t>15-05-2025 09:00</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>android, emulator, limbo, qemu, vectras-android</t>
+          <t>aiagents, artificial-intelligence, data-science, dataengineering, deep-learning</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Marktechpost/AI-Tutorial-Codes-Included</t>
+          <t>xoureldeen/Vectras-VM-Android</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://github.com/Marktechpost/AI-Tutorial-Codes-Included</t>
+          <t>https://github.com/xoureldeen/Vectras-VM-Android</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Codes/Notebooks for AI Projects</t>
+          <t>It's a Virtual Machine App for Android Which is Based on QEMU</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>21-11-2025 10:01</t>
+          <t>22-11-2025 00:10</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>15-05-2025 09:00</t>
+          <t>08-11-2023 00:09</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>aiagents, artificial-intelligence, data-science, dataengineering, deep-learning</t>
+          <t>android, emulator, limbo, qemu, vectras-android</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>20-11-2025 18:01</t>
+          <t>21-11-2025 21:39</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16757,7 +16757,7 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>21-11-2025 10:34</t>
+          <t>21-11-2025 21:09</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16892,11 +16892,11 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>21-11-2025 10:19</t>
+          <t>21-11-2025 22:13</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16977,11 +16977,11 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>21-11-2025 03:27</t>
+          <t>21-11-2025 21:03</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>21-11-2025 09:39</t>
+          <t>21-11-2025 23:35</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17107,11 +17107,11 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>21-11-2025 10:37</t>
+          <t>22-11-2025 00:37</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17224,7 +17224,7 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>21-11-2025 02:28</t>
+          <t>22-11-2025 00:33</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -17269,7 +17269,7 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>21-11-2025 09:45</t>
+          <t>21-11-2025 12:02</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -17355,7 +17355,7 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>21-11-2025 08:50</t>
+          <t>22-11-2025 00:26</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17400,7 +17400,7 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>20-11-2025 20:00</t>
+          <t>22-11-2025 00:25</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -17561,67 +17561,67 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>sickcodes/dock-droid</t>
+          <t>sauravpanda/BrowserAI</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://github.com/sickcodes/dock-droid</t>
+          <t>https://github.com/sauravpanda/BrowserAI</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Docker Android - Run QEMU Android in a Docker! X11 Forwarding! CI/CD for Android!</t>
+          <t>Run local LLMs like llama, deepseek-distill, kokoro and more inside your browser</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Dockerfile</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>19-11-2025 18:36</t>
+          <t>21-11-2025 19:57</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>03-07-2021 22:06</t>
+          <t>08-01-2025 00:26</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>android, docker, droid, kvm, linux</t>
+          <t>agents, ai, llama, llm, llm-inference</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>sauravpanda/BrowserAI</t>
+          <t>sickcodes/dock-droid</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://github.com/sauravpanda/BrowserAI</t>
+          <t>https://github.com/sickcodes/dock-droid</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Run local LLMs like llama, deepseek-distill, kokoro and more inside your browser</t>
+          <t>Docker Android - Run QEMU Android in a Docker! X11 Forwarding! CI/CD for Android!</t>
         </is>
       </c>
       <c r="E392" t="n">
@@ -17629,22 +17629,22 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Dockerfile</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>21-11-2025 06:49</t>
+          <t>19-11-2025 18:36</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>08-01-2025 00:26</t>
+          <t>03-07-2021 22:06</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>agents, ai, llama, llm, llm-inference</t>
+          <t>android, docker, droid, kvm, linux</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>21-11-2025 08:30</t>
+          <t>21-11-2025 11:45</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -17760,11 +17760,11 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>21-11-2025 01:39</t>
+          <t>21-11-2025 17:06</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>20-11-2025 15:45</t>
+          <t>21-11-2025 15:31</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -17890,7 +17890,7 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>20-11-2025 00:08</t>
+          <t>21-11-2025 22:14</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -18070,7 +18070,7 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>18-11-2025 17:09</t>
+          <t>21-11-2025 14:00</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18291,7 +18291,7 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>21-11-2025 09:57</t>
+          <t>21-11-2025 19:43</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>21-11-2025 08:13</t>
+          <t>21-11-2025 22:43</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -18593,11 +18593,11 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>20-11-2025 21:43</t>
+          <t>21-11-2025 23:57</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>20-11-2025 21:48</t>
+          <t>21-11-2025 22:05</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>21-11-2025 02:46</t>
+          <t>21-11-2025 18:51</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -19021,7 +19021,7 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>19-11-2025 19:49</t>
+          <t>21-11-2025 22:31</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -19165,7 +19165,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>20-11-2025 19:49</t>
+          <t>21-11-2025 15:54</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -19403,188 +19403,188 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Renset/macai</t>
+          <t>raghavyuva/nixopus</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://github.com/Renset/macai</t>
+          <t>https://github.com/raghavyuva/nixopus</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>All-in-one native macOS AI chat application for virtually any AI provider</t>
+          <t>Open Source Alternative to vercel, heroku, netlify with simplified workflows</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>759</v>
+        <v>770</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>20-11-2025 08:06</t>
+          <t>22-11-2025 00:47</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>21-03-2023 20:32</t>
+          <t>21-02-2025 11:17</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>ai, api-client, bot, chat, chatgpt</t>
+          <t>ci-cd, coolify, deployment, file-manager, golang</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Th30neAnd0nly/Ohm</t>
+          <t>Renset/macai</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://github.com/Th30neAnd0nly/Ohm</t>
+          <t>https://github.com/Renset/macai</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Android RAT with web panel and undetectable App</t>
+          <t>All-in-one native macOS AI chat application for virtually any AI provider</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>19-11-2025 15:32</t>
+          <t>20-11-2025 08:06</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>30-03-2021 05:57</t>
+          <t>21-03-2023 20:32</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>android, android-hack-rat, android-rat, android-remote, device-management</t>
+          <t>ai, api-client, bot, chat, chatgpt</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>senbo1/chat0</t>
+          <t>Th30neAnd0nly/Ohm</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://github.com/senbo1/chat0</t>
+          <t>https://github.com/Th30neAnd0nly/Ohm</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Blazingly-fast, free, open source AI chat app. Discord - https://discord.gg/mQSPrxVryy</t>
+          <t>Android RAT with web panel and undetectable App</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>10-11-2025 11:20</t>
+          <t>19-11-2025 15:32</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>17-05-2025 09:15</t>
-        </is>
-      </c>
-      <c r="I435" t="inlineStr"/>
+          <t>30-03-2021 05:57</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>android, android-hack-rat, android-rat, android-remote, device-management</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>bitcart/bitcart</t>
+          <t>senbo1/chat0</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://github.com/bitcart/bitcart</t>
+          <t>https://github.com/senbo1/chat0</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Bitcart is a free and open-source self-hosted payment processor for BTC, LTC, BCH, XMR, ETH, TRX, USDT and more</t>
+          <t>Blazingly-fast, free, open source AI chat app. Discord - https://discord.gg/mQSPrxVryy</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>21-11-2025 07:26</t>
+          <t>10-11-2025 11:20</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>03-03-2019 20:54</t>
-        </is>
-      </c>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>binance-smart-chain, bitcart, bitcoin, bitcoin-payment-gateway, docker</t>
-        </is>
-      </c>
+          <t>17-05-2025 09:15</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>dalisoft/awesome-hosting</t>
+          <t>bitcart/bitcart</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://github.com/dalisoft/awesome-hosting</t>
+          <t>https://github.com/bitcart/bitcart</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -19594,70 +19594,70 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>List of awesome hosting sorted by minimal plan price</t>
+          <t>Bitcart is a free and open-source self-hosted payment processor for BTC, LTC, BCH, XMR, ETH, TRX, USDT and more</t>
         </is>
       </c>
       <c r="E437" t="n">
         <v>751</v>
       </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>21-11-2025 09:27</t>
+          <t>21-11-2025 07:26</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>31-05-2019 12:27</t>
+          <t>03-03-2019 20:54</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>ai, cloud, database, deepseek-r1, free</t>
+          <t>binance-smart-chain, bitcart, bitcoin, bitcoin-payment-gateway, docker</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>raghavyuva/nixopus</t>
+          <t>dalisoft/awesome-hosting</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://github.com/raghavyuva/nixopus</t>
+          <t>https://github.com/dalisoft/awesome-hosting</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Open Source Alternative to vercel, heroku, netlify with simplified workflows</t>
+          <t>List of awesome hosting sorted by minimal plan price</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>733</v>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
+        <v>751</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>21-11-2025 10:40</t>
+          <t>21-11-2025 09:27</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>21-02-2025 11:17</t>
+          <t>31-05-2019 12:27</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>ci-cd, coolify, deployment, file-manager, golang</t>
+          <t>ai, cloud, database, deepseek-r1, free</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>20-11-2025 15:33</t>
+          <t>21-11-2025 17:08</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -20295,7 +20295,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>20-11-2025 13:39</t>
+          <t>21-11-2025 22:38</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -20385,7 +20385,7 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>21-11-2025 08:33</t>
+          <t>21-11-2025 18:01</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -20430,7 +20430,7 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>21-11-2025 10:24</t>
+          <t>21-11-2025 17:04</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -20475,7 +20475,7 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>18-11-2025 12:24</t>
+          <t>21-11-2025 21:39</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -20501,88 +20501,88 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Drugoy/Autohotkey-scripts-.ahk</t>
+          <t>Tablecruncher/tablecruncher</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://github.com/Drugoy/Autohotkey-scripts-.ahk</t>
+          <t>https://github.com/Tablecruncher/tablecruncher</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>AutoHotkey</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>My collection of autohotkey scripts. Some scripts are written by me, some are modified by me, some are completely created by others.</t>
+          <t>A lightweight, powerful CSV editor for macOS, Windows and Linux — with built-in JavaScript macros.</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>AutoHotkey</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>19-11-2025 11:12</t>
+          <t>22-11-2025 00:01</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>09-07-2013 23:53</t>
-        </is>
-      </c>
-      <c r="I458" t="inlineStr"/>
+          <t>25-04-2025 15:14</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>c-plus-plus, cpp, cross-platform, csv, csv-editor</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Tablecruncher/tablecruncher</t>
+          <t>Drugoy/Autohotkey-scripts-.ahk</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://github.com/Tablecruncher/tablecruncher</t>
+          <t>https://github.com/Drugoy/Autohotkey-scripts-.ahk</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>AutoHotkey</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>A lightweight, powerful CSV editor for macOS, Windows and Linux — with built-in JavaScript macros.</t>
+          <t>My collection of autohotkey scripts. Some scripts are written by me, some are modified by me, some are completely created by others.</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>AutoHotkey</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>21-11-2025 08:06</t>
+          <t>19-11-2025 11:12</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>25-04-2025 15:14</t>
-        </is>
-      </c>
-      <c r="I459" t="inlineStr">
-        <is>
-          <t>c-plus-plus, cpp, cross-platform, csv, csv-editor</t>
-        </is>
-      </c>
+          <t>09-07-2013 23:53</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -20651,7 +20651,7 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>20-11-2025 03:58</t>
+          <t>21-11-2025 22:40</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -20777,7 +20777,7 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>21-11-2025 09:34</t>
+          <t>21-11-2025 18:35</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -20831,7 +20831,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>20-11-2025 16:30</t>
+          <t>21-11-2025 21:10</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>20-11-2025 08:02</t>
+          <t>21-11-2025 23:26</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>19-11-2025 12:56</t>
+          <t>21-11-2025 17:44</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -21395,7 +21395,7 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>19-11-2025 14:08</t>
+          <t>21-11-2025 22:52</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -21440,7 +21440,7 @@
         </is>
       </c>
       <c r="E479" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>21-11-2025 07:24</t>
+          <t>21-11-2025 22:57</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>19-11-2025 15:33</t>
+          <t>21-11-2025 23:35</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -21530,7 +21530,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>19-11-2025 10:17</t>
+          <t>21-11-2025 23:48</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -21652,7 +21652,7 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>21-11-2025 07:57</t>
+          <t>21-11-2025 16:56</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -21697,7 +21697,7 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>20-11-2025 15:45</t>
+          <t>21-11-2025 16:39</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -22040,7 +22040,7 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>20-11-2025 16:41</t>
+          <t>21-11-2025 11:56</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -22085,7 +22085,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>18-11-2025 18:48</t>
+          <t>21-11-2025 14:30</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>21-11-2025 10:35</t>
+          <t>22-11-2025 00:49</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>20-11-2025 17:08</t>
+          <t>21-11-2025 17:20</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441358</v>
+        <v>441435</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 00:48</t>
+          <t>22-11-2025 03:42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416577</v>
+        <v>416606</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 00:38</t>
+          <t>22-11-2025 03:40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379971</v>
+        <v>379990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 00:14</t>
+          <t>22-11-2025 03:37</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270446</v>
+        <v>270457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 00:48</t>
+          <t>22-11-2025 03:30</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259286</v>
+        <v>259308</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 00:21</t>
+          <t>22-11-2025 03:35</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250544</v>
+        <v>250555</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 00:21</t>
+          <t>22-11-2025 03:30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198025</v>
+        <v>198027</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22-11-2025 00:45</t>
+          <t>22-11-2025 03:07</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195097</v>
+        <v>195117</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21-11-2025 23:39</t>
+          <t>22-11-2025 03:36</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>182889</v>
+        <v>182891</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21-11-2025 22:12</t>
+          <t>22-11-2025 02:20</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157849</v>
+        <v>157867</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 00:47</t>
+          <t>22-11-2025 03:43</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>156992</v>
+        <v>157007</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21-11-2025 23:29</t>
+          <t>22-11-2025 03:42</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>136761</v>
+        <v>136764</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22-11-2025 00:41</t>
+          <t>22-11-2025 03:31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135863</v>
+        <v>135873</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 00:42</t>
+          <t>22-11-2025 03:13</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131395</v>
+        <v>131400</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22-11-2025 00:32</t>
+          <t>22-11-2025 03:43</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125892</v>
+        <v>125895</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22-11-2025 00:42</t>
+          <t>22-11-2025 03:02</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115887</v>
+        <v>115892</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22-11-2025 00:45</t>
+          <t>22-11-2025 03:22</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1212,11 +1212,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115727</v>
+        <v>115729</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21-11-2025 22:12</t>
+          <t>22-11-2025 03:17</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115412</v>
+        <v>115446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 00:47</t>
+          <t>22-11-2025 03:41</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102864</v>
+        <v>102870</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22-11-2025 00:14</t>
+          <t>22-11-2025 03:22</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102420</v>
+        <v>102436</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 00:48</t>
+          <t>22-11-2025 03:30</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101000</v>
+        <v>101007</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22-11-2025 00:38</t>
+          <t>22-11-2025 03:35</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93777</v>
+        <v>93784</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21-11-2025 23:40</t>
+          <t>22-11-2025 03:41</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>92904</v>
+        <v>92905</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21-11-2025 19:50</t>
+          <t>22-11-2025 01:25</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21-11-2025 22:14</t>
+          <t>22-11-2025 02:48</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88182</v>
+        <v>88185</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>21-11-2025 22:01</t>
+          <t>22-11-2025 01:30</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>86466</v>
+        <v>86469</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21-11-2025 22:13</t>
+          <t>22-11-2025 03:13</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84707</v>
+        <v>84712</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 00:26</t>
+          <t>22-11-2025 03:43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83933</v>
+        <v>83947</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 00:47</t>
+          <t>22-11-2025 03:42</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83194</v>
+        <v>83195</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21-11-2025 23:05</t>
+          <t>22-11-2025 01:06</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>79929</v>
+        <v>79933</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22-11-2025 00:44</t>
+          <t>22-11-2025 03:35</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>79377</v>
+        <v>79376</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22-11-2025 00:20</t>
+          <t>22-11-2025 03:42</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21-11-2025 23:39</t>
+          <t>22-11-2025 02:49</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>76998</v>
+        <v>76999</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21-11-2025 22:42</t>
+          <t>22-11-2025 02:11</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75892</v>
+        <v>75895</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 00:05</t>
+          <t>22-11-2025 03:42</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>70461</v>
+        <v>70465</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21-11-2025 23:23</t>
+          <t>22-11-2025 03:15</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68282</v>
+        <v>68286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22-11-2025 00:42</t>
+          <t>22-11-2025 03:18</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>67929</v>
+        <v>67932</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21-11-2025 23:19</t>
+          <t>22-11-2025 03:20</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2137,11 +2137,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>66811</v>
+        <v>66813</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22-11-2025 00:07</t>
+          <t>22-11-2025 03:22</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>59602</v>
+        <v>59605</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21-11-2025 20:14</t>
+          <t>22-11-2025 03:21</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>58951</v>
+        <v>58959</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22-11-2025 00:49</t>
+          <t>22-11-2025 03:41</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2352,11 +2352,11 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>56785</v>
+        <v>56784</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>21-11-2025 22:18</t>
+          <t>22-11-2025 02:58</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56208</v>
+        <v>56211</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21-11-2025 23:56</t>
+          <t>22-11-2025 03:33</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53632</v>
+        <v>53633</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21-11-2025 23:03</t>
+          <t>22-11-2025 02:02</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2523,11 +2523,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53609</v>
+        <v>53610</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21-11-2025 23:42</t>
+          <t>22-11-2025 02:22</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51311</v>
+        <v>51322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22-11-2025 00:41</t>
+          <t>22-11-2025 03:40</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>48683</v>
+        <v>48686</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22-11-2025 00:33</t>
+          <t>22-11-2025 03:22</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47892</v>
+        <v>47893</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22-11-2025 00:46</t>
+          <t>22-11-2025 02:10</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>47864</v>
+        <v>47867</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21-11-2025 20:52</t>
+          <t>22-11-2025 03:26</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47561</v>
+        <v>47564</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22-11-2025 00:05</t>
+          <t>22-11-2025 03:02</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2919,11 +2919,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>47495</v>
+        <v>47498</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21-11-2025 22:16</t>
+          <t>22-11-2025 03:37</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47430</v>
+        <v>47433</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21-11-2025 21:06</t>
+          <t>22-11-2025 03:29</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3004,11 +3004,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>46343</v>
+        <v>46344</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21-11-2025 17:50</t>
+          <t>22-11-2025 02:23</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>22-11-2025 00:24</t>
+          <t>22-11-2025 03:34</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44398</v>
+        <v>44405</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21-11-2025 23:41</t>
+          <t>22-11-2025 03:35</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43168</v>
+        <v>43201</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 00:47</t>
+          <t>22-11-2025 03:40</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43120</v>
+        <v>43131</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21-11-2025 23:59</t>
+          <t>22-11-2025 03:43</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42966</v>
+        <v>42968</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>22-11-2025 00:00</t>
+          <t>22-11-2025 03:35</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>42510</v>
+        <v>42511</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>21-11-2025 23:14</t>
+          <t>22-11-2025 03:35</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21-11-2025 23:28</t>
+          <t>22-11-2025 03:36</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>39414</v>
+        <v>39416</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>22-11-2025 00:18</t>
+          <t>22-11-2025 03:08</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>39209</v>
+        <v>39214</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22-11-2025 00:16</t>
+          <t>22-11-2025 03:31</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>38970</v>
+        <v>38977</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>22-11-2025 00:35</t>
+          <t>22-11-2025 03:20</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>38619</v>
+        <v>38620</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>21-11-2025 18:38</t>
+          <t>22-11-2025 00:50</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37381</v>
+        <v>37383</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21-11-2025 21:22</t>
+          <t>22-11-2025 03:40</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>36933</v>
+        <v>36934</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>22-11-2025 00:46</t>
+          <t>22-11-2025 03:39</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>35654</v>
+        <v>35656</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>22-11-2025 00:32</t>
+          <t>22-11-2025 03:27</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>35498</v>
+        <v>35499</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>22-11-2025 00:48</t>
+          <t>22-11-2025 02:40</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3836,11 +3836,11 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34590</v>
+        <v>34591</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>21-11-2025 23:03</t>
+          <t>22-11-2025 02:01</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>34503</v>
+        <v>34504</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>21-11-2025 21:55</t>
+          <t>22-11-2025 03:06</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>33421</v>
+        <v>33423</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>22-11-2025 00:14</t>
+          <t>22-11-2025 03:28</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4011,11 +4011,11 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>32695</v>
+        <v>32697</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>21-11-2025 22:14</t>
+          <t>22-11-2025 02:40</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31851</v>
+        <v>31852</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>22-11-2025 00:24</t>
+          <t>22-11-2025 03:31</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4177,11 +4177,11 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>31817</v>
+        <v>31818</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>21-11-2025 23:23</t>
+          <t>22-11-2025 02:49</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>31639</v>
+        <v>31642</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>21-11-2025 23:38</t>
+          <t>22-11-2025 02:33</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31434</v>
+        <v>31439</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 00:48</t>
+          <t>22-11-2025 03:16</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>31131</v>
+        <v>31132</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>22-11-2025 00:04</t>
+          <t>22-11-2025 03:02</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>29302</v>
+        <v>29301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>22-11-2025 00:00</t>
+          <t>22-11-2025 01:23</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28896</v>
+        <v>28897</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>21-11-2025 23:24</t>
+          <t>22-11-2025 01:40</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>28090</v>
+        <v>28092</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>21-11-2025 17:33</t>
+          <t>22-11-2025 02:33</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>27109</v>
+        <v>27110</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>21-11-2025 17:53</t>
+          <t>22-11-2025 03:36</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4662,11 +4662,11 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>27104</v>
+        <v>27105</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>21-11-2025 23:02</t>
+          <t>22-11-2025 03:28</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>27060</v>
+        <v>27063</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>22-11-2025 00:36</t>
+          <t>22-11-2025 02:26</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26857</v>
+        <v>26858</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>21-11-2025 22:13</t>
+          <t>22-11-2025 01:15</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>26071</v>
+        <v>26072</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>22-11-2025 00:11</t>
+          <t>22-11-2025 03:05</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>25748</v>
+        <v>25750</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>21-11-2025 21:24</t>
+          <t>22-11-2025 02:34</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5013,11 +5013,11 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>25601</v>
+        <v>25602</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>21-11-2025 20:20</t>
+          <t>22-11-2025 02:09</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25585</v>
+        <v>25586</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>22-11-2025 00:25</t>
+          <t>22-11-2025 03:31</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>25454</v>
+        <v>25456</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>21-11-2025 20:10</t>
+          <t>22-11-2025 03:05</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5184,11 +5184,11 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>24536</v>
+        <v>24537</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>22-11-2025 00:07</t>
+          <t>22-11-2025 02:53</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>24436</v>
+        <v>24439</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>22-11-2025 00:36</t>
+          <t>22-11-2025 02:41</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>23807</v>
+        <v>23810</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>21-11-2025 22:24</t>
+          <t>22-11-2025 03:30</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>23141</v>
+        <v>23142</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>21-11-2025 21:55</t>
+          <t>22-11-2025 02:02</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22301</v>
+        <v>22311</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>22-11-2025 00:13</t>
+          <t>22-11-2025 03:43</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>22119</v>
+        <v>22124</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>22-11-2025 00:02</t>
+          <t>22-11-2025 03:11</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>21914</v>
+        <v>21915</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>21-11-2025 21:41</t>
+          <t>22-11-2025 02:43</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>21904</v>
+        <v>21908</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>22-11-2025 00:09</t>
+          <t>22-11-2025 03:22</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>21840</v>
+        <v>21841</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>21-11-2025 22:17</t>
+          <t>22-11-2025 03:31</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>21399</v>
+        <v>21404</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>21-11-2025 18:49</t>
+          <t>22-11-2025 03:27</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>20684</v>
+        <v>20685</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>21-11-2025 23:24</t>
+          <t>22-11-2025 03:41</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>20604</v>
+        <v>20606</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>21-11-2025 16:37</t>
+          <t>22-11-2025 02:36</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>20126</v>
+        <v>20127</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>21-11-2025 20:31</t>
+          <t>22-11-2025 01:06</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>19592</v>
+        <v>19593</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>22-11-2025 00:46</t>
+          <t>22-11-2025 02:55</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>19058</v>
+        <v>19060</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>22-11-2025 00:28</t>
+          <t>22-11-2025 01:56</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18598</v>
+        <v>18612</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 00:21</t>
+          <t>22-11-2025 03:34</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>21-11-2025 20:43</t>
+          <t>22-11-2025 02:15</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17630</v>
+        <v>17631</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>21-11-2025 21:37</t>
+          <t>22-11-2025 02:33</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>21-11-2025 19:00</t>
+          <t>22-11-2025 03:23</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>17274</v>
+        <v>17276</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>22-11-2025 00:35</t>
+          <t>22-11-2025 03:26</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>16765</v>
+        <v>16766</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>22-11-2025 00:11</t>
+          <t>22-11-2025 02:45</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>16326</v>
+        <v>16329</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>21-11-2025 21:13</t>
+          <t>22-11-2025 03:18</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6812,11 +6812,11 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>15917</v>
+        <v>15920</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>21-11-2025 23:43</t>
+          <t>22-11-2025 03:28</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>15896</v>
+        <v>15897</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>21-11-2025 17:28</t>
+          <t>22-11-2025 02:27</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>15744</v>
+        <v>15746</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>21-11-2025 23:17</t>
+          <t>22-11-2025 02:43</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15741</v>
+        <v>15744</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>22-11-2025 00:30</t>
+          <t>22-11-2025 03:10</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15657</v>
+        <v>15661</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22-11-2025 00:00</t>
+          <t>22-11-2025 02:53</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>15588</v>
+        <v>15589</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>21-11-2025 23:55</t>
+          <t>22-11-2025 02:22</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15087</v>
+        <v>15110</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 00:36</t>
+          <t>22-11-2025 03:42</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>15060</v>
+        <v>15062</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>21-11-2025 23:45</t>
+          <t>22-11-2025 03:20</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>15038</v>
+        <v>15040</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>21-11-2025 22:47</t>
+          <t>22-11-2025 03:21</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>14889</v>
+        <v>14891</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>22-11-2025 00:11</t>
+          <t>22-11-2025 03:13</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>14863</v>
+        <v>14864</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>22-11-2025 00:44</t>
+          <t>22-11-2025 01:19</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>14761</v>
+        <v>14762</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>21-11-2025 13:12</t>
+          <t>22-11-2025 02:20</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>14675</v>
+        <v>14676</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>22-11-2025 00:10</t>
+          <t>22-11-2025 01:33</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7781,7 +7781,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>13858</v>
+        <v>13859</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>21-11-2025 21:45</t>
+          <t>22-11-2025 03:03</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>13731</v>
+        <v>13738</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>22-11-2025 00:38</t>
+          <t>22-11-2025 03:43</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>13545</v>
+        <v>13546</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>21-11-2025 23:17</t>
+          <t>22-11-2025 01:57</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13539</v>
+        <v>13543</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>21-11-2025 17:11</t>
+          <t>22-11-2025 03:21</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8141,11 +8141,11 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>13332</v>
+        <v>13334</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>21-11-2025 23:22</t>
+          <t>22-11-2025 01:50</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13005</v>
+        <v>13019</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 00:34</t>
+          <t>22-11-2025 03:40</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>12438</v>
+        <v>12441</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>21-11-2025 20:57</t>
+          <t>22-11-2025 03:30</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>12010</v>
+        <v>12012</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>21-11-2025 22:50</t>
+          <t>22-11-2025 02:49</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>11941</v>
+        <v>11942</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>21-11-2025 23:39</t>
+          <t>22-11-2025 03:14</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>11651</v>
+        <v>11653</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>21-11-2025 21:25</t>
+          <t>22-11-2025 02:55</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>11507</v>
+        <v>11510</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>22-11-2025 00:38</t>
+          <t>22-11-2025 03:33</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>11385</v>
+        <v>11387</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>21-11-2025 20:06</t>
+          <t>22-11-2025 02:53</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>11318</v>
+        <v>11320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>21-11-2025 21:42</t>
+          <t>22-11-2025 01:40</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>10848</v>
+        <v>10849</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>21-11-2025 23:09</t>
+          <t>22-11-2025 02:24</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>10708</v>
+        <v>10709</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>21-11-2025 01:36</t>
+          <t>22-11-2025 02:25</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>10581</v>
+        <v>10582</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>21-11-2025 23:55</t>
+          <t>22-11-2025 03:17</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9238,11 +9238,11 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>10027</v>
+        <v>10030</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>22-11-2025 00:36</t>
+          <t>22-11-2025 02:29</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>9936</v>
+        <v>9945</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>22-11-2025 00:49</t>
+          <t>22-11-2025 03:39</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>9709</v>
+        <v>9710</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>21-11-2025 22:14</t>
+          <t>22-11-2025 02:21</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>9706</v>
+        <v>9708</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>21-11-2025 22:58</t>
+          <t>22-11-2025 01:37</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>9615</v>
+        <v>9616</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>21-11-2025 14:54</t>
+          <t>22-11-2025 02:00</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>9311</v>
+        <v>9312</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>21-11-2025 20:18</t>
+          <t>22-11-2025 03:18</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>9218</v>
+        <v>9222</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>22-11-2025 00:35</t>
+          <t>22-11-2025 02:49</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>9126</v>
+        <v>9127</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>21-11-2025 22:09</t>
+          <t>22-11-2025 02:49</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>8980</v>
+        <v>8983</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>21-11-2025 22:23</t>
+          <t>22-11-2025 03:19</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>8974</v>
+        <v>8976</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>21-11-2025 23:51</t>
+          <t>22-11-2025 03:33</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>8941</v>
+        <v>8942</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>21-11-2025 14:52</t>
+          <t>22-11-2025 01:25</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>8561</v>
+        <v>8562</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>21-11-2025 13:05</t>
+          <t>22-11-2025 03:30</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>8194</v>
+        <v>8195</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>21-11-2025 19:00</t>
+          <t>22-11-2025 03:24</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>8034</v>
+        <v>8036</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>22-11-2025 00:17</t>
+          <t>22-11-2025 03:10</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7986</v>
+        <v>7988</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>22-11-2025 00:01</t>
+          <t>22-11-2025 02:17</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10498,7 +10498,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>7610</v>
+        <v>7612</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>22-11-2025 00:46</t>
+          <t>22-11-2025 02:53</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>7596</v>
+        <v>7597</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>21-11-2025 22:43</t>
+          <t>22-11-2025 03:20</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10588,11 +10588,11 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>7595</v>
+        <v>7596</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>21-11-2025 22:34</t>
+          <t>22-11-2025 02:53</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>7403</v>
+        <v>7405</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>21-11-2025 19:40</t>
+          <t>22-11-2025 03:31</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6476</v>
+        <v>6477</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>22-11-2025 00:17</t>
+          <t>22-11-2025 01:18</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6421</v>
+        <v>6422</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>21-11-2025 20:36</t>
+          <t>22-11-2025 03:43</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6125</v>
+        <v>6126</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>21-11-2025 00:27</t>
+          <t>22-11-2025 02:53</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -11201,11 +11201,11 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6122</v>
+        <v>6124</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>21-11-2025 22:47</t>
+          <t>22-11-2025 02:07</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>21-11-2025 23:04</t>
+          <t>22-11-2025 01:39</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -11532,12 +11532,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>father-bot/chatgpt_telegram_bot</t>
+          <t>mistweaverco/bananas</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://github.com/father-bot/chatgpt_telegram_bot</t>
+          <t>https://github.com/mistweaverco/bananas</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11547,42 +11547,42 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>💬 Telegram bot with ChatGPT, Python-based, using OpenAI's API.</t>
+          <t>Bananas🍌, Cross-Platform screen 🖥️ sharing 📡 made simple ⚡.</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5482</v>
+        <v>5485</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Svelte</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>21-11-2025 23:52</t>
+          <t>22-11-2025 03:43</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>05-12-2022 00:12</t>
+          <t>10-10-2024 16:05</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>chat-gpt, chatbot, openai, python, telegram</t>
+          <t>cross-platform, multi-cursor, p2p, pair-programming, pairing</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>mistweaverco/bananas</t>
+          <t>father-bot/chatgpt_telegram_bot</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://github.com/mistweaverco/bananas</t>
+          <t>https://github.com/father-bot/chatgpt_telegram_bot</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -11592,30 +11592,30 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Bananas🍌, Cross-Platform screen 🖥️ sharing 📡 made simple ⚡.</t>
+          <t>💬 Telegram bot with ChatGPT, Python-based, using OpenAI's API.</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5479</v>
+        <v>5482</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Svelte</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>22-11-2025 00:41</t>
+          <t>21-11-2025 23:52</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>10-10-2024 16:05</t>
+          <t>05-12-2022 00:12</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>cross-platform, multi-cursor, p2p, pair-programming, pairing</t>
+          <t>chat-gpt, chatbot, openai, python, telegram</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5114</v>
+        <v>5115</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>21-11-2025 20:45</t>
+          <t>22-11-2025 02:40</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5020</v>
+        <v>5021</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>21-11-2025 18:56</t>
+          <t>22-11-2025 02:02</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -11956,7 +11956,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4950</v>
+        <v>4951</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>21-11-2025 15:27</t>
+          <t>22-11-2025 02:07</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -12176,7 +12176,7 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4790</v>
+        <v>4791</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>22-11-2025 00:35</t>
+          <t>22-11-2025 03:39</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -12536,7 +12536,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>4333</v>
+        <v>4334</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>21-11-2025 23:53</t>
+          <t>22-11-2025 03:13</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4284</v>
+        <v>4285</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>19-11-2025 15:31</t>
+          <t>22-11-2025 01:52</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -12671,7 +12671,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4254</v>
+        <v>4255</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>21-11-2025 22:42</t>
+          <t>22-11-2025 02:32</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4214</v>
+        <v>4213</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>21-11-2025 20:55</t>
+          <t>22-11-2025 01:45</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -12802,7 +12802,7 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4142</v>
+        <v>4144</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>22-11-2025 00:14</t>
+          <t>22-11-2025 03:30</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>21-11-2025 17:09</t>
+          <t>22-11-2025 03:16</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3632</v>
+        <v>3635</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>21-11-2025 17:53</t>
+          <t>22-11-2025 03:33</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -13411,7 +13411,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3365</v>
+        <v>3367</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>22-11-2025 00:50</t>
+          <t>22-11-2025 03:40</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3243</v>
+        <v>3248</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>21-11-2025 22:57</t>
+          <t>22-11-2025 03:41</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>21-11-2025 22:42</t>
+          <t>22-11-2025 01:28</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>21-11-2025 18:21</t>
+          <t>22-11-2025 03:41</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>20-11-2025 19:02</t>
+          <t>22-11-2025 02:09</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>21-11-2025 17:36</t>
+          <t>22-11-2025 02:54</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -13992,7 +13992,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>21-11-2025 14:22</t>
+          <t>22-11-2025 02:29</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>21-11-2025 23:52</t>
+          <t>22-11-2025 03:38</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14384,7 +14384,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>21-11-2025 18:06</t>
+          <t>22-11-2025 03:15</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -14429,11 +14429,11 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>21-11-2025 19:02</t>
+          <t>22-11-2025 03:36</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>21-11-2025 23:29</t>
+          <t>22-11-2025 03:20</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>2752</v>
+        <v>2754</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>21-11-2025 13:17</t>
+          <t>22-11-2025 02:41</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2557</v>
+        <v>2560</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>21-11-2025 17:53</t>
+          <t>22-11-2025 03:31</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>21-11-2025 21:14</t>
+          <t>22-11-2025 01:17</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15026,83 +15026,83 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>restyler/awesome-n8n</t>
+          <t>tonyantony300/alt-sendme</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://github.com/restyler/awesome-n8n</t>
+          <t>https://github.com/tonyantony300/alt-sendme</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Useful n8n resources: list of community nodes and tutorials</t>
+          <t>Send files and folders anywhere in the world without storing in cloud - any size, any format, no accounts, no restrictions. Simple, fast, and reliable.</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2421</v>
+        <v>2422</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>21-11-2025 19:26</t>
+          <t>22-11-2025 03:06</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>04-02-2025 10:30</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr"/>
+          <t>17-10-2025 09:08</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>encryption, file-sharing, file-transfer, ftp, iroh</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>tonyantony300/alt-sendme</t>
+          <t>restyler/awesome-n8n</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://github.com/tonyantony300/alt-sendme</t>
+          <t>https://github.com/restyler/awesome-n8n</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Send files and folders anywhere in the world without storing in cloud - any size, any format, no accounts, no restrictions. Simple, fast, and reliable.</t>
+          <t>Useful n8n resources: list of community nodes and tutorials</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2420</v>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
+        <v>2421</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>21-11-2025 23:25</t>
+          <t>21-11-2025 19:26</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>17-10-2025 09:08</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>encryption, file-sharing, file-transfer, ftp, iroh</t>
-        </is>
-      </c>
+          <t>04-02-2025 10:30</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15126,7 +15126,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>21-11-2025 13:09</t>
+          <t>22-11-2025 01:58</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>21-11-2025 07:57</t>
+          <t>22-11-2025 02:18</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>20-11-2025 20:44</t>
+          <t>22-11-2025 02:55</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -15874,7 +15874,7 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>19-11-2025 11:43</t>
+          <t>22-11-2025 03:40</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>22-11-2025 00:10</t>
+          <t>22-11-2025 03:38</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -16667,7 +16667,7 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>21-11-2025 21:39</t>
+          <t>22-11-2025 02:04</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16757,7 +16757,7 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>21-11-2025 21:09</t>
+          <t>22-11-2025 02:30</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16892,11 +16892,11 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>21-11-2025 22:13</t>
+          <t>22-11-2025 02:09</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>21-11-2025 23:35</t>
+          <t>22-11-2025 03:15</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>22-11-2025 00:37</t>
+          <t>22-11-2025 02:37</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>22-11-2025 00:33</t>
+          <t>22-11-2025 01:31</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -17355,7 +17355,7 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>22-11-2025 00:26</t>
+          <t>22-11-2025 02:42</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>22-11-2025 00:25</t>
+          <t>22-11-2025 00:51</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -18291,7 +18291,7 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>21-11-2025 19:43</t>
+          <t>22-11-2025 00:54</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18332,7 +18332,7 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>21-11-2025 00:41</t>
+          <t>22-11-2025 03:09</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>21-11-2025 22:43</t>
+          <t>22-11-2025 01:47</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -18593,11 +18593,11 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>21-11-2025 23:57</t>
+          <t>22-11-2025 02:52</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -18936,7 +18936,7 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>19-11-2025 16:15</t>
+          <t>22-11-2025 02:28</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -19066,7 +19066,7 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>21-11-2025 09:30</t>
+          <t>22-11-2025 00:57</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -19111,7 +19111,7 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>21-11-2025 08:35</t>
+          <t>22-11-2025 03:02</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>22-11-2025 00:47</t>
+          <t>22-11-2025 03:23</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>21-11-2025 06:35</t>
+          <t>22-11-2025 02:20</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -20115,7 +20115,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>18-11-2025 15:58</t>
+          <t>22-11-2025 03:10</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -20430,7 +20430,7 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>21-11-2025 17:04</t>
+          <t>22-11-2025 01:44</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>22-11-2025 00:01</t>
+          <t>22-11-2025 01:27</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>21-11-2025 00:51</t>
+          <t>22-11-2025 03:24</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 00:49</t>
+          <t>22-11-2025 03:40</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -4011,11 +4011,11 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>32697</v>
+        <v>32698</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>22-11-2025 02:40</t>
+          <t>22-11-2025 03:44</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441435</v>
+        <v>441439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 03:42</t>
+          <t>22-11-2025 03:52</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416606</v>
+        <v>416608</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 03:40</t>
+          <t>22-11-2025 03:51</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379990</v>
+        <v>379993</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 03:37</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270457</v>
+        <v>270458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 03:30</t>
+          <t>22-11-2025 03:51</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259308</v>
+        <v>259309</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 03:35</t>
+          <t>22-11-2025 03:51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250555</v>
+        <v>250558</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 03:30</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195117</v>
+        <v>195120</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 03:36</t>
+          <t>22-11-2025 03:51</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157867</v>
+        <v>157868</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 03:43</t>
+          <t>22-11-2025 03:52</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135873</v>
+        <v>135874</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 03:13</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125895</v>
+        <v>125896</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22-11-2025 03:02</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115892</v>
+        <v>115894</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22-11-2025 03:22</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115446</v>
+        <v>115448</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 03:41</t>
+          <t>22-11-2025 03:52</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102436</v>
+        <v>102437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 03:30</t>
+          <t>22-11-2025 03:48</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83947</v>
+        <v>83948</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 03:42</t>
+          <t>22-11-2025 03:50</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75895</v>
+        <v>75896</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 03:42</t>
+          <t>22-11-2025 03:51</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68286</v>
+        <v>68287</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22-11-2025 03:18</t>
+          <t>22-11-2025 03:50</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>22-11-2025 00:10</t>
+          <t>22-11-2025 03:47</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>22-11-2025 03:34</t>
+          <t>22-11-2025 03:50</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44405</v>
+        <v>44406</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22-11-2025 03:35</t>
+          <t>22-11-2025 03:50</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43201</v>
+        <v>43204</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 03:40</t>
+          <t>22-11-2025 03:51</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43131</v>
+        <v>43132</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22-11-2025 03:43</t>
+          <t>22-11-2025 03:47</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>39114</v>
+        <v>39115</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22-11-2025 00:14</t>
+          <t>22-11-2025 03:46</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>34504</v>
+        <v>34503</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>22-11-2025 03:06</t>
+          <t>22-11-2025 03:52</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4011,11 +4011,11 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>32697</v>
+        <v>32698</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>22-11-2025 02:40</t>
+          <t>22-11-2025 03:44</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>28092</v>
+        <v>28093</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>22-11-2025 02:33</t>
+          <t>22-11-2025 03:47</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>17445</v>
+        <v>17446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>22-11-2025 03:23</t>
+          <t>22-11-2025 03:52</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>22-11-2025 02:22</t>
+          <t>22-11-2025 03:47</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15110</v>
+        <v>15112</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 03:42</t>
+          <t>22-11-2025 03:52</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13019</v>
+        <v>13020</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 03:40</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>9945</v>
+        <v>9946</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>22-11-2025 03:39</t>
+          <t>22-11-2025 03:45</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>8976</v>
+        <v>8977</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>22-11-2025 03:33</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>8562</v>
+        <v>8563</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>22-11-2025 03:30</t>
+          <t>22-11-2025 03:45</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>7320</v>
+        <v>7321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>21-11-2025 06:41</t>
+          <t>22-11-2025 03:48</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>22-11-2025 03:43</t>
+          <t>22-11-2025 03:51</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11956,7 +11956,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4951</v>
+        <v>4952</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>22-11-2025 02:07</t>
+          <t>22-11-2025 03:46</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>21-11-2025 23:03</t>
+          <t>22-11-2025 03:45</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -16316,11 +16316,11 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>20-11-2025 23:36</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>22-11-2025 03:15</t>
+          <t>22-11-2025 03:45</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441439</v>
+        <v>441440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 03:52</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416608</v>
+        <v>416609</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 03:51</t>
+          <t>22-11-2025 03:54</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270458</v>
+        <v>270459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 03:51</t>
+          <t>22-11-2025 03:54</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259309</v>
+        <v>259310</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 03:51</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195120</v>
+        <v>195122</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 03:51</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157007</v>
+        <v>157008</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 03:42</t>
+          <t>22-11-2025 03:54</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115448</v>
+        <v>115449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 03:52</t>
+          <t>22-11-2025 03:53</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101007</v>
+        <v>101008</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22-11-2025 03:35</t>
+          <t>22-11-2025 03:53</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>58959</v>
+        <v>58960</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22-11-2025 03:41</t>
+          <t>22-11-2025 03:53</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47564</v>
+        <v>47565</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22-11-2025 03:02</t>
+          <t>22-11-2025 03:54</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>34230</v>
+        <v>34231</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>21-11-2025 18:57</t>
+          <t>22-11-2025 03:54</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31439</v>
+        <v>31440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 03:16</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22311</v>
+        <v>22312</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>22-11-2025 03:43</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15112</v>
+        <v>15113</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 03:52</t>
+          <t>22-11-2025 03:53</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>13135</v>
+        <v>13136</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>21-11-2025 21:14</t>
+          <t>22-11-2025 03:54</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>22-11-2025 03:38</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 03:40</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416609</v>
+        <v>416611</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 03:54</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157008</v>
+        <v>157011</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 03:54</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115449</v>
+        <v>115450</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 03:53</t>
+          <t>22-11-2025 03:57</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22-11-2025 01:25</t>
+          <t>22-11-2025 04:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>86469</v>
+        <v>86470</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22-11-2025 03:13</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83195</v>
+        <v>83196</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22-11-2025 01:06</t>
+          <t>22-11-2025 03:57</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51322</v>
+        <v>51323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22-11-2025 03:40</t>
+          <t>22-11-2025 03:58</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3004,11 +3004,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>22-11-2025 02:23</t>
+          <t>22-11-2025 03:59</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43204</v>
+        <v>43205</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 03:51</t>
+          <t>22-11-2025 03:57</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22-11-2025 03:47</t>
+          <t>22-11-2025 03:58</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>21-11-2025 21:35</t>
+          <t>22-11-2025 04:00</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>15693</v>
+        <v>15694</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>22-11-2025 00:39</t>
+          <t>22-11-2025 03:58</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15661</v>
+        <v>15662</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22-11-2025 02:53</t>
+          <t>22-11-2025 04:00</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9887,11 +9887,11 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>8815</v>
+        <v>8816</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>21-11-2025 22:06</t>
+          <t>22-11-2025 03:56</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -12001,11 +12001,11 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4947</v>
+        <v>4948</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>22-11-2025 00:49</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3248</v>
+        <v>3249</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>22-11-2025 03:41</t>
+          <t>22-11-2025 03:57</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -14429,11 +14429,11 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>22-11-2025 03:36</t>
+          <t>22-11-2025 03:56</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -18182,67 +18182,63 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>webrecorder/archiveweb.page</t>
+          <t>Ainz-devs/OVL-MD-V2</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://github.com/webrecorder/archiveweb.page</t>
+          <t>https://github.com/Ainz-devs/OVL-MD-V2</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>A High-Fidelity Web Archiving Extension for Chrome and Chromium based browsers!</t>
+          <t>OVL-MD-V2, développé par Ainz, est un bot WhatsApp multi-device performant, offrant de nombreuses fonctionnalités.</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>20-11-2025 15:57</t>
+          <t>22-11-2025 03:59</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>10-02-2020 20:17</t>
-        </is>
-      </c>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>archiving, browser-extension, chromium, extension, wacz</t>
-        </is>
-      </c>
+          <t>30-04-2025 19:02</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>jasperan/whatsapp-osint</t>
+          <t>webrecorder/archiveweb.page</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://github.com/jasperan/whatsapp-osint</t>
+          <t>https://github.com/webrecorder/archiveweb.page</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>WhatsApp spy - logs online/offline events from ANYONE in the world</t>
+          <t>A High-Fidelity Web Archiving Extension for Chrome and Chromium based browsers!</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -18250,44 +18246,44 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>19-11-2025 02:11</t>
+          <t>20-11-2025 15:57</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>14-11-2019 15:27</t>
+          <t>10-02-2020 20:17</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>bot, logger, osint, python, selenium</t>
+          <t>archiving, browser-extension, chromium, extension, wacz</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Ainz-devs/OVL-MD-V2</t>
+          <t>jasperan/whatsapp-osint</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://github.com/Ainz-devs/OVL-MD-V2</t>
+          <t>https://github.com/jasperan/whatsapp-osint</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>OVL-MD-V2, développé par Ainz, est un bot WhatsApp multi-device performant, offrant de nombreuses fonctionnalités.</t>
+          <t>WhatsApp spy - logs online/offline events from ANYONE in the world</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -18295,20 +18291,24 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>22-11-2025 00:54</t>
+          <t>19-11-2025 02:11</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>30-04-2025 19:02</t>
-        </is>
-      </c>
-      <c r="I407" t="inlineStr"/>
+          <t>14-11-2019 15:27</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>bot, logger, osint, python, selenium</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441444</v>
+        <v>441440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:10</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416612</v>
+        <v>416611</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:02</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379995</v>
+        <v>379993</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270460</v>
+        <v>270459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 04:07</t>
+          <t>22-11-2025 03:54</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250559</v>
+        <v>250558</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157869</v>
+        <v>157868</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 04:07</t>
+          <t>22-11-2025 03:52</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157012</v>
+        <v>157011</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 04:08</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102439</v>
+        <v>102437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 03:48</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93785</v>
+        <v>93784</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22-11-2025 04:04</t>
+          <t>22-11-2025 03:41</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84713</v>
+        <v>84712</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 04:04</t>
+          <t>22-11-2025 03:43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83949</v>
+        <v>83948</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:07</t>
+          <t>22-11-2025 03:50</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75897</v>
+        <v>75896</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 04:08</t>
+          <t>22-11-2025 03:51</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>58961</v>
+        <v>58960</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22-11-2025 04:05</t>
+          <t>22-11-2025 03:53</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22-11-2025 04:02</t>
+          <t>22-11-2025 03:22</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47434</v>
+        <v>47433</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 03:29</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44407</v>
+        <v>44406</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22-11-2025 04:07</t>
+          <t>22-11-2025 03:50</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43207</v>
+        <v>43205</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 04:09</t>
+          <t>22-11-2025 03:57</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>22-11-2025 04:09</t>
+          <t>22-11-2025 03:40</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31441</v>
+        <v>31440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22313</v>
+        <v>22312</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>22125</v>
+        <v>22124</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>22-11-2025 04:07</t>
+          <t>22-11-2025 03:11</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>19059</v>
+        <v>19060</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>22-11-2025 04:05</t>
+          <t>22-11-2025 01:56</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6812,11 +6812,11 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>22-11-2025 04:08</t>
+          <t>22-11-2025 03:28</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15114</v>
+        <v>15113</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 04:04</t>
+          <t>22-11-2025 03:53</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13022</v>
+        <v>13020</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 04:08</t>
+          <t>22-11-2025 03:49</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4872</v>
+        <v>4871</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>22-11-2025 04:02</t>
+          <t>21-11-2025 22:47</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>22-11-2025 04:09</t>
+          <t>21-11-2025 07:51</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 04:08</t>
+          <t>22-11-2025 03:55</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441440</v>
+        <v>441444</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416609</v>
+        <v>416612</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 03:54</t>
+          <t>22-11-2025 04:02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379993</v>
+        <v>379995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270459</v>
+        <v>270460</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 03:54</t>
+          <t>22-11-2025 04:07</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250558</v>
+        <v>250559</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157868</v>
+        <v>157869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 03:52</t>
+          <t>22-11-2025 04:07</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157008</v>
+        <v>157012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 03:54</t>
+          <t>22-11-2025 04:08</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115449</v>
+        <v>115450</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 03:53</t>
+          <t>22-11-2025 03:57</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102437</v>
+        <v>102439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 03:48</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93784</v>
+        <v>93785</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22-11-2025 03:41</t>
+          <t>22-11-2025 04:04</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22-11-2025 01:25</t>
+          <t>22-11-2025 04:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>86469</v>
+        <v>86470</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22-11-2025 03:13</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84712</v>
+        <v>84713</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 03:43</t>
+          <t>22-11-2025 04:04</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83948</v>
+        <v>83949</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 03:50</t>
+          <t>22-11-2025 04:07</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83195</v>
+        <v>83196</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22-11-2025 01:06</t>
+          <t>22-11-2025 03:57</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75896</v>
+        <v>75897</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 03:51</t>
+          <t>22-11-2025 04:08</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>58960</v>
+        <v>58961</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22-11-2025 03:53</t>
+          <t>22-11-2025 04:05</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51322</v>
+        <v>51323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22-11-2025 03:40</t>
+          <t>22-11-2025 03:58</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22-11-2025 03:22</t>
+          <t>22-11-2025 04:02</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47433</v>
+        <v>47434</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22-11-2025 03:29</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3004,11 +3004,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>22-11-2025 02:23</t>
+          <t>22-11-2025 03:59</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44406</v>
+        <v>44407</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22-11-2025 03:50</t>
+          <t>22-11-2025 04:07</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43204</v>
+        <v>43207</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 03:51</t>
+          <t>22-11-2025 04:09</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22-11-2025 03:47</t>
+          <t>22-11-2025 03:58</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>22-11-2025 03:40</t>
+          <t>22-11-2025 04:09</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31440</v>
+        <v>31441</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22312</v>
+        <v>22313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>22124</v>
+        <v>22125</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>22-11-2025 03:11</t>
+          <t>22-11-2025 04:07</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>19060</v>
+        <v>19059</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>22-11-2025 01:56</t>
+          <t>22-11-2025 04:05</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>21-11-2025 21:35</t>
+          <t>22-11-2025 04:00</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6812,11 +6812,11 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>15920</v>
+        <v>15923</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>22-11-2025 03:28</t>
+          <t>22-11-2025 04:08</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>15693</v>
+        <v>15694</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>22-11-2025 00:39</t>
+          <t>22-11-2025 03:58</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15661</v>
+        <v>15662</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22-11-2025 02:53</t>
+          <t>22-11-2025 04:00</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15113</v>
+        <v>15114</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 03:53</t>
+          <t>22-11-2025 04:04</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13020</v>
+        <v>13022</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:08</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9887,11 +9887,11 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>8815</v>
+        <v>8816</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>21-11-2025 22:06</t>
+          <t>22-11-2025 03:56</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -12001,11 +12001,11 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4947</v>
+        <v>4948</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>22-11-2025 00:49</t>
+          <t>22-11-2025 04:01</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4871</v>
+        <v>4872</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>21-11-2025 22:47</t>
+          <t>22-11-2025 04:02</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3248</v>
+        <v>3249</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>22-11-2025 03:41</t>
+          <t>22-11-2025 03:57</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -14429,11 +14429,11 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>22-11-2025 03:36</t>
+          <t>22-11-2025 03:56</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>21-11-2025 07:51</t>
+          <t>22-11-2025 04:09</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -18182,67 +18182,63 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>webrecorder/archiveweb.page</t>
+          <t>Ainz-devs/OVL-MD-V2</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://github.com/webrecorder/archiveweb.page</t>
+          <t>https://github.com/Ainz-devs/OVL-MD-V2</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>A High-Fidelity Web Archiving Extension for Chrome and Chromium based browsers!</t>
+          <t>OVL-MD-V2, développé par Ainz, est un bot WhatsApp multi-device performant, offrant de nombreuses fonctionnalités.</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>20-11-2025 15:57</t>
+          <t>22-11-2025 03:59</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>10-02-2020 20:17</t>
-        </is>
-      </c>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>archiving, browser-extension, chromium, extension, wacz</t>
-        </is>
-      </c>
+          <t>30-04-2025 19:02</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>jasperan/whatsapp-osint</t>
+          <t>webrecorder/archiveweb.page</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://github.com/jasperan/whatsapp-osint</t>
+          <t>https://github.com/webrecorder/archiveweb.page</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>WhatsApp spy - logs online/offline events from ANYONE in the world</t>
+          <t>A High-Fidelity Web Archiving Extension for Chrome and Chromium based browsers!</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -18250,44 +18246,44 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>19-11-2025 02:11</t>
+          <t>20-11-2025 15:57</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>14-11-2019 15:27</t>
+          <t>10-02-2020 20:17</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>bot, logger, osint, python, selenium</t>
+          <t>archiving, browser-extension, chromium, extension, wacz</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Ainz-devs/OVL-MD-V2</t>
+          <t>jasperan/whatsapp-osint</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://github.com/Ainz-devs/OVL-MD-V2</t>
+          <t>https://github.com/jasperan/whatsapp-osint</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>OVL-MD-V2, développé par Ainz, est un bot WhatsApp multi-device performant, offrant de nombreuses fonctionnalités.</t>
+          <t>WhatsApp spy - logs online/offline events from ANYONE in the world</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -18295,20 +18291,24 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>22-11-2025 00:54</t>
+          <t>19-11-2025 02:11</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>30-04-2025 19:02</t>
-        </is>
-      </c>
-      <c r="I407" t="inlineStr"/>
+          <t>14-11-2019 15:27</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>bot, logger, osint, python, selenium</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:08</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441440</v>
+        <v>441444</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416611</v>
+        <v>416613</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:01</t>
+          <t>22-11-2025 04:13</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379993</v>
+        <v>379995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270459</v>
+        <v>270460</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 03:54</t>
+          <t>22-11-2025 04:07</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250558</v>
+        <v>250559</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198027</v>
+        <v>198028</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22-11-2025 03:07</t>
+          <t>22-11-2025 04:13</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157868</v>
+        <v>157869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 03:52</t>
+          <t>22-11-2025 04:07</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157011</v>
+        <v>157014</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 04:01</t>
+          <t>22-11-2025 04:16</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135874</v>
+        <v>135875</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:15</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1212,11 +1212,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115729</v>
+        <v>115730</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22-11-2025 03:17</t>
+          <t>22-11-2025 04:13</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115450</v>
+        <v>115451</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 03:57</t>
+          <t>22-11-2025 04:11</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102437</v>
+        <v>102439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 03:48</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93784</v>
+        <v>93785</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22-11-2025 03:41</t>
+          <t>22-11-2025 04:04</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84712</v>
+        <v>84713</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 03:43</t>
+          <t>22-11-2025 04:04</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83948</v>
+        <v>83950</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 03:50</t>
+          <t>22-11-2025 04:14</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>78750</v>
+        <v>78751</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22-11-2025 02:49</t>
+          <t>22-11-2025 04:14</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75896</v>
+        <v>75897</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 03:51</t>
+          <t>22-11-2025 04:08</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>58960</v>
+        <v>58961</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22-11-2025 03:53</t>
+          <t>22-11-2025 04:05</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53638</v>
+        <v>53639</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>22-11-2025 03:47</t>
+          <t>22-11-2025 04:16</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51323</v>
+        <v>51324</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22-11-2025 03:58</t>
+          <t>22-11-2025 04:12</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22-11-2025 03:22</t>
+          <t>22-11-2025 04:02</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47433</v>
+        <v>47435</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22-11-2025 03:29</t>
+          <t>22-11-2025 04:13</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44406</v>
+        <v>44407</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22-11-2025 03:50</t>
+          <t>22-11-2025 04:07</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43205</v>
+        <v>43207</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 03:57</t>
+          <t>22-11-2025 04:09</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>22-11-2025 03:40</t>
+          <t>22-11-2025 04:09</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>35656</v>
+        <v>35658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>22-11-2025 03:27</t>
+          <t>22-11-2025 04:17</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31440</v>
+        <v>31441</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 04:01</t>
+          <t>22-11-2025 04:06</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>26072</v>
+        <v>26073</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>22-11-2025 03:05</t>
+          <t>22-11-2025 04:13</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25586</v>
+        <v>25587</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>22-11-2025 03:31</t>
+          <t>22-11-2025 04:12</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22312</v>
+        <v>22314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:10</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>22124</v>
+        <v>22126</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>22-11-2025 03:11</t>
+          <t>22-11-2025 04:17</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>22-11-2025 01:56</t>
+          <t>22-11-2025 04:11</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18612</v>
+        <v>18611</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 03:34</t>
+          <t>22-11-2025 04:14</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>17276</v>
+        <v>17277</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>22-11-2025 03:26</t>
+          <t>22-11-2025 04:11</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6812,11 +6812,11 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>15920</v>
+        <v>15923</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>22-11-2025 03:28</t>
+          <t>22-11-2025 04:08</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15113</v>
+        <v>15115</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 03:53</t>
+          <t>22-11-2025 04:15</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13020</v>
+        <v>13024</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:13</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>9710</v>
+        <v>9709</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>22-11-2025 02:21</t>
+          <t>22-11-2025 04:15</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>8977</v>
+        <v>8978</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:14</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7988</v>
+        <v>7989</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>22-11-2025 02:17</t>
+          <t>22-11-2025 04:14</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4871</v>
+        <v>4873</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>21-11-2025 22:47</t>
+          <t>22-11-2025 04:14</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>21-11-2025 07:51</t>
+          <t>22-11-2025 04:09</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:10</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441444</v>
+        <v>441445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:12</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379995</v>
+        <v>379996</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195122</v>
+        <v>195123</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157014</v>
+        <v>157015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 04:16</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135875</v>
+        <v>135876</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 04:15</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83950</v>
+        <v>83951</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:14</t>
+          <t>22-11-2025 04:19</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75897</v>
+        <v>75898</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 04:08</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68287</v>
+        <v>68288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22-11-2025 03:50</t>
+          <t>22-11-2025 04:19</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43207</v>
+        <v>43208</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 04:09</t>
+          <t>22-11-2025 04:19</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>20583</v>
+        <v>20584</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>21-11-2025 22:21</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 04:14</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>16329</v>
+        <v>16330</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>22-11-2025 03:18</t>
+          <t>22-11-2025 04:19</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13543</v>
+        <v>13544</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>22-11-2025 03:21</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>9708</v>
+        <v>9709</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>22-11-2025 01:37</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -18593,11 +18593,11 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>22-11-2025 02:52</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441445</v>
+        <v>441448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:20</t>
+          <t>22-11-2025 04:25</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416613</v>
+        <v>416614</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:13</t>
+          <t>22-11-2025 04:24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250559</v>
+        <v>250558</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 04:23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157869</v>
+        <v>157870</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 04:07</t>
+          <t>22-11-2025 04:25</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115894</v>
+        <v>115895</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115451</v>
+        <v>115453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 04:11</t>
+          <t>22-11-2025 04:25</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88185</v>
+        <v>88186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22-11-2025 01:30</t>
+          <t>22-11-2025 04:21</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83951</v>
+        <v>83952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:19</t>
+          <t>22-11-2025 04:25</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83196</v>
+        <v>83197</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22-11-2025 03:57</t>
+          <t>22-11-2025 04:21</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68288</v>
+        <v>68290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22-11-2025 04:19</t>
+          <t>22-11-2025 04:25</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>67932</v>
+        <v>67933</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22-11-2025 03:20</t>
+          <t>22-11-2025 04:23</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2137,11 +2137,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>66813</v>
+        <v>66814</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22-11-2025 03:22</t>
+          <t>22-11-2025 04:23</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>58961</v>
+        <v>58962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22-11-2025 04:05</t>
+          <t>22-11-2025 04:25</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47893</v>
+        <v>47892</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22-11-2025 02:10</t>
+          <t>22-11-2025 04:23</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43208</v>
+        <v>43209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 04:19</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43133</v>
+        <v>43134</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22-11-2025 03:58</t>
+          <t>22-11-2025 04:21</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42968</v>
+        <v>42969</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>22-11-2025 03:35</t>
+          <t>22-11-2025 04:22</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26858</v>
+        <v>26859</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>22-11-2025 01:15</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25587</v>
+        <v>25588</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>22-11-2025 04:12</t>
+          <t>22-11-2025 04:21</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>11510</v>
+        <v>11511</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>22-11-2025 03:33</t>
+          <t>22-11-2025 04:24</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7989</v>
+        <v>7990</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>22-11-2025 04:14</t>
+          <t>22-11-2025 04:22</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -11956,7 +11956,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4952</v>
+        <v>4953</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>22-11-2025 03:46</t>
+          <t>22-11-2025 04:21</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 04:10</t>
+          <t>22-11-2025 04:25</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441444</v>
+        <v>441452</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:12</t>
+          <t>22-11-2025 04:36</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416613</v>
+        <v>416617</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:13</t>
+          <t>22-11-2025 04:37</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>379995</v>
+        <v>380000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 04:34</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270460</v>
+        <v>270463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 04:07</t>
+          <t>22-11-2025 04:36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259310</v>
+        <v>259313</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250559</v>
+        <v>250560</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 04:37</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198028</v>
+        <v>198029</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22-11-2025 04:13</t>
+          <t>22-11-2025 04:38</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195122</v>
+        <v>195125</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:37</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>182891</v>
+        <v>182892</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22-11-2025 02:20</t>
+          <t>22-11-2025 04:30</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157869</v>
+        <v>157872</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 04:07</t>
+          <t>22-11-2025 04:31</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157014</v>
+        <v>157019</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 04:16</t>
+          <t>22-11-2025 04:33</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135875</v>
+        <v>135876</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 04:15</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115894</v>
+        <v>115895</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115451</v>
+        <v>115454</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 04:11</t>
+          <t>22-11-2025 04:35</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102870</v>
+        <v>102871</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22-11-2025 03:22</t>
+          <t>22-11-2025 04:36</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102439</v>
+        <v>102443</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 04:37</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93785</v>
+        <v>93786</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22-11-2025 04:04</t>
+          <t>22-11-2025 04:28</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>92145</v>
+        <v>92146</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22-11-2025 02:48</t>
+          <t>22-11-2025 04:35</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88185</v>
+        <v>88187</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22-11-2025 01:30</t>
+          <t>22-11-2025 04:38</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84713</v>
+        <v>84714</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 04:04</t>
+          <t>22-11-2025 04:29</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83950</v>
+        <v>83955</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:14</t>
+          <t>22-11-2025 04:31</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83196</v>
+        <v>83197</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22-11-2025 03:57</t>
+          <t>22-11-2025 04:21</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>78751</v>
+        <v>78752</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22-11-2025 04:14</t>
+          <t>22-11-2025 04:33</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75897</v>
+        <v>75898</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 04:08</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>70465</v>
+        <v>70466</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22-11-2025 03:15</t>
+          <t>22-11-2025 04:38</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68287</v>
+        <v>68291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22-11-2025 03:50</t>
+          <t>22-11-2025 04:32</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>67932</v>
+        <v>67933</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22-11-2025 03:20</t>
+          <t>22-11-2025 04:23</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2137,11 +2137,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>66813</v>
+        <v>66814</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22-11-2025 03:22</t>
+          <t>22-11-2025 04:23</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>58961</v>
+        <v>58962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22-11-2025 04:05</t>
+          <t>22-11-2025 04:25</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2523,11 +2523,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53610</v>
+        <v>53611</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>22-11-2025 02:22</t>
+          <t>22-11-2025 04:31</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51324</v>
+        <v>51325</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22-11-2025 04:12</t>
+          <t>22-11-2025 04:26</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47893</v>
+        <v>47892</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22-11-2025 02:10</t>
+          <t>22-11-2025 04:23</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47565</v>
+        <v>47566</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22-11-2025 03:54</t>
+          <t>22-11-2025 04:30</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>22-11-2025 03:50</t>
+          <t>22-11-2025 04:38</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43207</v>
+        <v>43209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 04:09</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43133</v>
+        <v>43134</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22-11-2025 03:58</t>
+          <t>22-11-2025 04:21</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42968</v>
+        <v>42969</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>22-11-2025 03:35</t>
+          <t>22-11-2025 04:22</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3301,11 +3301,11 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>40991</v>
+        <v>40992</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22-11-2025 03:36</t>
+          <t>22-11-2025 04:32</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>38977</v>
+        <v>38978</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>22-11-2025 03:20</t>
+          <t>22-11-2025 04:32</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>36934</v>
+        <v>36935</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>22-11-2025 03:39</t>
+          <t>22-11-2025 04:26</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>34231</v>
+        <v>34232</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>22-11-2025 03:54</t>
+          <t>22-11-2025 04:36</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31852</v>
+        <v>31853</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>22-11-2025 03:31</t>
+          <t>22-11-2025 04:36</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31441</v>
+        <v>31442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 04:06</t>
+          <t>22-11-2025 04:32</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>29825</v>
+        <v>29826</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>21-11-2025 23:19</t>
+          <t>22-11-2025 04:35</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4487,11 +4487,11 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>28463</v>
+        <v>28464</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>21-11-2025 23:02</t>
+          <t>22-11-2025 04:33</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>28093</v>
+        <v>28094</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>22-11-2025 03:47</t>
+          <t>22-11-2025 04:38</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26858</v>
+        <v>26860</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>22-11-2025 01:15</t>
+          <t>22-11-2025 04:35</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25587</v>
+        <v>25588</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>22-11-2025 04:12</t>
+          <t>22-11-2025 04:21</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>22126</v>
+        <v>22127</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>22-11-2025 04:17</t>
+          <t>22-11-2025 04:35</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>21404</v>
+        <v>21405</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>22-11-2025 03:27</t>
+          <t>22-11-2025 04:35</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>21059</v>
+        <v>21060</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>21-11-2025 16:43</t>
+          <t>22-11-2025 04:28</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>20685</v>
+        <v>20686</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>22-11-2025 03:41</t>
+          <t>22-11-2025 04:35</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>20583</v>
+        <v>20584</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>21-11-2025 22:21</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 04:14</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>21-11-2025 19:42</t>
+          <t>22-11-2025 04:34</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17631</v>
+        <v>17632</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22-11-2025 02:33</t>
+          <t>22-11-2025 04:28</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>16329</v>
+        <v>16330</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>22-11-2025 03:18</t>
+          <t>22-11-2025 04:19</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15662</v>
+        <v>15663</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22-11-2025 04:00</t>
+          <t>22-11-2025 04:37</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15115</v>
+        <v>15117</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 04:15</t>
+          <t>22-11-2025 04:32</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>14743</v>
+        <v>14742</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>21-11-2025 14:54</t>
+          <t>22-11-2025 04:36</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13543</v>
+        <v>13544</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>22-11-2025 03:21</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13024</v>
+        <v>13026</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 04:13</t>
+          <t>22-11-2025 04:34</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8527,11 +8527,11 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>12246</v>
+        <v>12247</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>21-11-2025 14:14</t>
+          <t>22-11-2025 04:31</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>11510</v>
+        <v>11511</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>22-11-2025 03:33</t>
+          <t>22-11-2025 04:24</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>9708</v>
+        <v>9709</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>22-11-2025 01:37</t>
+          <t>22-11-2025 04:18</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>9222</v>
+        <v>9223</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>22-11-2025 02:49</t>
+          <t>22-11-2025 04:33</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7989</v>
+        <v>7991</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>22-11-2025 04:14</t>
+          <t>22-11-2025 04:38</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10849,7 +10849,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6655</v>
+        <v>6656</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>21-11-2025 23:41</t>
+          <t>22-11-2025 04:38</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -11551,7 +11551,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5485</v>
+        <v>5486</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>22-11-2025 03:51</t>
+          <t>22-11-2025 04:37</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11956,7 +11956,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4952</v>
+        <v>4953</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>22-11-2025 03:46</t>
+          <t>22-11-2025 04:21</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -13411,7 +13411,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>22-11-2025 03:40</t>
+          <t>22-11-2025 04:31</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -14078,11 +14078,11 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>22-11-2025 03:55</t>
+          <t>22-11-2025 04:27</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -15045,7 +15045,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>22-11-2025 03:06</t>
+          <t>22-11-2025 04:29</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -16932,7 +16932,7 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>19-11-2025 10:34</t>
+          <t>22-11-2025 04:31</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -18593,11 +18593,11 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>22-11-2025 02:52</t>
+          <t>22-11-2025 04:20</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>22-11-2025 03:23</t>
+          <t>22-11-2025 04:32</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 04:10</t>
+          <t>22-11-2025 04:25</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>380000</v>
+        <v>380001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 04:34</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259313</v>
+        <v>259314</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 04:30</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 04:31</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135876</v>
+        <v>135877</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 04:20</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93786</v>
+        <v>93787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22-11-2025 04:28</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:31</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>22-11-2025 03:47</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15117</v>
+        <v>15118</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 04:32</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>9223</v>
+        <v>9224</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>22-11-2025 04:33</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -10849,7 +10849,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6656</v>
+        <v>6657</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>22-11-2025 04:38</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 04:25</t>
+          <t>22-11-2025 04:39</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441452</v>
+        <v>441453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:36</t>
+          <t>22-11-2025 04:41</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195125</v>
+        <v>195126</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 04:37</t>
+          <t>22-11-2025 04:40</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157872</v>
+        <v>157871</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 04:41</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131400</v>
+        <v>131401</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22-11-2025 03:43</t>
+          <t>22-11-2025 04:42</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115454</v>
+        <v>115455</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 04:35</t>
+          <t>22-11-2025 04:40</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84714</v>
+        <v>84715</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 04:29</t>
+          <t>22-11-2025 04:41</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83955</v>
+        <v>83954</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 04:41</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75898</v>
+        <v>75897</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 04:20</t>
+          <t>22-11-2025 04:42</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2137,11 +2137,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>66814</v>
+        <v>66813</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22-11-2025 04:23</t>
+          <t>22-11-2025 04:42</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2222,11 +2222,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>63777</v>
+        <v>63776</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21-11-2025 23:41</t>
+          <t>22-11-2025 04:42</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47435</v>
+        <v>47436</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22-11-2025 04:13</t>
+          <t>22-11-2025 04:41</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44407</v>
+        <v>44408</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22-11-2025 04:07</t>
+          <t>22-11-2025 04:41</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3836,11 +3836,11 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34591</v>
+        <v>34592</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>22-11-2025 02:01</t>
+          <t>22-11-2025 04:42</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>34503</v>
+        <v>34502</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>22-11-2025 03:52</t>
+          <t>22-11-2025 04:41</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>19060</v>
+        <v>19061</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>22-11-2025 04:11</t>
+          <t>22-11-2025 04:40</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 04:41</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>8942</v>
+        <v>8943</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>22-11-2025 01:25</t>
+          <t>22-11-2025 04:42</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13951,7 +13951,7 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>3043</v>
+        <v>3044</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>21-11-2025 20:50</t>
+          <t>22-11-2025 04:41</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 04:40</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441453</v>
+        <v>441456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:41</t>
+          <t>22-11-2025 04:44</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>380001</v>
+        <v>380002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 04:44</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270463</v>
+        <v>270462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 04:36</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259314</v>
+        <v>259313</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195126</v>
+        <v>195125</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 04:40</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157871</v>
+        <v>157872</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 04:41</t>
+          <t>22-11-2025 04:42</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>136764</v>
+        <v>136765</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22-11-2025 03:31</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115455</v>
+        <v>115456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 04:40</t>
+          <t>22-11-2025 04:44</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101008</v>
+        <v>101007</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22-11-2025 03:53</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2523,11 +2523,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53611</v>
+        <v>53610</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>22-11-2025 04:31</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>22-11-2025 04:38</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>42511</v>
+        <v>42510</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>22-11-2025 03:35</t>
+          <t>22-11-2025 04:44</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5184,11 +5184,11 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>24537</v>
+        <v>24536</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>22-11-2025 02:53</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>22-11-2025 04:34</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17632</v>
+        <v>17631</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22-11-2025 04:28</t>
+          <t>22-11-2025 04:44</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>17446</v>
+        <v>17445</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>22-11-2025 03:52</t>
+          <t>22-11-2025 04:44</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13026</v>
+        <v>13028</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 04:34</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>22-11-2025 04:27</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>21-11-2025 18:16</t>
+          <t>22-11-2025 04:44</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -18593,11 +18593,11 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>22-11-2025 04:20</t>
+          <t>22-11-2025 04:43</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441456</v>
+        <v>441458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:44</t>
+          <t>22-11-2025 04:50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416617</v>
+        <v>416618</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:37</t>
+          <t>22-11-2025 04:51</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>380002</v>
+        <v>380003</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 04:44</t>
+          <t>22-11-2025 04:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270462</v>
+        <v>270465</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 04:50</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157872</v>
+        <v>157875</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 04:42</t>
+          <t>22-11-2025 04:49</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>136765</v>
+        <v>136766</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 04:47</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135877</v>
+        <v>135876</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 04:46</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131401</v>
+        <v>131402</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22-11-2025 04:42</t>
+          <t>22-11-2025 04:45</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115895</v>
+        <v>115896</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22-11-2025 04:20</t>
+          <t>22-11-2025 04:46</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115456</v>
+        <v>115457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101007</v>
+        <v>101008</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 04:45</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>86470</v>
+        <v>86471</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22-11-2025 04:01</t>
+          <t>22-11-2025 04:45</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84715</v>
+        <v>84717</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 04:41</t>
+          <t>22-11-2025 04:46</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83954</v>
+        <v>83956</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:41</t>
+          <t>22-11-2025 04:46</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>79933</v>
+        <v>79934</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22-11-2025 03:35</t>
+          <t>22-11-2025 04:47</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>79376</v>
+        <v>79377</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22-11-2025 03:42</t>
+          <t>22-11-2025 04:49</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75897</v>
+        <v>75898</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 04:42</t>
+          <t>22-11-2025 04:47</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22-11-2025 04:32</t>
+          <t>22-11-2025 04:49</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47436</v>
+        <v>47437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22-11-2025 04:41</t>
+          <t>22-11-2025 04:49</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37383</v>
+        <v>37384</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>22-11-2025 04:09</t>
+          <t>22-11-2025 04:51</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>9946</v>
+        <v>9947</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>22-11-2025 03:45</t>
+          <t>22-11-2025 04:49</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7991</v>
+        <v>7993</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>22-11-2025 04:38</t>
+          <t>22-11-2025 04:49</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>22-11-2025 04:32</t>
+          <t>22-11-2025 04:47</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416618</v>
+        <v>416619</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:51</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270465</v>
+        <v>270464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 04:50</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102443</v>
+        <v>102442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 04:37</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93787</v>
+        <v>93788</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84717</v>
+        <v>84718</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 04:46</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83956</v>
+        <v>83957</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:46</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>79377</v>
+        <v>79378</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22-11-2025 04:49</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56211</v>
+        <v>56212</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22-11-2025 03:33</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53639</v>
+        <v>53640</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>22-11-2025 04:16</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43209</v>
+        <v>43211</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 04:20</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>22127</v>
+        <v>22128</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>22-11-2025 04:35</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>16330</v>
+        <v>16331</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>22-11-2025 04:19</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -12001,11 +12001,11 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4948</v>
+        <v>4949</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>22-11-2025 04:01</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441458</v>
+        <v>441459</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:50</t>
+          <t>22-11-2025 04:53</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416619</v>
+        <v>416620</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 04:53</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102442</v>
+        <v>102443</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83957</v>
+        <v>83958</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 04:53</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>76999</v>
+        <v>77000</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22-11-2025 02:11</t>
+          <t>22-11-2025 04:53</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22314</v>
+        <v>22315</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>22-11-2025 04:10</t>
+          <t>22-11-2025 04:53</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13544</v>
+        <v>13545</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>22-11-2025 04:18</t>
+          <t>22-11-2025 04:52</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441459</v>
+        <v>441460</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:53</t>
+          <t>22-11-2025 04:56</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416620</v>
+        <v>416621</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:53</t>
+          <t>22-11-2025 04:55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>380003</v>
+        <v>380005</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 04:45</t>
+          <t>22-11-2025 04:55</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270464</v>
+        <v>270466</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 04:55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259313</v>
+        <v>259315</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 04:55</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195125</v>
+        <v>195126</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 04:56</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115457</v>
+        <v>115458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 04:44</t>
+          <t>22-11-2025 04:55</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>67933</v>
+        <v>67932</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22-11-2025 04:23</t>
+          <t>22-11-2025 04:56</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4177,11 +4177,11 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>31818</v>
+        <v>31819</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>22-11-2025 02:49</t>
+          <t>22-11-2025 04:55</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18611</v>
+        <v>18612</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 04:18</t>
+          <t>22-11-2025 04:54</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17631</v>
+        <v>17632</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22-11-2025 04:44</t>
+          <t>22-11-2025 04:54</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15744</v>
+        <v>15745</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>22-11-2025 03:10</t>
+          <t>22-11-2025 04:54</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>10849</v>
+        <v>10850</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>22-11-2025 02:24</t>
+          <t>22-11-2025 04:55</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12626,7 +12626,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4272</v>
+        <v>4273</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>21-11-2025 22:33</t>
+          <t>22-11-2025 04:55</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -13411,7 +13411,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>22-11-2025 04:31</t>
+          <t>22-11-2025 04:56</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>22-11-2025 04:47</t>
+          <t>22-11-2025 04:54</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 04:40</t>
+          <t>22-11-2025 04:55</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441460</v>
+        <v>441462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 04:56</t>
+          <t>22-11-2025 05:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270466</v>
+        <v>270468</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259315</v>
+        <v>259316</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 04:57</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250560</v>
+        <v>250561</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 04:37</t>
+          <t>22-11-2025 05:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198029</v>
+        <v>198030</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22-11-2025 04:38</t>
+          <t>22-11-2025 04:57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131402</v>
+        <v>131403</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22-11-2025 04:45</t>
+          <t>22-11-2025 04:56</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56212</v>
+        <v>56213</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 04:57</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51325</v>
+        <v>51326</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22-11-2025 04:26</t>
+          <t>22-11-2025 04:59</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22-11-2025 04:41</t>
+          <t>22-11-2025 04:59</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43211</v>
+        <v>43212</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 04:57</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>21908</v>
+        <v>21909</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>22-11-2025 03:22</t>
+          <t>22-11-2025 04:58</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18612</v>
+        <v>18613</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 04:54</t>
+          <t>22-11-2025 04:58</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13028</v>
+        <v>13029</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 04:58</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9431,67 +9431,63 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>bytebot-ai/bytebot</t>
+          <t>BeehiveInnovations/zen-mcp-server</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://github.com/bytebot-ai/bytebot</t>
+          <t>https://github.com/BeehiveInnovations/zen-mcp-server</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Bytebot is a self-hosted AI desktop agent that automates computer tasks through natural language commands, operating within a containerized Linux desktop environment.</t>
+          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>9709</v>
+        <v>9710</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>22-11-2025 04:15</t>
+          <t>22-11-2025 04:58</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>03-02-2025 18:18</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>agent, agentic-ai, agents, ai, ai-agents</t>
-        </is>
-      </c>
+          <t>08-06-2025 15:36</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BeehiveInnovations/zen-mcp-server</t>
+          <t>bytebot-ai/bytebot</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://github.com/BeehiveInnovations/zen-mcp-server</t>
+          <t>https://github.com/bytebot-ai/bytebot</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
+          <t>Bytebot is a self-hosted AI desktop agent that automates computer tasks through natural language commands, operating within a containerized Linux desktop environment.</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -9499,20 +9495,24 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>22-11-2025 04:18</t>
+          <t>22-11-2025 04:15</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>08-06-2025 15:36</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>03-02-2025 18:18</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>agent, agentic-ai, agents, ai, ai-agents</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>7405</v>
+        <v>7406</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>22-11-2025 03:31</t>
+          <t>22-11-2025 04:57</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3635</v>
+        <v>3636</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>22-11-2025 03:33</t>
+          <t>22-11-2025 04:57</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>22-11-2025 03:31</t>
+          <t>22-11-2025 04:57</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157019</v>
+        <v>157020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 04:33</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115458</v>
+        <v>115460</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102443</v>
+        <v>102444</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84718</v>
+        <v>84719</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>39214</v>
+        <v>39215</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22-11-2025 03:31</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>21-11-2025 23:31</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>7406</v>
+        <v>7407</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3636</v>
+        <v>3637</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -16271,7 +16271,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>21-11-2025 21:14</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 05:00</t>
+          <t>22-11-2025 05:06</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416621</v>
+        <v>416622</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270468</v>
+        <v>270470</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 05:01</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259316</v>
+        <v>259317</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:02</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250561</v>
+        <v>250562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 05:00</t>
+          <t>22-11-2025 05:04</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135876</v>
+        <v>135877</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 04:46</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115460</v>
+        <v>115462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 05:01</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68291</v>
+        <v>68290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22-11-2025 04:49</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56213</v>
+        <v>56214</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:03</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15663</v>
+        <v>15664</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22-11-2025 04:37</t>
+          <t>22-11-2025 05:03</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15118</v>
+        <v>15121</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 05:04</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8316,11 +8316,11 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>12872</v>
+        <v>12873</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>21-11-2025 21:42</t>
+          <t>22-11-2025 05:03</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>8978</v>
+        <v>8979</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>22-11-2025 04:14</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>22-11-2025 03:57</t>
+          <t>22-11-2025 05:03</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>22-11-2025 01:47</t>
+          <t>22-11-2025 05:04</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -20822,7 +20822,7 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>21-11-2025 21:10</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441462</v>
+        <v>441464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 05:00</t>
+          <t>22-11-2025 05:07</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416621</v>
+        <v>416625</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 05:10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270468</v>
+        <v>270473</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 05:01</t>
+          <t>22-11-2025 05:12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259316</v>
+        <v>259317</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:02</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250561</v>
+        <v>250562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 05:00</t>
+          <t>22-11-2025 05:04</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195126</v>
+        <v>195127</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 04:56</t>
+          <t>22-11-2025 05:08</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157875</v>
+        <v>157876</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 04:49</t>
+          <t>22-11-2025 05:08</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157019</v>
+        <v>157021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 04:33</t>
+          <t>22-11-2025 05:11</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22-11-2025 04:47</t>
+          <t>22-11-2025 05:07</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135876</v>
+        <v>135877</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 04:46</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125896</v>
+        <v>125897</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 05:12</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115896</v>
+        <v>115897</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22-11-2025 04:46</t>
+          <t>22-11-2025 05:10</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115458</v>
+        <v>115463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 05:11</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:08</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84718</v>
+        <v>84719</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>79378</v>
+        <v>79379</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:09</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68291</v>
+        <v>68290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22-11-2025 04:49</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22-11-2025 04:56</t>
+          <t>22-11-2025 05:09</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56213</v>
+        <v>56214</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:03</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43134</v>
+        <v>43135</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22-11-2025 04:21</t>
+          <t>22-11-2025 05:07</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>39416</v>
+        <v>39417</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>22-11-2025 03:08</t>
+          <t>22-11-2025 05:11</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>39214</v>
+        <v>39215</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22-11-2025 03:31</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>35658</v>
+        <v>35657</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>22-11-2025 04:17</t>
+          <t>22-11-2025 05:12</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28897</v>
+        <v>28898</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>22-11-2025 01:40</t>
+          <t>22-11-2025 05:08</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>17445</v>
+        <v>17446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>22-11-2025 04:44</t>
+          <t>22-11-2025 05:11</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15663</v>
+        <v>15664</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22-11-2025 04:37</t>
+          <t>22-11-2025 05:03</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15118</v>
+        <v>15123</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 05:12</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>14676</v>
+        <v>14677</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>22-11-2025 01:33</t>
+          <t>22-11-2025 05:09</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13545</v>
+        <v>13546</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:10</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8316,11 +8316,11 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>12872</v>
+        <v>12873</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>21-11-2025 21:42</t>
+          <t>22-11-2025 05:03</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>9947</v>
+        <v>9948</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>22-11-2025 04:49</t>
+          <t>22-11-2025 05:09</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>8978</v>
+        <v>8979</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>22-11-2025 04:14</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>21-11-2025 23:31</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>7406</v>
+        <v>7407</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3636</v>
+        <v>3637</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>22-11-2025 03:57</t>
+          <t>22-11-2025 05:03</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -13771,7 +13771,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>21-11-2025 23:17</t>
+          <t>22-11-2025 05:12</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>21-11-2025 22:55</t>
+          <t>22-11-2025 05:10</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -16271,7 +16271,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>21-11-2025 21:14</t>
+          <t>22-11-2025 05:01</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>22-11-2025 01:47</t>
+          <t>22-11-2025 05:04</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -20385,7 +20385,7 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>21-11-2025 18:01</t>
+          <t>22-11-2025 05:10</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -20822,7 +20822,7 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>21-11-2025 21:10</t>
+          <t>22-11-2025 05:05</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 05:11</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416625</v>
+        <v>416626</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 05:10</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>380005</v>
+        <v>380006</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 05:15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259317</v>
+        <v>259318</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 05:02</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195127</v>
+        <v>195128</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 05:08</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115463</v>
+        <v>115464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 05:11</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47892</v>
+        <v>47893</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22-11-2025 04:23</t>
+          <t>22-11-2025 05:13</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47437</v>
+        <v>47438</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22-11-2025 04:49</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43212</v>
+        <v>43213</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43135</v>
+        <v>43136</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22-11-2025 05:07</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42969</v>
+        <v>42970</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>22-11-2025 04:22</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37384</v>
+        <v>37385</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>22-11-2025 04:51</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31442</v>
+        <v>31443</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 04:32</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28898</v>
+        <v>28899</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>22-11-2025 05:08</t>
+          <t>22-11-2025 05:13</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>23142</v>
+        <v>23143</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>22-11-2025 02:02</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18613</v>
+        <v>18612</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 04:58</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>17277</v>
+        <v>17278</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>22-11-2025 04:11</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>16331</v>
+        <v>16332</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:15</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15123</v>
+        <v>15124</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 05:12</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13029</v>
+        <v>13030</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 04:58</t>
+          <t>22-11-2025 05:15</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9431,22 +9431,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BeehiveInnovations/zen-mcp-server</t>
+          <t>bytebot-ai/bytebot</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://github.com/BeehiveInnovations/zen-mcp-server</t>
+          <t>https://github.com/bytebot-ai/bytebot</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
+          <t>Bytebot is a self-hosted AI desktop agent that automates computer tasks through natural language commands, operating within a containerized Linux desktop environment.</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -9454,65 +9454,65 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>22-11-2025 04:58</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>08-06-2025 15:36</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
+          <t>03-02-2025 18:18</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>agent, agentic-ai, agents, ai, ai-agents</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>bytebot-ai/bytebot</t>
+          <t>BeehiveInnovations/zen-mcp-server</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://github.com/bytebot-ai/bytebot</t>
+          <t>https://github.com/BeehiveInnovations/zen-mcp-server</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Bytebot is a self-hosted AI desktop agent that automates computer tasks through natural language commands, operating within a containerized Linux desktop environment.</t>
+          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>9709</v>
+        <v>9710</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>22-11-2025 04:15</t>
+          <t>22-11-2025 04:58</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>03-02-2025 18:18</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>agent, agentic-ai, agents, ai, ai-agents</t>
-        </is>
-      </c>
+          <t>08-06-2025 15:36</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>9127</v>
+        <v>9128</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>22-11-2025 02:49</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>8672</v>
+        <v>8673</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>22-11-2025 00:21</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>22-11-2025 05:03</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -15045,7 +15045,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>22-11-2025 04:29</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -15126,7 +15126,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>22-11-2025 01:58</t>
+          <t>22-11-2025 05:15</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>22-11-2025 04:54</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>22-11-2025 02:20</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441464</v>
+        <v>441467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 05:07</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>380006</v>
+        <v>380007</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 05:15</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198030</v>
+        <v>198029</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:20</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135877</v>
+        <v>135878</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 05:05</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88187</v>
+        <v>88188</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22-11-2025 04:38</t>
+          <t>22-11-2025 05:20</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83958</v>
+        <v>83959</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:53</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22-11-2025 05:09</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56214</v>
+        <v>56215</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22-11-2025 05:03</t>
+          <t>22-11-2025 05:18</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47438</v>
+        <v>47441</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22-11-2025 05:16</t>
+          <t>22-11-2025 05:23</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43213</v>
+        <v>43214</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 05:14</t>
+          <t>22-11-2025 05:18</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>34502</v>
+        <v>34503</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>22-11-2025 04:41</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31853</v>
+        <v>31854</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>22-11-2025 04:36</t>
+          <t>22-11-2025 05:19</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>29826</v>
+        <v>29827</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>22-11-2025 04:35</t>
+          <t>22-11-2025 05:19</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28899</v>
+        <v>28900</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>22-11-2025 05:13</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26860</v>
+        <v>26861</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>22-11-2025 04:35</t>
+          <t>22-11-2025 05:19</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>25056</v>
+        <v>25057</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>21-11-2025 23:10</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 05:14</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15664</v>
+        <v>15666</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22-11-2025 05:03</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 05:16</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>14864</v>
+        <v>14865</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>22-11-2025 01:19</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>13738</v>
+        <v>13739</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>22-11-2025 03:43</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13030</v>
+        <v>13031</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 05:15</t>
+          <t>22-11-2025 05:19</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6101</v>
+        <v>6102</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>21-11-2025 14:00</t>
+          <t>22-11-2025 05:20</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14429,11 +14429,11 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2824</v>
+        <v>2825</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>22-11-2025 03:56</t>
+          <t>22-11-2025 05:18</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19358,22 +19358,22 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>LLM-Red-Team/glm-free-api</t>
+          <t>raghavyuva/nixopus</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://github.com/LLM-Red-Team/glm-free-api</t>
+          <t>https://github.com/raghavyuva/nixopus</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>🚀 智谱清言ChatGLM-4-Plus大模型逆向API【特长：超强智能体】，支持高速流式输出、支持智能体对话、支持多轮对话、支持沉思模型、支持Zero思考推理模型、支持视频生成、支持AI绘图、支持联网搜索、支持长文档解读、支持代码调用、支持图像解析，零配置部署，多路token支持，自动清理会话痕迹，仅供测试，如需商用请前往官方开放平台。</t>
+          <t>Open Source Alternative to vercel, heroku, netlify with simplified workflows</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -19381,67 +19381,67 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>20-11-2025 15:00</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>17-03-2024 07:53</t>
+          <t>21-02-2025 11:17</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>chat-api, chatbot, chatglm-4, chatglm-api, deepresearch</t>
+          <t>ci-cd, coolify, deployment, file-manager, golang</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>raghavyuva/nixopus</t>
+          <t>LLM-Red-Team/glm-free-api</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://github.com/raghavyuva/nixopus</t>
+          <t>https://github.com/LLM-Red-Team/glm-free-api</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Open Source Alternative to vercel, heroku, netlify with simplified workflows</t>
+          <t>🚀 智谱清言ChatGLM-4-Plus大模型逆向API【特长：超强智能体】，支持高速流式输出、支持智能体对话、支持多轮对话、支持沉思模型、支持Zero思考推理模型、支持视频生成、支持AI绘图、支持联网搜索、支持长文档解读、支持代码调用、支持图像解析，零配置部署，多路token支持，自动清理会话痕迹，仅供测试，如需商用请前往官方开放平台。</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>22-11-2025 05:14</t>
+          <t>20-11-2025 15:00</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>21-02-2025 11:17</t>
+          <t>17-03-2024 07:53</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>ci-cd, coolify, deployment, file-manager, golang</t>
+          <t>chat-api, chatbot, chatglm-4, chatglm-api, deepresearch</t>
         </is>
       </c>
     </row>

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441464</v>
+        <v>441471</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 05:07</t>
+          <t>22-11-2025 05:28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416625</v>
+        <v>416626</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 05:10</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>380005</v>
+        <v>380007</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259317</v>
+        <v>259319</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 05:02</t>
+          <t>22-11-2025 05:25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198030</v>
+        <v>198029</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:20</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195127</v>
+        <v>195128</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 05:08</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157876</v>
+        <v>157877</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 05:08</t>
+          <t>22-11-2025 05:27</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135877</v>
+        <v>135878</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22-11-2025 05:05</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115463</v>
+        <v>115465</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 05:11</t>
+          <t>22-11-2025 05:24</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102871</v>
+        <v>102872</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22-11-2025 04:36</t>
+          <t>22-11-2025 05:26</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102443</v>
+        <v>102444</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 05:08</t>
+          <t>22-11-2025 05:23</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101008</v>
+        <v>101010</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22-11-2025 04:45</t>
+          <t>22-11-2025 05:25</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93788</v>
+        <v>93789</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:25</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88187</v>
+        <v>88188</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22-11-2025 04:38</t>
+          <t>22-11-2025 05:20</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83958</v>
+        <v>83960</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 04:53</t>
+          <t>22-11-2025 05:23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>79934</v>
+        <v>79935</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22-11-2025 04:47</t>
+          <t>22-11-2025 05:26</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22-11-2025 05:09</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56214</v>
+        <v>56215</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22-11-2025 05:03</t>
+          <t>22-11-2025 05:18</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53640</v>
+        <v>53641</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:28</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47892</v>
+        <v>47893</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22-11-2025 04:23</t>
+          <t>22-11-2025 05:13</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47437</v>
+        <v>47441</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22-11-2025 04:49</t>
+          <t>22-11-2025 05:23</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43212</v>
+        <v>43217</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 04:57</t>
+          <t>22-11-2025 05:27</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43135</v>
+        <v>43137</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22-11-2025 05:07</t>
+          <t>22-11-2025 05:28</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42969</v>
+        <v>42970</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>22-11-2025 04:22</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37384</v>
+        <v>37385</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>22-11-2025 04:51</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>36935</v>
+        <v>36936</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>22-11-2025 04:26</t>
+          <t>22-11-2025 05:27</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>35657</v>
+        <v>35658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>22-11-2025 05:12</t>
+          <t>22-11-2025 05:27</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>35499</v>
+        <v>35500</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>22-11-2025 02:40</t>
+          <t>22-11-2025 05:24</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>34502</v>
+        <v>34503</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>22-11-2025 04:41</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31853</v>
+        <v>31854</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>22-11-2025 04:36</t>
+          <t>22-11-2025 05:19</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31442</v>
+        <v>31443</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 04:32</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>29826</v>
+        <v>29827</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>22-11-2025 04:35</t>
+          <t>22-11-2025 05:19</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28898</v>
+        <v>28900</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>22-11-2025 05:08</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26860</v>
+        <v>26861</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>22-11-2025 04:35</t>
+          <t>22-11-2025 05:19</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>26089</v>
+        <v>26090</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>22-11-2025 00:31</t>
+          <t>22-11-2025 05:28</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>25056</v>
+        <v>25057</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>21-11-2025 23:10</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>23142</v>
+        <v>23143</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>22-11-2025 02:02</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22315</v>
+        <v>22316</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>22-11-2025 04:53</t>
+          <t>22-11-2025 05:25</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18613</v>
+        <v>18612</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 04:58</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>17277</v>
+        <v>17278</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>22-11-2025 04:11</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>16331</v>
+        <v>16332</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:15</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15664</v>
+        <v>15666</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22-11-2025 05:03</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15123</v>
+        <v>15124</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 05:12</t>
+          <t>22-11-2025 05:28</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>15040</v>
+        <v>15041</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>22-11-2025 03:21</t>
+          <t>22-11-2025 05:23</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>14864</v>
+        <v>14865</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>22-11-2025 01:19</t>
+          <t>22-11-2025 05:21</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>13738</v>
+        <v>13739</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>22-11-2025 03:43</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>13180</v>
+        <v>13181</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>22-11-2025 00:39</t>
+          <t>22-11-2025 05:23</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13029</v>
+        <v>13031</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 04:58</t>
+          <t>22-11-2025 05:19</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>12225</v>
+        <v>12226</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>22-11-2025 00:45</t>
+          <t>22-11-2025 05:24</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9431,22 +9431,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BeehiveInnovations/zen-mcp-server</t>
+          <t>bytebot-ai/bytebot</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://github.com/BeehiveInnovations/zen-mcp-server</t>
+          <t>https://github.com/bytebot-ai/bytebot</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
+          <t>Bytebot is a self-hosted AI desktop agent that automates computer tasks through natural language commands, operating within a containerized Linux desktop environment.</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -9454,65 +9454,65 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>22-11-2025 04:58</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>08-06-2025 15:36</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
+          <t>03-02-2025 18:18</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>agent, agentic-ai, agents, ai, ai-agents</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>bytebot-ai/bytebot</t>
+          <t>BeehiveInnovations/zen-mcp-server</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://github.com/bytebot-ai/bytebot</t>
+          <t>https://github.com/BeehiveInnovations/zen-mcp-server</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Bytebot is a self-hosted AI desktop agent that automates computer tasks through natural language commands, operating within a containerized Linux desktop environment.</t>
+          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>9709</v>
+        <v>9710</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>22-11-2025 04:15</t>
+          <t>22-11-2025 04:58</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>03-02-2025 18:18</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>agent, agentic-ai, agents, ai, ai-agents</t>
-        </is>
-      </c>
+          <t>08-06-2025 15:36</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>9127</v>
+        <v>9128</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>22-11-2025 02:49</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>8672</v>
+        <v>8673</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>22-11-2025 00:21</t>
+          <t>22-11-2025 05:17</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6101</v>
+        <v>6102</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>21-11-2025 14:00</t>
+          <t>22-11-2025 05:20</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -11821,7 +11821,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5082</v>
+        <v>5083</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>21-11-2025 22:10</t>
+          <t>22-11-2025 05:26</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -12266,7 +12266,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>4712</v>
+        <v>4713</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>21-11-2025 16:24</t>
+          <t>22-11-2025 05:27</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>22-11-2025 05:03</t>
+          <t>22-11-2025 05:14</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -13861,7 +13861,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>21-11-2025 22:42</t>
+          <t>22-11-2025 05:28</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>22-11-2025 04:52</t>
+          <t>22-11-2025 05:22</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14429,11 +14429,11 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2824</v>
+        <v>2825</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>22-11-2025 03:56</t>
+          <t>22-11-2025 05:18</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -15045,7 +15045,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>22-11-2025 04:29</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -15126,7 +15126,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>22-11-2025 01:58</t>
+          <t>22-11-2025 05:15</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -19358,90 +19358,90 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>LLM-Red-Team/glm-free-api</t>
+          <t>raghavyuva/nixopus</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://github.com/LLM-Red-Team/glm-free-api</t>
+          <t>https://github.com/raghavyuva/nixopus</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>🚀 智谱清言ChatGLM-4-Plus大模型逆向API【特长：超强智能体】，支持高速流式输出、支持智能体对话、支持多轮对话、支持沉思模型、支持Zero思考推理模型、支持视频生成、支持AI绘图、支持联网搜索、支持长文档解读、支持代码调用、支持图像解析，零配置部署，多路token支持，自动清理会话痕迹，仅供测试，如需商用请前往官方开放平台。</t>
+          <t>Open Source Alternative to vercel, heroku, netlify with simplified workflows</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>20-11-2025 15:00</t>
+          <t>22-11-2025 05:25</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>17-03-2024 07:53</t>
+          <t>21-02-2025 11:17</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>chat-api, chatbot, chatglm-4, chatglm-api, deepresearch</t>
+          <t>ci-cd, coolify, deployment, file-manager, golang</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>raghavyuva/nixopus</t>
+          <t>LLM-Red-Team/glm-free-api</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://github.com/raghavyuva/nixopus</t>
+          <t>https://github.com/LLM-Red-Team/glm-free-api</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Open Source Alternative to vercel, heroku, netlify with simplified workflows</t>
+          <t>🚀 智谱清言ChatGLM-4-Plus大模型逆向API【特长：超强智能体】，支持高速流式输出、支持智能体对话、支持多轮对话、支持沉思模型、支持Zero思考推理模型、支持视频生成、支持AI绘图、支持联网搜索、支持长文档解读、支持代码调用、支持图像解析，零配置部署，多路token支持，自动清理会话痕迹，仅供测试，如需商用请前往官方开放平台。</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>22-11-2025 04:54</t>
+          <t>20-11-2025 15:00</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>21-02-2025 11:17</t>
+          <t>17-03-2024 07:53</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>ci-cd, coolify, deployment, file-manager, golang</t>
+          <t>chat-api, chatbot, chatglm-4, chatglm-api, deepresearch</t>
         </is>
       </c>
     </row>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>22-11-2025 02:20</t>
+          <t>22-11-2025 05:16</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 05:11</t>
+          <t>22-11-2025 05:26</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441471</v>
+        <v>441473</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 05:28</t>
+          <t>22-11-2025 05:29</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157877</v>
+        <v>157878</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 05:27</t>
+          <t>22-11-2025 05:29</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42970</v>
+        <v>42971</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>22-11-2025 05:14</t>
+          <t>22-11-2025 05:29</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>8489</v>
+        <v>8490</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>22-11-2025 05:01</t>
+          <t>22-11-2025 05:30</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>441473</v>
+        <v>441487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22-11-2025 05:29</t>
+          <t>22-11-2025 06:14</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416626</v>
+        <v>416631</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-11-2025 05:16</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>380007</v>
+        <v>380008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22-11-2025 05:21</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>270473</v>
+        <v>270475</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-11-2025 05:12</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259319</v>
+        <v>259318</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-11-2025 05:25</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>250562</v>
+        <v>250565</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-11-2025 05:04</t>
+          <t>22-11-2025 06:05</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198029</v>
+        <v>198028</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22-11-2025 05:20</t>
+          <t>22-11-2025 06:13</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195128</v>
+        <v>195130</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-11-2025 05:17</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>157878</v>
+        <v>157883</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22-11-2025 05:29</t>
+          <t>22-11-2025 06:10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157021</v>
+        <v>157022</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22-11-2025 05:11</t>
+          <t>22-11-2025 06:09</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>125897</v>
+        <v>125898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22-11-2025 05:12</t>
+          <t>22-11-2025 05:53</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115897</v>
+        <v>115901</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22-11-2025 05:10</t>
+          <t>22-11-2025 06:07</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115465</v>
+        <v>115470</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-11-2025 05:24</t>
+          <t>22-11-2025 06:04</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102872</v>
+        <v>102873</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22-11-2025 05:26</t>
+          <t>22-11-2025 06:04</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102444</v>
+        <v>102452</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22-11-2025 05:23</t>
+          <t>22-11-2025 06:10</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101010</v>
+        <v>101009</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22-11-2025 05:25</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>93789</v>
+        <v>93790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22-11-2025 05:25</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>92146</v>
+        <v>92147</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22-11-2025 04:35</t>
+          <t>22-11-2025 06:06</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>84719</v>
+        <v>84721</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22-11-2025 05:01</t>
+          <t>22-11-2025 05:40</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>83960</v>
+        <v>83967</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22-11-2025 05:23</t>
+          <t>22-11-2025 06:07</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83197</v>
+        <v>83198</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22-11-2025 04:21</t>
+          <t>22-11-2025 06:07</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>79935</v>
+        <v>79936</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22-11-2025 05:26</t>
+          <t>22-11-2025 05:33</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>79379</v>
+        <v>79378</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22-11-2025 05:09</t>
+          <t>22-11-2025 06:04</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>78752</v>
+        <v>78753</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22-11-2025 04:33</t>
+          <t>22-11-2025 06:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75898</v>
+        <v>75900</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22-11-2025 04:47</t>
+          <t>22-11-2025 05:38</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>70466</v>
+        <v>70467</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22-11-2025 04:38</t>
+          <t>22-11-2025 05:53</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22-11-2025 05:05</t>
+          <t>22-11-2025 05:57</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22-11-2025 05:22</t>
+          <t>22-11-2025 06:13</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2137,11 +2137,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>66813</v>
+        <v>66812</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22-11-2025 04:42</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65563</v>
+        <v>65561</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22-11-2025 00:45</t>
+          <t>22-11-2025 06:06</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2222,11 +2222,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>63776</v>
+        <v>63775</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>22-11-2025 04:42</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>22-11-2025 03:21</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>58962</v>
+        <v>58964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22-11-2025 04:25</t>
+          <t>22-11-2025 05:47</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56215</v>
+        <v>56216</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22-11-2025 05:18</t>
+          <t>22-11-2025 06:04</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2523,11 +2523,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53610</v>
+        <v>53609</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51754</v>
+        <v>51753</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21-11-2025 21:10</t>
+          <t>22-11-2025 06:05</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51705</v>
+        <v>51706</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21-11-2025 21:09</t>
+          <t>22-11-2025 05:56</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51326</v>
+        <v>51327</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22-11-2025 04:59</t>
+          <t>22-11-2025 06:06</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47893</v>
+        <v>47896</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22-11-2025 05:13</t>
+          <t>22-11-2025 06:06</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47566</v>
+        <v>47567</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22-11-2025 04:30</t>
+          <t>22-11-2025 05:44</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2919,11 +2919,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>47498</v>
+        <v>47497</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>22-11-2025 03:37</t>
+          <t>22-11-2025 06:14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47441</v>
+        <v>47447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22-11-2025 05:23</t>
+          <t>22-11-2025 06:07</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>22-11-2025 03:59</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 05:54</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44408</v>
+        <v>44409</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22-11-2025 04:59</t>
+          <t>22-11-2025 06:04</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43217</v>
+        <v>43226</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22-11-2025 05:27</t>
+          <t>22-11-2025 06:14</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22-11-2025 05:28</t>
+          <t>22-11-2025 06:13</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3301,11 +3301,11 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>40992</v>
+        <v>40991</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22-11-2025 04:32</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>39115</v>
+        <v>39116</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22-11-2025 03:46</t>
+          <t>22-11-2025 06:06</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>38978</v>
+        <v>38979</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>22-11-2025 04:32</t>
+          <t>22-11-2025 05:55</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37385</v>
+        <v>37386</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>22-11-2025 05:17</t>
+          <t>22-11-2025 06:08</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3836,11 +3836,11 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34592</v>
+        <v>34591</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>22-11-2025 04:42</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>34232</v>
+        <v>34231</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>22-11-2025 04:36</t>
+          <t>22-11-2025 06:03</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>33423</v>
+        <v>33424</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>22-11-2025 03:28</t>
+          <t>22-11-2025 06:09</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4011,11 +4011,11 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>32698</v>
+        <v>32699</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>22-11-2025 03:44</t>
+          <t>22-11-2025 06:05</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31854</v>
+        <v>31855</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>22-11-2025 05:19</t>
+          <t>22-11-2025 05:42</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4177,11 +4177,11 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>31819</v>
+        <v>31818</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>22-11-2025 04:55</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31443</v>
+        <v>31445</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22-11-2025 05:14</t>
+          <t>22-11-2025 05:45</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>28900</v>
+        <v>28901</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>22-11-2025 05:17</t>
+          <t>22-11-2025 05:55</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4487,11 +4487,11 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>28464</v>
+        <v>28463</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>22-11-2025 04:33</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>28094</v>
+        <v>28095</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>22-11-2025 04:38</t>
+          <t>22-11-2025 06:13</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4662,11 +4662,11 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>27105</v>
+        <v>27104</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>22-11-2025 03:28</t>
+          <t>22-11-2025 06:12</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>27063</v>
+        <v>27065</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>22-11-2025 02:26</t>
+          <t>22-11-2025 06:05</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26861</v>
+        <v>26862</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>22-11-2025 05:19</t>
+          <t>22-11-2025 05:41</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25588</v>
+        <v>25589</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>22-11-2025 04:21</t>
+          <t>22-11-2025 05:32</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5184,11 +5184,11 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>24536</v>
+        <v>24535</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>22-11-2025 04:43</t>
+          <t>22-11-2025 06:13</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>22-11-2025 00:31</t>
+          <t>22-11-2025 05:35</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>23143</v>
+        <v>23142</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>22-11-2025 05:17</t>
+          <t>22-11-2025 06:13</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22316</v>
+        <v>22319</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>22-11-2025 05:25</t>
+          <t>22-11-2025 06:09</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>21915</v>
+        <v>21914</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>22-11-2025 02:43</t>
+          <t>22-11-2025 06:03</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>21909</v>
+        <v>21910</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>22-11-2025 04:58</t>
+          <t>22-11-2025 05:50</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>20127</v>
+        <v>20128</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>22-11-2025 01:06</t>
+          <t>22-11-2025 05:57</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>19061</v>
+        <v>19063</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>22-11-2025 04:40</t>
+          <t>22-11-2025 05:45</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18612</v>
+        <v>18615</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22-11-2025 05:22</t>
+          <t>22-11-2025 05:54</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>16766</v>
+        <v>16767</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>22-11-2025 02:45</t>
+          <t>22-11-2025 05:46</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>16332</v>
+        <v>16335</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>22-11-2025 05:15</t>
+          <t>22-11-2025 06:06</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6812,11 +6812,11 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>15923</v>
+        <v>15925</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>22-11-2025 04:08</t>
+          <t>22-11-2025 06:11</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6923,22 +6923,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>QwenLM/qwen-code</t>
+          <t>TibixDev/winboat</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://github.com/QwenLM/qwen-code</t>
+          <t>https://github.com/TibixDev/winboat</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Qwen Code is a coding agent that lives in the digital world.</t>
+          <t>Run Windows apps on 🐧 Linux with ✨ seamless integration</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -6951,39 +6951,43 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>22-11-2025 02:43</t>
+          <t>22-11-2025 05:41</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>26-06-2025 01:37</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>04-04-2025 12:03</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>docker, docker-compose, linux, rdp, virtualization</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TibixDev/winboat</t>
+          <t>QwenLM/qwen-code</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://github.com/TibixDev/winboat</t>
+          <t>https://github.com/QwenLM/qwen-code</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Run Windows apps on 🐧 Linux with ✨ seamless integration</t>
+          <t>Qwen Code is a coding agent that lives in the digital world.</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15745</v>
+        <v>15746</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6992,19 +6996,15 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>22-11-2025 04:54</t>
+          <t>22-11-2025 02:43</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>04-04-2025 12:03</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>docker, docker-compose, linux, rdp, virtualization</t>
-        </is>
-      </c>
+          <t>26-06-2025 01:37</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15666</v>
+        <v>15667</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22-11-2025 05:21</t>
+          <t>22-11-2025 05:57</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>15589</v>
+        <v>15590</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>22-11-2025 04:41</t>
+          <t>22-11-2025 06:01</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15124</v>
+        <v>15126</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22-11-2025 05:28</t>
+          <t>22-11-2025 05:50</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>15041</v>
+        <v>15042</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>22-11-2025 05:23</t>
+          <t>22-11-2025 06:10</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>14865</v>
+        <v>14867</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>22-11-2025 05:21</t>
+          <t>22-11-2025 06:02</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>13739</v>
+        <v>13742</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>22-11-2025 05:22</t>
+          <t>22-11-2025 06:05</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7942,26 +7942,26 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>budtmo/docker-android</t>
+          <t>AstrBotDevs/AstrBot</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://github.com/budtmo/docker-android</t>
+          <t>https://github.com/AstrBotDevs/AstrBot</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Android in docker solution with noVNC supported and video recording</t>
+          <t>✨ Agentic IM ChatBot Infrastructure ✨ Integration with multiple IMs, easy-to-use plugin system, supports OpenAI, Gemini, Anthropic, Dify, Coze, built-in Knowledge Base, Agent. ✨ 一站式大模型聊天机器人平台及开发框架 ...</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>13546</v>
+        <v>13547</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7970,39 +7970,39 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>22-11-2025 01:57</t>
+          <t>22-11-2025 06:07</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>22-12-2016 13:02</t>
+          <t>08-12-2022 13:27</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>alibabacloud, android, android-emulator, aws, azure</t>
+          <t>agent, ai, chatbot, chatgpt, docker</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>AstrBotDevs/AstrBot</t>
+          <t>budtmo/docker-android</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://github.com/AstrBotDevs/AstrBot</t>
+          <t>https://github.com/budtmo/docker-android</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>✨ Agentic IM ChatBot Infrastructure ✨ Integration with multiple IMs, easy-to-use plugin system, supports OpenAI, Gemini, Anthropic, Dify, Coze, built-in Knowledge Base, Agent. ✨ 一站式大模型聊天机器人平台及开发框架 ...</t>
+          <t>Android in docker solution with noVNC supported and video recording</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -8015,17 +8015,17 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>22-11-2025 05:10</t>
+          <t>22-11-2025 01:57</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>08-12-2022 13:27</t>
+          <t>22-12-2016 13:02</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>agent, ai, chatbot, chatgpt, docker</t>
+          <t>alibabacloud, android, android-emulator, aws, azure</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13031</v>
+        <v>13034</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22-11-2025 05:19</t>
+          <t>22-11-2025 06:14</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>11869</v>
+        <v>11870</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>21-11-2025 10:41</t>
+          <t>22-11-2025 05:50</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>11387</v>
+        <v>11388</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>22-11-2025 02:53</t>
+          <t>22-11-2025 05:35</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>9710</v>
+        <v>9711</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>22-11-2025 05:16</t>
+          <t>22-11-2025 05:33</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>9710</v>
+        <v>9711</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>22-11-2025 04:58</t>
+          <t>22-11-2025 05:46</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>9224</v>
+        <v>9225</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>22-11-2025 04:39</t>
+          <t>22-11-2025 06:11</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>8979</v>
+        <v>8980</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>22-11-2025 05:05</t>
+          <t>22-11-2025 05:53</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9887,11 +9887,11 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>8816</v>
+        <v>8817</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>22-11-2025 03:56</t>
+          <t>22-11-2025 06:09</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>8673</v>
+        <v>8674</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>22-11-2025 05:17</t>
+          <t>22-11-2025 05:54</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>7993</v>
+        <v>7995</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>22-11-2025 04:49</t>
+          <t>22-11-2025 05:33</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6102</v>
+        <v>6103</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>22-11-2025 05:20</t>
+          <t>22-11-2025 06:07</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -11551,7 +11551,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5486</v>
+        <v>5488</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>22-11-2025 04:37</t>
+          <t>22-11-2025 06:13</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11956,7 +11956,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4953</v>
+        <v>4952</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>22-11-2025 04:21</t>
+          <t>22-11-2025 05:55</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -12176,7 +12176,7 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4791</v>
+        <v>4792</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>22-11-2025 03:39</t>
+          <t>22-11-2025 05:30</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -12738,22 +12738,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>zhayujie/bot-on-anything</t>
+          <t>hotheadhacker/seedbox-lite</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://github.com/zhayujie/bot-on-anything</t>
+          <t>https://github.com/hotheadhacker/seedbox-lite</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>A large model-based chatbot builder that can quickly integrate AI models (including ChatGPT, Claude, Gemini) into various software applications (such as Telegram, Gmail, Slack, and websites).</t>
+          <t>A light-weight torrent media center at one place.</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -12761,65 +12761,65 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>21-11-2025 22:45</t>
+          <t>22-11-2025 05:49</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>09-02-2023 17:07</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>chatgpt, claude, gemini, gmail, slack</t>
-        </is>
-      </c>
+          <t>09-08-2025 14:00</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>hotheadhacker/seedbox-lite</t>
+          <t>zhayujie/bot-on-anything</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://github.com/hotheadhacker/seedbox-lite</t>
+          <t>https://github.com/zhayujie/bot-on-anything</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>A light-weight torrent media center at one place.</t>
+          <t>A large model-based chatbot builder that can quickly integrate AI models (including ChatGPT, Claude, Gemini) into various software applications (such as Telegram, Gmail, Slack, and websites).</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4144</v>
+        <v>4146</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>22-11-2025 03:30</t>
+          <t>21-11-2025 22:45</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>09-08-2025 14:00</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr"/>
+          <t>09-02-2023 17:07</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>chatgpt, claude, gemini, gmail, slack</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>22-11-2025 05:14</t>
+          <t>22-11-2025 05:40</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>21-11-2025 22:25</t>
+          <t>22-11-2025 06:05</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -14078,11 +14078,11 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>22-11-2025 05:22</t>
+          <t>22-11-2025 05:59</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14339,7 +14339,7 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>21-11-2025 19:40</t>
+          <t>22-11-2025 05:31</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>22-11-2025 00:46</t>
+          <t>22-11-2025 06:10</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>22-11-2025 01:17</t>
+          <t>22-11-2025 05:46</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15045,7 +15045,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>22-11-2025 05:16</t>
+          <t>22-11-2025 06:03</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -16316,11 +16316,11 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>22-11-2025 03:49</t>
+          <t>22-11-2025 06:09</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>22-11-2025 04:09</t>
+          <t>22-11-2025 06:07</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16892,11 +16892,11 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>22-11-2025 02:09</t>
+          <t>22-11-2025 06:07</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -17355,7 +17355,7 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>22-11-2025 02:42</t>
+          <t>22-11-2025 05:31</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17980,7 +17980,7 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>21-11-2025 06:44</t>
+          <t>22-11-2025 06:13</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -18096,63 +18096,67 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>kleneway/pastemax</t>
+          <t>AndnixSH/APKToolGUI</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://github.com/kleneway/pastemax</t>
+          <t>https://github.com/AndnixSH/APKToolGUI</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>A simple tool to select files from a repository to copy/paste into an LLM</t>
+          <t>GUI for apktool, signapk, zipalign and baksmali utilities.</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>19-11-2025 17:54</t>
+          <t>22-11-2025 05:59</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>01-03-2025 22:16</t>
-        </is>
-      </c>
-      <c r="I403" t="inlineStr"/>
+          <t>05-08-2021 16:11</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>apk, apk-tool-gui, apktool, gui, gui-apk-tool</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>AndnixSH/APKToolGUI</t>
+          <t>kleneway/pastemax</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://github.com/AndnixSH/APKToolGUI</t>
+          <t>https://github.com/kleneway/pastemax</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>GUI for apktool, signapk, zipalign and baksmali utilities.</t>
+          <t>A simple tool to select files from a repository to copy/paste into an LLM</t>
         </is>
       </c>
       <c r="E404" t="n">
@@ -18160,24 +18164,20 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>21-11-2025 06:30</t>
+          <t>19-11-2025 17:54</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>05-08-2021 16:11</t>
-        </is>
-      </c>
-      <c r="I404" t="inlineStr">
-        <is>
-          <t>apk, apk-tool-gui, apktool, gui, gui-apk-tool</t>
-        </is>
-      </c>
+          <t>01-03-2025 22:16</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>22-11-2025 05:04</t>
+          <t>22-11-2025 06:07</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -19111,7 +19111,7 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>22-11-2025 03:02</t>
+          <t>22-11-2025 06:05</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -20205,7 +20205,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>21-11-2025 17:08</t>
+          <t>22-11-2025 06:11</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>22-11-2025 03:24</t>
+          <t>22-11-2025 05:55</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -21697,7 +21697,7 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>21-11-2025 16:39</t>
+          <t>22-11-2025 06:06</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>22-11-2025 05:26</t>
+          <t>22-11-2025 06:11</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>444245</v>
+        <v>444478</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29-11-2025 00:50</t>
+          <t>30-11-2025 00:51</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>418651</v>
+        <v>418902</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>29-11-2025 00:40</t>
+          <t>30-11-2025 00:48</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>381654</v>
+        <v>381853</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>29-11-2025 00:51</t>
+          <t>30-11-2025 00:49</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>271571</v>
+        <v>271741</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>29-11-2025 00:47</t>
+          <t>30-11-2025 00:46</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>260507</v>
+        <v>260690</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29-11-2025 00:45</t>
+          <t>30-11-2025 00:59</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>251211</v>
+        <v>251299</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29-11-2025 00:48</t>
+          <t>30-11-2025 00:59</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198497</v>
+        <v>198525</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29-11-2025 00:50</t>
+          <t>29-11-2025 23:58</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>196001</v>
+        <v>196130</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29-11-2025 00:40</t>
+          <t>30-11-2025 00:59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>183034</v>
+        <v>183053</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29-11-2025 00:47</t>
+          <t>29-11-2025 22:57</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>159413</v>
+        <v>159588</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>30-11-2025 00:56</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157791</v>
+        <v>157914</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29-11-2025 00:41</t>
+          <t>30-11-2025 00:39</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>137660</v>
+        <v>137787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29-11-2025 00:34</t>
+          <t>30-11-2025 00:47</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>136561</v>
+        <v>136660</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29-11-2025 00:35</t>
+          <t>30-11-2025 00:59</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131706</v>
+        <v>131741</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29-11-2025 00:30</t>
+          <t>30-11-2025 00:42</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>126102</v>
+        <v>126127</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>29-11-2025 00:12</t>
+          <t>29-11-2025 23:37</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>116503</v>
+        <v>116573</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29-11-2025 00:14</t>
+          <t>30-11-2025 00:25</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115820</v>
+        <v>115845</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>28-11-2025 23:35</t>
+          <t>29-11-2025 23:32</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1257,11 +1257,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115779</v>
+        <v>115783</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>28-11-2025 22:30</t>
+          <t>30-11-2025 00:13</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103619</v>
+        <v>103779</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>29-11-2025 00:51</t>
+          <t>30-11-2025 00:40</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103196</v>
+        <v>103236</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>29-11-2025 00:27</t>
+          <t>29-11-2025 23:39</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101534</v>
+        <v>101658</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29-11-2025 00:22</t>
+          <t>30-11-2025 00:31</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>98345</v>
+        <v>98499</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29-11-2025 00:48</t>
+          <t>30-11-2025 00:58</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>94358</v>
+        <v>94427</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>29-11-2025 00:50</t>
+          <t>30-11-2025 00:17</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>92938</v>
+        <v>92944</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>28-11-2025 20:10</t>
+          <t>29-11-2025 21:39</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>92459</v>
+        <v>92485</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>29-11-2025 00:37</t>
+          <t>29-11-2025 22:03</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>88334</v>
+        <v>88342</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>29-11-2025 00:01</t>
+          <t>29-11-2025 22:41</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>86537</v>
+        <v>86544</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>28-11-2025 19:27</t>
+          <t>29-11-2025 22:35</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>85246</v>
+        <v>85303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>29-11-2025 00:50</t>
+          <t>29-11-2025 23:56</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>85079</v>
+        <v>85178</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>29-11-2025 00:43</t>
+          <t>30-11-2025 00:20</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>83417</v>
+        <v>83445</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>29-11-2025 00:50</t>
+          <t>29-11-2025 23:10</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>80646</v>
+        <v>80758</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>29-11-2025 00:38</t>
+          <t>30-11-2025 00:50</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>80143</v>
+        <v>80179</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>28-11-2025 23:57</t>
+          <t>30-11-2025 00:17</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>79048</v>
+        <v>79075</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>28-11-2025 22:48</t>
+          <t>29-11-2025 23:27</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>77140</v>
+        <v>77157</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>28-11-2025 23:38</t>
+          <t>30-11-2025 00:45</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>76028</v>
+        <v>76039</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>28-11-2025 23:05</t>
+          <t>29-11-2025 23:44</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>70603</v>
+        <v>70620</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29-11-2025 00:21</t>
+          <t>30-11-2025 00:25</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>68733</v>
+        <v>68802</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>29-11-2025 00:36</t>
+          <t>30-11-2025 00:40</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>68218</v>
+        <v>68250</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29-11-2025 00:41</t>
+          <t>30-11-2025 00:42</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2177,11 +2177,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>66949</v>
+        <v>66975</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>28-11-2025 23:58</t>
+          <t>30-11-2025 00:29</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>65586</v>
+        <v>65585</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>28-11-2025 19:23</t>
+          <t>30-11-2025 00:55</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2262,11 +2262,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>63880</v>
+        <v>63895</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>29-11-2025 00:37</t>
+          <t>30-11-2025 00:18</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>59722</v>
+        <v>59735</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>28-11-2025 16:30</t>
+          <t>30-11-2025 00:39</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>59647</v>
+        <v>59729</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>29-11-2025 00:43</t>
+          <t>30-11-2025 00:43</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2392,11 +2392,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>56929</v>
+        <v>56956</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>29-11-2025 00:38</t>
+          <t>29-11-2025 23:23</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>56497</v>
+        <v>56534</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>30-11-2025 00:15</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53759</v>
+        <v>53784</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>29-11-2025 22:36</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2518,11 +2518,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53740</v>
+        <v>53766</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>28-11-2025 23:59</t>
+          <t>30-11-2025 00:36</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53725</v>
+        <v>53736</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>29-11-2025 00:16</t>
+          <t>30-11-2025 00:11</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>52210</v>
+        <v>52213</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>28-11-2025 22:07</t>
+          <t>29-11-2025 20:40</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51784</v>
+        <v>51786</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>28-11-2025 17:53</t>
+          <t>29-11-2025 16:44</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51767</v>
+        <v>51774</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28-11-2025 23:05</t>
+          <t>29-11-2025 23:17</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>51619</v>
+        <v>51643</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>29-11-2025 00:04</t>
+          <t>30-11-2025 00:13</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>48803</v>
+        <v>48828</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>28-11-2025 20:58</t>
+          <t>30-11-2025 00:17</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>48064</v>
+        <v>48083</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>29-11-2025 00:34</t>
+          <t>29-11-2025 23:29</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47989</v>
+        <v>48004</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>29-11-2025 00:12</t>
+          <t>29-11-2025 20:18</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>47819</v>
+        <v>47853</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>28-11-2025 23:09</t>
+          <t>30-11-2025 00:38</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47654</v>
+        <v>47668</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>28-11-2025 18:35</t>
+          <t>29-11-2025 22:55</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3004,11 +3004,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>47587</v>
+        <v>47606</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>28-11-2025 20:02</t>
+          <t>29-11-2025 21:06</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>46555</v>
+        <v>46584</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>29-11-2025 00:37</t>
+          <t>30-11-2025 00:56</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>46433</v>
+        <v>46452</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>28-11-2025 23:48</t>
+          <t>29-11-2025 21:42</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3110,83 +3110,83 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cloudcommunity/Free-Certifications</t>
+          <t>Zie619/n8n-workflows</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://github.com/cloudcommunity/Free-Certifications</t>
+          <t>https://github.com/Zie619/n8n-workflows</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A curated list of free courses with certifications. Also available at https://free-certifications.com/</t>
+          <t>all of the workflows of n8n i could find (also from the site itself)</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>45381</v>
+        <v>45637</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>29-11-2025 00:46</t>
+          <t>30-11-2025 00:49</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>31-07-2020 10:26</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, awesome-lists, certification, certifications</t>
-        </is>
-      </c>
+          <t>14-05-2025 08:43</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zie619/n8n-workflows</t>
+          <t>cloudcommunity/Free-Certifications</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://github.com/Zie619/n8n-workflows</t>
+          <t>https://github.com/cloudcommunity/Free-Certifications</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>all of the workflows of n8n i could find (also from the site itself)</t>
+          <t>A curated list of free courses with certifications. Also available at https://free-certifications.com/</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>45378</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
+        <v>45565</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>29-11-2025 00:50</t>
+          <t>30-11-2025 00:59</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>14-05-2025 08:43</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>31-07-2020 10:26</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, awesome-lists, certification, certifications</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>44121</v>
+        <v>44236</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>30-11-2025 00:13</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>43241</v>
+        <v>43280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>28-11-2025 23:22</t>
+          <t>29-11-2025 23:17</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>42641</v>
+        <v>42665</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>30-11-2025 00:31</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3341,11 +3341,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>41102</v>
+        <v>41124</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>28-11-2025 23:42</t>
+          <t>29-11-2025 21:48</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>39523</v>
+        <v>39535</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>29-11-2025 00:35</t>
+          <t>29-11-2025 22:43</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>39433</v>
+        <v>39448</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>28-11-2025 22:23</t>
+          <t>30-11-2025 00:48</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>39379</v>
+        <v>39416</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>29-11-2025 00:45</t>
+          <t>30-11-2025 00:56</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>39360</v>
+        <v>39382</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>28-11-2025 22:23</t>
+          <t>30-11-2025 00:50</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>38650</v>
+        <v>38653</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>28-11-2025 21:46</t>
+          <t>29-11-2025 09:51</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37976</v>
+        <v>37983</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>29-11-2025 00:21</t>
+          <t>29-11-2025 23:20</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>37498</v>
+        <v>37507</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>28-11-2025 23:37</t>
+          <t>30-11-2025 00:38</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>36989</v>
+        <v>36991</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>28-11-2025 18:44</t>
+          <t>29-11-2025 07:36</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>35976</v>
+        <v>35990</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>28-11-2025 23:56</t>
+          <t>29-11-2025 23:37</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>35887</v>
+        <v>35922</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>28-11-2025 22:29</t>
+          <t>30-11-2025 00:47</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>35531</v>
+        <v>35540</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>29-11-2025 00:26</t>
+          <t>29-11-2025 18:59</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3876,11 +3876,11 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>34682</v>
+        <v>34699</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>28-11-2025 19:51</t>
+          <t>29-11-2025 22:07</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>34645</v>
+        <v>34656</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>28-11-2025 19:56</t>
+          <t>30-11-2025 00:23</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>34289</v>
+        <v>34295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>28-11-2025 22:30</t>
+          <t>29-11-2025 21:42</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>33477</v>
+        <v>33480</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>29-11-2025 00:13</t>
+          <t>30-11-2025 00:14</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4051,11 +4051,11 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>32764</v>
+        <v>32768</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>29-11-2025 00:07</t>
+          <t>30-11-2025 00:52</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>32021</v>
+        <v>32039</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>29-11-2025 00:03</t>
+          <t>30-11-2025 00:59</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4117,83 +4117,83 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Chanzhaoyu/chatgpt-web</t>
+          <t>awesome-foss/awesome-sysadmin</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://github.com/Chanzhaoyu/chatgpt-web</t>
+          <t>https://github.com/awesome-foss/awesome-sysadmin</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>用 Express 和  Vue3 搭建的 ChatGPT 演示网页</t>
+          <t>A curated list of amazingly awesome open-source sysadmin resources.</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>31902</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Vue</t>
-        </is>
+        <v>31917</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>28-11-2025 18:10</t>
+          <t>29-11-2025 23:44</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>09-02-2023 03:21</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>23-12-2014 08:41</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, devops, list, ops</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>awesome-foss/awesome-sysadmin</t>
+          <t>Chanzhaoyu/chatgpt-web</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://github.com/awesome-foss/awesome-sysadmin</t>
+          <t>https://github.com/Chanzhaoyu/chatgpt-web</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>A curated list of amazingly awesome open-source sysadmin resources.</t>
+          <t>用 Express 和  Vue3 搭建的 ChatGPT 演示网页</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>31899</v>
+        <v>31901</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vue</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>29-11-2025 00:47</t>
+          <t>29-11-2025 06:38</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>23-12-2014 08:41</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, devops, list, ops</t>
-        </is>
-      </c>
+          <t>09-02-2023 03:21</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>28-11-2025 23:35</t>
+          <t>29-11-2025 13:33</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31760</v>
+        <v>31792</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>29-11-2025 00:15</t>
+          <t>29-11-2025 23:13</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>31752</v>
+        <v>31761</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>28-11-2025 23:23</t>
+          <t>30-11-2025 00:13</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>31202</v>
+        <v>31209</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>28-11-2025 23:07</t>
+          <t>29-11-2025 23:57</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>29944</v>
+        <v>29965</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>29-11-2025 00:09</t>
+          <t>29-11-2025 23:39</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>29354</v>
+        <v>29358</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>29-11-2025 00:15</t>
+          <t>30-11-2025 00:33</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>29062</v>
+        <v>29081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>28-11-2025 23:37</t>
+          <t>29-11-2025 23:10</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4527,11 +4527,11 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>28517</v>
+        <v>28532</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>28-11-2025 23:28</t>
+          <t>29-11-2025 23:08</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>28457</v>
+        <v>28460</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>28-11-2025 23:25</t>
+          <t>29-11-2025 21:52</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>28211</v>
+        <v>28220</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>28-11-2025 14:45</t>
+          <t>29-11-2025 21:27</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>27330</v>
+        <v>27371</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>29-11-2025 00:42</t>
+          <t>30-11-2025 00:40</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4702,11 +4702,11 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>27134</v>
+        <v>27139</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>29-11-2025 00:49</t>
+          <t>29-11-2025 17:27</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>27126</v>
+        <v>27127</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>29-11-2025 21:43</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>26977</v>
+        <v>26983</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>28-11-2025 23:35</t>
+          <t>30-11-2025 00:37</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>26374</v>
+        <v>26382</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>28-11-2025 21:02</t>
+          <t>30-11-2025 00:22</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>26235</v>
+        <v>26257</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>29-11-2025 23:57</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>26159</v>
+        <v>26164</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>28-11-2025 18:53</t>
+          <t>29-11-2025 16:58</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>26115</v>
+        <v>26121</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>29-11-2025 00:06</t>
+          <t>29-11-2025 22:17</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4989,26 +4989,26 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>openfaas/faas</t>
+          <t>cloudreve/cloudreve</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://github.com/openfaas/faas</t>
+          <t>https://github.com/cloudreve/cloudreve</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OpenFaaS - Serverless Functions Made Simple</t>
+          <t>🌩 Self-hosted file management and sharing system, supports multiple storage providers</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>25989</v>
+        <v>25995</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5017,43 +5017,43 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>28-11-2025 19:13</t>
+          <t>30-11-2025 00:12</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>22-12-2016 12:51</t>
+          <t>04-02-2018 04:56</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>docker, faas, functions, functions-as-a-service, gitops</t>
+          <t>cloud, cloud-storage, cloudreve, file, file-manager</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>cloudreve/cloudreve</t>
+          <t>openfaas/faas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://github.com/cloudreve/cloudreve</t>
+          <t>https://github.com/openfaas/faas</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>🌩 Self-hosted file management and sharing system, supports multiple storage providers</t>
+          <t>OpenFaaS - Serverless Functions Made Simple</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25978</v>
+        <v>25991</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5062,17 +5062,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>28-11-2025 23:42</t>
+          <t>29-11-2025 22:54</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>04-02-2018 04:56</t>
+          <t>22-12-2016 12:51</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>cloud, cloud-storage, cloudreve, file, file-manager</t>
+          <t>docker, faas, functions, functions-as-a-service, gitops</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>25828</v>
+        <v>25836</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>28-11-2025 23:48</t>
+          <t>29-11-2025 19:41</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5143,11 +5143,11 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>25669</v>
+        <v>25675</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>28-11-2025 20:30</t>
+          <t>30-11-2025 00:38</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>25495</v>
+        <v>25499</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>28-11-2025 22:13</t>
+          <t>29-11-2025 22:33</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>25151</v>
+        <v>25159</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>29-11-2025 00:14</t>
+          <t>29-11-2025 23:52</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5269,11 +5269,11 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>24599</v>
+        <v>24608</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>29-11-2025 00:21</t>
+          <t>30-11-2025 00:41</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>24475</v>
+        <v>24487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>28-11-2025 22:12</t>
+          <t>29-11-2025 21:09</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>23938</v>
+        <v>23951</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>28-11-2025 23:55</t>
+          <t>29-11-2025 20:28</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>23890</v>
+        <v>23895</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>28-11-2025 22:30</t>
+          <t>29-11-2025 23:46</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>23886</v>
+        <v>23893</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>28-11-2025 23:17</t>
+          <t>29-11-2025 21:12</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>23218</v>
+        <v>23224</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>29-11-2025 00:19</t>
+          <t>30-11-2025 00:54</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5515,12 +5515,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>firecrawl/open-lovable</t>
+          <t>musistudio/claude-code-router</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://github.com/firecrawl/open-lovable</t>
+          <t>https://github.com/musistudio/claude-code-router</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5530,11 +5530,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>🔥 Clone and recreate any website as a modern React app in seconds</t>
+          <t>Use Claude Code as the foundation for coding infrastructure, allowing you to decide how to interact with the model while enjoying updates from Anthropic.</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>22548</v>
+        <v>22566</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5543,12 +5543,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>28-11-2025 23:22</t>
+          <t>30-11-2025 00:30</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>08-08-2025 13:04</t>
+          <t>25-02-2025 02:17</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -5556,12 +5556,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>musistudio/claude-code-router</t>
+          <t>firecrawl/open-lovable</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://github.com/musistudio/claude-code-router</t>
+          <t>https://github.com/firecrawl/open-lovable</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5571,11 +5571,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Use Claude Code as the foundation for coding infrastructure, allowing you to decide how to interact with the model while enjoying updates from Anthropic.</t>
+          <t>🔥 Clone and recreate any website as a modern React app in seconds</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>22523</v>
+        <v>22561</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -5584,12 +5584,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>29-11-2025 00:51</t>
+          <t>30-11-2025 00:07</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>25-02-2025 02:17</t>
+          <t>08-08-2025 13:04</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -5616,11 +5616,11 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>22452</v>
+        <v>22454</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>27-11-2025 20:45</t>
+          <t>29-11-2025 16:21</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>21968</v>
+        <v>21971</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>28-11-2025 16:50</t>
+          <t>29-11-2025 20:02</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>21935</v>
+        <v>21939</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>28-11-2025 22:22</t>
+          <t>29-11-2025 21:42</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>21900</v>
+        <v>21905</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>29-11-2025 00:29</t>
+          <t>29-11-2025 21:25</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>21524</v>
+        <v>21543</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>28-11-2025 21:51</t>
+          <t>30-11-2025 00:51</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>21139</v>
+        <v>21145</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>28-11-2025 23:11</t>
+          <t>29-11-2025 23:14</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>20739</v>
+        <v>20750</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>29-11-2025 00:39</t>
+          <t>29-11-2025 22:01</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>20683</v>
+        <v>20686</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>28-11-2025 23:51</t>
+          <t>29-11-2025 17:29</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>28-11-2025 15:46</t>
+          <t>29-11-2025 16:48</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>20221</v>
+        <v>20236</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>28-11-2025 17:49</t>
+          <t>29-11-2025 23:52</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>19619</v>
+        <v>19628</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>29-11-2025 00:34</t>
+          <t>30-11-2025 00:12</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6102,11 +6102,11 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>19539</v>
+        <v>19551</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>28-11-2025 23:25</t>
+          <t>29-11-2025 20:16</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>19272</v>
+        <v>19292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>29-11-2025 00:05</t>
+          <t>30-11-2025 00:40</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6187,11 +6187,11 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>19228</v>
+        <v>19238</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>28-11-2025 18:31</t>
+          <t>30-11-2025 00:10</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>19108</v>
+        <v>19151</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>29-11-2025 00:47</t>
+          <t>29-11-2025 23:52</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>18336</v>
+        <v>18344</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>28-11-2025 23:10</t>
+          <t>29-11-2025 21:09</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>18151</v>
+        <v>18153</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>28-11-2025 11:55</t>
+          <t>29-11-2025 23:37</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>18071</v>
+        <v>18074</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>28-11-2025 21:56</t>
+          <t>29-11-2025 23:25</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>17935</v>
+        <v>17939</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>28-11-2025 23:24</t>
+          <t>29-11-2025 13:43</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17892</v>
+        <v>17899</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>28-11-2025 21:20</t>
+          <t>29-11-2025 23:41</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>17792</v>
+        <v>17810</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>29-11-2025 00:18</t>
+          <t>30-11-2025 00:41</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>17690</v>
+        <v>17702</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>28-11-2025 21:14</t>
+          <t>29-11-2025 23:24</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>17570</v>
+        <v>17581</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>29-11-2025 00:40</t>
+          <t>30-11-2025 00:26</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>17506</v>
+        <v>17512</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>28-11-2025 21:15</t>
+          <t>29-11-2025 22:06</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>17376</v>
+        <v>17385</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>28-11-2025 20:18</t>
+          <t>29-11-2025 22:36</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>17310</v>
+        <v>17319</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>29-11-2025 00:48</t>
+          <t>29-11-2025 17:28</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>17159</v>
+        <v>17208</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>28-11-2025 23:48</t>
+          <t>30-11-2025 00:51</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6812,11 +6812,11 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>17062</v>
+        <v>17063</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>28-11-2025 14:52</t>
+          <t>29-11-2025 14:10</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>16482</v>
+        <v>16494</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>28-11-2025 23:06</t>
+          <t>30-11-2025 00:38</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>16211</v>
+        <v>16247</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>29-11-2025 00:35</t>
+          <t>29-11-2025 23:42</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6942,11 +6942,11 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>16193</v>
+        <v>16232</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>29-11-2025 00:20</t>
+          <t>30-11-2025 00:44</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>15959</v>
+        <v>15988</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>29-11-2025 00:01</t>
+          <t>30-11-2025 00:53</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>15944</v>
+        <v>15949</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>28-11-2025 20:35</t>
+          <t>29-11-2025 16:58</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15913</v>
+        <v>15927</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>28-11-2025 22:39</t>
+          <t>29-11-2025 16:17</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>15912</v>
+        <v>15917</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>29-11-2025 00:07</t>
+          <t>30-11-2025 00:09</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>15806</v>
+        <v>15813</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>28-11-2025 23:37</t>
+          <t>29-11-2025 22:14</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15742</v>
+        <v>15749</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>29-11-2025 00:50</t>
+          <t>29-11-2025 17:39</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>15551</v>
+        <v>15609</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>28-11-2025 22:57</t>
+          <t>30-11-2025 00:01</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>15110</v>
+        <v>15115</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>28-11-2025 21:05</t>
+          <t>29-11-2025 22:44</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>15103</v>
+        <v>15108</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>28-11-2025 21:51</t>
+          <t>29-11-2025 23:30</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7405,102 +7405,102 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>htr-tech/zphisher</t>
+          <t>usestrix/strix</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://github.com/htr-tech/zphisher</t>
+          <t>https://github.com/usestrix/strix</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>An automated phishing tool with 30+ templates. This Tool is made for educational purpose only ! Author will not be responsible for any misuse of this toolkit !</t>
+          <t>Open-source AI agents for penetration testing</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>14940</v>
+        <v>15084</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>28-11-2025 23:11</t>
+          <t>30-11-2025 00:59</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>25-11-2019 13:22</t>
+          <t>05-08-2025 21:28</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>htr-tech, phisher, phishing, phishing-attacks, phishing-pages</t>
+          <t>agents, artificial-intelligence, cybersecurity, generative-ai, llm</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>camel-ai/camel</t>
+          <t>htr-tech/zphisher</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://github.com/camel-ai/camel</t>
+          <t>https://github.com/htr-tech/zphisher</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>🐫 CAMEL: The first and the best multi-agent framework. Finding the Scaling Law of Agents. https://www.camel-ai.org</t>
+          <t>An automated phishing tool with 30+ templates. This Tool is made for educational purpose only ! Author will not be responsible for any misuse of this toolkit !</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>14920</v>
+        <v>14947</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>29-11-2025 00:40</t>
+          <t>29-11-2025 19:11</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>17-03-2023 21:41</t>
+          <t>25-11-2019 13:22</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>agent, ai-societies, artificial-intelligence, communicative-ai, cooperative-ai</t>
+          <t>htr-tech, phisher, phishing, phishing-attacks, phishing-pages</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ahmedkhaleel2004/gitdiagram</t>
+          <t>camel-ai/camel</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://github.com/ahmedkhaleel2004/gitdiagram</t>
+          <t>https://github.com/camel-ai/camel</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7510,218 +7510,218 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Free, simple, fast interactive diagrams for any GitHub repository</t>
+          <t>🐫 CAMEL: The first and the best multi-agent framework. Finding the Scaling Law of Agents. https://www.camel-ai.org</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>14819</v>
+        <v>14926</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>28-11-2025 23:07</t>
+          <t>29-11-2025 20:47</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>15-12-2024 10:32</t>
+          <t>17-03-2023 21:41</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>ai, code, github, system-design</t>
+          <t>agent, ai-societies, artificial-intelligence, communicative-ai, cooperative-ai</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>resemble-ai/chatterbox</t>
+          <t>ahmedkhaleel2004/gitdiagram</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://github.com/resemble-ai/chatterbox</t>
+          <t>https://github.com/ahmedkhaleel2004/gitdiagram</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>SoTA open-source TTS</t>
+          <t>Free, simple, fast interactive diagrams for any GitHub repository</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>14784</v>
+        <v>14861</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>29-11-2025 00:23</t>
+          <t>29-11-2025 21:21</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>23-04-2025 08:16</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>15-12-2024 10:32</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>ai, code, github, system-design</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ag-grid/ag-grid</t>
+          <t>resemble-ai/chatterbox</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://github.com/ag-grid/ag-grid</t>
+          <t>https://github.com/resemble-ai/chatterbox</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>The best JavaScript Data Table for building Enterprise Applications. Supports React / Angular / Vue / Plain JavaScript.</t>
+          <t>SoTA open-source TTS</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>14763</v>
+        <v>14804</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>28-11-2025 21:48</t>
+          <t>29-11-2025 23:52</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>23-12-2014 16:20</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>angular, angular-grid, angular-table, charting, datagrid</t>
-        </is>
-      </c>
+          <t>23-04-2025 08:16</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>cachethq/cachet</t>
+          <t>ag-grid/ag-grid</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://github.com/cachethq/cachet</t>
+          <t>https://github.com/ag-grid/ag-grid</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>🚦 Cachet, the open-source, self-hosted status page system.</t>
+          <t>The best JavaScript Data Table for building Enterprise Applications. Supports React / Angular / Vue / Plain JavaScript.</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>14753</v>
+        <v>14764</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>28-11-2025 10:51</t>
+          <t>29-11-2025 23:00</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>16-11-2014 22:23</t>
+          <t>23-12-2014 16:20</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>cachet, laravel, php, self-hosted, selfhosted</t>
+          <t>angular, angular-grid, angular-table, charting, datagrid</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>caprover/caprover</t>
+          <t>cachethq/cachet</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://github.com/caprover/caprover</t>
+          <t>https://github.com/cachethq/cachet</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Scalable PaaS (automated Docker+nginx) - aka Heroku on Steroids</t>
+          <t>🚦 Cachet, the open-source, self-hosted status page system.</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>14649</v>
+        <v>14754</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>28-11-2025 14:53</t>
+          <t>29-11-2025 15:38</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>25-10-2017 05:00</t>
+          <t>16-11-2014 22:23</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>aws, azure, caprover, captainduckduck, containers</t>
+          <t>cachet, laravel, php, self-hosted, selfhosted</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>usestrix/strix</t>
+          <t>caprover/caprover</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://github.com/usestrix/strix</t>
+          <t>https://github.com/caprover/caprover</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7731,30 +7731,30 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Open-source AI agents for penetration testing</t>
+          <t>Scalable PaaS (automated Docker+nginx) - aka Heroku on Steroids</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>14575</v>
+        <v>14649</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>29-11-2025 00:41</t>
+          <t>28-11-2025 14:53</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>05-08-2025 21:28</t>
+          <t>25-10-2017 05:00</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>agents, artificial-intelligence, cybersecurity, generative-ai, llm</t>
+          <t>aws, azure, caprover, captainduckduck, containers</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>14458</v>
+        <v>14457</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>28-11-2025 15:58</t>
+          <t>29-11-2025 18:24</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>14163</v>
+        <v>14239</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>29-11-2025 00:25</t>
+          <t>30-11-2025 00:51</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>14151</v>
+        <v>14212</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>30-11-2025 00:54</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>14145</v>
+        <v>14156</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>28-11-2025 23:20</t>
+          <t>29-11-2025 19:42</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7956,7 +7956,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>13899</v>
+        <v>13903</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>28-11-2025 20:26</t>
+          <t>29-11-2025 22:10</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13873</v>
+        <v>13874</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>28-11-2025 20:18</t>
+          <t>29-11-2025 07:00</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>13830</v>
+        <v>13832</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>28-11-2025 07:25</t>
+          <t>29-11-2025 17:27</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>13778</v>
+        <v>13783</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>28-11-2025 14:08</t>
+          <t>30-11-2025 00:49</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>13759</v>
+        <v>13782</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>28-11-2025 18:13</t>
+          <t>30-11-2025 00:57</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>13588</v>
+        <v>13590</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>28-11-2025 22:57</t>
+          <t>29-11-2025 22:59</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>28-11-2025 16:11</t>
+          <t>29-11-2025 13:54</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8271,11 +8271,11 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13397</v>
+        <v>13408</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>28-11-2025 11:12</t>
+          <t>29-11-2025 23:22</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>13363</v>
+        <v>13366</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>27-11-2025 20:20</t>
+          <t>30-11-2025 00:00</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>13225</v>
+        <v>13228</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>28-11-2025 22:24</t>
+          <t>29-11-2025 21:39</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8401,7 +8401,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>13200</v>
+        <v>13207</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>28-11-2025 21:37</t>
+          <t>29-11-2025 17:35</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8446,11 +8446,11 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>12916</v>
+        <v>12927</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>28-11-2025 20:26</t>
+          <t>30-11-2025 00:19</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>12657</v>
+        <v>12661</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>28-11-2025 19:44</t>
+          <t>29-11-2025 12:02</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8527,7 +8527,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>12611</v>
+        <v>12615</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>28-11-2025 20:43</t>
+          <t>29-11-2025 23:13</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8553,142 +8553,147 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ytisf/theZoo</t>
+          <t>winapps-org/winapps</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://github.com/ytisf/theZoo</t>
+          <t>https://github.com/winapps-org/winapps</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>A repository of LIVE malwares for your own joy and pleasure. theZoo is a project created to make the possibility of malware analysis open and available to the public.</t>
+          <t>Run Windows apps such as Microsoft Office/Adobe in Linux (Ubuntu/Fedora) and GNOME/KDE as if they were a part of the native OS, including Nautilus integration. Hard fork of https://github.com/Fmstr...</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>12472</v>
+        <v>12519</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>28-11-2025 19:40</t>
+          <t>30-11-2025 00:45</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>09-01-2014 18:55</t>
+          <t>05-07-2023 15:05</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>malware, malware-analysis, malware-research, malware-samples, malwareanalysis</t>
+          <t>cassowary, docker, freerdp, gnome, hacktoberfest</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>aaPanel/BillionMail</t>
+          <t>ytisf/theZoo</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://github.com/aaPanel/BillionMail</t>
+          <t>https://github.com/ytisf/theZoo</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>BillionMail gives you open-source MailServer, NewsLetter,  Email Marketing — fully self-hosted, dev-friendly, and free from monthly fees. Join the discord: https://discord.gg/asfXzBUhZr</t>
+          <t>A repository of LIVE malwares for your own joy and pleasure. theZoo is a project created to make the possibility of malware analysis open and available to the public.</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>12324</v>
+        <v>12478</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>28-11-2025 23:35</t>
+          <t>29-11-2025 21:15</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>14-02-2025 06:25</t>
+          <t>09-01-2014 18:55</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>dovecot, email, email-marketing, mail, mailserver</t>
+          <t>malware, malware-analysis, malware-research, malware-samples, malwareanalysis</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>255kb/stack-on-a-budget</t>
+          <t>aaPanel/BillionMail</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://github.com/255kb/stack-on-a-budget</t>
+          <t>https://github.com/aaPanel/BillionMail</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>A collection of services with great free tiers for developers on a budget. Sponsored by Mockoon, the best mock API tool. https://mockoon.com</t>
+          <t>BillionMail gives you open-source MailServer, NewsLetter,  Email Marketing — fully self-hosted, dev-friendly, and free from monthly fees. Join the discord: https://discord.gg/asfXzBUhZr</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>12301</v>
+        <v>12330</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>24-11-2025 08:15</t>
+          <t>29-11-2025 20:49</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>12-10-2016 06:55</t>
+          <t>14-02-2025 06:25</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>free, list, paas, saas</t>
+          <t>dovecot, email, email-marketing, mail, mailserver</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>zhuima/awesome-cloudflare</t>
+          <t>255kb/stack-on-a-budget</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://github.com/zhuima/awesome-cloudflare</t>
+          <t>https://github.com/255kb/stack-on-a-budget</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8698,78 +8703,73 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>⛅️ 精选的 Cloudflare 工具、开源项目、指南、博客和其他资源列表。/ ⛅️ A curated list of Cloudflare tools, open source projects, guides, blogs and other resources.</t>
+          <t>A collection of services with great free tiers for developers on a budget. Sponsored by Mockoon, the best mock API tool. https://mockoon.com</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>12287</v>
+        <v>12301</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>29-11-2025 00:07</t>
+          <t>24-11-2025 08:15</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>07-04-2024 02:19</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>12-10-2016 06:55</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>free, list, paas, saas</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>firebase/functions-samples</t>
+          <t>zhuima/awesome-cloudflare</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://github.com/firebase/functions-samples</t>
+          <t>https://github.com/zhuima/awesome-cloudflare</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Collection of sample apps showcasing popular use cases using Cloud Functions for Firebase</t>
+          <t>⛅️ 精选的 Cloudflare 工具、开源项目、指南、博客和其他资源列表。/ ⛅️ A curated list of Cloudflare tools, open source projects, guides, blogs and other resources.</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>12221</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
+        <v>12290</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>28-11-2025 18:09</t>
+          <t>30-11-2025 00:46</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>18-10-2016 17:40</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>faas, faas-platform, firebase, google, google-cloud-functions</t>
-        </is>
-      </c>
+          <t>07-04-2024 02:19</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>cloudflare/cloudflared</t>
+          <t>firebase/functions-samples</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://github.com/cloudflare/cloudflared</t>
+          <t>https://github.com/firebase/functions-samples</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8779,75 +8779,75 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cloudflare Tunnel client</t>
+          <t>Collection of sample apps showcasing popular use cases using Cloud Functions for Firebase</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>12112</v>
+        <v>12220</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>28-11-2025 21:00</t>
+          <t>30-11-2025 00:20</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>13-10-2017 19:54</t>
+          <t>18-10-2016 17:40</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>cloudflare, cloudflare-tunnel, reverse-proxy, zero-trust-network-access</t>
+          <t>faas, faas-platform, firebase, google, google-cloud-functions</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>winapps-org/winapps</t>
+          <t>cloudflare/cloudflared</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://github.com/winapps-org/winapps</t>
+          <t>https://github.com/cloudflare/cloudflared</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Run Windows apps such as Microsoft Office/Adobe in Linux (Ubuntu/Fedora) and GNOME/KDE as if they were a part of the native OS, including Nautilus integration. Hard fork of https://github.com/Fmstr...</t>
+          <t>Cloudflare Tunnel client</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>12109</v>
+        <v>12124</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>28-11-2025 16:33</t>
+          <t>29-11-2025 21:20</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>05-07-2023 15:05</t>
+          <t>13-10-2017 19:54</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>cassowary, docker, freerdp, gnome, hacktoberfest</t>
+          <t>cloudflare, cloudflare-tunnel, reverse-proxy, zero-trust-network-access</t>
         </is>
       </c>
     </row>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>11981</v>
+        <v>11982</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>28-11-2025 19:40</t>
+          <t>29-11-2025 23:17</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>11919</v>
+        <v>11922</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>28-11-2025 17:35</t>
+          <t>29-11-2025 23:00</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>11745</v>
+        <v>11809</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>28-11-2025 23:55</t>
+          <t>30-11-2025 00:41</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>11683</v>
+        <v>11685</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>28-11-2025 21:56</t>
+          <t>29-11-2025 19:44</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>11580</v>
+        <v>11587</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>28-11-2025 23:51</t>
+          <t>29-11-2025 22:56</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>11558</v>
+        <v>11557</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>28-11-2025 18:00</t>
+          <t>29-11-2025 19:21</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>11429</v>
+        <v>11436</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>30-11-2025 00:51</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9233,7 +9233,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>11381</v>
+        <v>11389</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>28-11-2025 21:10</t>
+          <t>29-11-2025 21:12</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>10918</v>
+        <v>10933</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>28-11-2025 19:25</t>
+          <t>30-11-2025 00:10</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>10713</v>
+        <v>10814</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>29-11-2025 00:37</t>
+          <t>30-11-2025 00:30</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>10713</v>
+        <v>10714</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>28-11-2025 17:53</t>
+          <t>30-11-2025 00:29</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>10622</v>
+        <v>10689</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>29-11-2025 00:44</t>
+          <t>30-11-2025 00:20</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>10607</v>
+        <v>10609</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>28-11-2025 22:46</t>
+          <t>30-11-2025 00:09</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>10590</v>
+        <v>10588</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>28-11-2025 19:54</t>
+          <t>29-11-2025 10:13</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9548,11 +9548,11 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>10087</v>
+        <v>10088</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>28-11-2025 19:59</t>
+          <t>29-11-2025 01:41</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9584,7 +9584,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>10020</v>
+        <v>10023</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>28-11-2025 09:21</t>
+          <t>29-11-2025 17:14</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>9896</v>
+        <v>9897</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>28-11-2025 09:50</t>
+          <t>29-11-2025 12:47</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9655,40 +9655,40 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>sdelements/lets-chat</t>
+          <t>BeehiveInnovations/zen-mcp-server</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://github.com/sdelements/lets-chat</t>
+          <t>https://github.com/BeehiveInnovations/zen-mcp-server</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Self-hosted chat app for small teams</t>
+          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>9823</v>
+        <v>9834</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>26-11-2025 12:37</t>
+          <t>29-11-2025 23:17</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>09-03-2012 19:32</t>
+          <t>08-06-2025 15:36</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -9696,40 +9696,40 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BeehiveInnovations/zen-mcp-server</t>
+          <t>sdelements/lets-chat</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://github.com/BeehiveInnovations/zen-mcp-server</t>
+          <t>https://github.com/sdelements/lets-chat</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
+          <t>Self-hosted chat app for small teams</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>9818</v>
+        <v>9823</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>29-11-2025 00:02</t>
+          <t>26-11-2025 12:37</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>08-06-2025 15:36</t>
+          <t>09-03-2012 19:32</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>9798</v>
+        <v>9807</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>28-11-2025 23:29</t>
+          <t>29-11-2025 21:53</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>9756</v>
+        <v>9767</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>29-11-2025 00:16</t>
+          <t>30-11-2025 00:42</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9846,7 +9846,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>9428</v>
+        <v>9429</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>28-11-2025 23:10</t>
+          <t>30-11-2025 00:24</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>9384</v>
+        <v>9394</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>28-11-2025 20:25</t>
+          <t>29-11-2025 17:54</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>9161</v>
+        <v>9165</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>28-11-2025 22:36</t>
+          <t>29-11-2025 14:05</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -9977,11 +9977,11 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>9060</v>
+        <v>9072</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>29-11-2025 00:51</t>
+          <t>29-11-2025 19:26</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10017,7 +10017,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>9043</v>
+        <v>9054</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>28-11-2025 20:49</t>
+          <t>30-11-2025 00:13</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>9024</v>
+        <v>9033</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>28-11-2025 20:38</t>
+          <t>29-11-2025 22:21</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10107,11 +10107,11 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>8854</v>
+        <v>8860</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>28-11-2025 22:39</t>
+          <t>29-11-2025 22:26</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>8700</v>
+        <v>8704</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>28-11-2025 14:24</t>
+          <t>29-11-2025 20:31</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>8660</v>
+        <v>8665</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>28-11-2025 23:07</t>
+          <t>29-11-2025 22:48</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10237,7 +10237,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>8643</v>
+        <v>8653</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>29-11-2025 00:19</t>
+          <t>30-11-2025 00:55</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10282,11 +10282,11 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>8631</v>
+        <v>8636</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>28-11-2025 08:14</t>
+          <t>29-11-2025 17:46</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>8617</v>
+        <v>8618</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>28-11-2025 03:19</t>
+          <t>29-11-2025 16:44</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>8512</v>
+        <v>8519</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>28-11-2025 15:01</t>
+          <t>29-11-2025 21:09</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>8476</v>
+        <v>8485</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>28-11-2025 22:53</t>
+          <t>29-11-2025 23:01</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>8400</v>
+        <v>8406</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>28-11-2025 17:54</t>
+          <t>29-11-2025 21:34</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>8256</v>
+        <v>8258</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>28-11-2025 14:59</t>
+          <t>29-11-2025 18:06</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>8203</v>
+        <v>8227</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>29-11-2025 00:46</t>
+          <t>29-11-2025 23:29</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>8062</v>
+        <v>8063</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>28-11-2025 21:40</t>
+          <t>29-11-2025 03:44</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10637,11 +10637,11 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>8033</v>
+        <v>8034</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>28-11-2025 17:45</t>
+          <t>29-11-2025 10:35</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>7894</v>
+        <v>7965</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>29-11-2025 00:16</t>
+          <t>30-11-2025 00:47</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>7761</v>
+        <v>7776</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>28-11-2025 23:33</t>
+          <t>30-11-2025 00:54</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10740,90 +10740,90 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Termix-SSH/Termix</t>
+          <t>Sjj1024/PakePlus</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://github.com/Termix-SSH/Termix</t>
+          <t>https://github.com/Sjj1024/PakePlus</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Termix is a web-based server management platform with SSH terminal, tunneling, and file editing capabilities.</t>
+          <t>Turn any webpage/Vue/React and so on into desktop and mobile app under 5M with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>7710</v>
+        <v>7753</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>29-11-2025 00:05</t>
+          <t>30-11-2025 00:57</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>25-11-2024 02:46</t>
+          <t>10-09-2024 13:12</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>docker, file-management, self-hosted, ssh, ssh-tunnel</t>
+          <t>pacbao, pake, pakeplus, rust, tauri</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Sjj1024/PakePlus</t>
+          <t>Termix-SSH/Termix</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://github.com/Sjj1024/PakePlus</t>
+          <t>https://github.com/Termix-SSH/Termix</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Turn any webpage/Vue/React and so on into desktop and mobile app under 5M with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app</t>
+          <t>Termix is a web-based server management platform with SSH terminal, tunneling, and file editing capabilities.</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>7700</v>
+        <v>7727</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>28-11-2025 23:53</t>
+          <t>29-11-2025 23:54</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>10-09-2024 13:12</t>
+          <t>25-11-2024 02:46</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>pacbao, pake, pakeplus, rust, tauri</t>
+          <t>docker, file-management, self-hosted, ssh, ssh-tunnel</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10849,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>7669</v>
+        <v>7673</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>28-11-2025 10:03</t>
+          <t>29-11-2025 21:02</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -10894,11 +10894,11 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>7602</v>
+        <v>7605</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>28-11-2025 21:59</t>
+          <t>29-11-2025 19:00</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>7330</v>
+        <v>7334</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>28-11-2025 23:51</t>
+          <t>29-11-2025 19:16</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7243</v>
+        <v>7246</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>28-11-2025 23:44</t>
+          <t>29-11-2025 19:57</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -11024,7 +11024,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>7063</v>
+        <v>7067</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>28-11-2025 23:37</t>
+          <t>29-11-2025 21:19</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6763</v>
+        <v>6779</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>29-11-2025 00:26</t>
+          <t>29-11-2025 23:17</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6738</v>
+        <v>6739</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>27-11-2025 22:50</t>
+          <t>29-11-2025 16:04</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6641</v>
+        <v>6650</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>28-11-2025 23:13</t>
+          <t>30-11-2025 00:57</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6590</v>
+        <v>6589</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>28-11-2025 08:08</t>
+          <t>29-11-2025 17:34</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6569</v>
+        <v>6570</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>28-11-2025 01:01</t>
+          <t>29-11-2025 02:44</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6505</v>
+        <v>6507</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>28-11-2025 22:06</t>
+          <t>29-11-2025 23:03</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6479</v>
+        <v>6497</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>28-11-2025 20:57</t>
+          <t>30-11-2025 00:06</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6435</v>
+        <v>6440</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>28-11-2025 21:48</t>
+          <t>29-11-2025 23:46</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -11466,11 +11466,11 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6174</v>
+        <v>6183</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>28-11-2025 21:34</t>
+          <t>29-11-2025 23:15</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6131</v>
+        <v>6134</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>28-11-2025 20:45</t>
+          <t>29-11-2025 15:13</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6116</v>
+        <v>6117</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>27-11-2025 12:01</t>
+          <t>29-11-2025 19:59</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>28-11-2025 00:48</t>
+          <t>29-11-2025 15:21</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5832</v>
+        <v>5833</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>28-11-2025 12:48</t>
+          <t>29-11-2025 16:03</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>27-11-2025 03:38</t>
+          <t>29-11-2025 17:25</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -11767,7 +11767,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5614</v>
+        <v>5616</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>28-11-2025 23:39</t>
+          <t>30-11-2025 00:21</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -11857,7 +11857,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5556</v>
+        <v>5561</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>28-11-2025 23:23</t>
+          <t>29-11-2025 14:54</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -11883,12 +11883,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>father-bot/chatgpt_telegram_bot</t>
+          <t>devlikeapro/waha</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://github.com/father-bot/chatgpt_telegram_bot</t>
+          <t>https://github.com/devlikeapro/waha</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>💬 Telegram bot with ChatGPT, Python-based, using OpenAI's API.</t>
+          <t>WAHA - WhatsApp HTTP API (REST API) that you can configure in a click! 3 engines: WEBJS (browser based), NOWEB (websocket nodejs), GOWS (websocket go)</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -11906,34 +11906,34 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>29-11-2025 00:19</t>
+          <t>29-11-2025 23:36</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>05-12-2022 00:12</t>
+          <t>20-10-2020 08:49</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>chat-gpt, chatbot, openai, python, telegram</t>
+          <t>ai-bot, bot, http-api, python-bot, whatsapp</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>devlikeapro/waha</t>
+          <t>father-bot/chatgpt_telegram_bot</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://github.com/devlikeapro/waha</t>
+          <t>https://github.com/father-bot/chatgpt_telegram_bot</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -11943,120 +11943,120 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>WAHA - WhatsApp HTTP API (REST API) that you can configure in a click! 3 engines: WEBJS (browser based), NOWEB (websocket nodejs), GOWS (websocket go)</t>
+          <t>💬 Telegram bot with ChatGPT, Python-based, using OpenAI's API.</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5477</v>
+        <v>5487</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>28-11-2025 21:33</t>
+          <t>29-11-2025 15:26</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>20-10-2020 08:49</t>
+          <t>05-12-2022 00:12</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>ai-bot, bot, http-api, python-bot, whatsapp</t>
+          <t>chat-gpt, chatbot, openai, python, telegram</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>mruniquehacker/Knightbot-MD</t>
+          <t>farion1231/cc-switch</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://github.com/mruniquehacker/Knightbot-MD</t>
+          <t>https://github.com/farion1231/cc-switch</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>A simple WhatsApp bot to manage groups</t>
+          <t>A cross-platform desktop All-in-One assistant tool for Claude Code, Codex &amp; Gemini CLI.</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5328</v>
+        <v>5361</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>29-11-2025 00:51</t>
+          <t>30-11-2025 00:21</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>28-01-2025 07:02</t>
+          <t>04-08-2025 14:16</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>github-whatsapp-bot, knight, knight-bot, knight-bot-md, knightbot</t>
+          <t>ai-tools, claude-code, codex, deepseek-v3, desktop-app</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>farion1231/cc-switch</t>
+          <t>mruniquehacker/Knightbot-MD</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://github.com/farion1231/cc-switch</t>
+          <t>https://github.com/mruniquehacker/Knightbot-MD</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>A cross-platform desktop All-in-One assistant tool for Claude Code, Codex &amp; Gemini CLI.</t>
+          <t>A simple WhatsApp bot to manage groups</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>5314</v>
+        <v>5349</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>28-11-2025 22:56</t>
+          <t>30-11-2025 00:26</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>04-08-2025 14:16</t>
+          <t>28-01-2025 07:02</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>ai-tools, claude-code, codex, deepseek-v3, desktop-app</t>
+          <t>github-whatsapp-bot, knight, knight-bot, knight-bot-md, knightbot</t>
         </is>
       </c>
     </row>
@@ -12082,11 +12082,11 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5185</v>
+        <v>5211</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>29-11-2025 00:12</t>
+          <t>30-11-2025 00:33</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5117</v>
+        <v>5119</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>28-11-2025 00:05</t>
+          <t>29-11-2025 12:33</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5107</v>
+        <v>5108</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>28-11-2025 18:10</t>
+          <t>29-11-2025 18:49</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -12212,7 +12212,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5095</v>
+        <v>5100</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>28-11-2025 22:30</t>
+          <t>29-11-2025 23:00</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -12302,11 +12302,11 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>4989</v>
+        <v>4994</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>28-11-2025 23:38</t>
+          <t>29-11-2025 15:08</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>4980</v>
+        <v>4986</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>28-11-2025 20:14</t>
+          <t>30-11-2025 00:48</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>4975</v>
+        <v>4977</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>28-11-2025 19:25</t>
+          <t>29-11-2025 13:04</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -12477,7 +12477,7 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>4896</v>
+        <v>4902</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>29-11-2025 00:10</t>
+          <t>29-11-2025 15:48</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>4873</v>
+        <v>4876</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>28-11-2025 22:29</t>
+          <t>29-11-2025 16:08</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -12657,7 +12657,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4759</v>
+        <v>4761</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>28-11-2025 20:06</t>
+          <t>29-11-2025 23:16</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -12702,7 +12702,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4731</v>
+        <v>4736</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>28-11-2025 18:45</t>
+          <t>30-11-2025 00:14</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -12747,7 +12747,7 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>4708</v>
+        <v>4709</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>27-11-2025 16:14</t>
+          <t>29-11-2025 19:13</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -12792,7 +12792,7 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4690</v>
+        <v>4691</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>28-11-2025 03:58</t>
+          <t>29-11-2025 21:02</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>28-11-2025 15:39</t>
+          <t>29-11-2025 16:22</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -12882,7 +12882,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>4587</v>
+        <v>4588</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>28-11-2025 10:58</t>
+          <t>29-11-2025 17:21</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4381</v>
+        <v>4380</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>28-11-2025 13:03</t>
+          <t>29-11-2025 08:30</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>28-11-2025 17:47</t>
+          <t>29-11-2025 15:13</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -13107,7 +13107,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>4283</v>
+        <v>4285</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>28-11-2025 08:00</t>
+          <t>29-11-2025 20:46</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>28-11-2025 15:53</t>
+          <t>29-11-2025 15:19</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4181</v>
+        <v>4182</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>29-11-2025 00:40</t>
+          <t>29-11-2025 22:21</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4153</v>
+        <v>4161</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>28-11-2025 23:14</t>
+          <t>29-11-2025 21:55</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -13369,7 +13369,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>4141</v>
+        <v>4143</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>28-11-2025 19:59</t>
+          <t>29-11-2025 07:21</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>4079</v>
+        <v>4086</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>29-11-2025 00:00</t>
+          <t>29-11-2025 13:58</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -13496,7 +13496,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3963</v>
+        <v>3966</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>28-11-2025 19:52</t>
+          <t>29-11-2025 23:48</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -13541,7 +13541,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>3950</v>
+        <v>3952</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>28-11-2025 08:24</t>
+          <t>29-11-2025 23:23</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -13567,135 +13567,135 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>erxes/erxes</t>
+          <t>Sjj1024/PakePlus-Android</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://github.com/erxes/erxes</t>
+          <t>https://github.com/Sjj1024/PakePlus-Android</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Lua</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Experience Operating System (XOS) that unifies marketing, sales, operations, and support — run your core business seamlessly while replacing HubSpot, Zendesk, Linear, Wix and more.</t>
+          <t>Turn any webpage/Vue/React and so on into desktop and mobile app with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app/</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>3860</v>
+        <v>3874</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Lua</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>28-11-2025 21:26</t>
+          <t>29-11-2025 18:20</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>11-11-2016 06:54</t>
+          <t>28-03-2025 14:47</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>customer-experience, employee-experience, experience-operating-system, front-alternative, hacktoberfest</t>
+          <t>build, pacbao, pack, pake, pakeplus</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>microfeed/microfeed</t>
+          <t>erxes/erxes</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://github.com/microfeed/microfeed</t>
+          <t>https://github.com/erxes/erxes</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>a lightweight cms self-hosted on cloudflare, for podcasts, blogs, photos, videos, documents, and curated urls.</t>
+          <t>Experience Operating System (XOS) that unifies marketing, sales, operations, and support — run your core business seamlessly while replacing HubSpot, Zendesk, Linear, Wix and more.</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>3857</v>
+        <v>3861</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>27-11-2025 14:00</t>
+          <t>29-11-2025 15:12</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>25-05-2020 03:50</t>
+          <t>11-11-2016 06:54</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>cloudflare, cloudflare-d1, cloudflare-pages, cloudflare-r2, cloudflare-zero-trust</t>
+          <t>customer-experience, employee-experience, experience-operating-system, front-alternative, hacktoberfest</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Sjj1024/PakePlus-Android</t>
+          <t>microfeed/microfeed</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://github.com/Sjj1024/PakePlus-Android</t>
+          <t>https://github.com/microfeed/microfeed</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Lua</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Turn any webpage/Vue/React and so on into desktop and mobile app with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app/</t>
+          <t>a lightweight cms self-hosted on cloudflare, for podcasts, blogs, photos, videos, documents, and curated urls.</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>3845</v>
+        <v>3857</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Lua</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>29-11-2025 00:49</t>
+          <t>27-11-2025 14:00</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>28-03-2025 14:47</t>
+          <t>25-05-2020 03:50</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>build, pacbao, pack, pake, pakeplus</t>
+          <t>cloudflare, cloudflare-d1, cloudflare-pages, cloudflare-r2, cloudflare-zero-trust</t>
         </is>
       </c>
     </row>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>28-11-2025 23:51</t>
+          <t>29-11-2025 15:04</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -13766,7 +13766,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>3728</v>
+        <v>3727</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>27-11-2025 16:48</t>
+          <t>29-11-2025 06:38</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3595</v>
+        <v>3664</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>29-11-2025 00:48</t>
+          <t>30-11-2025 00:15</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -13837,12 +13837,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>lijiejie/subDomainsBrute</t>
+          <t>cloudflare/workers-sdk</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://github.com/lijiejie/subDomainsBrute</t>
+          <t>https://github.com/cloudflare/workers-sdk</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -13852,38 +13852,42 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>A fast sub domain brute tool for pentesters</t>
+          <t>⛅️ Home to Wrangler, the CLI for Cloudflare Workers®</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>3592</v>
+        <v>3595</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>28-11-2025 02:49</t>
+          <t>29-11-2025 22:52</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>01-04-2015 07:22</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr"/>
+          <t>10-11-2021 14:45</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>cli, cloudflare, cloudflare-workers, javascript, serverless</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>cloudflare/workers-sdk</t>
+          <t>lijiejie/subDomainsBrute</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://github.com/cloudflare/workers-sdk</t>
+          <t>https://github.com/lijiejie/subDomainsBrute</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -13893,32 +13897,28 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>⛅️ Home to Wrangler, the CLI for Cloudflare Workers®</t>
+          <t>A fast sub domain brute tool for pentesters</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>3591</v>
+        <v>3592</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>28-11-2025 23:19</t>
+          <t>28-11-2025 02:49</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>10-11-2021 14:45</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>cli, cloudflare, cloudflare-workers, javascript, serverless</t>
-        </is>
-      </c>
+          <t>01-04-2015 07:22</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -13982,7 +13982,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3444</v>
+        <v>3457</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>28-11-2025 17:11</t>
+          <t>30-11-2025 00:18</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -14027,7 +14027,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>28-11-2025 16:36</t>
+          <t>29-11-2025 06:49</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -14072,7 +14072,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>3343</v>
+        <v>3351</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>28-11-2025 19:01</t>
+          <t>30-11-2025 00:48</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>3310</v>
+        <v>3316</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>28-11-2025 18:21</t>
+          <t>29-11-2025 20:54</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>3299</v>
+        <v>3309</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>28-11-2025 08:36</t>
+          <t>30-11-2025 00:50</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>3286</v>
+        <v>3298</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>28-11-2025 23:51</t>
+          <t>29-11-2025 23:48</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>3236</v>
+        <v>3238</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>28-11-2025 22:25</t>
+          <t>29-11-2025 21:08</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -14342,7 +14342,7 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>3201</v>
+        <v>3205</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>28-11-2025 22:03</t>
+          <t>29-11-2025 22:08</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>3164</v>
+        <v>3173</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>28-11-2025 11:20</t>
+          <t>29-11-2025 23:27</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -14432,7 +14432,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>3162</v>
+        <v>3165</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>28-11-2025 20:08</t>
+          <t>29-11-2025 17:27</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>3153</v>
+        <v>3157</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>29-11-2025 00:45</t>
+          <t>29-11-2025 19:00</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>3152</v>
+        <v>3154</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>28-11-2025 10:45</t>
+          <t>29-11-2025 22:26</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>28-11-2025 19:47</t>
+          <t>29-11-2025 21:20</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>3146</v>
+        <v>3148</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>28-11-2025 15:58</t>
+          <t>29-11-2025 03:44</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14653,11 +14653,11 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>3059</v>
+        <v>3065</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>28-11-2025 23:52</t>
+          <t>29-11-2025 23:52</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -14693,7 +14693,7 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>3055</v>
+        <v>3058</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>28-11-2025 16:36</t>
+          <t>30-11-2025 00:10</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -14734,7 +14734,7 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>3052</v>
+        <v>3054</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>28-11-2025 11:29</t>
+          <t>30-11-2025 00:33</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14775,7 +14775,7 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>27-11-2025 23:03</t>
+          <t>29-11-2025 07:35</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -14801,88 +14801,88 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>aviaryan/awesome-no-login-web-apps</t>
+          <t>QwenLM/Qwen3-Omni</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://github.com/aviaryan/awesome-no-login-web-apps</t>
+          <t>https://github.com/QwenLM/Qwen3-Omni</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>🚀 Awesome (free) web apps that work without login</t>
+          <t>Qwen3-omni is a natively end-to-end, omni-modal LLM developed by the Qwen team at Alibaba Cloud, capable of understanding text, audio, images, and video, as well as generating speech in real time.</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>2988</v>
+        <v>2992</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>28-11-2025 18:08</t>
+          <t>29-11-2025 08:30</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>06-12-2016 10:54</t>
-        </is>
-      </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>application, applications, awesome, awesome-list, awesomeness</t>
-        </is>
-      </c>
+          <t>21-09-2025 09:46</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>QwenLM/Qwen3-Omni</t>
+          <t>aviaryan/awesome-no-login-web-apps</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://github.com/QwenLM/Qwen3-Omni</t>
+          <t>https://github.com/aviaryan/awesome-no-login-web-apps</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Qwen3-omni is a natively end-to-end, omni-modal LLM developed by the Qwen team at Alibaba Cloud, capable of understanding text, audio, images, and video, as well as generating speech in real time.</t>
+          <t>🚀 Awesome (free) web apps that work without login</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>2988</v>
+        <v>2991</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>28-11-2025 22:42</t>
+          <t>29-11-2025 18:37</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>21-09-2025 09:46</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr"/>
+          <t>06-12-2016 10:54</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>application, applications, awesome, awesome-list, awesomeness</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>2950</v>
+        <v>2958</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>28-11-2025 23:45</t>
+          <t>29-11-2025 19:23</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>28-11-2025 15:28</t>
+          <t>29-11-2025 01:22</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -15131,11 +15131,11 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>28-11-2025 18:38</t>
+          <t>29-11-2025 19:42</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -15171,7 +15171,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>2820</v>
+        <v>2822</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>28-11-2025 14:17</t>
+          <t>29-11-2025 16:23</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -15216,7 +15216,7 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>2808</v>
+        <v>2809</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>28-11-2025 19:37</t>
+          <t>29-11-2025 23:37</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>2801</v>
+        <v>2803</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>28-11-2025 06:56</t>
+          <t>29-11-2025 09:52</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -15283,135 +15283,135 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>frappe/helpdesk</t>
+          <t>Sjj1024/PakePlus-iOS</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://github.com/frappe/helpdesk</t>
+          <t>https://github.com/Sjj1024/PakePlus-iOS</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Modern, Streamlined, Free and Open Source Customer Service Software</t>
+          <t>Turn any webpage/Vue/React and so on into desktop and mobile app with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app/</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>2785</v>
+        <v>2791</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>28-11-2025 23:25</t>
+          <t>30-11-2025 00:24</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>21-10-2021 08:09</t>
+          <t>28-03-2025 14:46</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>customer-support, foss, frappe, helpdesk, helpscout</t>
+          <t>build, ipa, pacbao, package, pake</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>rsxdalv/TTS-WebUI</t>
+          <t>frappe/helpdesk</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://github.com/rsxdalv/TTS-WebUI</t>
+          <t>https://github.com/frappe/helpdesk</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>A single Gradio + React WebUI with extensions for ACE-Step, Kimi Audio, Piper TTS, GPT-SoVITS, CosyVoice, XTTSv2, DIA, Kokoro, OpenVoice, ParlerTTS, Stable Audio, MMS, StyleTTS2, MAGNet, AudioGen, ...</t>
+          <t>Modern, Streamlined, Free and Open Source Customer Service Software</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>2768</v>
+        <v>2787</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Vue</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>28-11-2025 21:07</t>
+          <t>29-11-2025 21:47</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>27-04-2023 18:32</t>
+          <t>21-10-2021 08:09</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>ace-step, ai, audio-generation, cosyvoice, generative-ai</t>
+          <t>customer-support, foss, frappe, helpdesk, helpscout</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Sjj1024/PakePlus-iOS</t>
+          <t>rsxdalv/TTS-WebUI</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://github.com/Sjj1024/PakePlus-iOS</t>
+          <t>https://github.com/rsxdalv/TTS-WebUI</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Turn any webpage/Vue/React and so on into desktop and mobile app with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app/</t>
+          <t>A single Gradio + React WebUI with extensions for ACE-Step, Kimi Audio, Piper TTS, GPT-SoVITS, CosyVoice, XTTSv2, DIA, Kokoro, OpenVoice, ParlerTTS, Stable Audio, MMS, StyleTTS2, MAGNet, AudioGen, ...</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>2761</v>
+        <v>2769</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>29-11-2025 00:49</t>
+          <t>29-11-2025 04:26</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>28-03-2025 14:46</t>
+          <t>27-04-2023 18:32</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>build, ipa, pacbao, package, pake</t>
+          <t>ace-step, ai, audio-generation, cosyvoice, generative-ai</t>
         </is>
       </c>
     </row>
@@ -15437,11 +15437,11 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>28-11-2025 21:50</t>
+          <t>29-11-2025 19:07</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -15458,26 +15458,26 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>LLM-Red-Team/deepseek-free-api</t>
+          <t>easychen/CookieCloud</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://github.com/LLM-Red-Team/deepseek-free-api</t>
+          <t>https://github.com/easychen/CookieCloud</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>🚀 DeepSeek-V3 &amp; R1大模型逆向API【特长：良心厂商】（官方贼便宜，建议直接走官方），支持高速流式输出、多轮对话，联网搜索，R1深度思考，零配置部署，多路token支持，仅供测试，如需商用请前往官方开放平台。</t>
+          <t>CookieCloud是一个和自架服务器同步浏览器Cookie和LocalStorage的小工具，支持端对端加密，可设定同步时间间隔。本仓库包含了插件和服务器端源码。CookieCloud is a small tool for synchronizing browser cookies and LocalStorage with a self-hosted server. It suppo...</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -15486,43 +15486,43 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>28-11-2025 07:21</t>
+          <t>29-11-2025 08:57</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>07-05-2024 06:23</t>
+          <t>17-01-2023 03:11</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>chat-api, chatbot, chatgpt-api, deepseek, deepseek-api</t>
+          <t>cookie, cookies</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>easychen/CookieCloud</t>
+          <t>LLM-Red-Team/deepseek-free-api</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://github.com/easychen/CookieCloud</t>
+          <t>https://github.com/LLM-Red-Team/deepseek-free-api</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>CookieCloud是一个和自架服务器同步浏览器Cookie和LocalStorage的小工具，支持端对端加密，可设定同步时间间隔。本仓库包含了插件和服务器端源码。CookieCloud is a small tool for synchronizing browser cookies and LocalStorage with a self-hosted server. It suppo...</t>
+          <t>🚀 DeepSeek-V3 &amp; R1大模型逆向API【特长：良心厂商】（官方贼便宜，建议直接走官方），支持高速流式输出、多轮对话，联网搜索，R1深度思考，零配置部署，多路token支持，仅供测试，如需商用请前往官方开放平台。</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>2744</v>
+        <v>2746</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -15531,17 +15531,17 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>28-11-2025 16:04</t>
+          <t>28-11-2025 07:21</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>17-01-2023 03:11</t>
+          <t>07-05-2024 06:23</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>cookie, cookies</t>
+          <t>chat-api, chatbot, chatgpt-api, deepseek, deepseek-api</t>
         </is>
       </c>
     </row>
@@ -15567,7 +15567,7 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>28-11-2025 23:47</t>
+          <t>29-11-2025 14:01</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -15612,11 +15612,11 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2682</v>
+        <v>2690</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>29-11-2025 00:37</t>
+          <t>30-11-2025 00:44</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -15652,7 +15652,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>28-11-2025 16:06</t>
+          <t>29-11-2025 18:09</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>28-11-2025 22:14</t>
+          <t>30-11-2025 00:47</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -15742,7 +15742,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2521</v>
+        <v>2526</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>28-11-2025 16:28</t>
+          <t>29-11-2025 17:24</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15787,7 +15787,7 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>28-11-2025 16:24</t>
+          <t>29-11-2025 21:54</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -15832,11 +15832,11 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>2452</v>
+        <v>2457</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>28-11-2025 20:40</t>
+          <t>29-11-2025 23:49</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15868,7 +15868,7 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>28-11-2025 13:48</t>
+          <t>29-11-2025 11:09</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>27-11-2025 06:24</t>
+          <t>29-11-2025 18:28</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16012,7 +16012,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>28-11-2025 17:44</t>
+          <t>29-11-2025 21:09</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>28-11-2025 15:10</t>
+          <t>29-11-2025 15:16</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -16134,7 +16134,7 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>28-11-2025 17:54</t>
+          <t>29-11-2025 08:44</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -16179,7 +16179,7 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>28-11-2025 14:39</t>
+          <t>29-11-2025 15:47</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16269,11 +16269,11 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>28-11-2025 08:06</t>
+          <t>29-11-2025 08:39</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>28-11-2025 17:52</t>
+          <t>29-11-2025 15:46</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -16354,7 +16354,7 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>29-11-2025 00:30</t>
+          <t>29-11-2025 09:58</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -16399,7 +16399,7 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>27-11-2025 17:32</t>
+          <t>29-11-2025 12:40</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>28-11-2025 13:00</t>
+          <t>29-11-2025 17:27</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -16485,7 +16485,7 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>28-11-2025 22:56</t>
+          <t>29-11-2025 15:16</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -16530,7 +16530,7 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>28-11-2025 21:55</t>
+          <t>29-11-2025 20:06</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -16575,7 +16575,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>28-11-2025 03:11</t>
+          <t>29-11-2025 02:50</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>28-11-2025 18:42</t>
+          <t>29-11-2025 19:13</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>27-11-2025 18:06</t>
+          <t>29-11-2025 11:24</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16797,7 +16797,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>28-11-2025 09:54</t>
+          <t>29-11-2025 07:45</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16833,7 +16833,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>28-11-2025 13:03</t>
+          <t>29-11-2025 09:32</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>26-11-2025 20:29</t>
+          <t>29-11-2025 16:50</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16923,7 +16923,7 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>27-11-2025 10:18</t>
+          <t>30-11-2025 00:37</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -17013,7 +17013,7 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>28-11-2025 12:29</t>
+          <t>29-11-2025 18:19</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17058,7 +17058,7 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>28-11-2025 14:00</t>
+          <t>29-11-2025 20:30</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -17103,11 +17103,11 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>27-11-2025 17:56</t>
+          <t>29-11-2025 20:36</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17124,135 +17124,135 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>VisActor/VChart</t>
+          <t>Marktechpost/AI-Tutorial-Codes-Included</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://github.com/VisActor/VChart</t>
+          <t>https://github.com/Marktechpost/AI-Tutorial-Codes-Included</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>VChart, more than just a cross-platform charting library, but also an expressive data storyteller.</t>
+          <t>Codes/Notebooks for AI Projects</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>1716</v>
+        <v>1724</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>28-11-2025 08:15</t>
+          <t>29-11-2025 22:52</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>05-06-2023 05:41</t>
+          <t>15-05-2025 09:00</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>3dchart, canvas, canvas2d, chart, charting-library</t>
+          <t>aiagents, artificial-intelligence, data-science, dataengineering, deep-learning</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Marktechpost/AI-Tutorial-Codes-Included</t>
+          <t>xoureldeen/Vectras-VM-Android</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://github.com/Marktechpost/AI-Tutorial-Codes-Included</t>
+          <t>https://github.com/xoureldeen/Vectras-VM-Android</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Codes/Notebooks for AI Projects</t>
+          <t>It's a Virtual Machine App for Android Which is Based on QEMU</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>28-11-2025 12:24</t>
+          <t>29-11-2025 14:49</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>15-05-2025 09:00</t>
+          <t>08-11-2023 00:09</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>aiagents, artificial-intelligence, data-science, dataengineering, deep-learning</t>
+          <t>android, emulator, limbo, qemu, vectras-android</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>xoureldeen/Vectras-VM-Android</t>
+          <t>VisActor/VChart</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://github.com/xoureldeen/Vectras-VM-Android</t>
+          <t>https://github.com/VisActor/VChart</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>It's a Virtual Machine App for Android Which is Based on QEMU</t>
+          <t>VChart, more than just a cross-platform charting library, but also an expressive data storyteller.</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>28-11-2025 13:15</t>
+          <t>28-11-2025 08:15</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>08-11-2023 00:09</t>
+          <t>05-06-2023 05:41</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>android, emulator, limbo, qemu, vectras-android</t>
+          <t>3dchart, canvas, canvas2d, chart, charting-library</t>
         </is>
       </c>
     </row>
@@ -17364,7 +17364,7 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>1650</v>
+        <v>1657</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>28-11-2025 23:48</t>
+          <t>29-11-2025 12:03</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>28-11-2025 17:52</t>
+          <t>29-11-2025 22:46</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -17454,7 +17454,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>28-11-2025 14:25</t>
+          <t>29-11-2025 14:12</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17525,90 +17525,90 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>u14app/gemini-next-chat</t>
+          <t>ling-drag0n/CloudPaste</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://github.com/u14app/gemini-next-chat</t>
+          <t>https://github.com/ling-drag0n/CloudPaste</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Deploy your private Gemini application for free with one click, supporting Gemini 1.5, Gemini 2.0 models.</t>
+          <t>A Cloudflare-based online text/file sharing platform that supports multiple syntax Markdown rendering, self-destructing messages, S3/WebDav aggregated storage, password protection, and more. It can...</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>28-11-2025 08:18</t>
+          <t>29-11-2025 19:54</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>27-12-2023 08:48</t>
+          <t>02-04-2025 10:23</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>ai, gemini, gemini-15-flash, gemini-15-pro, gemini-2</t>
+          <t>b2, cloudflare, cloudflare-workers, docker, markdown</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ling-drag0n/CloudPaste</t>
+          <t>u14app/gemini-next-chat</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://github.com/ling-drag0n/CloudPaste</t>
+          <t>https://github.com/u14app/gemini-next-chat</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>A Cloudflare-based online text/large file sharing platform that supports multiple syntax Markdown rendering, self-destructing messages, S3/WebDav aggregated storage, password protection, and more. ...</t>
+          <t>Deploy your private Gemini application for free with one click, supporting Gemini 1.5, Gemini 2.0 models.</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>28-11-2025 16:48</t>
+          <t>29-11-2025 17:17</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>02-04-2025 10:23</t>
+          <t>27-12-2023 08:48</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>b2, cloudflare, cloudflare-workers, docker, markdown</t>
+          <t>ai, gemini, gemini-15-flash, gemini-15-pro, gemini-2</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17634,7 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>28-11-2025 14:24</t>
+          <t>29-11-2025 15:33</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -17679,11 +17679,11 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>1567</v>
+        <v>1570</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>28-11-2025 19:46</t>
+          <t>29-11-2025 19:08</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -17719,11 +17719,11 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>28-11-2025 16:48</t>
+          <t>29-11-2025 23:27</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -17759,7 +17759,7 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>25-11-2025 16:04</t>
+          <t>29-11-2025 07:12</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17804,7 +17804,7 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>28-11-2025 22:57</t>
+          <t>29-11-2025 19:42</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17894,7 +17894,7 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>1461</v>
+        <v>1466</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>28-11-2025 23:04</t>
+          <t>29-11-2025 17:21</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -17939,11 +17939,11 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>29-11-2025 00:37</t>
+          <t>30-11-2025 00:37</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>28-11-2025 19:32</t>
+          <t>29-11-2025 11:31</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -18056,7 +18056,7 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>28-11-2025 20:18</t>
+          <t>30-11-2025 00:59</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>29-11-2025 00:46</t>
+          <t>29-11-2025 01:14</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -18142,7 +18142,7 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>28-11-2025 04:48</t>
+          <t>29-11-2025 17:51</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>1328</v>
+        <v>1340</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>28-11-2025 23:00</t>
+          <t>30-11-2025 00:17</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -18232,7 +18232,7 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>27-11-2025 23:58</t>
+          <t>29-11-2025 10:37</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -18277,7 +18277,7 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>28-11-2025 19:52</t>
+          <t>29-11-2025 23:47</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18412,7 +18412,7 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>27-11-2025 07:19</t>
+          <t>29-11-2025 18:29</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -18438,22 +18438,22 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>sauravpanda/BrowserAI</t>
+          <t>sickcodes/dock-droid</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://github.com/sauravpanda/BrowserAI</t>
+          <t>https://github.com/sickcodes/dock-droid</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Run local LLMs like llama, deepseek-distill, kokoro and more inside your browser</t>
+          <t>Docker Android - Run QEMU Android in a Docker! X11 Forwarding! CI/CD for Android!</t>
         </is>
       </c>
       <c r="E411" t="n">
@@ -18461,67 +18461,67 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Dockerfile</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>28-11-2025 02:20</t>
+          <t>29-11-2025 03:51</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>08-01-2025 00:26</t>
+          <t>03-07-2021 22:06</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>agents, ai, llama, llm, llm-inference</t>
+          <t>android, docker, droid, kvm, linux</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>sickcodes/dock-droid</t>
+          <t>sauravpanda/BrowserAI</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://github.com/sickcodes/dock-droid</t>
+          <t>https://github.com/sauravpanda/BrowserAI</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Docker Android - Run QEMU Android in a Docker! X11 Forwarding! CI/CD for Android!</t>
+          <t>Run local LLMs like llama, deepseek-distill, kokoro and more inside your browser</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Dockerfile</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>26-11-2025 05:22</t>
+          <t>28-11-2025 02:20</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>03-07-2021 22:06</t>
+          <t>08-01-2025 00:26</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>android, docker, droid, kvm, linux</t>
+          <t>agents, ai, llama, llm, llm-inference</t>
         </is>
       </c>
     </row>
@@ -18722,7 +18722,7 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>1195</v>
+        <v>1207</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>28-11-2025 23:15</t>
+          <t>30-11-2025 00:39</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -18763,7 +18763,7 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>25-11-2025 03:55</t>
+          <t>29-11-2025 15:34</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>28-11-2025 19:45</t>
+          <t>29-11-2025 17:09</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -18894,7 +18894,7 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>28-11-2025 13:02</t>
+          <t>29-11-2025 22:53</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -18920,22 +18920,22 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>AndnixSH/APKToolGUI</t>
+          <t>rizwansoaib/whatsapp-monitor</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://github.com/AndnixSH/APKToolGUI</t>
+          <t>https://github.com/rizwansoaib/whatsapp-monitor</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>GUI for apktool, signapk, zipalign and baksmali utilities.</t>
+          <t>Free Whatsapp Online Tracker App Android,iOS, Windows, Linux,MAC📲    WhatsApp last seen tracker   [Get Notification 🔔  and history 📜 of Online WhatsApp Contact]</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -18943,67 +18943,67 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>28-11-2025 22:12</t>
+          <t>29-11-2025 21:45</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>05-08-2021 16:11</t>
+          <t>06-06-2019 13:09</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>apk, apk-tool-gui, apktool, gui, gui-apk-tool</t>
+          <t>android-notification-service, android-whatsapp-monitor, android-whatsapp-tracker, browser-extension, chrome-extensions</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>rizwansoaib/whatsapp-monitor</t>
+          <t>AndnixSH/APKToolGUI</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://github.com/rizwansoaib/whatsapp-monitor</t>
+          <t>https://github.com/AndnixSH/APKToolGUI</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Free Whatsapp Online Tracker App Android,iOS, Windows, Linux,MAC📲    WhatsApp last seen tracker   [Get Notification 🔔  and history 📜 of Online WhatsApp Contact]</t>
+          <t>GUI for apktool, signapk, zipalign and baksmali utilities.</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>27-11-2025 01:51</t>
+          <t>28-11-2025 22:12</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>06-06-2019 13:09</t>
+          <t>05-08-2021 16:11</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>android-notification-service, android-whatsapp-monitor, android-whatsapp-tracker, browser-extension, chrome-extensions</t>
+          <t>apk, apk-tool-gui, apktool, gui, gui-apk-tool</t>
         </is>
       </c>
     </row>
@@ -19055,88 +19055,88 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>jasperan/whatsapp-osint</t>
+          <t>kleneway/pastemax</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://github.com/jasperan/whatsapp-osint</t>
+          <t>https://github.com/kleneway/pastemax</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>WhatsApp spy - logs online/offline events from ANYONE in the world</t>
+          <t>A simple tool to select files from a repository to copy/paste into an LLM</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>27-11-2025 22:44</t>
+          <t>29-11-2025 22:01</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>14-11-2019 15:27</t>
-        </is>
-      </c>
-      <c r="I425" t="inlineStr">
-        <is>
-          <t>bot, logger, osint, python, selenium</t>
-        </is>
-      </c>
+          <t>01-03-2025 22:16</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>kleneway/pastemax</t>
+          <t>jasperan/whatsapp-osint</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://github.com/kleneway/pastemax</t>
+          <t>https://github.com/jasperan/whatsapp-osint</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>A simple tool to select files from a repository to copy/paste into an LLM</t>
+          <t>WhatsApp spy - logs online/offline events from ANYONE in the world</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>27-11-2025 09:33</t>
+          <t>30-11-2025 00:52</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>01-03-2025 22:16</t>
-        </is>
-      </c>
-      <c r="I426" t="inlineStr"/>
+          <t>14-11-2019 15:27</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>bot, logger, osint, python, selenium</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -19160,7 +19160,7 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>22-11-2025 10:09</t>
+          <t>29-11-2025 01:48</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -19290,7 +19290,7 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>14-11-2025 19:13</t>
+          <t>29-11-2025 14:14</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -19335,7 +19335,7 @@
         </is>
       </c>
       <c r="E431" t="n">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>28-11-2025 01:51</t>
+          <t>29-11-2025 10:05</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -19425,11 +19425,11 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>28-11-2025 22:17</t>
+          <t>29-11-2025 14:51</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -19506,7 +19506,7 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>27-11-2025 15:37</t>
+          <t>29-11-2025 13:56</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -19633,7 +19633,7 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>28-11-2025 13:29</t>
+          <t>29-11-2025 15:47</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>28-11-2025 21:16</t>
+          <t>29-11-2025 13:05</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>28-11-2025 04:00</t>
+          <t>29-11-2025 05:22</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -19768,7 +19768,7 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>28-11-2025 23:22</t>
+          <t>29-11-2025 14:55</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -19813,7 +19813,7 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>25-11-2025 10:56</t>
+          <t>29-11-2025 17:28</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -19854,7 +19854,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>29-11-2025 00:18</t>
+          <t>29-11-2025 00:52</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -19989,11 +19989,11 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>28-11-2025 00:50</t>
+          <t>29-11-2025 22:44</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -20029,7 +20029,7 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>28-11-2025 16:11</t>
+          <t>29-11-2025 21:38</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -20074,7 +20074,7 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>28-11-2025 10:20</t>
+          <t>29-11-2025 18:10</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -20115,7 +20115,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>27-11-2025 15:46</t>
+          <t>29-11-2025 11:40</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>28-11-2025 15:39</t>
+          <t>29-11-2025 19:29</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>28-11-2025 13:26</t>
+          <t>29-11-2025 19:30</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -20385,7 +20385,7 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>27-11-2025 07:27</t>
+          <t>29-11-2025 06:38</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -20556,7 +20556,7 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>28-11-2025 15:57</t>
+          <t>29-11-2025 17:43</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -20601,7 +20601,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>28-11-2025 08:24</t>
+          <t>29-11-2025 09:12</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -20736,11 +20736,11 @@
         </is>
       </c>
       <c r="E463" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>26-11-2025 10:24</t>
+          <t>29-11-2025 20:40</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -20757,83 +20757,83 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>MrTurvey/flareprox</t>
+          <t>The-Osint-Toolbox/Social-Media-OSINT</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://github.com/MrTurvey/flareprox</t>
+          <t>https://github.com/The-Osint-Toolbox/Social-Media-OSINT</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Use Cloudflare to create HTTP pass-through proxies for unique IP rotation, similar to fireprox</t>
+          <t>Social Media OSINT collection containing - tools, techniques &amp; tradecraft.</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>708</v>
-      </c>
-      <c r="F464" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
+        <v>709</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>27-11-2025 21:22</t>
+          <t>30-11-2025 00:43</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>26-09-2025 11:15</t>
-        </is>
-      </c>
-      <c r="I464" t="inlineStr"/>
+          <t>19-03-2023 16:19</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>bluesky, dating-app, discord, facebook, instagram</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>The-Osint-Toolbox/Social-Media-OSINT</t>
+          <t>MrTurvey/flareprox</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://github.com/The-Osint-Toolbox/Social-Media-OSINT</t>
+          <t>https://github.com/MrTurvey/flareprox</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Social Media OSINT collection containing - tools, techniques &amp; tradecraft.</t>
+          <t>Use Cloudflare to create HTTP pass-through proxies for unique IP rotation, similar to fireprox</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>707</v>
+        <v>708</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>27-11-2025 19:48</t>
+          <t>27-11-2025 21:22</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>19-03-2023 16:19</t>
-        </is>
-      </c>
-      <c r="I465" t="inlineStr">
-        <is>
-          <t>bluesky, dating-app, discord, facebook, instagram</t>
-        </is>
-      </c>
+          <t>26-09-2025 11:15</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -20857,7 +20857,7 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>24-11-2025 15:33</t>
+          <t>29-11-2025 16:46</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -20898,7 +20898,7 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>27-11-2025 12:12</t>
+          <t>29-11-2025 14:03</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -21014,12 +21014,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>IdefaSoft/Emora-Project</t>
+          <t>idefasoft/Emora-Project</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://github.com/IdefaSoft/Emora-Project</t>
+          <t>https://github.com/idefasoft/Emora-Project</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -21177,7 +21177,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>26-11-2025 23:27</t>
+          <t>29-11-2025 17:19</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -21213,7 +21213,7 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>28-11-2025 16:35</t>
+          <t>29-11-2025 19:09</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -21258,7 +21258,7 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>27-11-2025 04:10</t>
+          <t>29-11-2025 09:57</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -21348,7 +21348,7 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>27-11-2025 06:25</t>
+          <t>29-11-2025 14:12</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -21479,7 +21479,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>28-11-2025 15:30</t>
+          <t>29-11-2025 21:31</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -21524,7 +21524,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>28-11-2025 14:25</t>
+          <t>29-11-2025 22:21</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -21565,7 +21565,7 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>28-11-2025 02:59</t>
+          <t>29-11-2025 17:30</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -21591,52 +21591,57 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>cloudcommunity/Free-Hosting</t>
+          <t>BlackTechX011/Hacx-GPT</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://github.com/cloudcommunity/Free-Hosting</t>
+          <t>https://github.com/BlackTechX011/Hacx-GPT</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Overview of free hosting offers, incl. compute hosting, app hosting, databases, serverless etc.</t>
+          <t>Hacx GPT a powerful, evil brother of WormGPT.</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>506</v>
+        <v>508</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>24-11-2025 01:03</t>
+          <t>29-11-2025 21:43</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>22-08-2020 13:48</t>
+          <t>15-02-2024 06:58</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>cdn, free, free-for-developers, free-hosting, free-software</t>
+          <t>ai, blacktechx, blacktechx011, chatbot, chatgpt</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>BlackTechX011/Hacx-GPT</t>
+          <t>haileyydev/maildrop</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://github.com/BlackTechX011/Hacx-GPT</t>
+          <t>https://github.com/haileyydev/maildrop</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -21646,75 +21651,70 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Hacx GPT a powerful, evil brother of WormGPT.</t>
+          <t>✉️ A self hostable disposable email service</t>
         </is>
       </c>
       <c r="E484" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>28-11-2025 21:15</t>
+          <t>29-11-2025 22:09</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>15-02-2024 06:58</t>
+          <t>13-09-2025 06:33</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>ai, blacktechx, blacktechx011, chatbot, chatgpt</t>
+          <t>disposable-email, email, webiste</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>haileyydev/maildrop</t>
+          <t>cloudcommunity/Free-Hosting</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://github.com/haileyydev/maildrop</t>
+          <t>https://github.com/cloudcommunity/Free-Hosting</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>✉️ A self hostable disposable email service</t>
+          <t>Overview of free hosting offers, incl. compute hosting, app hosting, databases, serverless etc.</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>505</v>
-      </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
+        <v>506</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>27-11-2025 14:42</t>
+          <t>24-11-2025 01:03</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>13-09-2025 06:33</t>
+          <t>22-08-2020 13:48</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>disposable-email, email, webiste</t>
+          <t>cdn, free, free-for-developers, free-hosting, free-software</t>
         </is>
       </c>
     </row>
@@ -21826,7 +21826,7 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>27-11-2025 10:25</t>
+          <t>29-11-2025 04:04</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -21957,7 +21957,7 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>22-11-2025 17:48</t>
+          <t>29-11-2025 14:45</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>28-11-2025 07:57</t>
+          <t>30-11-2025 00:25</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -22088,7 +22088,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>26-11-2025 20:47</t>
+          <t>29-11-2025 16:19</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -22277,7 +22277,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>28-11-2025 07:57</t>
+          <t>29-11-2025 14:40</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -22313,7 +22313,7 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>27-11-2025 20:06</t>
+          <t>29-11-2025 05:35</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -22339,90 +22339,90 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>miroslavpejic85/mirotalkwebrtc</t>
+          <t>offerrall/FuncToWeb</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://github.com/miroslavpejic85/mirotalkwebrtc</t>
+          <t>https://github.com/offerrall/FuncToWeb</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>🛠 MiroTalk's WebRTC rooms scheduler.</t>
+          <t>Minimal-boilerplate web apps from Python functions.</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>26-11-2025 22:21</t>
+          <t>29-11-2025 16:18</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>27-12-2022 12:57</t>
+          <t>05-10-2025 02:14</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>admin-dashboard, awesome, cloud, collaboration, conferencing</t>
+          <t>css, fastapi, html, javascript, pydantic</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>offerrall/FuncToWeb</t>
+          <t>miroslavpejic85/mirotalkwebrtc</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://github.com/offerrall/FuncToWeb</t>
+          <t>https://github.com/miroslavpejic85/mirotalkwebrtc</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Minimal-boilerplate web apps from Python functions.</t>
+          <t>🛠 MiroTalk's WebRTC rooms scheduler.</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>26-11-2025 15:30</t>
+          <t>26-11-2025 22:21</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>05-10-2025 02:14</t>
+          <t>27-12-2022 12:57</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>css, fastapi, html, javascript, pydantic</t>
+          <t>admin-dashboard, awesome, cloud, collaboration, conferencing</t>
         </is>
       </c>
     </row>
@@ -22448,11 +22448,11 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>21-11-2025 00:22</t>
+          <t>29-11-2025 05:14</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -22570,7 +22570,7 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>28-11-2025 16:10</t>
+          <t>29-11-2025 18:48</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -22611,7 +22611,7 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>28-11-2025 23:27</t>
+          <t>29-11-2025 15:58</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -22868,7 +22868,7 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>26-11-2025 13:20</t>
+          <t>29-11-2025 13:28</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -22958,7 +22958,7 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>24-11-2025 19:05</t>
+          <t>29-11-2025 05:08</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -23306,11 +23306,11 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>28-11-2025 14:46</t>
+          <t>29-11-2025 08:04</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -23355,7 +23355,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>14-11-2025 06:21</t>
+          <t>29-11-2025 16:37</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -23432,7 +23432,7 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>29-11-2025 00:50</t>
+          <t>30-11-2025 00:49</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -23563,11 +23563,11 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>28-11-2025 03:31</t>
+          <t>29-11-2025 21:22</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -23693,11 +23693,11 @@
         </is>
       </c>
       <c r="E531" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>28-11-2025 08:50</t>
+          <t>29-11-2025 09:02</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>28-11-2025 13:44</t>
+          <t>29-11-2025 17:03</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -23778,7 +23778,7 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>24-11-2025 23:46</t>
+          <t>29-11-2025 12:12</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -24026,7 +24026,7 @@
         </is>
       </c>
       <c r="E539" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>15-11-2025 19:40</t>
+          <t>29-11-2025 05:36</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -24161,7 +24161,7 @@
         </is>
       </c>
       <c r="E542" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>23-11-2025 08:59</t>
+          <t>29-11-2025 09:33</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>446219</v>
+        <v>446656</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05-12-2025 00:52</t>
+          <t>06-12-2025 00:49</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>420103</v>
+        <v>420358</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05-12-2025 00:53</t>
+          <t>06-12-2025 00:49</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>382644</v>
+        <v>382772</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05-12-2025 00:50</t>
+          <t>06-12-2025 00:33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>272437</v>
+        <v>272571</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05-12-2025 00:31</t>
+          <t>06-12-2025 00:41</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>261486</v>
+        <v>261654</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05-12-2025 00:23</t>
+          <t>06-12-2025 00:47</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>251740</v>
+        <v>251824</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05-12-2025 00:51</t>
+          <t>06-12-2025 00:50</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>198688</v>
+        <v>198714</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05-12-2025 00:22</t>
+          <t>06-12-2025 00:44</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>196768</v>
+        <v>196873</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05-12-2025 00:25</t>
+          <t>06-12-2025 00:45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>183121</v>
+        <v>183153</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05-12-2025 00:20</t>
+          <t>05-12-2025 21:28</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>160654</v>
+        <v>160844</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05-12-2025 00:37</t>
+          <t>06-12-2025 00:46</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>158396</v>
+        <v>158493</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>04-12-2025 23:41</t>
+          <t>06-12-2025 00:30</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>138424</v>
+        <v>138513</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05-12-2025 00:42</t>
+          <t>06-12-2025 00:31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>137140</v>
+        <v>137249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05-12-2025 00:52</t>
+          <t>05-12-2025 23:59</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131994</v>
+        <v>132051</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05-12-2025 00:26</t>
+          <t>06-12-2025 00:12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>126231</v>
+        <v>126259</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05-12-2025 00:47</t>
+          <t>05-12-2025 23:50</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>116968</v>
+        <v>117062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05-12-2025 00:46</t>
+          <t>06-12-2025 00:48</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115952</v>
+        <v>115983</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05-12-2025 00:08</t>
+          <t>05-12-2025 23:50</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1257,11 +1257,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115818</v>
+        <v>115819</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>04-12-2025 19:20</t>
+          <t>06-12-2025 00:39</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>104562</v>
+        <v>104594</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05-12-2025 00:37</t>
+          <t>06-12-2025 00:12</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103481</v>
+        <v>103517</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05-12-2025 00:40</t>
+          <t>06-12-2025 00:45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101995</v>
+        <v>102050</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>04-12-2025 23:23</t>
+          <t>06-12-2025 00:33</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>99386</v>
+        <v>99572</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05-12-2025 00:51</t>
+          <t>06-12-2025 00:50</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>95610</v>
+        <v>95784</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05-12-2025 00:53</t>
+          <t>06-12-2025 00:32</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>94769</v>
+        <v>94819</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>04-12-2025 23:23</t>
+          <t>05-12-2025 23:51</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>92988</v>
+        <v>92997</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>04-12-2025 23:07</t>
+          <t>05-12-2025 23:52</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>92659</v>
+        <v>92730</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05-12-2025 00:50</t>
+          <t>06-12-2025 00:37</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1647,11 +1647,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>88554</v>
+        <v>88604</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05-12-2025 00:49</t>
+          <t>06-12-2025 00:05</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>86588</v>
+        <v>86601</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>04-12-2025 22:32</t>
+          <t>06-12-2025 00:10</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>85823</v>
+        <v>85972</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05-12-2025 00:49</t>
+          <t>06-12-2025 00:42</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>85663</v>
+        <v>85730</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05-12-2025 00:50</t>
+          <t>06-12-2025 00:37</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>83829</v>
+        <v>83886</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>05-12-2025 00:44</t>
+          <t>06-12-2025 00:52</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>81632</v>
+        <v>81722</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>05-12-2025 00:24</t>
+          <t>06-12-2025 00:30</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>80312</v>
+        <v>80332</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>04-12-2025 23:23</t>
+          <t>06-12-2025 00:37</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>79331</v>
+        <v>79389</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>05-12-2025 00:03</t>
+          <t>05-12-2025 23:51</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>77275</v>
+        <v>77302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>05-12-2025 00:19</t>
+          <t>06-12-2025 00:43</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>76121</v>
+        <v>76144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>04-12-2025 22:15</t>
+          <t>06-12-2025 00:30</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>70713</v>
+        <v>70728</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>04-12-2025 21:38</t>
+          <t>05-12-2025 18:54</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>69121</v>
+        <v>69193</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>05-12-2025 00:21</t>
+          <t>06-12-2025 00:38</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>68549</v>
+        <v>68625</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>04-12-2025 23:46</t>
+          <t>06-12-2025 00:36</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2222,11 +2222,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>67033</v>
+        <v>67045</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>04-12-2025 23:23</t>
+          <t>05-12-2025 22:18</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>65609</v>
+        <v>65619</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>04-12-2025 23:32</t>
+          <t>06-12-2025 00:13</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2307,11 +2307,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>63949</v>
+        <v>63963</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>04-12-2025 23:23</t>
+          <t>05-12-2025 23:51</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>60181</v>
+        <v>60220</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>05-12-2025 00:20</t>
+          <t>05-12-2025 23:53</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>59831</v>
+        <v>59856</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>05-12-2025 00:28</t>
+          <t>06-12-2025 00:07</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2437,11 +2437,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>57045</v>
+        <v>57061</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05-12-2025 00:42</t>
+          <t>06-12-2025 00:33</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>56781</v>
+        <v>56825</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>05-12-2025 00:30</t>
+          <t>05-12-2025 23:50</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2518,11 +2518,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53902</v>
+        <v>53920</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>04-12-2025 23:23</t>
+          <t>05-12-2025 23:51</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53885</v>
+        <v>53912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>05-12-2025 00:46</t>
+          <t>05-12-2025 22:20</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53788</v>
+        <v>53798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>04-12-2025 22:40</t>
+          <t>05-12-2025 23:53</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>52216</v>
+        <v>52223</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>04-12-2025 13:52</t>
+          <t>05-12-2025 23:53</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51852</v>
+        <v>51881</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>04-12-2025 23:26</t>
+          <t>05-12-2025 23:18</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>51835</v>
+        <v>51852</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>04-12-2025 22:17</t>
+          <t>06-12-2025 00:47</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>51804</v>
+        <v>51806</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>05-12-2025 00:28</t>
+          <t>05-12-2025 13:49</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>48930</v>
+        <v>48948</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>04-12-2025 23:18</t>
+          <t>06-12-2025 00:49</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>48212</v>
+        <v>48233</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>04-12-2025 22:30</t>
+          <t>06-12-2025 00:29</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>48105</v>
+        <v>48130</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>04-12-2025 19:11</t>
+          <t>06-12-2025 00:45</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>48059</v>
+        <v>48096</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>05-12-2025 00:14</t>
+          <t>05-12-2025 21:27</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>47698</v>
+        <v>47694</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>04-12-2025 23:27</t>
+          <t>05-12-2025 19:17</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3049,11 +3049,11 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>47656</v>
+        <v>47674</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>04-12-2025 23:23</t>
+          <t>05-12-2025 23:43</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>46830</v>
+        <v>46993</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>05-12-2025 00:46</t>
+          <t>06-12-2025 00:38</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>46822</v>
+        <v>46870</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>05-12-2025 00:51</t>
+          <t>05-12-2025 23:39</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3175,11 +3175,11 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>46496</v>
+        <v>46509</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>05-12-2025 00:28</t>
+          <t>05-12-2025 23:51</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>45831</v>
+        <v>45894</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00</t>
+          <t>06-12-2025 00:03</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>45095</v>
+        <v>45190</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>05-12-2025 00:53</t>
+          <t>05-12-2025 23:52</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>43521</v>
+        <v>43548</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>05-12-2025 00:49</t>
+          <t>06-12-2025 00:10</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>42737</v>
+        <v>42752</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>05-12-2025 00:38</t>
+          <t>06-12-2025 00:40</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3386,11 +3386,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>41195</v>
+        <v>41207</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>04-12-2025 23:23</t>
+          <t>05-12-2025 23:54</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>39755</v>
+        <v>39823</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>04-12-2025 23:46</t>
+          <t>06-12-2025 00:47</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>39580</v>
+        <v>39590</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>05-12-2025 00:15</t>
+          <t>05-12-2025 21:41</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>39564</v>
+        <v>39589</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>05-12-2025 00:50</t>
+          <t>05-12-2025 22:27</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>39502</v>
+        <v>39530</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>04-12-2025 23:48</t>
+          <t>05-12-2025 23:42</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>38673</v>
+        <v>38678</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>04-12-2025 22:17</t>
+          <t>05-12-2025 17:47</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>37999</v>
+        <v>38003</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>04-12-2025 21:04</t>
+          <t>05-12-2025 19:59</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>37604</v>
+        <v>37630</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>05-12-2025 00:50</t>
+          <t>05-12-2025 20:34</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>37012</v>
+        <v>37018</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>04-12-2025 17:59</t>
+          <t>05-12-2025 21:32</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>36209</v>
+        <v>36248</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>04-12-2025 23:10</t>
+          <t>05-12-2025 19:05</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>36026</v>
+        <v>36031</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>04-12-2025 19:45</t>
+          <t>05-12-2025 18:05</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>35573</v>
+        <v>35581</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>05-12-2025 00:04</t>
+          <t>05-12-2025 20:10</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>34752</v>
+        <v>34777</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>04-12-2025 16:50</t>
+          <t>05-12-2025 20:57</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3966,11 +3966,11 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>34752</v>
+        <v>34759</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>05-12-2025 00:41</t>
+          <t>05-12-2025 20:40</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>34333</v>
+        <v>34343</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>04-12-2025 18:52</t>
+          <t>05-12-2025 23:53</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>33532</v>
+        <v>33538</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>05-12-2025 00:13</t>
+          <t>06-12-2025 00:13</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4096,11 +4096,11 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>32809</v>
+        <v>32826</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>04-12-2025 23:48</t>
+          <t>05-12-2025 22:17</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>32163</v>
+        <v>32184</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>05-12-2025 00:52</t>
+          <t>05-12-2025 19:57</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>32022</v>
+        <v>32057</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>05-12-2025 00:43</t>
+          <t>06-12-2025 00:44</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4226,11 +4226,11 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>31975</v>
+        <v>31985</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>05-12-2025 00:22</t>
+          <t>06-12-2025 00:22</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>31895</v>
+        <v>31894</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>04-12-2025 14:29</t>
+          <t>05-12-2025 17:16</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4288,85 +4288,85 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Trinea/android-open-project</t>
+          <t>khoj-ai/khoj</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://github.com/Trinea/android-open-project</t>
+          <t>https://github.com/khoj-ai/khoj</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>A categorized collection of Android Open Source Projects,  More powerful web version:</t>
+          <t>Your AI second brain. Self-hostable. Get answers from the web or your docs.</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>31830</v>
+        <v>31839</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>04-12-2025 07:32</t>
+          <t>05-12-2025 21:27</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>05-01-2014 15:20</t>
+          <t>16-08-2021 01:48</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>android, open-source-project</t>
+          <t>agent, ai, assistant, chat, chatgpt</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>khoj-ai/khoj</t>
+          <t>Trinea/android-open-project</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://github.com/khoj-ai/khoj</t>
+          <t>https://github.com/Trinea/android-open-project</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Your AI second brain. Self-hostable. Get answers from the web or your docs.</t>
+          <t>A categorized collection of Android Open Source Projects,  More powerful web version:</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>31825</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
+        <v>31828</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>04-12-2025 23:18</t>
+          <t>05-12-2025 07:59</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>16-08-2021 01:48</t>
+          <t>05-01-2014 15:20</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>agent, ai, assistant, chat, chatgpt</t>
+          <t>android, open-source-project</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>31268</v>
+        <v>31279</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>04-12-2025 23:40</t>
+          <t>05-12-2025 19:29</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>30119</v>
+        <v>30144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>04-12-2025 21:42</t>
+          <t>06-12-2025 00:27</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>29388</v>
+        <v>29392</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>05-12-2025 00:54</t>
+          <t>06-12-2025 00:26</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>29155</v>
+        <v>29164</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>04-12-2025 23:50</t>
+          <t>05-12-2025 23:02</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4572,11 +4572,11 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>28580</v>
+        <v>28589</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>04-12-2025 22:30</t>
+          <t>05-12-2025 17:04</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>28476</v>
+        <v>28485</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>04-12-2025 23:37</t>
+          <t>05-12-2025 23:23</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>28304</v>
+        <v>28324</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>04-12-2025 22:32</t>
+          <t>05-12-2025 23:06</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>27565</v>
+        <v>27606</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>04-12-2025 23:47</t>
+          <t>06-12-2025 00:41</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4747,11 +4747,11 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>27153</v>
+        <v>27157</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>04-12-2025 15:25</t>
+          <t>05-12-2025 23:53</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>27136</v>
+        <v>27142</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>04-12-2025 20:32</t>
+          <t>05-12-2025 21:05</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>27063</v>
+        <v>27085</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>04-12-2025 23:53</t>
+          <t>05-12-2025 21:49</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>26443</v>
+        <v>26476</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>04-12-2025 23:38</t>
+          <t>05-12-2025 19:30</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>26364</v>
+        <v>26378</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>05-12-2025 00:51</t>
+          <t>06-12-2025 00:28</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>26214</v>
+        <v>26221</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>05-12-2025 00:08</t>
+          <t>05-12-2025 21:02</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>26153</v>
+        <v>26157</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>04-12-2025 23:26</t>
+          <t>05-12-2025 16:40</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>26077</v>
+        <v>26098</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>05-12-2025 00:41</t>
+          <t>06-12-2025 00:16</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>25992</v>
+        <v>25995</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>04-12-2025 14:17</t>
+          <t>05-12-2025 22:51</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>25862</v>
+        <v>25868</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>04-12-2025 09:07</t>
+          <t>05-12-2025 23:56</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5188,11 +5188,11 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>25703</v>
+        <v>25710</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>04-12-2025 17:48</t>
+          <t>06-12-2025 00:09</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>25526</v>
+        <v>25530</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>04-12-2025 23:05</t>
+          <t>05-12-2025 23:35</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>25246</v>
+        <v>25262</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>05-12-2025 00:01</t>
+          <t>05-12-2025 23:25</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5314,11 +5314,11 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>24657</v>
+        <v>24669</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>04-12-2025 20:04</t>
+          <t>05-12-2025 23:53</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>24506</v>
+        <v>24512</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>04-12-2025 22:18</t>
+          <t>05-12-2025 22:52</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>24066</v>
+        <v>24079</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>04-12-2025 20:22</t>
+          <t>05-12-2025 20:41</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>23933</v>
+        <v>23942</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>05-12-2025 00:43</t>
+          <t>06-12-2025 00:17</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>04-12-2025 15:20</t>
+          <t>05-12-2025 20:03</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>23260</v>
+        <v>23276</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>04-12-2025 15:30</t>
+          <t>05-12-2025 22:47</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>22846</v>
+        <v>22910</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>05-12-2025 00:54</t>
+          <t>06-12-2025 00:25</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>22644</v>
+        <v>22661</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>05-12-2025 00:35</t>
+          <t>05-12-2025 22:38</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5661,11 +5661,11 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>22456</v>
+        <v>22457</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>04-12-2025 16:54</t>
+          <t>05-12-2025 15:08</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>21980</v>
+        <v>21985</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>05-12-2025 00:26</t>
+          <t>05-12-2025 21:03</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>21959</v>
+        <v>21964</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>04-12-2025 13:29</t>
+          <t>05-12-2025 19:49</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>21928</v>
+        <v>21932</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>04-12-2025 20:09</t>
+          <t>05-12-2025 20:02</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>ai-crawler, ai-scraping, ai-search, automated-scraper, crawler</t>
+          <t>ai-crawler, ai-scraping, ai-search, crawler, data-extraction</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>21666</v>
+        <v>21684</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>04-12-2025 22:32</t>
+          <t>06-12-2025 00:27</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>21201</v>
+        <v>21205</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>04-12-2025 21:05</t>
+          <t>05-12-2025 19:49</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>20796</v>
+        <v>20800</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>04-12-2025 23:52</t>
+          <t>05-12-2025 22:07</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>20730</v>
+        <v>20737</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>04-12-2025 22:40</t>
+          <t>05-12-2025 19:52</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>20628</v>
+        <v>20634</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>05-12-2025 00:25</t>
+          <t>06-12-2025 00:19</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>20275</v>
+        <v>20285</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>04-12-2025 18:45</t>
+          <t>06-12-2025 00:24</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>19760</v>
+        <v>19793</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>05-12-2025 00:33</t>
+          <t>05-12-2025 22:56</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>19674</v>
+        <v>19681</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>05-12-2025 00:42</t>
+          <t>05-12-2025 23:45</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6192,11 +6192,11 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>19606</v>
+        <v>19637</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>04-12-2025 23:40</t>
+          <t>05-12-2025 22:07</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>19439</v>
+        <v>19536</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>04-12-2025 23:56</t>
+          <t>06-12-2025 00:23</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6277,11 +6277,11 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>19278</v>
+        <v>19286</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>04-12-2025 16:37</t>
+          <t>05-12-2025 16:59</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>18369</v>
+        <v>18372</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>04-12-2025 22:51</t>
+          <t>05-12-2025 16:13</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>18165</v>
+        <v>18168</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>04-12-2025 19:18</t>
+          <t>05-12-2025 20:00</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>18087</v>
+        <v>18086</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>04-12-2025 22:35</t>
+          <t>05-12-2025 10:47</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17956</v>
+        <v>17960</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>04-12-2025 12:04</t>
+          <t>05-12-2025 22:18</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>17935</v>
+        <v>17943</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>04-12-2025 16:32</t>
+          <t>05-12-2025 23:05</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>17870</v>
+        <v>17881</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>04-12-2025 23:21</t>
+          <t>05-12-2025 22:48</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>17750</v>
+        <v>17751</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>04-12-2025 23:41</t>
+          <t>05-12-2025 22:52</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>17646</v>
+        <v>17656</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>04-12-2025 22:36</t>
+          <t>05-12-2025 23:15</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>17530</v>
+        <v>17544</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>04-12-2025 23:34</t>
+          <t>05-12-2025 23:31</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>17473</v>
+        <v>17481</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>04-12-2025 22:02</t>
+          <t>05-12-2025 17:16</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>17436</v>
+        <v>17478</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>05-12-2025 00:28</t>
+          <t>05-12-2025 23:50</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>17370</v>
+        <v>17386</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>04-12-2025 20:53</t>
+          <t>05-12-2025 19:13</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6857,11 +6857,11 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>17059</v>
+        <v>17058</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>04-12-2025 16:50</t>
+          <t>05-12-2025 11:42</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>16660</v>
+        <v>16802</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>05-12-2025 00:52</t>
+          <t>06-12-2025 00:29</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>16585</v>
+        <v>16605</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>05-12-2025 00:14</t>
+          <t>05-12-2025 23:00</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>16489</v>
+        <v>16521</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>05-12-2025 00:34</t>
+          <t>05-12-2025 22:22</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7032,11 +7032,11 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>16439</v>
+        <v>16477</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>04-12-2025 22:11</t>
+          <t>05-12-2025 21:11</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>16179</v>
+        <v>16222</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>05-12-2025 00:40</t>
+          <t>06-12-2025 00:28</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>16051</v>
+        <v>16080</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>04-12-2025 23:50</t>
+          <t>06-12-2025 00:40</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>15987</v>
+        <v>16050</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>05-12-2025 00:14</t>
+          <t>06-12-2025 00:46</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15953</v>
+        <v>16018</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>05-12-2025 00:50</t>
+          <t>06-12-2025 00:39</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>15943</v>
+        <v>15950</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>04-12-2025 22:37</t>
+          <t>06-12-2025 00:25</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>15888</v>
+        <v>15906</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>05-12-2025 00:35</t>
+          <t>06-12-2025 00:06</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>15780</v>
+        <v>15787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>05-12-2025 00:19</t>
+          <t>05-12-2025 14:17</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>15268</v>
+        <v>15271</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>04-12-2025 20:19</t>
+          <t>05-12-2025 20:19</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>15160</v>
+        <v>15164</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>04-12-2025 21:16</t>
+          <t>05-12-2025 23:51</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>15136</v>
+        <v>15144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>04-12-2025 22:37</t>
+          <t>05-12-2025 18:50</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>14972</v>
+        <v>14981</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>04-12-2025 23:44</t>
+          <t>06-12-2025 00:09</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>14952</v>
+        <v>14963</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>04-12-2025 23:58</t>
+          <t>05-12-2025 17:47</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>14910</v>
+        <v>14938</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>04-12-2025 12:10</t>
+          <t>06-12-2025 00:45</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>14875</v>
+        <v>14890</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>04-12-2025 22:48</t>
+          <t>05-12-2025 23:08</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7690,7 +7690,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>14788</v>
+        <v>14795</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>04-12-2025 19:15</t>
+          <t>05-12-2025 21:24</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>14763</v>
+        <v>14765</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>04-12-2025 11:31</t>
+          <t>05-12-2025 04:46</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>14703</v>
+        <v>14762</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>05-12-2025 00:46</t>
+          <t>06-12-2025 00:25</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>14659</v>
+        <v>14664</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>04-12-2025 22:46</t>
+          <t>06-12-2025 00:08</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>14526</v>
+        <v>14535</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>04-12-2025 22:29</t>
+          <t>05-12-2025 23:55</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>14457</v>
+        <v>14456</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>04-12-2025 22:11</t>
+          <t>05-12-2025 18:39</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>14187</v>
+        <v>14197</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>04-12-2025 23:17</t>
+          <t>05-12-2025 22:36</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>13959</v>
+        <v>13967</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>04-12-2025 18:23</t>
+          <t>05-12-2025 21:55</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>13925</v>
+        <v>13939</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>04-12-2025 23:52</t>
+          <t>05-12-2025 16:59</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>13874</v>
+        <v>13876</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>04-12-2025 19:59</t>
+          <t>05-12-2025 06:33</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>13841</v>
+        <v>13842</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>04-12-2025 13:29</t>
+          <t>05-12-2025 01:20</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>13801</v>
+        <v>13802</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>04-12-2025 17:32</t>
+          <t>05-12-2025 03:02</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>13627</v>
+        <v>13635</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>05-12-2025 00:04</t>
+          <t>05-12-2025 22:54</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8271,11 +8271,11 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>13452</v>
+        <v>13461</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>04-12-2025 22:54</t>
+          <t>05-12-2025 23:30</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>13369</v>
+        <v>13372</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>05-12-2025 00:44</t>
+          <t>05-12-2025 16:14</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8382,57 +8382,53 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FreshRSS/FreshRSS</t>
+          <t>trustedsec/social-engineer-toolkit</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://github.com/FreshRSS/FreshRSS</t>
+          <t>https://github.com/trustedsec/social-engineer-toolkit</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>A free, self-hostable news aggregator…</t>
+          <t>The Social-Engineer Toolkit (SET) repository from TrustedSec - All new versions of SET will be deployed here.</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>13250</v>
+        <v>13284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>04-12-2025 23:36</t>
+          <t>06-12-2025 00:36</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>21-10-2012 16:48</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>feed, freshrss, news-aggregator, php, rss</t>
-        </is>
-      </c>
+          <t>31-12-2012 22:01</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>streetwriters/notesnook</t>
+          <t>FreshRSS/FreshRSS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://github.com/streetwriters/notesnook</t>
+          <t>https://github.com/FreshRSS/FreshRSS</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8442,73 +8438,77 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>A fully open source &amp; end-to-end encrypted note taking alternative to Evernote.</t>
+          <t>A free, self-hostable news aggregator…</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>13247</v>
+        <v>13257</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>04-12-2025 21:17</t>
+          <t>06-12-2025 00:46</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>01-04-2021 17:25</t>
+          <t>21-10-2012 16:48</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>asp-net-core, dotnet-core, electron, foss, hacktoberfest</t>
+          <t>feed, freshrss, news-aggregator, php, rss</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>trustedsec/social-engineer-toolkit</t>
+          <t>streetwriters/notesnook</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://github.com/trustedsec/social-engineer-toolkit</t>
+          <t>https://github.com/streetwriters/notesnook</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>The Social-Engineer Toolkit (SET) repository from TrustedSec - All new versions of SET will be deployed here.</t>
+          <t>A fully open source &amp; end-to-end encrypted note taking alternative to Evernote.</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>13036</v>
+        <v>13254</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>05-12-2025 00:52</t>
+          <t>05-12-2025 22:02</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>31-12-2012 22:01</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>01-04-2021 17:25</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>asp-net-core, dotnet-core, electron, foss, hacktoberfest</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8532,11 +8532,11 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>12955</v>
+        <v>12960</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>04-12-2025 22:02</t>
+          <t>05-12-2025 15:57</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>12668</v>
+        <v>12711</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>05-12-2025 00:42</t>
+          <t>06-12-2025 00:04</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>12636</v>
+        <v>12640</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>04-12-2025 22:50</t>
+          <t>05-12-2025 23:29</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>04-12-2025 21:25</t>
+          <t>05-12-2025 12:44</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>12365</v>
+        <v>12377</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>04-12-2025 21:31</t>
+          <t>05-12-2025 21:21</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8752,11 +8752,11 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>12316</v>
+        <v>12333</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>04-12-2025 14:46</t>
+          <t>05-12-2025 22:14</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8809,26 +8809,26 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>firebase/functions-samples</t>
+          <t>davila7/claude-code-templates</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://github.com/firebase/functions-samples</t>
+          <t>https://github.com/davila7/claude-code-templates</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Collection of sample apps showcasing popular use cases using Cloud Functions for Firebase</t>
+          <t>CLI tool for configuring and monitoring Claude Code</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>12220</v>
+        <v>12261</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -8837,43 +8837,43 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>04-12-2025 13:02</t>
+          <t>06-12-2025 00:26</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>18-10-2016 17:40</t>
+          <t>04-07-2025 01:26</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>faas, faas-platform, firebase, google, google-cloud-functions</t>
+          <t>anthropic, anthropic-claude, claude, claude-code</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>davila7/claude-code-templates</t>
+          <t>firebase/functions-samples</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://github.com/davila7/claude-code-templates</t>
+          <t>https://github.com/firebase/functions-samples</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>CLI tool for configuring and monitoring Claude Code</t>
+          <t>Collection of sample apps showcasing popular use cases using Cloud Functions for Firebase</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>12217</v>
+        <v>12220</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -8882,17 +8882,17 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>05-12-2025 00:31</t>
+          <t>04-12-2025 13:02</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>04-07-2025 01:26</t>
+          <t>18-10-2016 17:40</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>anthropic, anthropic-claude, claude, claude-code</t>
+          <t>faas, faas-platform, firebase, google, google-cloud-functions</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>12178</v>
+        <v>12190</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>04-12-2025 23:42</t>
+          <t>05-12-2025 23:55</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>12067</v>
+        <v>12086</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>04-12-2025 23:36</t>
+          <t>05-12-2025 23:48</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>11964</v>
+        <v>11971</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>04-12-2025 23:43</t>
+          <t>06-12-2025 00:14</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>11711</v>
+        <v>11721</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>04-12-2025 19:10</t>
+          <t>05-12-2025 22:59</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>11641</v>
+        <v>11649</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>05-12-2025 00:51</t>
+          <t>05-12-2025 22:27</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9124,135 +9124,135 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TheR1D/shell_gpt</t>
+          <t>VERT-sh/VERT</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://github.com/TheR1D/shell_gpt</t>
+          <t>https://github.com/VERT-sh/VERT</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Svelte</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>A command-line productivity tool powered by AI large language models like GPT-4, will help you accomplish your tasks faster and more efficiently.</t>
+          <t>The next-generation file converter. Open source, fully local* and free forever.</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>11563</v>
+        <v>11580</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Svelte</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>04-12-2025 19:41</t>
+          <t>06-12-2025 00:48</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>18-01-2023 19:40</t>
+          <t>11-11-2024 14:27</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>chatgpt, cheat-sheet, cli, commands, gpt-3</t>
+          <t>conversion, ffmpeg, imagemagick, magick, pandoc</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>serverless/examples</t>
+          <t>TheR1D/shell_gpt</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://github.com/serverless/examples</t>
+          <t>https://github.com/TheR1D/shell_gpt</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Serverless Examples – A collection of boilerplates and examples of serverless architectures built with the Serverless Framework on AWS Lambda, Microsoft Azure, Google Cloud Functions, and more.</t>
+          <t>A command-line productivity tool powered by AI large language models like GPT-4, will help you accomplish your tasks faster and more efficiently.</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>11550</v>
+        <v>11564</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>03-12-2025 06:20</t>
+          <t>05-12-2025 13:09</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>12-11-2016 02:14</t>
+          <t>18-01-2023 19:40</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>examples, serverless, serverless-framework</t>
+          <t>chatgpt, cheat-sheet, cli, commands, gpt-3</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>VERT-sh/VERT</t>
+          <t>serverless/examples</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://github.com/VERT-sh/VERT</t>
+          <t>https://github.com/serverless/examples</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Svelte</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>The next-generation file converter. Open source, fully local* and free forever.</t>
+          <t>Serverless Examples – A collection of boilerplates and examples of serverless architectures built with the Serverless Framework on AWS Lambda, Microsoft Azure, Google Cloud Functions, and more.</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>11508</v>
+        <v>11550</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svelte</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>05-12-2025 00:30</t>
+          <t>03-12-2025 06:20</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>11-11-2024 14:27</t>
+          <t>12-11-2016 02:14</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>conversion, ffmpeg, imagemagick, magick, pandoc</t>
+          <t>examples, serverless, serverless-framework</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>11488</v>
+        <v>11495</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>04-12-2025 22:45</t>
+          <t>05-12-2025 22:34</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9304,90 +9304,90 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>trycua/cua</t>
+          <t>Fission-AI/OpenSpec</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://github.com/trycua/cua</t>
+          <t>https://github.com/Fission-AI/OpenSpec</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Open-source infrastructure for Computer-Use Agents. Sandboxes, SDKs, and benchmarks to train and evaluate AI agents that can control full desktops (macOS, Linux, Windows).</t>
+          <t>Spec-driven development for AI coding assistants.</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>11418</v>
+        <v>11433</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>04-12-2025 23:22</t>
+          <t>06-12-2025 00:49</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>31-01-2025 15:02</t>
+          <t>05-08-2025 10:37</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>agent, ai-agent, apple, computer-use, computer-use-agent</t>
+          <t>spec</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Fission-AI/OpenSpec</t>
+          <t>trycua/cua</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://github.com/Fission-AI/OpenSpec</t>
+          <t>https://github.com/trycua/cua</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Spec-driven development for AI coding assistants.</t>
+          <t>Open-source infrastructure for Computer-Use Agents. Sandboxes, SDKs, and benchmarks to train and evaluate AI agents that can control full desktops (macOS, Linux, Windows).</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>11277</v>
+        <v>11429</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>05-12-2025 00:34</t>
+          <t>05-12-2025 15:43</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>05-08-2025 10:37</t>
+          <t>31-01-2025 15:02</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>agent, ai-agent, apple, computer-use, computer-use-agent</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>10982</v>
+        <v>10994</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>05-12-2025 00:54</t>
+          <t>05-12-2025 20:20</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>10633</v>
+        <v>10642</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>04-12-2025 23:25</t>
+          <t>06-12-2025 00:20</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9589,11 +9589,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Frontier Open-Source Voice AI</t>
+          <t>Open-Source Frontier Voice AI</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>10186</v>
+        <v>10530</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>05-12-2025 00:42</t>
+          <t>06-12-2025 00:45</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>10040</v>
+        <v>10045</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>04-12-2025 08:20</t>
+          <t>05-12-2025 15:23</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9660,88 +9660,88 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>LouisShark/chatgpt_system_prompt</t>
+          <t>BeehiveInnovations/pal-mcp-server</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://github.com/LouisShark/chatgpt_system_prompt</t>
+          <t>https://github.com/BeehiveInnovations/pal-mcp-server</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>A collection of GPT system prompts and various prompt injection/leaking knowledge.</t>
+          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>9914</v>
+        <v>9922</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>04-12-2025 21:36</t>
+          <t>06-12-2025 00:36</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>01-11-2023 12:35</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>gpt, prompt, prompt-engineering</t>
-        </is>
-      </c>
+          <t>08-06-2025 15:36</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BeehiveInnovations/pal-mcp-server</t>
+          <t>LouisShark/chatgpt_system_prompt</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://github.com/BeehiveInnovations/pal-mcp-server</t>
+          <t>https://github.com/LouisShark/chatgpt_system_prompt</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>The power of Claude Code / GeminiCLI / CodexCLI + [Gemini / OpenAI / OpenRouter / Azure / Grok / Ollama / Custom Model / All Of The Above] working as one.</t>
+          <t>A collection of GPT system prompts and various prompt injection/leaking knowledge.</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>9901</v>
+        <v>9922</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>04-12-2025 20:52</t>
+          <t>05-12-2025 17:40</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>08-06-2025 15:36</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
+          <t>01-11-2023 12:35</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>gpt, prompt, prompt-engineering</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>9866</v>
+        <v>9874</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>04-12-2025 23:03</t>
+          <t>05-12-2025 21:52</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9791,88 +9791,88 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>sdelements/lets-chat</t>
+          <t>C4illin/ConvertX</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://github.com/sdelements/lets-chat</t>
+          <t>https://github.com/C4illin/ConvertX</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Self-hosted chat app for small teams</t>
+          <t>💾 Self-hosted online file converter. Supports 1000+ formats ⚙️</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>9823</v>
+        <v>9829</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>01-12-2025 20:55</t>
+          <t>05-12-2025 22:29</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>09-03-2012 19:32</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>07-04-2024 16:21</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>bun, conversion, convert, converter, document-conversion</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>C4illin/ConvertX</t>
+          <t>sdelements/lets-chat</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://github.com/C4illin/ConvertX</t>
+          <t>https://github.com/sdelements/lets-chat</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>💾 Self-hosted online file converter. Supports 1000+ formats ⚙️</t>
+          <t>Self-hosted chat app for small teams</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>9819</v>
+        <v>9823</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>04-12-2025 21:51</t>
+          <t>01-12-2025 20:55</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>07-04-2024 16:21</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>bun, conversion, convert, converter, document-conversion</t>
-        </is>
-      </c>
+          <t>09-03-2012 19:32</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>9450</v>
+        <v>9458</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>04-12-2025 19:49</t>
+          <t>05-12-2025 22:13</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>9443</v>
+        <v>9445</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>04-12-2025 19:13</t>
+          <t>05-12-2025 23:49</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>9179</v>
+        <v>9180</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>04-12-2025 21:33</t>
+          <t>05-12-2025 19:12</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10008,85 +10008,85 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>NopeCHALLC/nopecha-extension</t>
+          <t>justcallmekoko/ESP32Marauder</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://github.com/NopeCHALLC/nopecha-extension</t>
+          <t>https://github.com/justcallmekoko/ESP32Marauder</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>CLI Tools</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Automated CAPTCHA solver for your browser. Works with Selenium, Puppeteer, Playwright, and more.</t>
+          <t>A suite of WiFi/Bluetooth offensive and defensive tools for the ESP32</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>9120</v>
+        <v>9135</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>C++</t>
+        </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>05-12-2025 00:34</t>
+          <t>06-12-2025 00:35</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>23-03-2023 17:59</t>
+          <t>13-09-2019 18:37</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>aws-waf-captcha, captcha, captcha-breaking, captcha-bypass, captcha-recognition</t>
+          <t>arduino, beacon, bluetooth, command-line, deauth</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>justcallmekoko/ESP32Marauder</t>
+          <t>NopeCHALLC/nopecha-extension</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://github.com/justcallmekoko/ESP32Marauder</t>
+          <t>https://github.com/NopeCHALLC/nopecha-extension</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>CLI Tools</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>A suite of WiFi/Bluetooth offensive and defensive tools for the ESP32</t>
+          <t>Automated CAPTCHA solver for your browser. Works with Selenium, Puppeteer, Playwright, and more.</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>9102</v>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>C++</t>
-        </is>
+        <v>9131</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>04-12-2025 23:36</t>
+          <t>06-12-2025 00:51</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>13-09-2019 18:37</t>
+          <t>23-03-2023 17:59</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>arduino, beacon, bluetooth, command-line, deauth</t>
+          <t>aws-waf-captcha, captcha, captcha-breaking, captcha-bypass, captcha-recognition</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>9090</v>
+        <v>9095</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>05-12-2025 00:21</t>
+          <t>05-12-2025 23:15</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10157,11 +10157,11 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>8874</v>
+        <v>8875</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>04-12-2025 17:23</t>
+          <t>05-12-2025 22:51</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10178,88 +10178,88 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>YaoFANGUK/video-subtitle-remover</t>
+          <t>obra/superpowers</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://github.com/YaoFANGUK/video-subtitle-remover</t>
+          <t>https://github.com/obra/superpowers</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>基于AI的图片/视频硬字幕去除、文本水印去除，无损分辨率生成去字幕、去水印后的图片/视频文件。无需申请第三方API，本地实现。AI-based tool for removing hard-coded subtitles and text-like watermarks from videos or Pictures.</t>
+          <t>Claude Code superpowers: core skills library</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>8756</v>
+        <v>8805</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>04-12-2025 22:14</t>
+          <t>06-12-2025 00:25</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>25-10-2023 02:50</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>ai, deepleanring, sub-remove, subtile, vsr</t>
-        </is>
-      </c>
+          <t>09-10-2025 19:45</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>obra/superpowers</t>
+          <t>YaoFANGUK/video-subtitle-remover</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://github.com/obra/superpowers</t>
+          <t>https://github.com/YaoFANGUK/video-subtitle-remover</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Claude Code superpowers: core skills library</t>
+          <t>基于AI的图片/视频硬字幕去除、文本水印去除，无损分辨率生成去字幕、去水印后的图片/视频文件。无需申请第三方API，本地实现。AI-based tool for removing hard-coded subtitles and text-like watermarks from videos or Pictures.</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>8722</v>
+        <v>8785</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>05-12-2025 00:52</t>
+          <t>06-12-2025 00:17</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>09-10-2025 19:45</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr"/>
+          <t>25-10-2023 02:50</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>ai, deepleanring, sub-remove, subtile, vsr</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>8716</v>
+        <v>8720</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>04-12-2025 21:22</t>
+          <t>05-12-2025 17:56</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>8680</v>
+        <v>8683</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>04-12-2025 20:49</t>
+          <t>05-12-2025 23:50</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10373,11 +10373,11 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>8644</v>
+        <v>8645</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>04-12-2025 14:46</t>
+          <t>05-12-2025 22:52</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>8621</v>
+        <v>8624</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>04-12-2025 20:17</t>
+          <t>05-12-2025 13:04</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10454,11 +10454,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Open-source Rust based AI meeting assistant with Parakeet/Whisper live transcription, speaker diarization, and Ollama summarization. 100% local processing. no cloud required.</t>
+          <t>Open-source Rust based AI meeting assistant with 4x faster Parakeet/Whisper live transcription, speaker diarization, and Ollama summarization. 100% local processing. no cloud required.</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>8544</v>
+        <v>8583</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>04-12-2025 22:52</t>
+          <t>06-12-2025 00:22</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>8536</v>
+        <v>8541</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>04-12-2025 19:40</t>
+          <t>05-12-2025 22:52</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>8526</v>
+        <v>8535</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>04-12-2025 20:51</t>
+          <t>05-12-2025 16:48</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>8342</v>
+        <v>8353</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>04-12-2025 22:42</t>
+          <t>05-12-2025 21:15</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>8268</v>
+        <v>8272</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>04-12-2025 23:18</t>
+          <t>05-12-2025 20:59</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>8073</v>
+        <v>8077</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>04-12-2025 19:51</t>
+          <t>05-12-2025 21:44</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10745,90 +10745,90 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Termix-SSH/Termix</t>
+          <t>Sjj1024/PakePlus</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://github.com/Termix-SSH/Termix</t>
+          <t>https://github.com/Sjj1024/PakePlus</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Termix is a web-based server management platform with SSH terminal, tunneling, and file editing capabilities.</t>
+          <t>Turn any webpage/Vue/React and so on into desktop and mobile app under 5M with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>7981</v>
+        <v>8011</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>04-12-2025 23:28</t>
+          <t>06-12-2025 00:41</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>25-11-2024 02:46</t>
+          <t>10-09-2024 13:12</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>docker, file-management, self-hosted, ssh, ssh-tunnel</t>
+          <t>pacbao, pake, pakeplus, rust, tauri</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Sjj1024/PakePlus</t>
+          <t>Termix-SSH/Termix</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://github.com/Sjj1024/PakePlus</t>
+          <t>https://github.com/Termix-SSH/Termix</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Turn any webpage/Vue/React and so on into desktop and mobile app under 5M with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app</t>
+          <t>Termix is a web-based server management platform with SSH terminal, tunneling, and file editing capabilities.</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>7971</v>
+        <v>8009</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>05-12-2025 00:50</t>
+          <t>06-12-2025 00:39</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>10-09-2024 13:12</t>
+          <t>25-11-2024 02:46</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>pacbao, pake, pakeplus, rust, tauri</t>
+          <t>docker, file-management, self-hosted, ssh, ssh-tunnel</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>7797</v>
+        <v>7800</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>04-12-2025 21:17</t>
+          <t>05-12-2025 16:49</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -10899,7 +10899,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>7712</v>
+        <v>7719</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>04-12-2025 23:57</t>
+          <t>05-12-2025 23:18</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -10944,11 +10944,11 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>7615</v>
+        <v>7618</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>04-12-2025 21:08</t>
+          <t>06-12-2025 00:08</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -10984,7 +10984,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7343</v>
+        <v>7345</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>04-12-2025 20:32</t>
+          <t>05-12-2025 14:47</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>04-12-2025 12:26</t>
+          <t>05-12-2025 19:36</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>7097</v>
+        <v>7106</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>05-12-2025 00:46</t>
+          <t>05-12-2025 23:48</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6839</v>
+        <v>6842</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>05-12-2025 00:02</t>
+          <t>05-12-2025 23:09</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>04-12-2025 07:18</t>
+          <t>05-12-2025 09:29</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -11205,7 +11205,7 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6688</v>
+        <v>6692</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>04-12-2025 16:24</t>
+          <t>05-12-2025 22:19</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -11250,7 +11250,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6589</v>
+        <v>6588</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>04-12-2025 18:54</t>
+          <t>05-12-2025 11:47</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6572</v>
+        <v>6573</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>03-12-2025 07:40</t>
+          <t>05-12-2025 23:43</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -11336,7 +11336,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6563</v>
+        <v>6569</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>05-12-2025 00:51</t>
+          <t>05-12-2025 21:25</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -11381,7 +11381,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6528</v>
+        <v>6535</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>04-12-2025 10:41</t>
+          <t>05-12-2025 17:06</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -11426,7 +11426,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6438</v>
+        <v>6439</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>04-12-2025 10:48</t>
+          <t>05-12-2025 18:06</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -11471,7 +11471,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6265</v>
+        <v>6267</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>04-12-2025 16:28</t>
+          <t>05-12-2025 17:23</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -11516,11 +11516,11 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6209</v>
+        <v>6212</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>04-12-2025 17:19</t>
+          <t>05-12-2025 22:54</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6141</v>
+        <v>6142</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>04-12-2025 11:37</t>
+          <t>05-12-2025 15:16</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11597,7 +11597,7 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6131</v>
+        <v>6132</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>04-12-2025 14:25</t>
+          <t>05-12-2025 12:32</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6123</v>
+        <v>6122</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>04-12-2025 21:47</t>
+          <t>05-12-2025 11:04</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -11687,7 +11687,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5925</v>
+        <v>5930</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>04-12-2025 15:40</t>
+          <t>05-12-2025 19:18</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5838</v>
+        <v>5839</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>04-12-2025 05:41</t>
+          <t>05-12-2025 20:28</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5747</v>
+        <v>5836</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>05-12-2025 00:47</t>
+          <t>05-12-2025 23:46</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>04-12-2025 16:40</t>
+          <t>05-12-2025 17:31</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5626</v>
+        <v>5653</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>05-12-2025 00:19</t>
+          <t>05-12-2025 21:29</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5624</v>
+        <v>5627</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>04-12-2025 09:55</t>
+          <t>05-12-2025 13:32</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5575</v>
+        <v>5576</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>04-12-2025 20:23</t>
+          <t>05-12-2025 21:35</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5518</v>
+        <v>5527</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>04-12-2025 17:57</t>
+          <t>06-12-2025 00:25</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12087,7 +12087,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5446</v>
+        <v>5462</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>04-12-2025 23:42</t>
+          <t>06-12-2025 00:02</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -12132,11 +12132,11 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>5415</v>
+        <v>5453</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>05-12-2025 00:34</t>
+          <t>06-12-2025 00:46</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5120</v>
+        <v>5122</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>04-12-2025 14:42</t>
+          <t>05-12-2025 21:31</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5118</v>
+        <v>5119</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>04-12-2025 07:15</t>
+          <t>05-12-2025 10:46</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5109</v>
+        <v>5111</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>03-12-2025 17:41</t>
+          <t>05-12-2025 12:54</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -12307,7 +12307,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>5046</v>
+        <v>5048</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>05-12-2025 00:05</t>
+          <t>05-12-2025 22:57</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -12352,11 +12352,11 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5024</v>
+        <v>5026</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>04-12-2025 19:37</t>
+          <t>05-12-2025 16:36</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5023</v>
+        <v>5024</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>04-12-2025 16:58</t>
+          <t>05-12-2025 16:00</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4984</v>
+        <v>4983</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>04-12-2025 19:21</t>
+          <t>05-12-2025 23:58</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>4928</v>
+        <v>4940</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>04-12-2025 23:59</t>
+          <t>05-12-2025 23:13</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -12572,7 +12572,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4921</v>
+        <v>4926</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>04-12-2025 22:51</t>
+          <t>05-12-2025 19:18</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -12662,7 +12662,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4821</v>
+        <v>4823</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>03-12-2025 12:24</t>
+          <t>05-12-2025 10:00</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -12707,7 +12707,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4773</v>
+        <v>4774</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>04-12-2025 16:21</t>
+          <t>05-12-2025 14:43</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>4744</v>
+        <v>4746</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>04-12-2025 18:49</t>
+          <t>05-12-2025 18:52</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -12797,7 +12797,7 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4708</v>
+        <v>4709</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>04-12-2025 16:50</t>
+          <t>05-12-2025 03:34</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>04-12-2025 05:33</t>
+          <t>05-12-2025 15:01</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>4415</v>
+        <v>4418</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>04-12-2025 21:12</t>
+          <t>05-12-2025 14:11</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -13067,7 +13067,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>4347</v>
+        <v>4348</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>04-12-2025 02:00</t>
+          <t>05-12-2025 11:42</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -13112,7 +13112,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>4310</v>
+        <v>4316</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>04-12-2025 23:47</t>
+          <t>05-12-2025 19:10</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>4284</v>
+        <v>4283</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>03-12-2025 07:29</t>
+          <t>05-12-2025 03:35</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -13202,7 +13202,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>4277</v>
+        <v>4281</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>04-12-2025 16:50</t>
+          <t>05-12-2025 20:04</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4204</v>
+        <v>4212</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>04-12-2025 14:27</t>
+          <t>05-12-2025 23:43</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>bruce, cardputer, embedded-systems, esp32-s3, flipperzero</t>
+          <t>bruce, cardputer, embedded-systems, esp32-c5, esp32-s3</t>
         </is>
       </c>
     </row>
@@ -13333,7 +13333,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>4189</v>
+        <v>4192</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>04-12-2025 05:30</t>
+          <t>06-12-2025 00:23</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>4151</v>
+        <v>4152</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>04-12-2025 13:08</t>
+          <t>05-12-2025 06:00</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -13460,7 +13460,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>4107</v>
+        <v>4112</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>04-12-2025 18:06</t>
+          <t>05-12-2025 19:17</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>4044</v>
+        <v>4071</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>05-12-2025 00:50</t>
+          <t>06-12-2025 00:41</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>4031</v>
+        <v>4032</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>04-12-2025 15:10</t>
+          <t>05-12-2025 14:48</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>3979</v>
+        <v>3980</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>04-12-2025 16:22</t>
+          <t>05-12-2025 21:55</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>3963</v>
+        <v>3967</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>03-12-2025 13:46</t>
+          <t>05-12-2025 17:39</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>3878</v>
+        <v>3907</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>05-12-2025 00:30</t>
+          <t>05-12-2025 23:48</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -13700,74 +13700,74 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>blake3, de-google, encryption, file-transfer, hole-punching</t>
+          <t>blake3, blip, blip-alternative, de-google, encryption</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>erxes/erxes</t>
+          <t>microfeed/microfeed</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://github.com/erxes/erxes</t>
+          <t>https://github.com/microfeed/microfeed</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Experience Operating System (XOS) that unifies marketing, sales, operations, and support — run your core business seamlessly while replacing HubSpot, Zendesk, Linear, Wix and more.</t>
+          <t>a lightweight cms self-hosted on cloudflare, for podcasts, blogs, photos, videos, documents, and curated urls.</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>3861</v>
+        <v>3863</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>04-12-2025 12:01</t>
+          <t>05-12-2025 03:39</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>11-11-2016 06:54</t>
+          <t>25-05-2020 03:50</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>customer-experience, employee-experience, experience-operating-system, front-alternative, hacktoberfest</t>
+          <t>cloudflare, cloudflare-d1, cloudflare-pages, cloudflare-r2, cloudflare-zero-trust</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>microfeed/microfeed</t>
+          <t>erxes/erxes</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://github.com/microfeed/microfeed</t>
+          <t>https://github.com/erxes/erxes</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>a lightweight cms self-hosted on cloudflare, for podcasts, blogs, photos, videos, documents, and curated urls.</t>
+          <t>Experience Operating System (XOS) that unifies marketing, sales, operations, and support — run your core business seamlessly while replacing HubSpot, Zendesk, Linear, Wix and more.</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -13775,22 +13775,22 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>03-12-2025 02:02</t>
+          <t>04-12-2025 12:01</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>25-05-2020 03:50</t>
+          <t>11-11-2016 06:54</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>cloudflare, cloudflare-d1, cloudflare-pages, cloudflare-r2, cloudflare-zero-trust</t>
+          <t>customer-experience, employee-experience, experience-operating-system, front-alternative, hacktoberfest</t>
         </is>
       </c>
     </row>
@@ -13816,7 +13816,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3780</v>
+        <v>3781</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>03-12-2025 12:32</t>
+          <t>05-12-2025 02:28</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -13906,7 +13906,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>3606</v>
+        <v>3607</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>04-12-2025 20:55</t>
+          <t>05-12-2025 23:49</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -13992,11 +13992,11 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3549</v>
+        <v>3551</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>04-12-2025 12:04</t>
+          <t>05-12-2025 21:55</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -14032,7 +14032,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3517</v>
+        <v>3531</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>05-12-2025 00:03</t>
+          <t>05-12-2025 22:59</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>3438</v>
+        <v>3459</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>05-12-2025 00:29</t>
+          <t>05-12-2025 21:44</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14122,7 +14122,7 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>04-12-2025 11:00</t>
+          <t>05-12-2025 15:10</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -14167,7 +14167,7 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>3353</v>
+        <v>3358</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>04-12-2025 22:02</t>
+          <t>05-12-2025 20:08</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -14212,7 +14212,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>3344</v>
+        <v>3350</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>04-12-2025 22:46</t>
+          <t>05-12-2025 23:46</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -14257,7 +14257,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>3337</v>
+        <v>3340</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>04-12-2025 21:19</t>
+          <t>05-12-2025 16:44</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>04-12-2025 16:14</t>
+          <t>05-12-2025 02:01</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -14328,102 +14328,102 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ddclient/ddclient</t>
+          <t>khcrysalis/Feather</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://github.com/ddclient/ddclient</t>
+          <t>https://github.com/khcrysalis/Feather</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CLI Tools</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>ddclient updates dynamic DNS entries for accounts on a wide range of dynamic DNS services.</t>
+          <t>Free on-device iOS/iPadOS application manager/installer, using certificates part of the Apple Developer Program.</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>3224</v>
+        <v>3228</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Perl</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>04-12-2025 18:45</t>
+          <t>05-12-2025 20:28</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>14-08-2012 13:40</t>
+          <t>19-05-2024 17:44</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>ddclient, dynamic-dns-services</t>
+          <t>esign, ios, ipa, ipados, kravasign</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>khcrysalis/Feather</t>
+          <t>ddclient/ddclient</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://github.com/khcrysalis/Feather</t>
+          <t>https://github.com/ddclient/ddclient</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>CLI Tools</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Free on-device iOS/iPadOS application manager/installer, using certificates part of the Apple Developer Program.</t>
+          <t>ddclient updates dynamic DNS entries for accounts on a wide range of dynamic DNS services.</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Perl</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>04-12-2025 20:54</t>
+          <t>04-12-2025 18:45</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>19-05-2024 17:44</t>
+          <t>14-08-2012 13:40</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>esign, ios, ipa, ipados, kravasign</t>
+          <t>ddclient, dynamic-dns-services</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>revolist/revogrid</t>
+          <t>aldinokemal/go-whatsapp-web-multidevice</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://github.com/revolist/revogrid</t>
+          <t>https://github.com/aldinokemal/go-whatsapp-web-multidevice</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -14433,42 +14433,42 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Powerful virtual data table smartsheet with advanced customization. Best features from excel plus incredible  performance 🔋</t>
+          <t>GOWA - WhatsApp REST API with support for UI, Webhooks, and MCP. Built with Golang for efficient memory use.</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>3184</v>
+        <v>3189</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>04-12-2025 11:09</t>
+          <t>05-12-2025 12:36</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>04-05-2020 21:23</t>
+          <t>09-02-2022 16:19</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>angular, angular-datagrid, data-grid, excel, excel-grid</t>
+          <t>bot, go, golang, golang-whatsapp, golang-whatsapp-api</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>aldinokemal/go-whatsapp-web-multidevice</t>
+          <t>revolist/revogrid</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://github.com/aldinokemal/go-whatsapp-web-multidevice</t>
+          <t>https://github.com/revolist/revogrid</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -14478,30 +14478,30 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>GOWA - WhatsApp REST API with support for UI, Webhooks, and MCP. Built with Golang for efficient memory use.</t>
+          <t>Powerful virtual data table smartsheet with advanced customization. Best features from excel plus incredible  performance 🔋</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>3183</v>
+        <v>3185</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>04-12-2025 19:36</t>
+          <t>05-12-2025 23:50</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>09-02-2022 16:19</t>
+          <t>04-05-2020 21:23</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>bot, go, golang, golang-whatsapp, golang-whatsapp-api</t>
+          <t>angular, angular-datagrid, data-grid, excel, excel-grid</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>3177</v>
+        <v>3181</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>04-12-2025 18:04</t>
+          <t>05-12-2025 09:35</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -14572,7 +14572,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>04-12-2025 19:03</t>
+          <t>05-12-2025 08:28</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -14617,7 +14617,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>3170</v>
+        <v>3173</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>05-12-2025 00:15</t>
+          <t>05-12-2025 17:59</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>3160</v>
+        <v>3168</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>04-12-2025 18:09</t>
+          <t>05-12-2025 15:41</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -14703,11 +14703,11 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>3107</v>
+        <v>3115</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>04-12-2025 23:52</t>
+          <t>05-12-2025 23:52</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -14743,7 +14743,7 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>3075</v>
+        <v>3085</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>04-12-2025 23:23</t>
+          <t>05-12-2025 19:50</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>04-12-2025 19:42</t>
+          <t>06-12-2025 00:48</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>04-12-2025 10:57</t>
+          <t>05-12-2025 04:32</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -14870,7 +14870,7 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>3030</v>
+        <v>3038</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>04-12-2025 22:06</t>
+          <t>05-12-2025 21:40</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -14892,90 +14892,90 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>aviaryan/awesome-no-login-web-apps</t>
+          <t>Sjj1024/PakePlus-iOS</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://github.com/aviaryan/awesome-no-login-web-apps</t>
+          <t>https://github.com/Sjj1024/PakePlus-iOS</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>🚀 Awesome (free) web apps that work without login</t>
+          <t>Turn any webpage/Vue/React and so on into desktop and mobile app with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app/</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2991</v>
+        <v>2995</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>04-12-2025 05:33</t>
+          <t>06-12-2025 00:41</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>06-12-2016 10:54</t>
+          <t>28-03-2025 14:46</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>application, applications, awesome, awesome-list, awesomeness</t>
+          <t>build, ipa, pacbao, package, pake</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Nain57/Smart-AutoClicker</t>
+          <t>aviaryan/awesome-no-login-web-apps</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://github.com/Nain57/Smart-AutoClicker</t>
+          <t>https://github.com/aviaryan/awesome-no-login-web-apps</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>An open-source auto clicker on images for Android</t>
+          <t>🚀 Awesome (free) web apps that work without login</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>2986</v>
+        <v>2993</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Kotlin</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>04-12-2025 13:18</t>
+          <t>05-12-2025 08:25</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>30-08-2020 13:07</t>
+          <t>06-12-2016 10:54</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>android, autoclicker, fdroid, kotlin, material-design</t>
+          <t>application, applications, awesome, awesome-list, awesomeness</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>2986</v>
+        <v>2989</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>05-12-2025 00:03</t>
+          <t>05-12-2025 22:12</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15027,90 +15027,90 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>kevinzg/facebook-scraper</t>
+          <t>Nain57/Smart-AutoClicker</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://github.com/kevinzg/facebook-scraper</t>
+          <t>https://github.com/Nain57/Smart-AutoClicker</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Scrape Facebook public pages without an API key</t>
+          <t>An open-source auto clicker on images for Android</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2981</v>
+        <v>2986</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Kotlin</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>04-12-2025 18:11</t>
+          <t>04-12-2025 13:18</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>15-03-2019 04:36</t>
+          <t>30-08-2020 13:07</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>facebook, facebook-scraper, facebook-scraping, hacktoberfest, scraping</t>
+          <t>android, autoclicker, fdroid, kotlin, material-design</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Sjj1024/PakePlus-iOS</t>
+          <t>kevinzg/facebook-scraper</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://github.com/Sjj1024/PakePlus-iOS</t>
+          <t>https://github.com/kevinzg/facebook-scraper</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Turn any webpage/Vue/React and so on into desktop and mobile app with easy in few minutes. 轻松将任意网站/Vue/React等项目构建为轻量级(小于5M)多端桌面应用和手机应用仅需几分钟. https://ppofficial.netlify.app/</t>
+          <t>Scrape Facebook public pages without an API key</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2968</v>
+        <v>2982</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>05-12-2025 00:50</t>
+          <t>05-12-2025 06:10</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>28-03-2025 14:46</t>
+          <t>15-03-2019 04:36</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>build, ipa, pacbao, package, pake</t>
+          <t>facebook, facebook-scraper, facebook-scraping, hacktoberfest, scraping</t>
         </is>
       </c>
     </row>
@@ -15145,7 +15145,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>03-12-2025 13:13</t>
+          <t>05-12-2025 14:50</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -15181,7 +15181,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>2862</v>
+        <v>2868</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>04-12-2025 16:39</t>
+          <t>06-12-2025 00:29</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -15226,11 +15226,11 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>2841</v>
+        <v>2847</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>04-12-2025 15:06</t>
+          <t>05-12-2025 16:15</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -15266,7 +15266,7 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>2829</v>
+        <v>2834</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>04-12-2025 08:28</t>
+          <t>05-12-2025 22:04</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -15311,7 +15311,7 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>2814</v>
+        <v>2816</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>04-12-2025 19:13</t>
+          <t>05-12-2025 19:18</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -15356,7 +15356,7 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>2810</v>
+        <v>2812</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>04-12-2025 07:15</t>
+          <t>05-12-2025 20:01</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -15397,7 +15397,7 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>2798</v>
+        <v>2802</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>04-12-2025 05:35</t>
+          <t>05-12-2025 17:17</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>2752</v>
+        <v>2754</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>04-12-2025 15:53</t>
+          <t>05-12-2025 13:55</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>04-12-2025 18:11</t>
+          <t>05-12-2025 18:10</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>04-12-2025 20:45</t>
+          <t>05-12-2025 14:37</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>04-12-2025 07:18</t>
+          <t>05-12-2025 19:21</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -15662,11 +15662,11 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2712</v>
+        <v>2719</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>05-12-2025 00:40</t>
+          <t>06-12-2025 00:38</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -15702,7 +15702,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>05-12-2025 00:11</t>
+          <t>05-12-2025 14:06</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -15747,7 +15747,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2566</v>
+        <v>2573</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>04-12-2025 17:04</t>
+          <t>05-12-2025 16:20</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15837,7 +15837,7 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>04-12-2025 05:31</t>
+          <t>05-12-2025 12:57</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15882,11 +15882,11 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>2473</v>
+        <v>2476</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>04-12-2025 14:10</t>
+          <t>05-12-2025 21:33</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15918,7 +15918,7 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>04-12-2025 19:33</t>
+          <t>05-12-2025 09:22</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15963,7 +15963,7 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>04-12-2025 13:13</t>
+          <t>05-12-2025 15:53</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16008,7 +16008,7 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>02-12-2025 12:43</t>
+          <t>05-12-2025 10:04</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>04-12-2025 18:02</t>
+          <t>06-12-2025 00:00</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -16098,7 +16098,7 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>2269</v>
+        <v>2273</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>04-12-2025 17:35</t>
+          <t>05-12-2025 23:29</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -16143,7 +16143,7 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>2222</v>
+        <v>2227</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>04-12-2025 23:44</t>
+          <t>05-12-2025 19:15</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -16165,83 +16165,83 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>gabrielpetersson/fast-grid</t>
+          <t>oxylabs/free-proxy-list</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://github.com/gabrielpetersson/fast-grid</t>
+          <t>https://github.com/oxylabs/free-proxy-list</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>World's most performant DOM-based web table. Try it! fast-grid.vercel.app/</t>
+          <t>Claim Free proxy list with United States IP addresses and use it for your projects.</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>2189</v>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
+        <v>2190</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>03-12-2025 10:12</t>
+          <t>06-12-2025 00:15</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>28-04-2023 06:52</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr"/>
+          <t>06-02-2025 07:41</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>free-proxies, free-proxies-for-web-scraping, free-proxy, free-proxy-ip, free-proxy-list</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>oxylabs/free-proxy-list</t>
+          <t>gabrielpetersson/fast-grid</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://github.com/oxylabs/free-proxy-list</t>
+          <t>https://github.com/gabrielpetersson/fast-grid</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Claim Free proxy list with United States IP addresses and use it for your projects.</t>
+          <t>World's most performant DOM-based web table. Try it! fast-grid.vercel.app/</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>2188</v>
+        <v>2190</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>04-12-2025 22:36</t>
+          <t>05-12-2025 06:51</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>06-02-2025 07:41</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>free-proxies, free-proxies-for-web-scraping, free-proxy, free-proxy-ip, free-proxy-list</t>
-        </is>
-      </c>
+          <t>28-04-2023 06:52</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>04-12-2025 23:55</t>
+          <t>05-12-2025 14:22</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -16310,7 +16310,7 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>04-12-2025 20:25</t>
+          <t>05-12-2025 19:16</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>02-12-2025 03:23</t>
+          <t>05-12-2025 12:19</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -16400,7 +16400,7 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>04-12-2025 19:26</t>
+          <t>05-12-2025 10:31</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>04-12-2025 13:01</t>
+          <t>05-12-2025 11:15</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -16535,7 +16535,7 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>05-12-2025 00:05</t>
+          <t>05-12-2025 13:15</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -16606,88 +16606,88 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>spyboy-productions/CloakQuest3r</t>
+          <t>lyfe00011/levanter</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://github.com/spyboy-productions/CloakQuest3r</t>
+          <t>https://github.com/lyfe00011/levanter</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Uncover the true IP address of websites safeguarded by Cloudflare &amp; Others</t>
+          <t>Feature-rich WhatsApp bot supporting multiple sessions</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>04-12-2025 16:21</t>
+          <t>05-12-2025 18:10</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>02-11-2023 05:47</t>
-        </is>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t>bypass-cloudflare, bypass-hostname, bypass-waf, cloudflare, cloudflare-ip</t>
-        </is>
-      </c>
+          <t>21-08-2024 23:11</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>lyfe00011/levanter</t>
+          <t>spyboy-productions/CloakQuest3r</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://github.com/lyfe00011/levanter</t>
+          <t>https://github.com/spyboy-productions/CloakQuest3r</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Feature-rich WhatsApp bot supporting multiple sessions</t>
+          <t>Uncover the true IP address of websites safeguarded by Cloudflare &amp; Others</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>04-12-2025 21:26</t>
+          <t>05-12-2025 10:47</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>21-08-2024 23:11</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr"/>
+          <t>02-11-2023 05:47</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>bypass-cloudflare, bypass-hostname, bypass-waf, cloudflare, cloudflare-ip</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -16756,7 +16756,7 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>03-12-2025 13:47</t>
+          <t>05-12-2025 22:11</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16797,7 +16797,7 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>04-12-2025 16:10</t>
+          <t>05-12-2025 09:34</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>04-12-2025 15:38</t>
+          <t>05-12-2025 08:19</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16883,7 +16883,7 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>04-12-2025 10:12</t>
+          <t>05-12-2025 14:43</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>04-12-2025 21:16</t>
+          <t>05-12-2025 18:47</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -17018,7 +17018,7 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>04-12-2025 15:56</t>
+          <t>05-12-2025 18:26</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17063,7 +17063,7 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>04-12-2025 23:58</t>
+          <t>05-12-2025 10:17</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>03-12-2025 20:43</t>
+          <t>05-12-2025 15:40</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>04-12-2025 19:34</t>
+          <t>05-12-2025 18:22</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -17198,7 +17198,7 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>04-12-2025 23:56</t>
+          <t>05-12-2025 15:18</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -17373,7 +17373,7 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>04-12-2025 15:15</t>
+          <t>05-12-2025 21:31</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -17440,130 +17440,130 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1234567Yang/cf-proxy-ex</t>
+          <t>filipecalegario/awesome-vibe-coding</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://github.com/1234567Yang/cf-proxy-ex</t>
+          <t>https://github.com/filipecalegario/awesome-vibe-coding</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Cloudflare超级代理，无服务器代理，Duckduckgo代理（可用AI聊天，包含GPT4o/Claude3），Github加速，支持解锁Libgen，在线代理。现已支持多平台部署。Cloudflare super proxy, setting up a free serverless proxy by using Cloudflare worker, support Duckduck...</t>
+          <t>A curated list of vibe coding references, collaborating with AI to write code.</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>1635</v>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
+        <v>1651</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>02-12-2025 00:25</t>
+          <t>06-12-2025 00:11</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>15-06-2024 15:54</t>
+          <t>13-03-2025 17:46</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>bypass, cloudflare-proxy, cloudflare-reverse-proxy, cloudflare-workers, free-proxy</t>
+          <t>ai-agent, ai-agents, ai-coding-assistant, ai-coding-tools, awesome</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Ankit404butfound/PyWhatKit</t>
+          <t>1234567Yang/cf-proxy-ex</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://github.com/Ankit404butfound/PyWhatKit</t>
+          <t>https://github.com/1234567Yang/cf-proxy-ex</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Send WhatsApp message at certain time and many other things.</t>
+          <t>Cloudflare超级代理，无服务器代理，Duckduckgo代理（可用AI聊天，包含GPT4o/Claude3），Github加速，支持解锁Libgen，在线代理。现已支持多平台部署。Cloudflare super proxy, setting up a free serverless proxy by using Cloudflare worker, support Duckduck...</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>04-12-2025 07:14</t>
+          <t>05-12-2025 10:32</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>21-11-2019 02:44</t>
+          <t>15-06-2024 15:54</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>hacktoberfest, hacktoberfest-accepted, hacktoberfest2021, pywhatkit</t>
+          <t>bypass, cloudflare-proxy, cloudflare-reverse-proxy, cloudflare-workers, free-proxy</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>filipecalegario/awesome-vibe-coding</t>
+          <t>Ankit404butfound/PyWhatKit</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://github.com/filipecalegario/awesome-vibe-coding</t>
+          <t>https://github.com/Ankit404butfound/PyWhatKit</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>A curated list of vibe coding references, collaborating with AI to write code.</t>
+          <t>Send WhatsApp message at certain time and many other things.</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>1626</v>
+        <v>1634</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>04-12-2025 22:45</t>
+          <t>05-12-2025 15:59</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>13-03-2025 17:46</t>
+          <t>21-11-2019 02:44</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>ai-agent, ai-agents, ai-coding-assistant, ai-coding-tools, awesome</t>
+          <t>hacktoberfest, hacktoberfest-accepted, hacktoberfest2021, pywhatkit</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17589,7 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>04-12-2025 17:21</t>
+          <t>05-12-2025 19:01</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -17769,11 +17769,11 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>04-12-2025 17:18</t>
+          <t>05-12-2025 15:07</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>05-12-2025 00:07</t>
+          <t>05-12-2025 02:02</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17854,7 +17854,7 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>30-11-2025 16:36</t>
+          <t>05-12-2025 17:41</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -17899,7 +17899,7 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>03-12-2025 16:41</t>
+          <t>05-12-2025 18:54</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>1496</v>
+        <v>1504</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>04-12-2025 22:28</t>
+          <t>05-12-2025 10:10</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>05-12-2025 00:37</t>
+          <t>06-12-2025 00:37</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -18029,11 +18029,11 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>01-12-2025 11:01</t>
+          <t>05-12-2025 19:48</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>04-12-2025 16:46</t>
+          <t>05-12-2025 10:47</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18106,7 +18106,7 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>04-12-2025 22:26</t>
+          <t>05-12-2025 19:20</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>04-12-2025 23:52</t>
+          <t>05-12-2025 22:10</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>04-12-2025 17:56</t>
+          <t>05-12-2025 09:32</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -18237,7 +18237,7 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>04-12-2025 18:37</t>
+          <t>05-12-2025 14:59</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>04-12-2025 23:54</t>
+          <t>06-12-2025 00:49</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -18327,7 +18327,7 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>04-12-2025 19:43</t>
+          <t>05-12-2025 13:41</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -18372,7 +18372,7 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>04-12-2025 18:00</t>
+          <t>05-12-2025 23:57</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>04-12-2025 18:35</t>
+          <t>05-12-2025 12:03</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>04-12-2025 16:23</t>
+          <t>05-12-2025 04:03</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -18597,7 +18597,7 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>04-12-2025 05:34</t>
+          <t>05-12-2025 17:25</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -18642,11 +18642,11 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>04-12-2025 19:08</t>
+          <t>05-12-2025 21:41</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>1251</v>
+        <v>1260</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>04-12-2025 20:40</t>
+          <t>06-12-2025 00:25</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -18768,7 +18768,7 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>03-12-2025 22:54</t>
+          <t>05-12-2025 12:18</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -18813,7 +18813,7 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>02-12-2025 11:07</t>
+          <t>05-12-2025 03:39</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -18858,7 +18858,7 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>04-12-2025 09:24</t>
+          <t>05-12-2025 15:14</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -18944,7 +18944,7 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>04-12-2025 18:24</t>
+          <t>05-12-2025 06:30</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>04-12-2025 18:45</t>
+          <t>06-12-2025 00:33</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>03-12-2025 13:08</t>
+          <t>06-12-2025 00:26</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>04-12-2025 21:39</t>
+          <t>05-12-2025 01:56</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -19281,85 +19281,85 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>zukixa/cool-ai-stuff</t>
+          <t>LLM-Red-Team/qwen-free-api</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://github.com/zukixa/cool-ai-stuff</t>
+          <t>https://github.com/LLM-Red-Team/qwen-free-api</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>This repository contains a list of free to use AI APIs and sites. We are NOT endorsing ANY of the listed services!</t>
+          <t>🚀 阿里通义千问2.5大模型逆向API【特长：六边形战士】，支持高速流式输出、无水印AI绘图、长文档解读、图像解析、联网检索、多轮对话，零配置部署，多路token支持，自动清理会话痕迹，仅供测试，如需商用请前往官方开放平台。</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>1109</v>
+        <v>1110</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>04-12-2025 22:08</t>
+          <t>05-12-2025 19:28</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>02-09-2023 23:24</t>
+          <t>23-03-2024 17:49</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>ai, awesome-list, chatgpt, chatgpt-api, free-chatgpt-4</t>
+          <t>chat-api, chatbot, chatgpt-api, llm, qwen</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>LLM-Red-Team/qwen-free-api</t>
+          <t>zukixa/cool-ai-stuff</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://github.com/LLM-Red-Team/qwen-free-api</t>
+          <t>https://github.com/zukixa/cool-ai-stuff</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>🚀 阿里通义千问2.5大模型逆向API【特长：六边形战士】，支持高速流式输出、无水印AI绘图、长文档解读、图像解析、联网检索、多轮对话，零配置部署，多路token支持，自动清理会话痕迹，仅供测试，如需商用请前往官方开放平台。</t>
+          <t>This repository contains a list of free to use AI APIs and sites. We are NOT endorsing ANY of the listed services!</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>1107</v>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
+        <v>1109</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>03-12-2025 23:03</t>
+          <t>04-12-2025 22:08</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>23-03-2024 17:49</t>
+          <t>02-09-2023 23:24</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>chat-api, chatbot, chatgpt-api, llm, qwen</t>
+          <t>ai, awesome-list, chatgpt, chatgpt-api, free-chatgpt-4</t>
         </is>
       </c>
     </row>
@@ -19430,11 +19430,11 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>04-12-2025 19:43</t>
+          <t>05-12-2025 13:12</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -19470,7 +19470,7 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>17-11-2025 05:39</t>
+          <t>05-12-2025 08:20</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -19515,7 +19515,7 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>04-12-2025 13:02</t>
+          <t>05-12-2025 04:50</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -19556,7 +19556,7 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>03-12-2025 13:11</t>
+          <t>05-12-2025 10:11</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -19597,7 +19597,7 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>03-12-2025 19:17</t>
+          <t>05-12-2025 11:15</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -19683,7 +19683,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>03-12-2025 21:18</t>
+          <t>05-12-2025 10:59</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>04-12-2025 21:46</t>
+          <t>05-12-2025 21:47</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -19773,7 +19773,7 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>04-12-2025 11:59</t>
+          <t>05-12-2025 18:10</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -19863,7 +19863,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>04-12-2025 14:40</t>
+          <t>05-12-2025 01:44</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -19949,7 +19949,7 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>02-12-2025 09:03</t>
+          <t>05-12-2025 23:38</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -20079,7 +20079,7 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>04-12-2025 22:03</t>
+          <t>05-12-2025 14:48</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -20124,7 +20124,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>04-12-2025 18:23</t>
+          <t>05-12-2025 14:12</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -20210,7 +20210,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>04-12-2025 20:57</t>
+          <t>05-12-2025 13:39</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -20255,7 +20255,7 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>04-12-2025 18:09</t>
+          <t>05-12-2025 16:42</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -20300,7 +20300,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>04-12-2025 22:18</t>
+          <t>05-12-2025 21:55</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -20390,7 +20390,7 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>03-12-2025 23:03</t>
+          <t>05-12-2025 11:42</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -20435,7 +20435,7 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>02-12-2025 07:47</t>
+          <t>05-12-2025 16:31</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -20606,7 +20606,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>03-12-2025 17:13</t>
+          <t>05-12-2025 13:13</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -20651,7 +20651,7 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>04-12-2025 05:37</t>
+          <t>05-12-2025 03:40</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -20696,7 +20696,7 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>04-12-2025 21:50</t>
+          <t>05-12-2025 22:44</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -20826,11 +20826,11 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>04-12-2025 21:49</t>
+          <t>05-12-2025 21:40</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -20847,67 +20847,63 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>yllhwa/RSSWorker</t>
+          <t>MrTurvey/flareprox</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://github.com/yllhwa/RSSWorker</t>
+          <t>https://github.com/MrTurvey/flareprox</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>运行在Cloudflare Worker上的RSS订阅生成器</t>
+          <t>Use Cloudflare to create HTTP pass-through proxies for unique IP rotation, similar to fireprox</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>25-11-2025 16:39</t>
+          <t>05-12-2025 09:12</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>08-10-2023 09:59</t>
-        </is>
-      </c>
-      <c r="I466" t="inlineStr">
-        <is>
-          <t>bilibili, rss, rss-generator, telegram, weibo</t>
-        </is>
-      </c>
+          <t>26-09-2025 11:15</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>MrTurvey/flareprox</t>
+          <t>yllhwa/RSSWorker</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://github.com/MrTurvey/flareprox</t>
+          <t>https://github.com/yllhwa/RSSWorker</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Use Cloudflare to create HTTP pass-through proxies for unique IP rotation, similar to fireprox</t>
+          <t>运行在Cloudflare Worker上的RSS订阅生成器</t>
         </is>
       </c>
       <c r="E467" t="n">
@@ -20915,20 +20911,24 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>04-12-2025 17:39</t>
+          <t>05-12-2025 09:54</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>26-09-2025 11:15</t>
-        </is>
-      </c>
-      <c r="I467" t="inlineStr"/>
+          <t>08-10-2023 09:59</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>bilibili, rss, rss-generator, telegram, weibo</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -20952,7 +20952,7 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>29-11-2025 16:46</t>
+          <t>05-12-2025 22:10</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -21038,7 +21038,7 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>01-12-2025 18:48</t>
+          <t>05-12-2025 07:18</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -21128,7 +21128,7 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>03-12-2025 11:47</t>
+          <t>05-12-2025 14:41</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -21218,7 +21218,7 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>03-12-2025 02:20</t>
+          <t>05-12-2025 21:14</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -21308,7 +21308,7 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>04-12-2025 20:24</t>
+          <t>05-12-2025 10:50</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -21353,7 +21353,7 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>03-12-2025 23:03</t>
+          <t>05-12-2025 07:11</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>03-12-2025 22:52</t>
+          <t>05-12-2025 10:44</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -21488,7 +21488,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>03-12-2025 08:54</t>
+          <t>05-12-2025 10:42</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>24-11-2025 05:24</t>
+          <t>05-12-2025 06:18</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -21664,7 +21664,7 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>04-12-2025 16:21</t>
+          <t>05-12-2025 13:06</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>02-12-2025 11:44</t>
+          <t>05-12-2025 13:40</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -22093,7 +22093,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>03-12-2025 23:03</t>
+          <t>05-12-2025 04:26</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -22318,7 +22318,7 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>04-12-2025 23:07</t>
+          <t>05-12-2025 23:46</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -22363,7 +22363,7 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>04-12-2025 09:17</t>
+          <t>05-12-2025 13:53</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -22462,7 +22462,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>26-11-2025 22:21</t>
+          <t>05-12-2025 20:19</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -22575,7 +22575,7 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>04-12-2025 17:16</t>
+          <t>05-12-2025 06:57</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -22616,7 +22616,7 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>04-12-2025 21:25</t>
+          <t>05-12-2025 16:14</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>02-12-2025 17:27</t>
+          <t>05-12-2025 16:45</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>03-12-2025 15:31</t>
+          <t>05-12-2025 06:49</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -22963,7 +22963,7 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>30-11-2025 19:50</t>
+          <t>05-12-2025 03:06</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -23008,7 +23008,7 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>03-12-2025 04:54</t>
+          <t>05-12-2025 16:30</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -23053,7 +23053,7 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>05-12-2025 00:14</t>
+          <t>05-12-2025 11:07</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -23197,7 +23197,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>04-12-2025 19:27</t>
+          <t>05-12-2025 21:53</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -23356,7 +23356,7 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>01-12-2025 20:47</t>
+          <t>05-12-2025 13:35</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -23401,11 +23401,11 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>29-11-2025 08:04</t>
+          <t>06-12-2025 00:22</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -23441,7 +23441,7 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>05-12-2025 00:46</t>
+          <t>06-12-2025 00:48</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>ToolSDK.ai's Awesome MCP Servers and Packages Registry and Database with Structured JSON configurations</t>
+          <t>ToolSDK.ai's Awesome MCP Servers and Packages Registry and Database with Structured JSON configurations. Supports OAuth2.1, DCR...</t>
         </is>
       </c>
       <c r="E528" t="n">
@@ -23577,7 +23577,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>04-12-2025 09:12</t>
+          <t>05-12-2025 12:00</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -23724,85 +23724,85 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>rkwyu/scribd-dl</t>
+          <t>cloudcommunity/Free-for-Startups</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://github.com/rkwyu/scribd-dl</t>
+          <t>https://github.com/cloudcommunity/Free-for-Startups</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Scribd.com &amp; Slideshare.net Downloader</t>
+          <t>A curated collection of free resources for startups and entrepreneurs. Also available at https://freeforstartups.com/</t>
         </is>
       </c>
       <c r="E532" t="n">
         <v>120</v>
       </c>
-      <c r="F532" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>04-12-2025 16:37</t>
+          <t>05-12-2025 08:17</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>28-04-2024 00:35</t>
+          <t>13-02-2025 05:25</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>download, downloader, file-downloader, scribd, scribd-downloader</t>
+          <t>awesome, awesome-list, startup</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>cloudcommunity/Free-for-Startups</t>
+          <t>rkwyu/scribd-dl</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://github.com/cloudcommunity/Free-for-Startups</t>
+          <t>https://github.com/rkwyu/scribd-dl</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>A curated collection of free resources for startups and entrepreneurs. Also available at https://freeforstartups.com/</t>
+          <t>Scribd.com &amp; Slideshare.net Downloader</t>
         </is>
       </c>
       <c r="E533" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>01-12-2025 19:48</t>
+          <t>04-12-2025 16:37</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>13-02-2025 05:25</t>
+          <t>28-04-2024 00:35</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, startup</t>
+          <t>download, downloader, file-downloader, scribd, scribd-downloader</t>
         </is>
       </c>
     </row>
@@ -23837,7 +23837,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>04-12-2025 15:44</t>
+          <t>05-12-2025 20:27</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -23914,7 +23914,7 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>18-09-2025 03:47</t>
+          <t>05-12-2025 06:47</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">

--- a/starred_repos.xlsx
+++ b/starred_repos.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>501171</v>
+        <v>501244</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>14-05-2026 02:28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>465963</v>
+        <v>466054</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13-05-2026 17:48</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>434817</v>
+        <v>434859</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13-05-2026 17:54</t>
+          <t>14-05-2026 02:25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>371545</v>
+        <v>371635</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13-05-2026 17:53</t>
+          <t>14-05-2026 02:30</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>297455</v>
+        <v>297503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13-05-2026 17:51</t>
+          <t>14-05-2026 02:23</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -732,11 +732,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>291880</v>
+        <v>291946</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>13-05-2026 17:42</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -772,11 +772,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>265597</v>
+        <v>265626</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13-05-2026 17:50</t>
+          <t>14-05-2026 02:19</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220089</v>
+        <v>220145</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>203767</v>
+        <v>203779</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13-05-2026 17:35</t>
+          <t>14-05-2026 02:06</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>189277</v>
+        <v>189665</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13-05-2026 17:52</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>187706</v>
+        <v>187743</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>13-05-2026 17:48</t>
+          <t>14-05-2026 02:22</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>186985</v>
+        <v>186993</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13-05-2026 17:45</t>
+          <t>14-05-2026 02:04</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>184289</v>
+        <v>184290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13-05-2026 17:23</t>
+          <t>14-05-2026 02:07</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>175128</v>
+        <v>175164</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13-05-2026 17:37</t>
+          <t>14-05-2026 02:19</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>162190</v>
+        <v>162228</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13-05-2026 17:37</t>
+          <t>14-05-2026 02:17</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>162180</v>
+        <v>162192</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>13-05-2026 17:33</t>
+          <t>14-05-2026 02:26</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>162097</v>
+        <v>162131</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13-05-2026 17:17</t>
+          <t>14-05-2026 02:23</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>159693</v>
+        <v>159836</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>13-05-2026 17:47</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>148357</v>
+        <v>148816</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13-05-2026 17:53</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>140478</v>
+        <v>140761</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>13-05-2026 17:53</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1384,11 +1384,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>137318</v>
+        <v>137328</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>13-05-2026 17:35</t>
+          <t>14-05-2026 02:30</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>136912</v>
+        <v>136955</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>133117</v>
+        <v>133124</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>14-05-2026 02:27</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>123031</v>
+        <v>123057</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13-05-2026 17:51</t>
+          <t>14-05-2026 02:13</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>122268</v>
+        <v>122276</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>13-05-2026 17:54</t>
+          <t>14-05-2026 02:05</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>119347</v>
+        <v>119502</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>13-05-2026 17:54</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1649,11 +1649,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>116930</v>
+        <v>116934</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>13-05-2026 16:21</t>
+          <t>14-05-2026 01:23</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>116189</v>
+        <v>116195</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>13-05-2026 17:46</t>
+          <t>14-05-2026 01:57</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>114090</v>
+        <v>114109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13-05-2026 17:37</t>
+          <t>14-05-2026 02:28</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112772</v>
+        <v>112810</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1824,11 +1824,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>112141</v>
+        <v>112161</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>13-05-2026 17:18</t>
+          <t>14-05-2026 02:21</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>110127</v>
+        <v>110186</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13-05-2026 17:51</t>
+          <t>14-05-2026 02:27</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103975</v>
+        <v>103995</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>13-05-2026 17:37</t>
+          <t>14-05-2026 01:52</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103877</v>
+        <v>103908</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>13-05-2026 17:48</t>
+          <t>14-05-2026 02:26</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100462</v>
+        <v>100483</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>13-05-2026 17:47</t>
+          <t>14-05-2026 01:53</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>98166</v>
+        <v>98172</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13-05-2026 17:45</t>
+          <t>14-05-2026 02:20</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>94311</v>
+        <v>94314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>13-05-2026 16:50</t>
+          <t>14-05-2026 02:09</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2134,11 +2134,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>93870</v>
+        <v>93881</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>13-05-2026 17:46</t>
+          <t>14-05-2026 01:24</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>92966</v>
+        <v>92971</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13-05-2026 16:50</t>
+          <t>14-05-2026 02:16</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>89989</v>
+        <v>89999</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13-05-2026 17:12</t>
+          <t>14-05-2026 02:17</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>13-05-2026 16:13</t>
+          <t>13-05-2026 23:56</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>86664</v>
+        <v>86672</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>13-05-2026 17:38</t>
+          <t>14-05-2026 01:52</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2354,11 +2354,11 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>85549</v>
+        <v>85563</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>13-05-2026 17:44</t>
+          <t>14-05-2026 01:32</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>83278</v>
+        <v>83291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>13-05-2026 16:07</t>
+          <t>14-05-2026 02:27</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>81178</v>
+        <v>81194</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>13-05-2026 17:47</t>
+          <t>14-05-2026 02:19</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>79411</v>
+        <v>79414</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>13-05-2026 16:16</t>
+          <t>13-05-2026 23:03</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>77003</v>
+        <v>77023</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>13-05-2026 17:53</t>
+          <t>14-05-2026 02:25</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>72577</v>
+        <v>72576</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>13-05-2026 13:09</t>
+          <t>14-05-2026 00:30</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2615,11 +2615,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>70993</v>
+        <v>70998</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>13-05-2026 16:27</t>
+          <t>14-05-2026 02:26</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>70429</v>
+        <v>70435</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>13-05-2026 17:44</t>
+          <t>14-05-2026 01:51</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>69710</v>
+        <v>69879</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>13-05-2026 17:53</t>
+          <t>14-05-2026 02:30</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>67948</v>
+        <v>67954</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>13-05-2026 17:42</t>
+          <t>14-05-2026 02:17</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>66216</v>
+        <v>66219</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>13-05-2026 14:38</t>
+          <t>14-05-2026 02:25</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65681</v>
+        <v>65686</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13-05-2026 15:17</t>
+          <t>14-05-2026 01:07</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65479</v>
+        <v>65493</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>13-05-2026 17:21</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>13-05-2026 17:14</t>
+          <t>14-05-2026 02:29</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2961,11 +2961,11 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60035</v>
+        <v>60037</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>13-05-2026 17:22</t>
+          <t>14-05-2026 01:53</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59987</v>
+        <v>60003</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>13-05-2026 17:52</t>
+          <t>14-05-2026 02:19</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>59746</v>
+        <v>59742</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>13-05-2026 17:07</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59540</v>
+        <v>59543</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>13-05-2026 17:26</t>
+          <t>14-05-2026 01:44</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>58594</v>
+        <v>58600</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>13-05-2026 16:02</t>
+          <t>13-05-2026 23:49</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>57166</v>
+        <v>57172</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13-05-2026 17:53</t>
+          <t>14-05-2026 01:47</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>57154</v>
+        <v>57162</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>13-05-2026 17:32</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3271,11 +3271,11 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>56827</v>
+        <v>56838</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>13-05-2026 17:35</t>
+          <t>14-05-2026 02:18</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>56062</v>
+        <v>56063</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>13-05-2026 17:18</t>
+          <t>14-05-2026 01:41</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>54979</v>
+        <v>54988</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>13-05-2026 17:44</t>
+          <t>14-05-2026 01:38</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>54394</v>
+        <v>54409</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>13-05-2026 17:40</t>
+          <t>14-05-2026 02:23</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>54359</v>
+        <v>54360</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>13-05-2026 17:39</t>
+          <t>14-05-2026 02:27</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>54162</v>
+        <v>54164</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>13-05-2026 17:45</t>
+          <t>13-05-2026 23:24</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>13-05-2026 17:33</t>
+          <t>14-05-2026 01:59</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>13-05-2026 15:05</t>
+          <t>14-05-2026 01:12</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>13-05-2026 14:29</t>
+          <t>13-05-2026 23:55</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>51661</v>
+        <v>51666</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>13-05-2026 17:47</t>
+          <t>14-05-2026 02:14</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>51339</v>
+        <v>51340</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>13-05-2026 16:58</t>
+          <t>14-05-2026 00:47</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>51025</v>
+        <v>51029</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>13-05-2026 17:52</t>
+          <t>14-05-2026 01:36</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3794,11 +3794,11 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>50254</v>
+        <v>50258</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>13-05-2026 16:45</t>
+          <t>14-05-2026 02:23</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>49288</v>
+        <v>49344</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>13-05-2026 17:50</t>
+          <t>14-05-2026 02:28</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3879,11 +3879,11 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>48580</v>
+        <v>48613</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>13-05-2026 17:26</t>
+          <t>14-05-2026 02:24</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3919,11 +3919,11 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>48560</v>
+        <v>48564</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>13-05-2026 14:17</t>
+          <t>14-05-2026 02:05</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>47689</v>
+        <v>47775</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>14-05-2026 02:29</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>47074</v>
+        <v>47087</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>13-05-2026 17:36</t>
+          <t>14-05-2026 02:21</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>46835</v>
+        <v>46867</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>13-05-2026 17:33</t>
+          <t>14-05-2026 02:26</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>13-05-2026 17:54</t>
+          <t>14-05-2026 02:29</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4135,11 +4135,11 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>45719</v>
+        <v>45729</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>13-05-2026 17:25</t>
+          <t>14-05-2026 01:34</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>45583</v>
+        <v>45595</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>13-05-2026 17:52</t>
+          <t>14-05-2026 02:07</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>45303</v>
+        <v>45302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>13-05-2026 16:52</t>
+          <t>14-05-2026 01:10</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>45238</v>
+        <v>45250</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>13-05-2026 16:47</t>
+          <t>14-05-2026 02:30</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>44781</v>
+        <v>44780</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>12-05-2026 17:59</t>
+          <t>13-05-2026 18:43</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>43852</v>
+        <v>43856</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>13-05-2026 16:32</t>
+          <t>14-05-2026 02:22</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>43135</v>
+        <v>43142</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>13-05-2026 16:49</t>
+          <t>14-05-2026 02:14</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>42504</v>
+        <v>42506</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>13-05-2026 16:17</t>
+          <t>14-05-2026 01:09</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4471,90 +4471,90 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>payloadcms/payload</t>
+          <t>HKUDS/nanobot</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://github.com/payloadcms/payload</t>
+          <t>https://github.com/HKUDS/nanobot</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Payload is the open-source, fullstack Next.js framework, giving you instant backend superpowers. Get a full TypeScript backend and admin panel instantly. Use Payload as a headless CMS or for buildi...</t>
+          <t>"🐈 nanobot: The Ultra-Lightweight Personal AI Agent"</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>42370</v>
+        <v>42380</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>13-05-2026 17:48</t>
+          <t>14-05-2026 02:10</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>05-01-2021 18:49</t>
+          <t>01-02-2026 07:16</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>cms, content-management, content-management-system, express, graphql</t>
+          <t>ai, ai-agent, ai-agents, anthropic, chatgpt</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HKUDS/nanobot</t>
+          <t>payloadcms/payload</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://github.com/HKUDS/nanobot</t>
+          <t>https://github.com/payloadcms/payload</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>"🐈 nanobot: The Ultra-Lightweight Personal AI Agent"</t>
+          <t>Payload is the open-source, fullstack Next.js framework, giving you instant backend superpowers. Get a full TypeScript backend and admin panel instantly. Use Payload as a headless CMS or for buildi...</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>42364</v>
+        <v>42376</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>13-05-2026 17:52</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01-02-2026 07:16</t>
+          <t>05-01-2021 18:49</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ai, ai-agent, ai-agents, anthropic, chatgpt</t>
+          <t>cms, content-management, content-management-system, express, graphql</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>41204</v>
+        <v>41236</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>13-05-2026 17:11</t>
+          <t>14-05-2026 02:23</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>39618</v>
+        <v>39619</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>13-05-2026 15:17</t>
+          <t>13-05-2026 19:57</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>39472</v>
+        <v>39502</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>13-05-2026 17:42</t>
+          <t>14-05-2026 02:28</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>38518</v>
+        <v>38522</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>13-05-2026 14:51</t>
+          <t>13-05-2026 20:38</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>38394</v>
+        <v>38393</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>13-05-2026 14:57</t>
+          <t>14-05-2026 00:49</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>38004</v>
+        <v>38009</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>13-05-2026 15:20</t>
+          <t>14-05-2026 02:05</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4850,11 +4850,11 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>37927</v>
+        <v>37933</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>13-05-2026 16:22</t>
+          <t>14-05-2026 02:24</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>37901</v>
+        <v>37902</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>13-05-2026 14:33</t>
+          <t>14-05-2026 00:59</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>37349</v>
+        <v>37352</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>13-05-2026 14:12</t>
+          <t>14-05-2026 01:40</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>36957</v>
+        <v>36972</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>13-05-2026 17:50</t>
+          <t>14-05-2026 01:39</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>36497</v>
+        <v>36496</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>13-05-2026 12:17</t>
+          <t>13-05-2026 17:56</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5070,11 +5070,11 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>35981</v>
+        <v>35985</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>13-05-2026 15:08</t>
+          <t>13-05-2026 23:45</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>35484</v>
+        <v>35487</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>13-05-2026 14:57</t>
+          <t>14-05-2026 00:36</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>13-05-2026 17:45</t>
+          <t>14-05-2026 00:20</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>34687</v>
+        <v>34694</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>13-05-2026 17:12</t>
+          <t>14-05-2026 02:26</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>34537</v>
+        <v>34540</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>13-05-2026 16:07</t>
+          <t>14-05-2026 01:51</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>34377</v>
+        <v>34392</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>13-05-2026 17:03</t>
+          <t>14-05-2026 02:24</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>34364</v>
+        <v>34368</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>13-05-2026 15:57</t>
+          <t>14-05-2026 02:20</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>34302</v>
+        <v>34310</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>14-05-2026 00:54</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5421,11 +5421,11 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>34195</v>
+        <v>34194</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>13-05-2026 16:05</t>
+          <t>13-05-2026 23:55</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>34123</v>
+        <v>34126</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>13-05-2026 17:28</t>
+          <t>14-05-2026 01:25</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5506,7 +5506,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>33956</v>
+        <v>33965</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>13-05-2026 17:41</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>33921</v>
+        <v>33932</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>13-05-2026 17:46</t>
+          <t>14-05-2026 02:20</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5592,11 +5592,11 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>33871</v>
+        <v>33874</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>13-05-2026 15:04</t>
+          <t>14-05-2026 01:10</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>33814</v>
+        <v>33816</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>13-05-2026 13:17</t>
+          <t>14-05-2026 00:02</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>33649</v>
+        <v>33658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>13-05-2026 17:33</t>
+          <t>14-05-2026 02:16</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>32812</v>
+        <v>32815</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>13-05-2026 17:36</t>
+          <t>14-05-2026 02:29</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>32089</v>
+        <v>32104</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>13-05-2026 17:35</t>
+          <t>14-05-2026 02:26</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>31674</v>
+        <v>31672</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>13-05-2026 14:10</t>
+          <t>14-05-2026 00:49</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>31520</v>
+        <v>31531</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>13-05-2026 17:51</t>
+          <t>14-05-2026 01:48</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5938,7 +5938,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>31449</v>
+        <v>31451</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>13-05-2026 17:39</t>
+          <t>14-05-2026 00:06</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>31349</v>
+        <v>31374</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>13-05-2026 17:48</t>
+          <t>14-05-2026 02:16</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>31313</v>
+        <v>31320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>13-05-2026 17:10</t>
+          <t>14-05-2026 02:00</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>14-05-2026 02:03</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>30345</v>
+        <v>30346</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>13-05-2026 17:33</t>
+          <t>13-05-2026 22:37</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>30333</v>
+        <v>30343</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>13-05-2026 17:42</t>
+          <t>14-05-2026 02:16</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>30050</v>
+        <v>30055</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>13-05-2026 15:53</t>
+          <t>14-05-2026 00:35</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>30048</v>
+        <v>30051</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>13-05-2026 17:13</t>
+          <t>14-05-2026 02:27</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>13-05-2026 12:44</t>
+          <t>13-05-2026 21:22</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>29478</v>
+        <v>29485</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>13-05-2026 16:29</t>
+          <t>14-05-2026 02:05</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>29199</v>
+        <v>29201</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>13-05-2026 16:58</t>
+          <t>14-05-2026 02:04</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>29120</v>
+        <v>29123</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>13-05-2026 17:47</t>
+          <t>14-05-2026 01:33</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>29030</v>
+        <v>29032</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>13-05-2026 17:35</t>
+          <t>14-05-2026 02:21</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>28966</v>
+        <v>28970</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>13-05-2026 17:26</t>
+          <t>14-05-2026 02:00</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>28837</v>
+        <v>28841</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>13-05-2026 17:40</t>
+          <t>14-05-2026 02:27</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>28025</v>
+        <v>28024</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>13-05-2026 15:52</t>
+          <t>14-05-2026 01:33</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6644,11 +6644,11 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>27778</v>
+        <v>27781</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>13-05-2026 12:28</t>
+          <t>13-05-2026 21:58</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>27534</v>
+        <v>27535</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>13-05-2026 14:35</t>
+          <t>13-05-2026 23:54</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>27465</v>
+        <v>27464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>13-05-2026 16:08</t>
+          <t>14-05-2026 02:10</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>27246</v>
+        <v>27252</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>13-05-2026 16:04</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>13-05-2026 17:11</t>
+          <t>13-05-2026 23:58</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>27089</v>
+        <v>27092</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>13-05-2026 15:54</t>
+          <t>14-05-2026 01:43</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>27064</v>
+        <v>27065</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>13-05-2026 11:08</t>
+          <t>14-05-2026 00:16</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6950,11 +6950,11 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>26802</v>
+        <v>26803</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>13-05-2026 16:19</t>
+          <t>14-05-2026 01:30</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>26699</v>
+        <v>26700</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>13-05-2026 15:10</t>
+          <t>14-05-2026 00:51</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>26312</v>
+        <v>26317</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>13-05-2026 16:11</t>
+          <t>14-05-2026 02:24</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>26274</v>
+        <v>26279</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>13-05-2026 17:13</t>
+          <t>14-05-2026 02:30</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>26155</v>
+        <v>26154</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>13-05-2026 14:49</t>
+          <t>13-05-2026 23:54</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>13-05-2026 14:34</t>
+          <t>13-05-2026 21:01</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7207,11 +7207,11 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>26101</v>
+        <v>26105</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>13-05-2026 16:44</t>
+          <t>14-05-2026 00:26</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>25915</v>
+        <v>25928</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>13-05-2026 17:20</t>
+          <t>14-05-2026 01:56</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>25269</v>
+        <v>25276</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>13-05-2026 16:28</t>
+          <t>14-05-2026 01:54</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>25223</v>
+        <v>25244</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>13-05-2026 17:36</t>
+          <t>14-05-2026 02:02</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>25166</v>
+        <v>25168</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>13-05-2026 15:30</t>
+          <t>14-05-2026 02:25</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>25105</v>
+        <v>25111</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>13-05-2026 17:26</t>
+          <t>14-05-2026 02:24</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>25090</v>
+        <v>25092</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>13-05-2026 17:16</t>
+          <t>14-05-2026 02:01</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>25001</v>
+        <v>25030</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>13-05-2026 17:25</t>
+          <t>14-05-2026 02:22</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>13-05-2026 14:43</t>
+          <t>13-05-2026 23:00</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>24728</v>
+        <v>24732</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>13-05-2026 17:47</t>
+          <t>14-05-2026 01:15</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>24692</v>
+        <v>24696</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>13-05-2026 16:04</t>
+          <t>14-05-2026 01:36</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7674,40 +7674,40 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>QwenLM/qwen-code</t>
+          <t>Alishahryar1/free-claude-code</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://github.com/QwenLM/qwen-code</t>
+          <t>https://github.com/Alishahryar1/free-claude-code</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>An open-source AI agent that lives in your terminal.</t>
+          <t>Use claude-code for free in the terminal, VSCode extension or discord like OpenClaw (voice supported)</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>24365</v>
+        <v>24397</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>13-05-2026 16:37</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>26-06-2025 01:37</t>
+          <t>28-01-2026 19:02</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -7715,88 +7715,88 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>arendst/Tasmota</t>
+          <t>QwenLM/qwen-code</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://github.com/arendst/Tasmota</t>
+          <t>https://github.com/QwenLM/qwen-code</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Alternative firmware for ESP8266 and ESP32 based devices with easy configuration using webUI, OTA updates, automation using timers or rules, expandability and entirely local control over MQTT, HTTP...</t>
+          <t>An open-source AI agent that lives in your terminal.</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>24362</v>
+        <v>24371</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>13-05-2026 15:34</t>
+          <t>14-05-2026 02:20</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>28-01-2017 13:37</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>arduino, automation, esp32, esp8266, firmware</t>
-        </is>
-      </c>
+          <t>26-06-2025 01:37</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Alishahryar1/free-claude-code</t>
+          <t>arendst/Tasmota</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://github.com/Alishahryar1/free-claude-code</t>
+          <t>https://github.com/arendst/Tasmota</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Use claude-code for free in the terminal, VSCode extension or discord like OpenClaw (voice supported)</t>
+          <t>Alternative firmware for ESP8266 and ESP32 based devices with easy configuration using webUI, OTA updates, automation using timers or rules, expandability and entirely local control over MQTT, HTTP...</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>24320</v>
+        <v>24364</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>13-05-2026 17:51</t>
+          <t>14-05-2026 01:26</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>28-01-2026 19:02</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>28-01-2017 13:37</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>arduino, automation, esp32, esp8266, firmware</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>24249</v>
+        <v>24257</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>13-05-2026 17:38</t>
+          <t>14-05-2026 02:29</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7865,11 +7865,11 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>23508</v>
+        <v>23507</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>13-05-2026 16:01</t>
+          <t>13-05-2026 21:31</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>23251</v>
+        <v>23254</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>13-05-2026 17:10</t>
+          <t>14-05-2026 02:10</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>23244</v>
+        <v>23243</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>13-05-2026 17:13</t>
+          <t>13-05-2026 23:53</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>22946</v>
+        <v>22949</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>13-05-2026 17:46</t>
+          <t>14-05-2026 00:28</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>13-05-2026 14:37</t>
+          <t>14-05-2026 01:03</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>22744</v>
+        <v>22760</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>13-05-2026 17:09</t>
+          <t>14-05-2026 01:47</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>22613</v>
+        <v>22615</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>13-05-2026 16:24</t>
+          <t>13-05-2026 20:24</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>22525</v>
+        <v>22529</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>13-05-2026 17:29</t>
+          <t>14-05-2026 02:04</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>22172</v>
+        <v>22173</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>13-05-2026 17:37</t>
+          <t>14-05-2026 01:54</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8305,11 +8305,11 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>22130</v>
+        <v>22134</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>13-05-2026 16:56</t>
+          <t>14-05-2026 01:35</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>13-05-2026 16:02</t>
+          <t>13-05-2026 22:06</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8431,7 +8431,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>21600</v>
+        <v>21598</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>13-05-2026 17:05</t>
+          <t>14-05-2026 02:02</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8476,7 +8476,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>21402</v>
+        <v>21419</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>13-05-2026 16:55</t>
+          <t>14-05-2026 02:09</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8521,11 +8521,11 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>21366</v>
+        <v>21370</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>13-05-2026 16:33</t>
+          <t>14-05-2026 02:28</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>13-05-2026 15:59</t>
+          <t>14-05-2026 00:26</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8606,7 +8606,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>21100</v>
+        <v>21101</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>13-05-2026 16:08</t>
+          <t>13-05-2026 20:29</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>21054</v>
+        <v>21053</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>13-05-2026 16:49</t>
+          <t>14-05-2026 01:05</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>20921</v>
+        <v>20925</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>13-05-2026 14:28</t>
+          <t>14-05-2026 02:29</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>20909</v>
+        <v>20910</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>13-05-2026 16:36</t>
+          <t>14-05-2026 01:15</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8786,11 +8786,11 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>20867</v>
+        <v>20873</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>13-05-2026 17:01</t>
+          <t>14-05-2026 01:28</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>20740</v>
+        <v>20745</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>13-05-2026 16:20</t>
+          <t>14-05-2026 00:47</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>20485</v>
+        <v>20488</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>13-05-2026 15:53</t>
+          <t>14-05-2026 01:49</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>20383</v>
+        <v>20385</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>13-05-2026 17:42</t>
+          <t>14-05-2026 02:17</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>20374</v>
+        <v>20378</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>13-05-2026 16:42</t>
+          <t>14-05-2026 01:52</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>20337</v>
+        <v>20338</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>13-05-2026 16:04</t>
+          <t>14-05-2026 00:44</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>20039</v>
+        <v>20050</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>13-05-2026 17:01</t>
+          <t>13-05-2026 23:49</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>13-05-2026 16:06</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>19730</v>
+        <v>19753</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>13-05-2026 17:48</t>
+          <t>14-05-2026 02:25</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>19679</v>
+        <v>19686</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>13-05-2026 14:58</t>
+          <t>13-05-2026 21:57</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>18922</v>
+        <v>18926</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>13-05-2026 15:58</t>
+          <t>14-05-2026 01:34</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9272,7 +9272,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>18877</v>
+        <v>18878</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>13-05-2026 15:08</t>
+          <t>13-05-2026 19:19</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>18854</v>
+        <v>18858</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>13-05-2026 16:03</t>
+          <t>14-05-2026 02:09</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>13-05-2026 08:40</t>
+          <t>13-05-2026 22:59</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>18754</v>
+        <v>18755</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>13-05-2026 12:21</t>
+          <t>14-05-2026 02:25</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>18312</v>
+        <v>18311</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>13-05-2026 17:37</t>
+          <t>13-05-2026 23:53</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>18228</v>
+        <v>18229</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>13-05-2026 14:12</t>
+          <t>13-05-2026 23:53</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>18069</v>
+        <v>18068</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>13-05-2026 11:02</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>18041</v>
+        <v>18045</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>13-05-2026 17:19</t>
+          <t>14-05-2026 01:24</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>17601</v>
+        <v>17605</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>13-05-2026 17:22</t>
+          <t>14-05-2026 02:17</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>17274</v>
+        <v>17281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>13-05-2026 17:06</t>
+          <t>14-05-2026 02:16</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9722,11 +9722,11 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>17081</v>
+        <v>17082</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>13-05-2026 13:58</t>
+          <t>14-05-2026 01:04</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9762,7 +9762,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>16942</v>
+        <v>16945</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>13-05-2026 10:47</t>
+          <t>14-05-2026 01:22</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9807,7 +9807,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>16811</v>
+        <v>16810</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>13-05-2026 14:29</t>
+          <t>13-05-2026 21:01</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>16793</v>
+        <v>16795</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>13-05-2026 15:40</t>
+          <t>14-05-2026 01:27</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>16763</v>
+        <v>16766</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>13-05-2026 13:17</t>
+          <t>13-05-2026 23:24</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>16615</v>
+        <v>16620</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>13-05-2026 17:29</t>
+          <t>14-05-2026 02:24</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>16457</v>
+        <v>16571</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>13-05-2026 17:48</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>16197</v>
+        <v>16200</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>13-05-2026 14:39</t>
+          <t>14-05-2026 02:15</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>15961</v>
+        <v>15963</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>13-05-2026 16:06</t>
+          <t>14-05-2026 00:43</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>15943</v>
+        <v>15946</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>13-05-2026 17:29</t>
+          <t>14-05-2026 00:40</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>15878</v>
+        <v>15877</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>13-05-2026 14:32</t>
+          <t>13-05-2026 21:01</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>15592</v>
+        <v>15595</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>13-05-2026 14:18</t>
+          <t>14-05-2026 02:10</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>15592</v>
+        <v>15591</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>13-05-2026 14:56</t>
+          <t>14-05-2026 01:39</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>13-05-2026 15:42</t>
+          <t>13-05-2026 23:53</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>15095</v>
+        <v>15091</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>13-05-2026 12:57</t>
+          <t>13-05-2026 23:55</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>15088</v>
+        <v>15090</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>13-05-2026 14:45</t>
+          <t>14-05-2026 00:49</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>15072</v>
+        <v>15073</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>13-05-2026 16:58</t>
+          <t>13-05-2026 21:00</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>15017</v>
+        <v>15019</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>13-05-2026 14:47</t>
+          <t>13-05-2026 20:03</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>13-05-2026 16:53</t>
+          <t>13-05-2026 23:56</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>15008</v>
+        <v>15011</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>13-05-2026 15:03</t>
+          <t>14-05-2026 01:18</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>14899</v>
+        <v>14897</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>13-05-2026 14:01</t>
+          <t>13-05-2026 23:53</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>14858</v>
+        <v>14859</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>13-05-2026 17:32</t>
+          <t>14-05-2026 00:55</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10740,11 +10740,11 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>14808</v>
+        <v>14809</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>13-05-2026 16:08</t>
+          <t>13-05-2026 22:25</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>14785</v>
+        <v>14786</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>13-05-2026 15:34</t>
+          <t>13-05-2026 23:22</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>14698</v>
+        <v>14699</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>13-05-2026 16:33</t>
+          <t>13-05-2026 22:03</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>14691</v>
+        <v>14692</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>13-05-2026 14:50</t>
+          <t>13-05-2026 18:33</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>14668</v>
+        <v>14671</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>13-05-2026 17:48</t>
+          <t>14-05-2026 01:09</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>14606</v>
+        <v>14614</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>13-05-2026 17:32</t>
+          <t>14-05-2026 01:57</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -11046,11 +11046,11 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>14431</v>
+        <v>14433</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>13-05-2026 17:09</t>
+          <t>13-05-2026 23:02</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -11086,7 +11086,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>14210</v>
+        <v>14209</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>13-05-2026 17:26</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>14181</v>
+        <v>14178</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>13-05-2026 17:35</t>
+          <t>14-05-2026 02:11</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>14173</v>
+        <v>14174</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>13-05-2026 14:59</t>
+          <t>13-05-2026 21:59</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -11221,7 +11221,7 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>14060</v>
+        <v>14061</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>13-05-2026 14:26</t>
+          <t>13-05-2026 23:56</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -11266,7 +11266,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>14038</v>
+        <v>14039</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>13-05-2026 16:02</t>
+          <t>13-05-2026 23:52</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>13-05-2026 15:00</t>
+          <t>13-05-2026 19:53</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>13871</v>
+        <v>13876</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>13-05-2026 12:52</t>
+          <t>13-05-2026 21:33</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -11491,7 +11491,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>13833</v>
+        <v>13832</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>13-05-2026 17:16</t>
+          <t>13-05-2026 19:49</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -11536,11 +11536,11 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>13813</v>
+        <v>13816</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>13-05-2026 17:32</t>
+          <t>14-05-2026 00:35</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>13708</v>
+        <v>13709</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>13-05-2026 17:41</t>
+          <t>13-05-2026 18:54</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>13615</v>
+        <v>13617</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>13-05-2026 13:27</t>
+          <t>13-05-2026 19:42</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>13509</v>
+        <v>13511</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>13-05-2026 15:39</t>
+          <t>13-05-2026 19:35</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>13142</v>
+        <v>13145</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>13-05-2026 17:43</t>
+          <t>14-05-2026 02:01</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -11842,7 +11842,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>13075</v>
+        <v>13080</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>13-05-2026 15:43</t>
+          <t>14-05-2026 02:12</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>13032</v>
+        <v>13035</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>13-05-2026 17:35</t>
+          <t>14-05-2026 02:19</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>12998</v>
+        <v>12999</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>13-05-2026 11:13</t>
+          <t>14-05-2026 00:03</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -11977,7 +11977,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>12973</v>
+        <v>12974</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>13-05-2026 17:46</t>
+          <t>14-05-2026 02:19</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>12751</v>
+        <v>12756</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>13-05-2026 17:10</t>
+          <t>14-05-2026 00:06</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>12405</v>
+        <v>12406</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>13-05-2026 15:49</t>
+          <t>13-05-2026 23:30</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>12354</v>
+        <v>12355</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>13-05-2026 14:30</t>
+          <t>13-05-2026 20:04</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>12232</v>
+        <v>12235</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>13-05-2026 17:11</t>
+          <t>14-05-2026 02:01</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -12332,7 +12332,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>12164</v>
+        <v>12171</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>13-05-2026 17:44</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>12055</v>
+        <v>12054</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>13-05-2026 15:32</t>
+          <t>13-05-2026 23:56</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>12017</v>
+        <v>12016</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>13-05-2026 11:52</t>
+          <t>13-05-2026 22:00</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>11978</v>
+        <v>11976</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>13-05-2026 09:59</t>
+          <t>13-05-2026 19:49</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -12512,7 +12512,7 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>11973</v>
+        <v>11976</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>13-05-2026 16:57</t>
+          <t>13-05-2026 23:15</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>11968</v>
+        <v>11972</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>13-05-2026 16:53</t>
+          <t>14-05-2026 02:04</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>11834</v>
+        <v>11836</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>13-05-2026 14:39</t>
+          <t>13-05-2026 21:38</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -12687,7 +12687,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>11773</v>
+        <v>11781</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>13-05-2026 17:38</t>
+          <t>14-05-2026 02:26</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>11610</v>
+        <v>11612</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>13-05-2026 16:34</t>
+          <t>13-05-2026 19:52</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>11596</v>
+        <v>11609</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>13-05-2026 17:37</t>
+          <t>14-05-2026 02:01</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>13-05-2026 17:46</t>
+          <t>13-05-2026 23:58</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>11369</v>
+        <v>11367</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>13-05-2026 16:55</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>11043</v>
+        <v>11045</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>13-05-2026 14:22</t>
+          <t>13-05-2026 19:36</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -12990,7 +12990,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>11014</v>
+        <v>11012</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>13-05-2026 16:07</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -13035,7 +13035,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>10923</v>
+        <v>10927</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>13-05-2026 17:34</t>
+          <t>14-05-2026 01:14</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -13080,7 +13080,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>10880</v>
+        <v>10889</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>14-05-2026 02:02</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -13125,7 +13125,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>10864</v>
+        <v>10866</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>13-05-2026 15:17</t>
+          <t>14-05-2026 00:03</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -13170,7 +13170,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>10784</v>
+        <v>10791</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>13-05-2026 15:59</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>10739</v>
+        <v>10737</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>13-05-2026 10:12</t>
+          <t>13-05-2026 23:56</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -13260,7 +13260,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>10677</v>
+        <v>10678</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>13-05-2026 17:38</t>
+          <t>13-05-2026 19:29</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -13350,7 +13350,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>10563</v>
+        <v>10562</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>13-05-2026 01:57</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>10371</v>
+        <v>10374</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>13-05-2026 13:49</t>
+          <t>14-05-2026 01:26</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>10371</v>
+        <v>10373</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>13-05-2026 06:01</t>
+          <t>13-05-2026 21:54</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>13-05-2026 12:22</t>
+          <t>14-05-2026 01:36</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -13525,7 +13525,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>10276</v>
+        <v>10281</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>13-05-2026 15:34</t>
+          <t>13-05-2026 22:34</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>9931</v>
+        <v>9934</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>13-05-2026 15:16</t>
+          <t>14-05-2026 02:10</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>13-05-2026 06:34</t>
+          <t>13-05-2026 22:48</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -13727,90 +13727,90 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>nextcloud/all-in-one</t>
+          <t>cocoindex-io/cocoindex</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://github.com/nextcloud/all-in-one</t>
+          <t>https://github.com/cocoindex-io/cocoindex</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>📦 The official Nextcloud installation method. Provides easy deployment and maintenance with most features included in this one Nextcloud instance.</t>
+          <t>Incremental engine for long horizon agents 🌟 Star if you like it!</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>9711</v>
+        <v>9715</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>13-05-2026 16:05</t>
+          <t>14-05-2026 01:20</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>30-11-2021 10:16</t>
+          <t>03-03-2025 23:03</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>backup, docker, nextcloud, restore</t>
+          <t>agentic-data-framework, ai, ai-agents, change-data-capture, codebase-intelligence</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>cocoindex-io/cocoindex</t>
+          <t>nextcloud/all-in-one</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://github.com/cocoindex-io/cocoindex</t>
+          <t>https://github.com/nextcloud/all-in-one</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Incremental engine for long horizon agents 🌟 Star if you like it!</t>
+          <t>📦 The official Nextcloud installation method. Provides easy deployment and maintenance with most features included in this one Nextcloud instance.</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>9709</v>
+        <v>9714</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>13-05-2026 17:45</t>
+          <t>14-05-2026 01:04</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>03-03-2025 23:03</t>
+          <t>30-11-2021 10:16</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>agentic-data-framework, ai, ai-agents, change-data-capture, codebase-intelligence</t>
+          <t>backup, docker, nextcloud, restore</t>
         </is>
       </c>
     </row>
@@ -13836,7 +13836,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>9546</v>
+        <v>9547</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>13-05-2026 16:38</t>
+          <t>13-05-2026 21:33</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -13881,7 +13881,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>9507</v>
+        <v>9509</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>13-05-2026 14:17</t>
+          <t>14-05-2026 02:23</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -13926,11 +13926,11 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>9431</v>
+        <v>9433</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>12-05-2026 17:27</t>
+          <t>14-05-2026 01:50</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -13966,7 +13966,7 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>9364</v>
+        <v>9367</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>13-05-2026 16:58</t>
+          <t>14-05-2026 01:34</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -14011,7 +14011,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>9311</v>
+        <v>9313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>13-05-2026 16:52</t>
+          <t>14-05-2026 01:31</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -14056,7 +14056,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>9299</v>
+        <v>9310</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>13-05-2026 17:41</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -14101,7 +14101,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>9228</v>
+        <v>9229</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>13-05-2026 17:10</t>
+          <t>13-05-2026 18:55</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>9197</v>
+        <v>9196</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>13-05-2026 17:40</t>
+          <t>14-05-2026 02:17</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>9179</v>
+        <v>9180</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>13-05-2026 08:29</t>
+          <t>13-05-2026 21:52</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -14236,7 +14236,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>9097</v>
+        <v>9096</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>13-05-2026 17:16</t>
+          <t>13-05-2026 20:59</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>9039</v>
+        <v>9041</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>13-05-2026 16:18</t>
+          <t>14-05-2026 01:12</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -14326,7 +14326,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>9031</v>
+        <v>9039</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>13-05-2026 17:43</t>
+          <t>14-05-2026 02:15</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>9005</v>
+        <v>9009</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>13-05-2026 16:47</t>
+          <t>14-05-2026 01:45</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>8999</v>
+        <v>8997</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>13-05-2026 14:54</t>
+          <t>13-05-2026 21:03</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -14461,11 +14461,11 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>8924</v>
+        <v>8925</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>13-05-2026 13:17</t>
+          <t>13-05-2026 19:28</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>8818</v>
+        <v>8819</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>12-05-2026 18:30</t>
+          <t>13-05-2026 17:59</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>8666</v>
+        <v>8668</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>13-05-2026 15:31</t>
+          <t>14-05-2026 00:28</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>8584</v>
+        <v>8587</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>13-05-2026 17:49</t>
+          <t>13-05-2026 22:24</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -14726,7 +14726,7 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>8556</v>
+        <v>8562</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>13-05-2026 13:17</t>
+          <t>14-05-2026 01:32</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>8280</v>
+        <v>8281</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>13-05-2026 13:08</t>
+          <t>13-05-2026 19:15</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14852,7 +14852,7 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>8077</v>
+        <v>8075</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>13-05-2026 17:04</t>
+          <t>13-05-2026 23:58</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -14897,11 +14897,11 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>7917</v>
+        <v>7916</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>13-05-2026 14:14</t>
+          <t>13-05-2026 20:59</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -14937,7 +14937,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>13-05-2026 17:16</t>
+          <t>13-05-2026 19:11</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -14982,7 +14982,7 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>7840</v>
+        <v>7843</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>13-05-2026 16:41</t>
+          <t>14-05-2026 01:21</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>7726</v>
+        <v>7727</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>13-05-2026 16:23</t>
+          <t>13-05-2026 18:48</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -15072,7 +15072,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>7659</v>
+        <v>7666</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>13-05-2026 17:44</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>7550</v>
+        <v>7554</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>13-05-2026 15:45</t>
+          <t>14-05-2026 02:30</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -15162,7 +15162,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>7448</v>
+        <v>7452</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>13-05-2026 16:42</t>
+          <t>13-05-2026 23:50</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>7438</v>
+        <v>7436</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>13-05-2026 17:32</t>
+          <t>14-05-2026 00:54</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -15252,7 +15252,7 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>7350</v>
+        <v>7351</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>13-05-2026 16:11</t>
+          <t>13-05-2026 21:08</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -15297,7 +15297,7 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>7219</v>
+        <v>7220</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>13-05-2026 14:26</t>
+          <t>13-05-2026 21:29</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>13-05-2026 14:27</t>
+          <t>13-05-2026 23:05</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>13-05-2026 07:12</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -15563,7 +15563,7 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>6841</v>
+        <v>6866</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>13-05-2026 17:48</t>
+          <t>14-05-2026 02:31</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -15608,7 +15608,7 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>6737</v>
+        <v>6736</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>13-05-2026 15:52</t>
+          <t>13-05-2026 18:36</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -15698,7 +15698,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>6631</v>
+        <v>6632</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>13-05-2026 02:26</t>
+          <t>13-05-2026 19:49</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -15784,7 +15784,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>6604</v>
+        <v>6603</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>13-05-2026 16:08</t>
+          <t>14-05-2026 02:30</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>6521</v>
+        <v>6520</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>13-05-2026 17:29</t>
+          <t>13-05-2026 21:54</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>13-05-2026 07:34</t>
+          <t>14-05-2026 01:03</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6367</v>
+        <v>6368</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>13-05-2026 13:17</t>
+          <t>14-05-2026 01:33</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>6351</v>
+        <v>6350</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>13-05-2026 15:45</t>
+          <t>13-05-2026 19:49</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>6253</v>
+        <v>6255</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>13-05-2026 17:27</t>
+          <t>14-05-2026 02:21</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>6223</v>
+        <v>6222</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>13-05-2026 08:47</t>
+          <t>13-05-2026 21:03</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>6036</v>
+        <v>6035</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>13-05-2026 05:54</t>
+          <t>13-05-2026 22:58</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16275,7 +16275,7 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>13-05-2026 16:30</t>
+          <t>13-05-2026 21:21</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -16320,7 +16320,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>5892</v>
+        <v>5893</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>13-05-2026 04:40</t>
+          <t>13-05-2026 22:07</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -16450,7 +16450,7 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>5788</v>
+        <v>5789</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>13-05-2026 16:45</t>
+          <t>14-05-2026 02:11</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>13-05-2026 13:34</t>
+          <t>13-05-2026 23:24</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>5606</v>
+        <v>5609</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>13-05-2026 16:40</t>
+          <t>14-05-2026 01:07</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -16715,7 +16715,7 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>5593</v>
+        <v>5596</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>13-05-2026 14:39</t>
+          <t>13-05-2026 20:52</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>5552</v>
+        <v>5554</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>13-05-2026 15:29</t>
+          <t>13-05-2026 23:58</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16850,7 +16850,7 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>5508</v>
+        <v>5509</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>13-05-2026 17:13</t>
+          <t>13-05-2026 21:34</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16895,7 +16895,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>5500</v>
+        <v>5499</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>12-05-2026 17:36</t>
+          <t>13-05-2026 20:50</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -16940,7 +16940,7 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>5459</v>
+        <v>5461</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>13-05-2026 16:07</t>
+          <t>13-05-2026 23:54</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>5455</v>
+        <v>5459</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>13-05-2026 17:38</t>
+          <t>14-05-2026 01:51</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>13-05-2026 16:31</t>
+          <t>13-05-2026 22:27</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>5396</v>
+        <v>5398</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>13-05-2026 17:30</t>
+          <t>13-05-2026 20:00</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>5378</v>
+        <v>5375</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>13-05-2026 15:06</t>
+          <t>13-05-2026 21:00</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>5340</v>
+        <v>5348</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>13-05-2026 10:26</t>
+          <t>14-05-2026 02:19</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -17202,7 +17202,7 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>5244</v>
+        <v>5245</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>13-05-2026 07:42</t>
+          <t>14-05-2026 02:24</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>5241</v>
+        <v>5244</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>13-05-2026 16:10</t>
+          <t>14-05-2026 02:23</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>13-05-2026 15:00</t>
+          <t>13-05-2026 23:55</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -17382,11 +17382,11 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>5163</v>
+        <v>5167</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>13-05-2026 17:50</t>
+          <t>14-05-2026 02:03</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -17512,7 +17512,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>5092</v>
+        <v>5093</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>13-05-2026 17:32</t>
+          <t>13-05-2026 22:14</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>13-05-2026 14:12</t>
+          <t>13-05-2026 21:03</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -17692,7 +17692,7 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>5031</v>
+        <v>5035</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>13-05-2026 15:48</t>
+          <t>14-05-2026 02:01</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>5024</v>
+        <v>5025</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>13-05-2026 16:02</t>
+          <t>13-05-2026 18:20</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -17827,7 +17827,7 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>5002</v>
+        <v>5007</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>13-05-2026 16:24</t>
+          <t>14-05-2026 02:04</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>4982</v>
+        <v>4985</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>13-05-2026 15:07</t>
+          <t>14-05-2026 00:26</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17917,7 +17917,7 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>4944</v>
+        <v>4942</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>13-05-2026 06:22</t>
+          <t>13-05-2026 22:43</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>4934</v>
+        <v>4932</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>12-05-2026 15:50</t>
+          <t>13-05-2026 23:54</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -18097,7 +18097,7 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>4816</v>
+        <v>4817</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>12-05-2026 07:08</t>
+          <t>13-05-2026 19:27</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -18142,7 +18142,7 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>4816</v>
+        <v>4817</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>13-05-2026 16:04</t>
+          <t>14-05-2026 02:07</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>4792</v>
+        <v>4796</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>13-05-2026 14:37</t>
+          <t>14-05-2026 01:59</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>13-05-2026 15:29</t>
+          <t>14-05-2026 02:06</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18273,7 +18273,7 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>4728</v>
+        <v>4729</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>13-05-2026 09:06</t>
+          <t>13-05-2026 19:17</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>4652</v>
+        <v>4653</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>13-05-2026 12:48</t>
+          <t>14-05-2026 01:08</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>4600</v>
+        <v>4598</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>12-05-2026 18:52</t>
+          <t>13-05-2026 21:00</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -18614,63 +18614,67 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>spipm/Depixelization_poc</t>
+          <t>rikkahub/rikkahub</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://github.com/spipm/Depixelization_poc</t>
+          <t>https://github.com/rikkahub/rikkahub</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Depix is a PoC for a technique to recover plaintext from pixelized screenshots.</t>
+          <t>RikkaHub is an Android APP that supports for multiple LLM providers.</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>4528</v>
+        <v>4531</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Kotlin</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>12-05-2026 20:05</t>
+          <t>14-05-2026 01:50</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>06-12-2020 12:39</t>
-        </is>
-      </c>
-      <c r="I413" t="inlineStr"/>
+          <t>11-03-2025 14:46</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>android, app, chatbot-ui, chatbox, chatgpt</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>rikkahub/rikkahub</t>
+          <t>spipm/Depixelization_poc</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://github.com/rikkahub/rikkahub</t>
+          <t>https://github.com/spipm/Depixelization_poc</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>RikkaHub is an Android APP that supports for multiple LLM providers.</t>
+          <t>Depix is a PoC for a technique to recover plaintext from pixelized screenshots.</t>
         </is>
       </c>
       <c r="E414" t="n">
@@ -18678,24 +18682,20 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Kotlin</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>13-05-2026 16:47</t>
+          <t>12-05-2026 20:05</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>11-03-2025 14:46</t>
-        </is>
-      </c>
-      <c r="I414" t="inlineStr">
-        <is>
-          <t>android, app, chatbot-ui, chatbox, chatgpt</t>
-        </is>
-      </c>
+          <t>06-12-2020 12:39</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>4487</v>
+        <v>4486</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>13-05-2026 16:08</t>
+          <t>14-05-2026 02:23</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>4480</v>
+        <v>4482</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>13-05-2026 16:03</t>
+          <t>14-05-2026 00:31</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -18932,11 +18932,11 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>13-05-2026 16:23</t>
+          <t>14-05-2026 01:44</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -19017,7 +19017,7 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>4247</v>
+        <v>4249</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>13-05-2026 15:22</t>
+          <t>13-05-2026 20:37</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -19062,7 +19062,7 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>4204</v>
+        <v>4203</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>13-05-2026 08:24</t>
+          <t>13-05-2026 23:56</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -19279,7 +19279,7 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>4156</v>
+        <v>4158</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>13-05-2026 17:26</t>
+          <t>14-05-2026 01:06</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -19324,11 +19324,11 @@
         </is>
       </c>
       <c r="E429" t="n">
-        <v>4120</v>
+        <v>4119</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>13-05-2026 15:31</t>
+          <t>14-05-2026 01:14</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -19364,7 +19364,7 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>13-05-2026 17:22</t>
+          <t>13-05-2026 18:33</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -19454,7 +19454,7 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>12-05-2026 14:25</t>
+          <t>13-05-2026 18:16</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>4061</v>
+        <v>4063</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>13-05-2026 17:23</t>
+          <t>13-05-2026 20:10</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>4028</v>
+        <v>4029</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>13-05-2026 16:10</t>
+          <t>14-05-2026 02:26</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>13-05-2026 14:29</t>
+          <t>13-05-2026 19:36</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>13-05-2026 17:46</t>
+          <t>14-05-2026 01:33</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>13-05-2026 15:24</t>
+          <t>14-05-2026 01:08</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -19764,7 +19764,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>3911</v>
+        <v>3914</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>13-05-2026 07:02</t>
+          <t>13-05-2026 23:43</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>13-05-2026 12:39</t>
+          <t>14-05-2026 02:15</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>3872</v>
+        <v>3874</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>13-05-2026 01:46</t>
+          <t>14-05-2026 02:25</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -19944,7 +19944,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>3833</v>
+        <v>3845</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>13-05-2026 17:46</t>
+          <t>14-05-2026 02:30</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -20210,7 +20210,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>13-05-2026 06:23</t>
+          <t>13-05-2026 23:58</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>12-05-2026 19:23</t>
+          <t>13-05-2026 23:35</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -20345,7 +20345,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>13-05-2026 16:00</t>
+          <t>14-05-2026 02:12</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -20418,7 +20418,7 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>3592</v>
+        <v>3593</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>13-05-2026 13:57</t>
+          <t>13-05-2026 20:11</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>3565</v>
+        <v>3566</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>13-05-2026 16:33</t>
+          <t>13-05-2026 19:03</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -20534,22 +20534,22 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>offen/docker-volume-backup</t>
+          <t>TinyAGI/tinyagi</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://github.com/offen/docker-volume-backup</t>
+          <t>https://github.com/TinyAGI/tinyagi</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Backup Docker volumes locally or to any S3, WebDAV, Azure Blob Storage, Dropbox, Google Drive or SSH compatible storage</t>
+          <t>TinyAGI is the agent teams orchestrator for One Person Company. (fka TinyClaw)</t>
         </is>
       </c>
       <c r="E457" t="n">
@@ -20557,65 +20557,65 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>13-05-2026 04:41</t>
+          <t>13-05-2026 22:45</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>02-04-2021 11:45</t>
-        </is>
-      </c>
-      <c r="I457" t="inlineStr">
-        <is>
-          <t>backup, docker, docker-compose, docker-swarm, docker-volume</t>
-        </is>
-      </c>
+          <t>09-02-2026 00:34</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>TinyAGI/tinyagi</t>
+          <t>offen/docker-volume-backup</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://github.com/TinyAGI/tinyagi</t>
+          <t>https://github.com/offen/docker-volume-backup</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>TinyAGI is the agent teams orchestrator for One Person Company. (fka TinyClaw)</t>
+          <t>Backup Docker volumes locally or to any S3, WebDAV, Azure Blob Storage, Dropbox, Google Drive or SSH compatible storage</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>3561</v>
+        <v>3562</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>13-05-2026 08:28</t>
+          <t>13-05-2026 04:41</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>09-02-2026 00:34</t>
-        </is>
-      </c>
-      <c r="I458" t="inlineStr"/>
+          <t>02-04-2021 11:45</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>backup, docker, docker-compose, docker-swarm, docker-volume</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -20639,7 +20639,7 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>3549</v>
+        <v>3550</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>12-05-2026 14:26</t>
+          <t>13-05-2026 20:37</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -20680,7 +20680,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>13-05-2026 07:40</t>
+          <t>14-05-2026 00:44</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -20770,7 +20770,7 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>11-05-2026 11:56</t>
+          <t>13-05-2026 21:15</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -20860,7 +20860,7 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>3380</v>
+        <v>3383</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>13-05-2026 17:14</t>
+          <t>14-05-2026 01:47</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -20946,7 +20946,7 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>13-05-2026 14:29</t>
+          <t>13-05-2026 23:36</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -20991,7 +20991,7 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>13-05-2026 14:39</t>
+          <t>14-05-2026 02:13</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -21036,7 +21036,7 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>13-05-2026 13:38</t>
+          <t>13-05-2026 22:32</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -21081,7 +21081,7 @@
         </is>
       </c>
       <c r="E469" t="n">
-        <v>3279</v>
+        <v>3281</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>13-05-2026 09:30</t>
+          <t>13-05-2026 22:06</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -21135,7 +21135,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>13-05-2026 15:57</t>
+          <t>14-05-2026 01:26</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -21351,7 +21351,7 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>3167</v>
+        <v>3170</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>13-05-2026 07:43</t>
+          <t>13-05-2026 20:30</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -21392,7 +21392,7 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>3135</v>
+        <v>3137</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>13-05-2026 10:54</t>
+          <t>13-05-2026 20:25</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -21418,85 +21418,85 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>thomiceli/opengist</t>
+          <t>pawelborkar/awesome-repos</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://github.com/thomiceli/opengist</t>
+          <t>https://github.com/pawelborkar/awesome-repos</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Self-hosted pastebin powered by Git, open-source alternative to Github Gist.</t>
+          <t>A curated list of GitHub Repositories full of FREE Resources.</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>3130</v>
-      </c>
-      <c r="F477" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
+        <v>3132</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>13-05-2026 17:04</t>
+          <t>14-05-2026 01:29</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>10-04-2023 20:58</t>
+          <t>08-04-2021 15:17</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>docker, gist, git, go, golang</t>
+          <t>awesome, awesome-repos, awesome-repositories, free, github</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>pawelborkar/awesome-repos</t>
+          <t>thomiceli/opengist</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://github.com/pawelborkar/awesome-repos</t>
+          <t>https://github.com/thomiceli/opengist</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>A curated list of GitHub Repositories full of FREE Resources.</t>
+          <t>Self-hosted pastebin powered by Git, open-source alternative to Github Gist.</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>3129</v>
+        <v>3130</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>13-05-2026 15:10</t>
+          <t>13-05-2026 21:02</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>08-04-2021 15:17</t>
+          <t>10-04-2023 20:58</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>awesome, awesome-repos, awesome-repositories, free, github</t>
+          <t>docker, gist, git, go, golang</t>
         </is>
       </c>
     </row>
@@ -21567,7 +21567,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>12-05-2026 18:46</t>
+          <t>13-05-2026 23:35</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -21612,7 +21612,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>13-05-2026 13:46</t>
+          <t>14-05-2026 02:27</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -21702,7 +21702,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>2995</v>
+        <v>2996</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>13-05-2026 05:12</t>
+          <t>14-05-2026 01:43</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -21747,7 +21747,7 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>13-05-2026 08:55</t>
+          <t>13-05-2026 21:00</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -21792,7 +21792,7 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>13-05-2026 15:52</t>
+          <t>14-05-2026 01:10</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -21837,11 +21837,11 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>2961</v>
+        <v>2964</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>13-05-2026 16:52</t>
+          <t>14-05-2026 01:29</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>13-05-2026 04:22</t>
+          <t>13-05-2026 22:53</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>13-05-2026 02:55</t>
+          <t>14-05-2026 01:48</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="E489" t="n">
-        <v>2865</v>
+        <v>2867</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>13-05-2026 12:07</t>
+          <t>13-05-2026 21:37</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -22089,7 +22089,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>2828</v>
+        <v>2830</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>13-05-2026 15:09</t>
+          <t>14-05-2026 01:41</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -22138,7 +22138,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>13-05-2026 10:21</t>
+          <t>13-05-2026 18:10</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -22174,7 +22174,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>2762</v>
+        <v>2764</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>10-05-2026 15:34</t>
+          <t>14-05-2026 00:39</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -22219,7 +22219,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>2725</v>
+        <v>2728</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>13-05-2026 17:39</t>
+          <t>14-05-2026 02:18</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>2710</v>
+        <v>2712</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>13-05-2026 09:35</t>
+          <t>13-05-2026 20:25</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -22309,7 +22309,7 @@
         </is>
       </c>
       <c r="E497" t="n">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>13-05-2026 17:32</t>
+          <t>13-05-2026 21:02</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -22439,7 +22439,7 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>12-05-2026 18:56</t>
+          <t>13-05-2026 18:58</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>13-05-2026 15:13</t>
+          <t>13-05-2026 21:57</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -22570,7 +22570,7 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>13-05-2026 16:55</t>
+          <t>13-05-2026 20:27</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -22641,63 +22641,67 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Afilmory/afilmory</t>
+          <t>favonia/cloudflare-ddns</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://github.com/Afilmory/afilmory</t>
+          <t>https://github.com/favonia/cloudflare-ddns</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Modern photo gallery for photographers, with S3/GitHub sync, EXIF details, maps, and a WebGL viewer.</t>
+          <t>🌟 A small, feature-rich, and robust Cloudflare DDNS updater</t>
         </is>
       </c>
       <c r="E505" t="n">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>13-05-2026 09:16</t>
+          <t>13-05-2026 16:01</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>05-06-2025 05:16</t>
-        </is>
-      </c>
-      <c r="I505" t="inlineStr"/>
+          <t>04-06-2021 14:20</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>cloudflare, cloudflare-ddns, ddns, ddns-client, ddns-updater</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>favonia/cloudflare-ddns</t>
+          <t>Afilmory/afilmory</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://github.com/favonia/cloudflare-ddns</t>
+          <t>https://github.com/Afilmory/afilmory</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>🌟 A small, feature-rich, and robust Cloudflare DDNS updater</t>
+          <t>Modern photo gallery for photographers, with S3/GitHub sync, EXIF details, maps, and a WebGL viewer.</t>
         </is>
       </c>
       <c r="E506" t="n">
@@ -22705,24 +22709,20 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>13-05-2026 16:01</t>
+          <t>13-05-2026 23:58</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>04-06-2021 14:20</t>
-        </is>
-      </c>
-      <c r="I506" t="inlineStr">
-        <is>
-          <t>cloudflare, cloudflare-ddns, ddns, ddns-client, ddns-updater</t>
-        </is>
-      </c>
+          <t>05-06-2025 05:16</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>13-05-2026 17:37</t>
+          <t>13-05-2026 23:01</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -22791,7 +22791,7 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>11-05-2026 03:42</t>
+          <t>13-05-2026 19:14</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -22926,7 +22926,7 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>13-05-2026 16:12</t>
+          <t>14-05-2026 00:08</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -22971,7 +22971,7 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>13-05-2026 15:39</t>
+          <t>13-05-2026 23:55</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -23016,7 +23016,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>2393</v>
+        <v>2397</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>13-05-2026 16:23</t>
+          <t>14-05-2026 01:43</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -23042,88 +23042,88 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>ling-drag0n/CloudPaste</t>
+          <t>RookieEnough/Orion-Store</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://github.com/ling-drag0n/CloudPaste</t>
+          <t>https://github.com/RookieEnough/Orion-Store</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Web Development</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>🌩️ Serverless 自托管的文件管理与文本分享工具/网盘，支持多存储聚合管理和WebDAV 服务挂载。兼容 S3、WebDAV、OneDrive、Google Drive、Telegram、HF、GitHub 等。内置   Markdown 编辑器、30+文件格式预览。支持 Cloudflare Workers 或 Docker 部署。</t>
+          <t>The ultimate home for modded apps. OrionStore offers instant access to YouTube Morphe, YT Music Morphe, and essential open-source tools without the clutter. No servers, no tracking, just a beautifu...</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>2376</v>
+        <v>2380</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>13-05-2026 14:36</t>
+          <t>14-05-2026 01:56</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>02-04-2025 10:23</t>
-        </is>
-      </c>
-      <c r="I514" t="inlineStr">
-        <is>
-          <t>cloudflare, cloudflare-workers, docker, file-browser, huggingface</t>
-        </is>
-      </c>
+          <t>28-11-2025 11:15</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>RookieEnough/Orion-Store</t>
+          <t>ling-drag0n/CloudPaste</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://github.com/RookieEnough/Orion-Store</t>
+          <t>https://github.com/ling-drag0n/CloudPaste</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>The ultimate home for modded apps. OrionStore offers instant access to YouTube Morphe, YT Music Morphe, and essential open-source tools without the clutter. No servers, no tracking, just a beautifu...</t>
+          <t>🌩️ Serverless 自托管的文件管理与文本分享工具/网盘，支持多存储聚合管理和WebDAV 服务挂载。兼容 S3、WebDAV、OneDrive、Google Drive、Telegram、HF、GitHub 等。内置   Markdown 编辑器、30+文件格式预览。支持 Cloudflare Workers 或 Docker 部署。</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>13-05-2026 15:03</t>
+          <t>14-05-2026 00:42</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>28-11-2025 11:15</t>
-        </is>
-      </c>
-      <c r="I515" t="inlineStr"/>
+          <t>02-04-2025 10:23</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>cloudflare, cloudflare-workers, docker, file-browser, huggingface</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>13-05-2026 17:26</t>
+          <t>13-05-2026 22:57</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -23192,7 +23192,7 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>13-05-2026 13:39</t>
+          <t>13-05-2026 23:56</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -23363,7 +23363,7 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>13-05-2026 13:41</t>
+          <t>13-05-2026 18:45</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -23669,7 +23669,7 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>13-05-2026 12:08</t>
+          <t>13-05-2026 21:39</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -23719,7 +23719,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>13-05-2026 12:28</t>
+          <t>13-05-2026 19:47</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -23764,7 +23764,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>12-05-2026 13:46</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -23800,11 +23800,11 @@
         </is>
       </c>
       <c r="E531" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>12-05-2026 18:29</t>
+          <t>13-05-2026 23:44</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -23840,7 +23840,7 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>13-05-2026 13:10</t>
+          <t>13-05-2026 21:04</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="E541" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>13-05-2026 13:49</t>
+          <t>14-05-2026 01:51</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -24282,7 +24282,7 @@
         </is>
       </c>
       <c r="E542" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>13-05-2026 08:38</t>
+          <t>13-05-2026 18:14</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -24413,7 +24413,7 @@
         </is>
       </c>
       <c r="E545" t="n">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>13-05-2026 09:26</t>
+          <t>13-05-2026 22:46</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -24458,11 +24458,11 @@
         </is>
       </c>
       <c r="E546" t="n">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>13-05-2026 09:38</t>
+          <t>13-05-2026 21:54</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -24507,7 +24507,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>13-05-2026 16:16</t>
+          <t>13-05-2026 19:48</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -24638,7 +24638,7 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>13-05-2026 06:52</t>
+          <t>13-05-2026 23:56</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>13-05-2026 10:52</t>
+          <t>13-05-2026 22:29</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -24764,7 +24764,7 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>13-05-2026 09:01</t>
+          <t>13-05-2026 23:56</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -24809,7 +24809,7 @@
         </is>
       </c>
       <c r="E554" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>13-05-2026 07:55</t>
+          <t>13-05-2026 21:27</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -24854,7 +24854,7 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>13-05-2026 16:03</t>
+          <t>13-05-2026 19:22</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -25025,7 +25025,7 @@
         </is>
       </c>
       <c r="E559" t="n">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>13-05-2026 15:26</t>
+          <t>13-05-2026 19:41</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -25066,7 +25066,7 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>13-05-2026 05:04</t>
+          <t>13-05-2026 23:58</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -25201,7 +25201,7 @@
         </is>
       </c>
       <c r="E563" t="n">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>11-05-2026 15:59</t>
+          <t>13-05-2026 21:00</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -25651,7 +25651,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>13-05-2026 00:24</t>
+          <t>14-05-2026 02:17</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -25687,7 +25687,7 @@
         </is>
       </c>
       <c r="E574" t="n">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>11-05-2026 21:36</t>
+          <t>13-05-2026 21:03</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="E575" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>12-05-2026 14:55</t>
+          <t>13-05-2026 21:18</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -25863,11 +25863,11 @@
         </is>
       </c>
       <c r="E578" t="n">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>13-05-2026 15:01</t>
+          <t>13-05-2026 21:00</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -25948,7 +25948,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>13-05-2026 13:17</t>
+          <t>13-05-2026 20:26</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -26074,11 +26074,11 @@
         </is>
       </c>
       <c r="E583" t="n">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>13-05-2026 17:11</t>
+          <t>14-05-2026 00:56</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -26239,7 +26239,7 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>13-05-2026 11:05</t>
+          <t>13-05-2026 22:31</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -26505,7 +26505,7 @@
         </is>
       </c>
       <c r="E593" t="n">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>09-05-2026 12:52</t>
+          <t>13-05-2026 23:57</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -26550,7 +26550,7 @@
         </is>
       </c>
       <c r="E594" t="n">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>13-05-2026 16:26</t>
+          <t>14-05-2026 02:14</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -26595,7 +26595,7 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>12-05-2026 10:54</t>
+          <t>14-05-2026 00:28</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -26820,7 +26820,7 @@
         </is>
       </c>
       <c r="E600" t="n">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>13-05-2026 15:08</t>
+          <t>13-05-2026 23:44</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -26870,7 +26870,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>12-05-2026 22:21</t>
+          <t>13-05-2026 21:40</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -27081,7 +27081,7 @@
         </is>
       </c>
       <c r="E606" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>19-04-2026 15:21</t>
+          <t>13-05-2026 23:53</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -27563,7 +27563,7 @@
         </is>
       </c>
       <c r="E617" t="n">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>13-05-2026 14:47</t>
+          <t>13-05-2026 23:58</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -27690,7 +27690,7 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>12-05-2026 05:44</t>
+          <t>13-05-2026 23:16</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>13-05-2026 08:13</t>
+          <t>13-05-2026 21:24</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -28045,7 +28045,7 @@
         </is>
       </c>
       <c r="E628" t="n">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>10-05-2026 20:17</t>
+          <t>14-05-2026 00:31</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -28131,7 +28131,7 @@
         </is>
       </c>
       <c r="E630" t="n">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>13-05-2026 17:06</t>
+          <t>14-05-2026 01:34</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -28311,7 +28311,7 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>10-05-2026 20:13</t>
+          <t>13-05-2026 18:42</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="E635" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>12-05-2026 13:54</t>
+          <t>13-05-2026 18:43</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -28662,7 +28662,7 @@
         </is>
       </c>
       <c r="E642" t="n">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>12-05-2026 13:48</t>
+          <t>13-05-2026 23:23</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="E644" t="n">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>13-05-2026 16:45</t>
+          <t>14-05-2026 01:00</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="E645" t="n">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>13-05-2026 16:38</t>
+          <t>14-05-2026 01:42</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -29018,7 +29018,7 @@
         </is>
       </c>
       <c r="E650" t="n">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>13-05-2026 07:53</t>
+          <t>13-05-2026 19:20</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -29278,7 +29278,7 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>10-05-2026 17:25</t>
+          <t>13-05-2026 21:03</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -29404,7 +29404,7 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>13-05-2026 12:16</t>
+          <t>13-05-2026 20:25</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -30157,7 +30157,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>13-05-2026 16:06</t>
+          <t>13-05-2026 21:58</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -30193,7 +30193,7 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>13-05-2026 07:00</t>
+          <t>14-05-2026 01:49</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -30504,7 +30504,7 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>08-05-2026 00:07</t>
+          <t>14-05-2026 01:57</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -30721,7 +30721,7 @@
         </is>
       </c>
       <c r="E689" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>13-05-2026 08:57</t>
+          <t>13-05-2026 21:17</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -30938,7 +30938,7 @@
         </is>
       </c>
       <c r="E694" t="n">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>13-05-2026 12:51</t>
+          <t>14-05-2026 00:28</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="E696" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>13-05-2026 15:32</t>
+          <t>13-05-2026 21:56</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -31065,7 +31065,7 @@
         </is>
       </c>
       <c r="E697" t="n">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>13-05-2026 14:31</t>
+          <t>14-05-2026 01:28</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -31110,7 +31110,7 @@
         </is>
       </c>
       <c r="E698" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>12-05-2026 22:35</t>
+          <t>13-05-2026 23:50</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -31254,7 +31254,7 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>13-05-2026 07:08</t>
+          <t>13-05-2026 21:09</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -31451,12 +31451,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>fangyuan99/cookie-share</t>
+          <t>lifo-sh/lifo</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>https://github.com/fangyuan99/cookie-share</t>
+          <t>https://github.com/lifo-sh/lifo</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -31466,38 +31466,42 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Cookie-share is a tampermonkey script that allows users to send and receive cookies between different devices or browsers. It can be used for multi-account switching, sharing video memberships, co-...</t>
+          <t>A browser-native operating system. Unix/Linux reimagined where the browser IS the kernel and Web APIs ARE syscalls. 60+ commands, bash-like shell, virtual filesystem, and IndexedDB persistence.</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>11-05-2026 13:58</t>
+          <t>09-05-2026 02:10</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>01-09-2024 14:30</t>
-        </is>
-      </c>
-      <c r="I706" t="inlineStr"/>
+          <t>23-02-2026 08:32</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>browser, linux, sandbox</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>lifo-sh/lifo</t>
+          <t>punkpeye/pipenet</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>https://github.com/lifo-sh/lifo</t>
+          <t>https://github.com/punkpeye/pipenet</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -31507,7 +31511,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>A browser-native operating system. Unix/Linux reimagined where the browser IS the kernel and Web APIs ARE syscalls. 60+ commands, bash-like shell, virtual filesystem, and IndexedDB persistence.</t>
+          <t>Expose your local server to the public internet instantly</t>
         </is>
       </c>
       <c r="E707" t="n">
@@ -31520,29 +31524,25 @@
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>09-05-2026 02:10</t>
+          <t>13-05-2026 21:32</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>23-02-2026 08:32</t>
-        </is>
-      </c>
-      <c r="I707" t="inlineStr">
-        <is>
-          <t>browser, linux, sandbox</t>
-        </is>
-      </c>
+          <t>19-01-2026 07:34</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>punkpeye/pipenet</t>
+          <t>fangyuan99/cookie-share</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>https://github.com/punkpeye/pipenet</t>
+          <t>https://github.com/fangyuan99/cookie-share</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -31552,7 +31552,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Expose your local server to the public internet instantly</t>
+          <t>Cookie-share is a tampermonkey script that allows users to send and receive cookies between different devices or browsers. It can be used for multi-account switching, sharing video memberships, co-...</t>
         </is>
       </c>
       <c r="E708" t="n">
@@ -31560,17 +31560,17 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>06-05-2026 15:14</t>
+          <t>13-05-2026 21:03</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>19-01-2026 07:34</t>
+          <t>01-09-2024 14:30</t>
         </is>
       </c>
       <c r="I708" t="inlineStr"/>
@@ -31696,7 +31696,7 @@
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>13-05-2026 08:46</t>
+          <t>14-05-2026 00:00</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -32124,7 +32124,7 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>12-05-2026 09:45</t>
+          <t>13-05-2026 21:01</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -32214,7 +32214,7 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>13-05-2026 17:40</t>
+          <t>13-05-2026 18:53</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -32349,7 +32349,7 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>12-05-2026 16:55</t>
+          <t>14-05-2026 00:54</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -32603,7 +32603,7 @@
         </is>
       </c>
       <c r="E732" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>07-05-2026 20:30</t>
+          <t>13-05-2026 22:50</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -32648,7 +32648,7 @@
         </is>
       </c>
       <c r="E733" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>13-05-2026 14:38</t>
+          <t>14-05-2026 00:39</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -32995,7 +32995,7 @@
         </is>
       </c>
       <c r="E741" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>12-05-2026 21:24</t>
+          <t>13-05-2026 21:03</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -33049,7 +33049,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>13-05-2026 17:51</t>
+          <t>14-05-2026 02:32</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -33081,7 +33081,7 @@
         </is>
       </c>
       <c r="E743" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>13-05-2026 04:42</t>
+          <t>13-05-2026 21:02</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -33207,7 +33207,7 @@
         </is>
       </c>
       <c r="E746" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>13-05-2026 15:10</t>
+          <t>13-05-2026 22:04</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -33604,7 +33604,7 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>12-05-2026 09:29</t>
+          <t>13-05-2026 23:33</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -34087,7 +34087,7 @@
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>13-05-2026 00:30</t>
+          <t>14-05-2026 00:31</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -34566,7 +34566,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>13-05-2026 15:45</t>
+          <t>13-05-2026 21:54</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>28-04-2026 09:33</t>
+          <t>14-05-2026 02:00</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
